--- a/Mini-Project/Agricultural Machinery Inventory from ABEMIS/Regression Parameters Output V3/RF_Predictions.xlsx
+++ b/Mini-Project/Agricultural Machinery Inventory from ABEMIS/Regression Parameters Output V3/RF_Predictions.xlsx
@@ -9,10 +9,12 @@
   <sheets>
     <sheet name="RF Predictions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metrics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Feature Importance" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Encoder machinery_type" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Encoder machinery_family" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Encoder analysis_subset" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CV Metrics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Per-Type Residuals" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Feature Importance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Encoder machinery_type" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Encoder machinery_family" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Encoder analysis_subset" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -746,13 +748,13 @@
         <v>1.523347182539683</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.356652817460317</v>
+        <v>0.3566528174603165</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.356652817460317</v>
+        <v>0.3566528174603165</v>
       </c>
       <c r="AM2" t="n">
-        <v>18.97089454576154</v>
+        <v>18.97089454576152</v>
       </c>
     </row>
     <row r="3">
@@ -883,13 +885,13 @@
         <v>2.137224229196729</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.257224229196729</v>
+        <v>-0.2572242291967295</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.257224229196729</v>
+        <v>0.2572242291967295</v>
       </c>
       <c r="AM3" t="n">
-        <v>13.68213985088984</v>
+        <v>13.68213985088987</v>
       </c>
     </row>
     <row r="4">
@@ -1154,16 +1156,16 @@
         <v>1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.260812592592592</v>
+        <v>2.260812592592594</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.2408125925925924</v>
+        <v>-0.2408125925925937</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.2408125925925924</v>
+        <v>0.2408125925925937</v>
       </c>
       <c r="AM5" t="n">
-        <v>11.92141547488081</v>
+        <v>11.92141547488088</v>
       </c>
     </row>
     <row r="6">
@@ -1303,16 +1305,16 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>8.177128125670633</v>
+        <v>8.177128125670629</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.3971281256706325</v>
+        <v>-0.3971281256706289</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.3971281256706325</v>
+        <v>0.3971281256706289</v>
       </c>
       <c r="AM6" t="n">
-        <v>5.104474623015841</v>
+        <v>5.104474623015796</v>
       </c>
     </row>
     <row r="7">
@@ -1741,13 +1743,13 @@
         <v>1.514341825396825</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.7943418253968253</v>
+        <v>-0.7943418253968255</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.7943418253968253</v>
+        <v>0.7943418253968255</v>
       </c>
       <c r="AM9" t="n">
-        <v>110.3252535273368</v>
+        <v>110.3252535273369</v>
       </c>
     </row>
     <row r="10">
@@ -1884,13 +1886,13 @@
         <v>17.0488765873016</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.7511234126984014</v>
+        <v>0.7511234126983979</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.7511234126984014</v>
+        <v>0.7511234126983979</v>
       </c>
       <c r="AM10" t="n">
-        <v>4.219794453361805</v>
+        <v>4.219794453361786</v>
       </c>
     </row>
     <row r="11">
@@ -2155,16 +2157,16 @@
         <v>1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.698877890812891</v>
+        <v>1.698877890812892</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.2988778908128911</v>
+        <v>-0.2988778908128917</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.2988778908128911</v>
+        <v>0.2988778908128917</v>
       </c>
       <c r="AM12" t="n">
-        <v>21.34842077234936</v>
+        <v>21.34842077234941</v>
       </c>
     </row>
     <row r="13">
@@ -2292,16 +2294,16 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.698877890812891</v>
+        <v>1.698877890812892</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.498877890812891</v>
+        <v>-0.4988778908128917</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.498877890812891</v>
+        <v>0.4988778908128917</v>
       </c>
       <c r="AM13" t="n">
-        <v>41.57315756774092</v>
+        <v>41.57315756774098</v>
       </c>
     </row>
     <row r="14">
@@ -2703,16 +2705,16 @@
         <v>1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.350100976430977</v>
+        <v>1.350100976430976</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.3598990235690234</v>
+        <v>0.3598990235690236</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.3598990235690234</v>
+        <v>0.3598990235690236</v>
       </c>
       <c r="AM16" t="n">
-        <v>21.04672652450429</v>
+        <v>21.0467265245043</v>
       </c>
     </row>
     <row r="17">
@@ -2855,13 +2857,13 @@
         <v>1.404248373015872</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.0542483730158716</v>
+        <v>-0.05424837301587204</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.0542483730158716</v>
+        <v>0.05424837301587204</v>
       </c>
       <c r="AM17" t="n">
-        <v>4.018398001175673</v>
+        <v>4.018398001175707</v>
       </c>
     </row>
     <row r="18">
@@ -3263,16 +3265,16 @@
         <v>1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3.688955656565655</v>
+        <v>3.688955656565656</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.1610443434343454</v>
+        <v>0.1610443434343445</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.1610443434343454</v>
+        <v>0.1610443434343445</v>
       </c>
       <c r="AM20" t="n">
-        <v>4.182969959333646</v>
+        <v>4.182969959333622</v>
       </c>
     </row>
     <row r="21">
@@ -3403,13 +3405,13 @@
         <v>1.523347182539683</v>
       </c>
       <c r="AK21" t="n">
-        <v>-0.5033471825396829</v>
+        <v>-0.5033471825396834</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.5033471825396829</v>
+        <v>0.5033471825396834</v>
       </c>
       <c r="AM21" t="n">
-        <v>49.34776299408656</v>
+        <v>49.3477629940866</v>
       </c>
     </row>
     <row r="22">
@@ -3540,13 +3542,13 @@
         <v>1.208739208754209</v>
       </c>
       <c r="AK22" t="n">
-        <v>-0.1487392087542092</v>
+        <v>-0.1487392087542085</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.1487392087542092</v>
+        <v>0.1487392087542085</v>
       </c>
       <c r="AM22" t="n">
-        <v>14.03200082586879</v>
+        <v>14.03200082586873</v>
       </c>
     </row>
     <row r="23">
@@ -3814,13 +3816,13 @@
         <v>1.245543742183742</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.2444562578162579</v>
+        <v>0.2444562578162583</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.2444562578162579</v>
+        <v>0.2444562578162583</v>
       </c>
       <c r="AM24" t="n">
-        <v>16.40646025612469</v>
+        <v>16.40646025612472</v>
       </c>
     </row>
     <row r="25">
@@ -3946,16 +3948,16 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.483596145983648</v>
+        <v>3.483596145983647</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.223596145983648</v>
+        <v>-0.2235961459836475</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.223596145983648</v>
+        <v>0.2235961459836475</v>
       </c>
       <c r="AM25" t="n">
-        <v>6.858777484160981</v>
+        <v>6.858777484160967</v>
       </c>
     </row>
     <row r="26">
@@ -4086,13 +4088,13 @@
         <v>1.174051801346801</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.09594819865319892</v>
+        <v>0.09594819865319937</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.09594819865319892</v>
+        <v>0.09594819865319937</v>
       </c>
       <c r="AM26" t="n">
-        <v>7.554976271905427</v>
+        <v>7.554976271905462</v>
       </c>
     </row>
     <row r="27">
@@ -4223,13 +4225,13 @@
         <v>1.094937065897066</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.4450629341029342</v>
+        <v>0.445062934102934</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.4450629341029342</v>
+        <v>0.445062934102934</v>
       </c>
       <c r="AM27" t="n">
-        <v>28.90019052616455</v>
+        <v>28.90019052616454</v>
       </c>
     </row>
     <row r="28">
@@ -4355,16 +4357,16 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3.483596145983648</v>
+        <v>3.483596145983647</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.4835961459836478</v>
+        <v>-0.4835961459836473</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.4835961459836478</v>
+        <v>0.4835961459836473</v>
       </c>
       <c r="AM28" t="n">
-        <v>16.11987153278826</v>
+        <v>16.11987153278825</v>
       </c>
     </row>
     <row r="29">
@@ -4495,13 +4497,13 @@
         <v>1.695082328504828</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.8649176714951721</v>
+        <v>0.8649176714951723</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.8649176714951721</v>
+        <v>0.8649176714951723</v>
       </c>
       <c r="AM29" t="n">
-        <v>33.78584654278016</v>
+        <v>33.78584654278017</v>
       </c>
     </row>
     <row r="30">
@@ -4635,16 +4637,16 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>12.82157649831649</v>
+        <v>12.8215764983165</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0.4215764983164938</v>
+        <v>-0.4215764983164956</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.4215764983164938</v>
+        <v>0.4215764983164956</v>
       </c>
       <c r="AM30" t="n">
-        <v>3.399810470294304</v>
+        <v>3.399810470294319</v>
       </c>
     </row>
     <row r="31">
@@ -4784,16 +4786,16 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>8.723547365689868</v>
+        <v>8.723547365689871</v>
       </c>
       <c r="AK31" t="n">
-        <v>-1.063547365689868</v>
+        <v>-1.063547365689871</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.063547365689868</v>
+        <v>1.063547365689871</v>
       </c>
       <c r="AM31" t="n">
-        <v>13.88443036148652</v>
+        <v>13.88443036148657</v>
       </c>
     </row>
     <row r="32">
@@ -5332,16 +5334,16 @@
         <v>1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.837548237133236</v>
+        <v>1.837548237133235</v>
       </c>
       <c r="AK35" t="n">
-        <v>-0.2175482371332358</v>
+        <v>-0.2175482371332353</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.2175482371332358</v>
+        <v>0.2175482371332353</v>
       </c>
       <c r="AM35" t="n">
-        <v>13.42890352674295</v>
+        <v>13.42890352674292</v>
       </c>
     </row>
     <row r="36">
@@ -5614,16 +5616,16 @@
         <v>1</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.779066433381432</v>
+        <v>1.779066433381433</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.1209335666185676</v>
+        <v>0.1209335666185674</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.1209335666185676</v>
+        <v>0.1209335666185674</v>
       </c>
       <c r="AM37" t="n">
-        <v>6.364924558871977</v>
+        <v>6.364924558871967</v>
       </c>
     </row>
     <row r="38">
@@ -5751,16 +5753,16 @@
         <v>1</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.829038950216449</v>
+        <v>1.82903895021645</v>
       </c>
       <c r="AK38" t="n">
-        <v>-0.2890389502164494</v>
+        <v>-0.2890389502164499</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.2890389502164494</v>
+        <v>0.2890389502164499</v>
       </c>
       <c r="AM38" t="n">
-        <v>18.76876300106814</v>
+        <v>18.76876300106817</v>
       </c>
     </row>
     <row r="39">
@@ -5888,16 +5890,16 @@
         <v>1</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.636376863876864</v>
+        <v>1.636376863876863</v>
       </c>
       <c r="AK39" t="n">
-        <v>-0.1463768638768637</v>
+        <v>-0.1463768638768634</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.1463768638768637</v>
+        <v>0.1463768638768634</v>
       </c>
       <c r="AM39" t="n">
-        <v>9.823950595762662</v>
+        <v>9.823950595762646</v>
       </c>
     </row>
     <row r="40">
@@ -6177,13 +6179,13 @@
         <v>1.363555513468013</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.8364444865319876</v>
+        <v>0.8364444865319873</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.8364444865319876</v>
+        <v>0.8364444865319873</v>
       </c>
       <c r="AM41" t="n">
-        <v>38.02020393327216</v>
+        <v>38.02020393327215</v>
       </c>
     </row>
     <row r="42">
@@ -6984,16 +6986,16 @@
         <v>1</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.010180886243385</v>
+        <v>2.010180886243386</v>
       </c>
       <c r="AK47" t="n">
-        <v>-0.7501808862433854</v>
+        <v>-0.7501808862433859</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.7501808862433854</v>
+        <v>0.7501808862433859</v>
       </c>
       <c r="AM47" t="n">
-        <v>59.53816557487186</v>
+        <v>59.53816557487189</v>
       </c>
     </row>
     <row r="48">
@@ -7117,16 +7119,16 @@
         <v>1</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.010180886243385</v>
+        <v>2.010180886243386</v>
       </c>
       <c r="AK48" t="n">
-        <v>-0.5201808862433854</v>
+        <v>-0.5201808862433859</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.5201808862433854</v>
+        <v>0.5201808862433859</v>
       </c>
       <c r="AM48" t="n">
-        <v>34.91146887539499</v>
+        <v>34.91146887539502</v>
       </c>
     </row>
     <row r="49">
@@ -7394,13 +7396,13 @@
         <v>2.054023315295813</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.6559766847041875</v>
+        <v>0.655976684704187</v>
       </c>
       <c r="AL50" t="n">
-        <v>0.6559766847041875</v>
+        <v>0.655976684704187</v>
       </c>
       <c r="AM50" t="n">
-        <v>24.20578172340175</v>
+        <v>24.20578172340173</v>
       </c>
     </row>
     <row r="51">
@@ -7531,13 +7533,13 @@
         <v>1.608741855459354</v>
       </c>
       <c r="AK51" t="n">
-        <v>-0.9487418554593542</v>
+        <v>-0.9487418554593535</v>
       </c>
       <c r="AL51" t="n">
-        <v>0.9487418554593542</v>
+        <v>0.9487418554593535</v>
       </c>
       <c r="AM51" t="n">
-        <v>143.74876597869</v>
+        <v>143.7487659786899</v>
       </c>
     </row>
     <row r="52">
@@ -8094,16 +8096,16 @@
         <v>1</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.877354537083287</v>
+        <v>1.877354537083286</v>
       </c>
       <c r="AK55" t="n">
-        <v>-0.5073545370832873</v>
+        <v>-0.5073545370832864</v>
       </c>
       <c r="AL55" t="n">
-        <v>0.5073545370832873</v>
+        <v>0.5073545370832864</v>
       </c>
       <c r="AM55" t="n">
-        <v>37.03317788929104</v>
+        <v>37.03317788929098</v>
       </c>
     </row>
     <row r="56">
@@ -8243,16 +8245,16 @@
         <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>2.936877585377583</v>
+        <v>2.936877585377585</v>
       </c>
       <c r="AK56" t="n">
-        <v>-0.5468775853775831</v>
+        <v>-0.5468775853775845</v>
       </c>
       <c r="AL56" t="n">
-        <v>0.5468775853775831</v>
+        <v>0.5468775853775845</v>
       </c>
       <c r="AM56" t="n">
-        <v>22.88190733797419</v>
+        <v>22.88190733797424</v>
       </c>
     </row>
     <row r="57">
@@ -8544,13 +8546,13 @@
         <v>1.478863716931216</v>
       </c>
       <c r="AK58" t="n">
-        <v>0.1411362830687841</v>
+        <v>0.1411362830687839</v>
       </c>
       <c r="AL58" t="n">
-        <v>0.1411362830687841</v>
+        <v>0.1411362830687839</v>
       </c>
       <c r="AM58" t="n">
-        <v>8.712116238813834</v>
+        <v>8.71211623881382</v>
       </c>
     </row>
     <row r="59">
@@ -8681,13 +8683,13 @@
         <v>1.186744737854738</v>
       </c>
       <c r="AK59" t="n">
-        <v>-0.556744737854738</v>
+        <v>-0.5567447378547375</v>
       </c>
       <c r="AL59" t="n">
-        <v>0.556744737854738</v>
+        <v>0.5567447378547375</v>
       </c>
       <c r="AM59" t="n">
-        <v>88.37218061186317</v>
+        <v>88.3721806118631</v>
       </c>
     </row>
     <row r="60">
@@ -8952,16 +8954,16 @@
         <v>1</v>
       </c>
       <c r="AJ61" t="n">
-        <v>4.012119516594517</v>
+        <v>4.012119516594518</v>
       </c>
       <c r="AK61" t="n">
-        <v>0.3178804834054834</v>
+        <v>0.3178804834054825</v>
       </c>
       <c r="AL61" t="n">
-        <v>0.3178804834054834</v>
+        <v>0.3178804834054825</v>
       </c>
       <c r="AM61" t="n">
-        <v>7.341350656015782</v>
+        <v>7.341350656015762</v>
       </c>
     </row>
     <row r="62">
@@ -9359,16 +9361,16 @@
         <v>1</v>
       </c>
       <c r="AJ64" t="n">
-        <v>2.231474066859064</v>
+        <v>2.231474066859065</v>
       </c>
       <c r="AK64" t="n">
-        <v>-0.9014740668590644</v>
+        <v>-0.9014740668590653</v>
       </c>
       <c r="AL64" t="n">
-        <v>0.9014740668590644</v>
+        <v>0.9014740668590653</v>
       </c>
       <c r="AM64" t="n">
-        <v>67.78000502699732</v>
+        <v>67.78000502699739</v>
       </c>
     </row>
     <row r="65">
@@ -9492,16 +9494,16 @@
         <v>1</v>
       </c>
       <c r="AJ65" t="n">
-        <v>1.891756534854035</v>
+        <v>1.891756534854036</v>
       </c>
       <c r="AK65" t="n">
-        <v>-0.4817565348540351</v>
+        <v>-0.4817565348540362</v>
       </c>
       <c r="AL65" t="n">
-        <v>0.4817565348540351</v>
+        <v>0.4817565348540362</v>
       </c>
       <c r="AM65" t="n">
-        <v>34.16713013149186</v>
+        <v>34.16713013149194</v>
       </c>
     </row>
     <row r="66">
@@ -9629,13 +9631,13 @@
         <v>1</v>
       </c>
       <c r="AJ66" t="n">
-        <v>2.231474066859064</v>
+        <v>2.231474066859065</v>
       </c>
       <c r="AK66" t="n">
-        <v>-1.211474066859064</v>
+        <v>-1.211474066859065</v>
       </c>
       <c r="AL66" t="n">
-        <v>1.211474066859064</v>
+        <v>1.211474066859065</v>
       </c>
       <c r="AM66" t="n">
         <v>118.771967339124</v>
@@ -9766,16 +9768,16 @@
         <v>1</v>
       </c>
       <c r="AJ67" t="n">
-        <v>1.829038950216449</v>
+        <v>1.82903895021645</v>
       </c>
       <c r="AK67" t="n">
-        <v>0.4309610497835503</v>
+        <v>0.4309610497835499</v>
       </c>
       <c r="AL67" t="n">
-        <v>0.4309610497835503</v>
+        <v>0.4309610497835499</v>
       </c>
       <c r="AM67" t="n">
-        <v>19.06907299927214</v>
+        <v>19.06907299927212</v>
       </c>
     </row>
     <row r="68">
@@ -9903,16 +9905,16 @@
         <v>1</v>
       </c>
       <c r="AJ68" t="n">
-        <v>2.821963003848002</v>
+        <v>2.821963003848003</v>
       </c>
       <c r="AK68" t="n">
-        <v>-0.3819630038480022</v>
+        <v>-0.3819630038480026</v>
       </c>
       <c r="AL68" t="n">
-        <v>0.3819630038480022</v>
+        <v>0.3819630038480026</v>
       </c>
       <c r="AM68" t="n">
-        <v>15.65422146918042</v>
+        <v>15.65422146918043</v>
       </c>
     </row>
     <row r="69">
@@ -10180,13 +10182,13 @@
         <v>2.044210597643098</v>
       </c>
       <c r="AK70" t="n">
-        <v>-0.7542105976430977</v>
+        <v>-0.7542105976430982</v>
       </c>
       <c r="AL70" t="n">
-        <v>0.7542105976430977</v>
+        <v>0.7542105976430982</v>
       </c>
       <c r="AM70" t="n">
-        <v>58.46593780179052</v>
+        <v>58.46593780179056</v>
       </c>
     </row>
     <row r="71">
@@ -10450,13 +10452,13 @@
         <v>2.22507146103896</v>
       </c>
       <c r="AK72" t="n">
-        <v>-0.7450714610389597</v>
+        <v>-0.7450714610389602</v>
       </c>
       <c r="AL72" t="n">
-        <v>0.7450714610389597</v>
+        <v>0.7450714610389602</v>
       </c>
       <c r="AM72" t="n">
-        <v>50.34266628641619</v>
+        <v>50.34266628641623</v>
       </c>
     </row>
     <row r="73">
@@ -10717,16 +10719,16 @@
         <v>1</v>
       </c>
       <c r="AJ74" t="n">
-        <v>2.093057682040181</v>
+        <v>2.093057682040182</v>
       </c>
       <c r="AK74" t="n">
-        <v>0.0469423179598194</v>
+        <v>0.04694231795981851</v>
       </c>
       <c r="AL74" t="n">
-        <v>0.0469423179598194</v>
+        <v>0.04694231795981851</v>
       </c>
       <c r="AM74" t="n">
-        <v>2.193566259804645</v>
+        <v>2.193566259804603</v>
       </c>
     </row>
     <row r="75">
@@ -10854,16 +10856,16 @@
         <v>1</v>
       </c>
       <c r="AJ75" t="n">
-        <v>2.151781865079366</v>
+        <v>2.151781865079367</v>
       </c>
       <c r="AK75" t="n">
-        <v>0.5982181349206339</v>
+        <v>0.598218134920633</v>
       </c>
       <c r="AL75" t="n">
-        <v>0.5982181349206339</v>
+        <v>0.598218134920633</v>
       </c>
       <c r="AM75" t="n">
-        <v>21.75338672438669</v>
+        <v>21.75338672438665</v>
       </c>
     </row>
     <row r="76">
@@ -10987,16 +10989,16 @@
         <v>1</v>
       </c>
       <c r="AJ76" t="n">
-        <v>2.064991154401155</v>
+        <v>2.064991154401156</v>
       </c>
       <c r="AK76" t="n">
-        <v>-0.3249911544011554</v>
+        <v>-0.3249911544011559</v>
       </c>
       <c r="AL76" t="n">
-        <v>0.3249911544011554</v>
+        <v>0.3249911544011559</v>
       </c>
       <c r="AM76" t="n">
-        <v>18.67765255179054</v>
+        <v>18.67765255179057</v>
       </c>
     </row>
     <row r="77">
@@ -11130,16 +11132,16 @@
         <v>0</v>
       </c>
       <c r="AJ77" t="n">
-        <v>8.194272632275135</v>
+        <v>8.194272632275132</v>
       </c>
       <c r="AK77" t="n">
-        <v>0.05572736772486486</v>
+        <v>0.05572736772486842</v>
       </c>
       <c r="AL77" t="n">
-        <v>0.05572736772486486</v>
+        <v>0.05572736772486842</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.6754832451498771</v>
+        <v>0.6754832451499202</v>
       </c>
     </row>
     <row r="78">
@@ -11267,16 +11269,16 @@
         <v>1</v>
       </c>
       <c r="AJ78" t="n">
-        <v>4.073140752765753</v>
+        <v>4.073140752765754</v>
       </c>
       <c r="AK78" t="n">
-        <v>0.5768592472342471</v>
+        <v>0.5768592472342462</v>
       </c>
       <c r="AL78" t="n">
-        <v>0.5768592472342471</v>
+        <v>0.5768592472342462</v>
       </c>
       <c r="AM78" t="n">
-        <v>12.40557520933864</v>
+        <v>12.40557520933863</v>
       </c>
     </row>
     <row r="79">
@@ -11547,16 +11549,16 @@
         <v>1</v>
       </c>
       <c r="AJ80" t="n">
-        <v>2.022963152958153</v>
+        <v>2.022963152958154</v>
       </c>
       <c r="AK80" t="n">
-        <v>0.1270368470418473</v>
+        <v>0.1270368470418464</v>
       </c>
       <c r="AL80" t="n">
-        <v>0.1270368470418473</v>
+        <v>0.1270368470418464</v>
       </c>
       <c r="AM80" t="n">
-        <v>5.908690560085919</v>
+        <v>5.908690560085878</v>
       </c>
     </row>
     <row r="81">
@@ -11684,16 +11686,16 @@
         <v>1</v>
       </c>
       <c r="AJ81" t="n">
-        <v>4.073140752765753</v>
+        <v>4.073140752765754</v>
       </c>
       <c r="AK81" t="n">
-        <v>0.1768592472342467</v>
+        <v>0.1768592472342458</v>
       </c>
       <c r="AL81" t="n">
-        <v>0.1768592472342467</v>
+        <v>0.1768592472342458</v>
       </c>
       <c r="AM81" t="n">
-        <v>4.161394052570511</v>
+        <v>4.161394052570491</v>
       </c>
     </row>
     <row r="82">
@@ -11821,16 +11823,16 @@
         <v>1</v>
       </c>
       <c r="AJ82" t="n">
-        <v>1.722108873256374</v>
+        <v>1.722108873256373</v>
       </c>
       <c r="AK82" t="n">
-        <v>-0.02210887325637367</v>
+        <v>-0.02210887325637345</v>
       </c>
       <c r="AL82" t="n">
-        <v>0.02210887325637367</v>
+        <v>0.02210887325637345</v>
       </c>
       <c r="AM82" t="n">
-        <v>1.300521956257275</v>
+        <v>1.300521956257262</v>
       </c>
     </row>
     <row r="83">
@@ -11958,16 +11960,16 @@
         <v>1</v>
       </c>
       <c r="AJ83" t="n">
-        <v>2.298053090428089</v>
+        <v>2.298053090428091</v>
       </c>
       <c r="AK83" t="n">
-        <v>-0.04805309042808936</v>
+        <v>-0.04805309042809069</v>
       </c>
       <c r="AL83" t="n">
-        <v>0.04805309042808936</v>
+        <v>0.04805309042809069</v>
       </c>
       <c r="AM83" t="n">
-        <v>2.135692907915083</v>
+        <v>2.135692907915142</v>
       </c>
     </row>
     <row r="84">
@@ -12375,16 +12377,16 @@
         <v>0</v>
       </c>
       <c r="AJ86" t="n">
-        <v>9.608748654401156</v>
+        <v>9.608748654401158</v>
       </c>
       <c r="AK86" t="n">
-        <v>0.6912513455988449</v>
+        <v>0.6912513455988432</v>
       </c>
       <c r="AL86" t="n">
-        <v>0.6912513455988449</v>
+        <v>0.6912513455988432</v>
       </c>
       <c r="AM86" t="n">
-        <v>6.711178112610145</v>
+        <v>6.711178112610128</v>
       </c>
     </row>
     <row r="87">
@@ -12652,13 +12654,13 @@
         <v>1.640803971861473</v>
       </c>
       <c r="AK88" t="n">
-        <v>-0.5408039718614728</v>
+        <v>-0.5408039718614732</v>
       </c>
       <c r="AL88" t="n">
-        <v>0.5408039718614728</v>
+        <v>0.5408039718614732</v>
       </c>
       <c r="AM88" t="n">
-        <v>49.16399744195207</v>
+        <v>49.16399744195211</v>
       </c>
     </row>
     <row r="89">
@@ -13474,13 +13476,13 @@
         <v>2.1477751984127</v>
       </c>
       <c r="AK94" t="n">
-        <v>0.4522248015873003</v>
+        <v>0.4522248015872998</v>
       </c>
       <c r="AL94" t="n">
-        <v>0.4522248015873003</v>
+        <v>0.4522248015872998</v>
       </c>
       <c r="AM94" t="n">
-        <v>17.39326159951155</v>
+        <v>17.39326159951153</v>
       </c>
     </row>
     <row r="95">
@@ -13608,16 +13610,16 @@
         <v>1</v>
       </c>
       <c r="AJ95" t="n">
-        <v>1.759485185185184</v>
+        <v>1.759485185185185</v>
       </c>
       <c r="AK95" t="n">
-        <v>0.01051481481481575</v>
+        <v>0.01051481481481531</v>
       </c>
       <c r="AL95" t="n">
-        <v>0.01051481481481575</v>
+        <v>0.01051481481481531</v>
       </c>
       <c r="AM95" t="n">
-        <v>0.5940573341703815</v>
+        <v>0.5940573341703564</v>
       </c>
     </row>
     <row r="96">
@@ -13745,16 +13747,16 @@
         <v>1</v>
       </c>
       <c r="AJ96" t="n">
-        <v>4.171668719336219</v>
+        <v>4.171668719336217</v>
       </c>
       <c r="AK96" t="n">
-        <v>-0.3916687193362196</v>
+        <v>-0.3916687193362169</v>
       </c>
       <c r="AL96" t="n">
-        <v>0.3916687193362196</v>
+        <v>0.3916687193362169</v>
       </c>
       <c r="AM96" t="n">
-        <v>10.36160633164602</v>
+        <v>10.36160633164595</v>
       </c>
     </row>
     <row r="97">
@@ -14019,16 +14021,16 @@
         <v>1</v>
       </c>
       <c r="AJ98" t="n">
-        <v>4.24605095478596</v>
+        <v>4.246050954785961</v>
       </c>
       <c r="AK98" t="n">
-        <v>2.38394904521404</v>
+        <v>2.383949045214039</v>
       </c>
       <c r="AL98" t="n">
-        <v>2.38394904521404</v>
+        <v>2.383949045214039</v>
       </c>
       <c r="AM98" t="n">
-        <v>35.95699917366576</v>
+        <v>35.95699917366575</v>
       </c>
     </row>
     <row r="99">
@@ -14159,13 +14161,13 @@
         <v>1.20945357984608</v>
       </c>
       <c r="AK99" t="n">
-        <v>-0.1394535798460801</v>
+        <v>-0.1394535798460799</v>
       </c>
       <c r="AL99" t="n">
-        <v>0.1394535798460801</v>
+        <v>0.1394535798460799</v>
       </c>
       <c r="AM99" t="n">
-        <v>13.03304484542805</v>
+        <v>13.03304484542802</v>
       </c>
     </row>
     <row r="100">
@@ -14293,16 +14295,16 @@
         <v>1</v>
       </c>
       <c r="AJ100" t="n">
-        <v>1.483510278980279</v>
+        <v>1.483510278980278</v>
       </c>
       <c r="AK100" t="n">
-        <v>0.09648972101972153</v>
+        <v>0.09648972101972175</v>
       </c>
       <c r="AL100" t="n">
-        <v>0.09648972101972153</v>
+        <v>0.09648972101972175</v>
       </c>
       <c r="AM100" t="n">
-        <v>6.106944368336806</v>
+        <v>6.106944368336819</v>
       </c>
     </row>
     <row r="101">
@@ -14430,7 +14432,7 @@
         <v>1</v>
       </c>
       <c r="AJ101" t="n">
-        <v>2.753208061568061</v>
+        <v>2.753208061568062</v>
       </c>
       <c r="AK101" t="n">
         <v>2.276791938431939</v>
@@ -14978,16 +14980,16 @@
         <v>1</v>
       </c>
       <c r="AJ105" t="n">
-        <v>3.818820851139602</v>
+        <v>3.818820851139601</v>
       </c>
       <c r="AK105" t="n">
-        <v>2.191179148860398</v>
+        <v>2.191179148860399</v>
       </c>
       <c r="AL105" t="n">
-        <v>2.191179148860398</v>
+        <v>2.191179148860399</v>
       </c>
       <c r="AM105" t="n">
-        <v>36.45888766822626</v>
+        <v>36.45888766822627</v>
       </c>
     </row>
     <row r="106">
@@ -15118,13 +15120,13 @@
         <v>2.044210597643098</v>
       </c>
       <c r="AK106" t="n">
-        <v>-0.7942105976430978</v>
+        <v>-0.7942105976430982</v>
       </c>
       <c r="AL106" t="n">
-        <v>0.7942105976430978</v>
+        <v>0.7942105976430982</v>
       </c>
       <c r="AM106" t="n">
-        <v>63.53684781144781</v>
+        <v>63.53684781144786</v>
       </c>
     </row>
     <row r="107">
@@ -15255,13 +15257,13 @@
         <v>1.640803971861473</v>
       </c>
       <c r="AK107" t="n">
-        <v>-0.9908039718614728</v>
+        <v>-0.9908039718614733</v>
       </c>
       <c r="AL107" t="n">
-        <v>0.9908039718614728</v>
+        <v>0.9908039718614733</v>
       </c>
       <c r="AM107" t="n">
-        <v>152.4313802863804</v>
+        <v>152.4313802863805</v>
       </c>
     </row>
     <row r="108">
@@ -15389,16 +15391,16 @@
         <v>1</v>
       </c>
       <c r="AJ108" t="n">
-        <v>1.858971534391535</v>
+        <v>1.858971534391536</v>
       </c>
       <c r="AK108" t="n">
-        <v>-0.7889715343915353</v>
+        <v>-0.7889715343915358</v>
       </c>
       <c r="AL108" t="n">
-        <v>0.7889715343915353</v>
+        <v>0.7889715343915358</v>
       </c>
       <c r="AM108" t="n">
-        <v>73.73565741976965</v>
+        <v>73.73565741976969</v>
       </c>
     </row>
     <row r="109">
@@ -15538,16 +15540,16 @@
         <v>1</v>
       </c>
       <c r="AJ109" t="n">
-        <v>2.771547337662336</v>
+        <v>2.771547337662337</v>
       </c>
       <c r="AK109" t="n">
-        <v>-0.9015473376623357</v>
+        <v>-0.9015473376623366</v>
       </c>
       <c r="AL109" t="n">
-        <v>0.9015473376623357</v>
+        <v>0.9015473376623366</v>
       </c>
       <c r="AM109" t="n">
-        <v>48.21108757552597</v>
+        <v>48.21108757552602</v>
       </c>
     </row>
     <row r="110">
@@ -15675,16 +15677,16 @@
         <v>1</v>
       </c>
       <c r="AJ110" t="n">
-        <v>4.073140752765753</v>
+        <v>4.073140752765754</v>
       </c>
       <c r="AK110" t="n">
-        <v>0.02685924723424638</v>
+        <v>0.02685924723424549</v>
       </c>
       <c r="AL110" t="n">
-        <v>0.02685924723424638</v>
+        <v>0.02685924723424549</v>
       </c>
       <c r="AM110" t="n">
-        <v>0.6551035910791799</v>
+        <v>0.6551035910791583</v>
       </c>
     </row>
     <row r="111">
@@ -15815,13 +15817,13 @@
         <v>1.27242664983165</v>
       </c>
       <c r="AK111" t="n">
-        <v>0.3375733501683502</v>
+        <v>0.3375733501683504</v>
       </c>
       <c r="AL111" t="n">
-        <v>0.3375733501683502</v>
+        <v>0.3375733501683504</v>
       </c>
       <c r="AM111" t="n">
-        <v>20.96728883033231</v>
+        <v>20.96728883033232</v>
       </c>
     </row>
     <row r="112">
@@ -15961,16 +15963,16 @@
         <v>0</v>
       </c>
       <c r="AJ112" t="n">
-        <v>1.88945811928812</v>
+        <v>1.889458119288121</v>
       </c>
       <c r="AK112" t="n">
-        <v>-0.5594581192881198</v>
+        <v>-0.5594581192881207</v>
       </c>
       <c r="AL112" t="n">
-        <v>0.5594581192881198</v>
+        <v>0.5594581192881207</v>
       </c>
       <c r="AM112" t="n">
-        <v>42.06452024722706</v>
+        <v>42.06452024722712</v>
       </c>
     </row>
     <row r="113">
@@ -16113,13 +16115,13 @@
         <v>1.478863716931216</v>
       </c>
       <c r="AK113" t="n">
-        <v>-0.06886371693121607</v>
+        <v>-0.06886371693121629</v>
       </c>
       <c r="AL113" t="n">
-        <v>0.06886371693121607</v>
+        <v>0.06886371693121629</v>
       </c>
       <c r="AM113" t="n">
-        <v>4.883951555405395</v>
+        <v>4.883951555405411</v>
       </c>
     </row>
     <row r="114">
@@ -16247,16 +16249,16 @@
         <v>1</v>
       </c>
       <c r="AJ114" t="n">
-        <v>4.171668719336219</v>
+        <v>4.171668719336217</v>
       </c>
       <c r="AK114" t="n">
-        <v>0.2083312806637805</v>
+        <v>0.2083312806637831</v>
       </c>
       <c r="AL114" t="n">
-        <v>0.2083312806637805</v>
+        <v>0.2083312806637831</v>
       </c>
       <c r="AM114" t="n">
-        <v>4.756421932963026</v>
+        <v>4.756421932963086</v>
       </c>
     </row>
     <row r="115">
@@ -16387,13 +16389,13 @@
         <v>2.234771305916304</v>
       </c>
       <c r="AK115" t="n">
-        <v>0.2052286940836958</v>
+        <v>0.2052286940836963</v>
       </c>
       <c r="AL115" t="n">
-        <v>0.2052286940836958</v>
+        <v>0.2052286940836963</v>
       </c>
       <c r="AM115" t="n">
-        <v>8.411012052610484</v>
+        <v>8.411012052610504</v>
       </c>
     </row>
     <row r="116">
@@ -16661,13 +16663,13 @@
         <v>1.725648755411257</v>
       </c>
       <c r="AK117" t="n">
-        <v>-0.1256487554112573</v>
+        <v>-0.1256487554112564</v>
       </c>
       <c r="AL117" t="n">
-        <v>0.1256487554112573</v>
+        <v>0.1256487554112564</v>
       </c>
       <c r="AM117" t="n">
-        <v>7.853047213203582</v>
+        <v>7.853047213203526</v>
       </c>
     </row>
     <row r="118">
@@ -16795,16 +16797,16 @@
         <v>1</v>
       </c>
       <c r="AJ118" t="n">
-        <v>4.24605095478596</v>
+        <v>4.246050954785961</v>
       </c>
       <c r="AK118" t="n">
-        <v>-1.25605095478596</v>
+        <v>-1.256050954785961</v>
       </c>
       <c r="AL118" t="n">
-        <v>1.25605095478596</v>
+        <v>1.256050954785961</v>
       </c>
       <c r="AM118" t="n">
-        <v>42.00839313665417</v>
+        <v>42.0083931366542</v>
       </c>
     </row>
     <row r="119">
@@ -16932,16 +16934,16 @@
         <v>1</v>
       </c>
       <c r="AJ119" t="n">
-        <v>3.938079410774409</v>
+        <v>3.93807941077441</v>
       </c>
       <c r="AK119" t="n">
-        <v>0.1419205892255908</v>
+        <v>0.1419205892255899</v>
       </c>
       <c r="AL119" t="n">
-        <v>0.1419205892255908</v>
+        <v>0.1419205892255899</v>
       </c>
       <c r="AM119" t="n">
-        <v>3.478445814352716</v>
+        <v>3.478445814352694</v>
       </c>
     </row>
     <row r="120">
@@ -17072,13 +17074,13 @@
         <v>2.676362099567099</v>
       </c>
       <c r="AK120" t="n">
-        <v>-0.2963620995670988</v>
+        <v>-0.2963620995670992</v>
       </c>
       <c r="AL120" t="n">
-        <v>0.2963620995670988</v>
+        <v>0.2963620995670992</v>
       </c>
       <c r="AM120" t="n">
-        <v>12.45218905744113</v>
+        <v>12.45218905744115</v>
       </c>
     </row>
     <row r="121">
@@ -17206,16 +17208,16 @@
         <v>1</v>
       </c>
       <c r="AJ121" t="n">
-        <v>4.171668719336219</v>
+        <v>4.171668719336217</v>
       </c>
       <c r="AK121" t="n">
-        <v>0.2083312806637805</v>
+        <v>0.2083312806637831</v>
       </c>
       <c r="AL121" t="n">
-        <v>0.2083312806637805</v>
+        <v>0.2083312806637831</v>
       </c>
       <c r="AM121" t="n">
-        <v>4.756421932963026</v>
+        <v>4.756421932963086</v>
       </c>
     </row>
     <row r="122">
@@ -17486,16 +17488,16 @@
         <v>0</v>
       </c>
       <c r="AJ123" t="n">
-        <v>9.138460515873021</v>
+        <v>9.138460515873023</v>
       </c>
       <c r="AK123" t="n">
-        <v>0.3415394841269794</v>
+        <v>0.3415394841269777</v>
       </c>
       <c r="AL123" t="n">
-        <v>0.3415394841269794</v>
+        <v>0.3415394841269777</v>
       </c>
       <c r="AM123" t="n">
-        <v>3.602737174335226</v>
+        <v>3.602737174335207</v>
       </c>
     </row>
     <row r="124">
@@ -17623,16 +17625,16 @@
         <v>1</v>
       </c>
       <c r="AJ124" t="n">
-        <v>1.937888163780664</v>
+        <v>1.937888163780665</v>
       </c>
       <c r="AK124" t="n">
-        <v>-1.397888163780664</v>
+        <v>-1.397888163780665</v>
       </c>
       <c r="AL124" t="n">
-        <v>1.397888163780664</v>
+        <v>1.397888163780665</v>
       </c>
       <c r="AM124" t="n">
-        <v>258.8681784779008</v>
+        <v>258.868178477901</v>
       </c>
     </row>
     <row r="125">
@@ -17766,16 +17768,16 @@
         <v>0</v>
       </c>
       <c r="AJ125" t="n">
-        <v>17.64464351851853</v>
+        <v>17.64464351851852</v>
       </c>
       <c r="AK125" t="n">
-        <v>-0.9446435185185322</v>
+        <v>-0.9446435185185251</v>
       </c>
       <c r="AL125" t="n">
-        <v>0.9446435185185322</v>
+        <v>0.9446435185185251</v>
       </c>
       <c r="AM125" t="n">
-        <v>5.656548015081031</v>
+        <v>5.65654801508099</v>
       </c>
     </row>
     <row r="126">
@@ -17912,13 +17914,13 @@
         <v>6.321415555555554</v>
       </c>
       <c r="AK126" t="n">
-        <v>1.158584444444447</v>
+        <v>1.158584444444446</v>
       </c>
       <c r="AL126" t="n">
-        <v>1.158584444444447</v>
+        <v>1.158584444444446</v>
       </c>
       <c r="AM126" t="n">
-        <v>15.48909685086159</v>
+        <v>15.48909685086157</v>
       </c>
     </row>
     <row r="127">
@@ -18055,13 +18057,13 @@
         <v>1.172928170995671</v>
       </c>
       <c r="AK127" t="n">
-        <v>-0.3629281709956707</v>
+        <v>-0.3629281709956713</v>
       </c>
       <c r="AL127" t="n">
-        <v>0.3629281709956707</v>
+        <v>0.3629281709956713</v>
       </c>
       <c r="AM127" t="n">
-        <v>44.80594703650254</v>
+        <v>44.80594703650263</v>
       </c>
     </row>
     <row r="128">
@@ -18198,13 +18200,13 @@
         <v>12.37218268879269</v>
       </c>
       <c r="AK128" t="n">
-        <v>-1.072182688792688</v>
+        <v>-1.07218268879269</v>
       </c>
       <c r="AL128" t="n">
-        <v>1.072182688792688</v>
+        <v>1.07218268879269</v>
       </c>
       <c r="AM128" t="n">
-        <v>9.488342378696357</v>
+        <v>9.488342378696373</v>
       </c>
     </row>
     <row r="129">
@@ -18347,13 +18349,13 @@
         <v>2.676362099567099</v>
       </c>
       <c r="AK129" t="n">
-        <v>0.3236379004329013</v>
+        <v>0.3236379004329009</v>
       </c>
       <c r="AL129" t="n">
-        <v>0.3236379004329013</v>
+        <v>0.3236379004329009</v>
       </c>
       <c r="AM129" t="n">
-        <v>10.78793001443004</v>
+        <v>10.78793001443003</v>
       </c>
     </row>
     <row r="130">
@@ -18493,16 +18495,16 @@
         <v>1</v>
       </c>
       <c r="AJ130" t="n">
-        <v>1.858971534391535</v>
+        <v>1.858971534391536</v>
       </c>
       <c r="AK130" t="n">
-        <v>-0.1889715343915355</v>
+        <v>-0.1889715343915359</v>
       </c>
       <c r="AL130" t="n">
-        <v>0.1889715343915355</v>
+        <v>0.1889715343915359</v>
       </c>
       <c r="AM130" t="n">
-        <v>11.31566074200811</v>
+        <v>11.31566074200814</v>
       </c>
     </row>
     <row r="131">
@@ -18913,7 +18915,7 @@
         <v>1.409196028138527</v>
       </c>
       <c r="AM133" t="n">
-        <v>46.20314846355826</v>
+        <v>46.20314846355825</v>
       </c>
     </row>
     <row r="134">
@@ -19044,13 +19046,13 @@
         <v>1.981831563251564</v>
       </c>
       <c r="AK134" t="n">
-        <v>-0.2018315632515639</v>
+        <v>-0.2018315632515635</v>
       </c>
       <c r="AL134" t="n">
-        <v>0.2018315632515639</v>
+        <v>0.2018315632515635</v>
       </c>
       <c r="AM134" t="n">
-        <v>11.33885186806539</v>
+        <v>11.33885186806536</v>
       </c>
     </row>
     <row r="135">
@@ -19187,13 +19189,13 @@
         <v>14.97462283429535</v>
       </c>
       <c r="AK135" t="n">
-        <v>-0.6746228342953469</v>
+        <v>-0.6746228342953504</v>
       </c>
       <c r="AL135" t="n">
-        <v>0.6746228342953469</v>
+        <v>0.6746228342953504</v>
       </c>
       <c r="AM135" t="n">
-        <v>4.717642197869558</v>
+        <v>4.717642197869583</v>
       </c>
     </row>
     <row r="136">
@@ -19324,13 +19326,13 @@
         <v>1.981831563251564</v>
       </c>
       <c r="AK136" t="n">
-        <v>-0.1518315632515639</v>
+        <v>-0.1518315632515634</v>
       </c>
       <c r="AL136" t="n">
-        <v>0.1518315632515639</v>
+        <v>0.1518315632515634</v>
       </c>
       <c r="AM136" t="n">
-        <v>8.296806735058135</v>
+        <v>8.296806735058111</v>
       </c>
     </row>
     <row r="137">
@@ -19458,7 +19460,7 @@
         <v>1</v>
       </c>
       <c r="AJ137" t="n">
-        <v>3.850082833092834</v>
+        <v>3.850082833092833</v>
       </c>
       <c r="AK137" t="n">
         <v>-1.090082833092834</v>
@@ -19467,7 +19469,7 @@
         <v>1.090082833092834</v>
       </c>
       <c r="AM137" t="n">
-        <v>39.49575482220415</v>
+        <v>39.49575482220412</v>
       </c>
     </row>
     <row r="138">
@@ -19738,16 +19740,16 @@
         <v>1</v>
       </c>
       <c r="AJ139" t="n">
-        <v>2.231474066859064</v>
+        <v>2.231474066859065</v>
       </c>
       <c r="AK139" t="n">
-        <v>0.6285259331409354</v>
+        <v>0.6285259331409345</v>
       </c>
       <c r="AL139" t="n">
-        <v>0.6285259331409354</v>
+        <v>0.6285259331409345</v>
       </c>
       <c r="AM139" t="n">
-        <v>21.97643122870404</v>
+        <v>21.976431228704</v>
       </c>
     </row>
     <row r="140">
@@ -20188,13 +20190,13 @@
         <v>2.676362099567099</v>
       </c>
       <c r="AK142" t="n">
-        <v>-0.3963620995670989</v>
+        <v>-0.3963620995670993</v>
       </c>
       <c r="AL142" t="n">
-        <v>0.3963620995670989</v>
+        <v>0.3963620995670993</v>
       </c>
       <c r="AM142" t="n">
-        <v>17.38430261259206</v>
+        <v>17.38430261259208</v>
       </c>
     </row>
     <row r="143">
@@ -20337,13 +20339,13 @@
         <v>2.676362099567099</v>
       </c>
       <c r="AK143" t="n">
-        <v>0.9136379004329012</v>
+        <v>0.9136379004329007</v>
       </c>
       <c r="AL143" t="n">
-        <v>0.9136379004329012</v>
+        <v>0.9136379004329007</v>
       </c>
       <c r="AM143" t="n">
-        <v>25.44952368893875</v>
+        <v>25.44952368893874</v>
       </c>
     </row>
     <row r="144">
@@ -20471,16 +20473,16 @@
         <v>1</v>
       </c>
       <c r="AJ144" t="n">
-        <v>3.590833862433861</v>
+        <v>3.590833862433862</v>
       </c>
       <c r="AK144" t="n">
-        <v>0.04916613756613897</v>
+        <v>0.04916613756613852</v>
       </c>
       <c r="AL144" t="n">
-        <v>0.04916613756613897</v>
+        <v>0.04916613756613852</v>
       </c>
       <c r="AM144" t="n">
-        <v>1.350718065003818</v>
+        <v>1.350718065003806</v>
       </c>
     </row>
     <row r="145">
@@ -20608,16 +20610,16 @@
         <v>1</v>
       </c>
       <c r="AJ145" t="n">
-        <v>2.343441899951899</v>
+        <v>2.3434418999519</v>
       </c>
       <c r="AK145" t="n">
-        <v>0.4965581000481012</v>
+        <v>0.4965581000481003</v>
       </c>
       <c r="AL145" t="n">
-        <v>0.4965581000481012</v>
+        <v>0.4965581000481003</v>
       </c>
       <c r="AM145" t="n">
-        <v>17.48444014253878</v>
+        <v>17.48444014253874</v>
       </c>
     </row>
     <row r="146">
@@ -20894,16 +20896,16 @@
         <v>0</v>
       </c>
       <c r="AJ147" t="n">
-        <v>1.922985945165944</v>
+        <v>1.922985945165945</v>
       </c>
       <c r="AK147" t="n">
-        <v>-0.2729859451659442</v>
+        <v>-0.2729859451659449</v>
       </c>
       <c r="AL147" t="n">
-        <v>0.2729859451659442</v>
+        <v>0.2729859451659449</v>
       </c>
       <c r="AM147" t="n">
-        <v>16.54460273732995</v>
+        <v>16.54460273733</v>
       </c>
     </row>
     <row r="148">
@@ -21031,16 +21033,16 @@
         <v>1</v>
       </c>
       <c r="AJ148" t="n">
-        <v>1.858971534391535</v>
+        <v>1.858971534391536</v>
       </c>
       <c r="AK148" t="n">
-        <v>0.3310284656084646</v>
+        <v>0.3310284656084641</v>
       </c>
       <c r="AL148" t="n">
-        <v>0.3310284656084646</v>
+        <v>0.3310284656084641</v>
       </c>
       <c r="AM148" t="n">
-        <v>15.11545505061482</v>
+        <v>15.1154550506148</v>
       </c>
     </row>
     <row r="149">
@@ -21168,16 +21170,16 @@
         <v>1</v>
       </c>
       <c r="AJ149" t="n">
-        <v>4.524030925925926</v>
+        <v>4.524030925925928</v>
       </c>
       <c r="AK149" t="n">
-        <v>-0.394030925925926</v>
+        <v>-0.3940309259259278</v>
       </c>
       <c r="AL149" t="n">
-        <v>0.394030925925926</v>
+        <v>0.3940309259259278</v>
       </c>
       <c r="AM149" t="n">
-        <v>9.540700385615644</v>
+        <v>9.540700385615686</v>
       </c>
     </row>
     <row r="150">
@@ -21442,16 +21444,16 @@
         <v>1</v>
       </c>
       <c r="AJ151" t="n">
-        <v>2.960096401931401</v>
+        <v>2.960096401931402</v>
       </c>
       <c r="AK151" t="n">
-        <v>0.2099035980685988</v>
+        <v>0.2099035980685984</v>
       </c>
       <c r="AL151" t="n">
-        <v>0.2099035980685988</v>
+        <v>0.2099035980685984</v>
       </c>
       <c r="AM151" t="n">
-        <v>6.621564607842235</v>
+        <v>6.62156460784222</v>
       </c>
     </row>
     <row r="152">
@@ -21579,16 +21581,16 @@
         <v>1</v>
       </c>
       <c r="AJ152" t="n">
-        <v>3.256547846967845</v>
+        <v>3.256547846967844</v>
       </c>
       <c r="AK152" t="n">
-        <v>-0.3565478469678451</v>
+        <v>-0.3565478469678443</v>
       </c>
       <c r="AL152" t="n">
-        <v>0.3565478469678451</v>
+        <v>0.3565478469678443</v>
       </c>
       <c r="AM152" t="n">
-        <v>12.2947533437188</v>
+        <v>12.29475334371877</v>
       </c>
     </row>
     <row r="153">
@@ -21722,16 +21724,16 @@
         <v>0</v>
       </c>
       <c r="AJ153" t="n">
-        <v>18.96333425925926</v>
+        <v>18.96333425925925</v>
       </c>
       <c r="AK153" t="n">
-        <v>1.136665740740746</v>
+        <v>1.136665740740753</v>
       </c>
       <c r="AL153" t="n">
-        <v>1.136665740740746</v>
+        <v>1.136665740740753</v>
       </c>
       <c r="AM153" t="n">
-        <v>5.655053436521124</v>
+        <v>5.655053436521159</v>
       </c>
     </row>
     <row r="154">
@@ -22142,13 +22144,13 @@
         <v>18.88632325637325</v>
       </c>
       <c r="AK156" t="n">
-        <v>1.51367674362675</v>
+        <v>1.513676743626753</v>
       </c>
       <c r="AL156" t="n">
-        <v>1.51367674362675</v>
+        <v>1.513676743626753</v>
       </c>
       <c r="AM156" t="n">
-        <v>7.41998403738603</v>
+        <v>7.419984037386046</v>
       </c>
     </row>
     <row r="157">
@@ -22276,16 +22278,16 @@
         <v>1</v>
       </c>
       <c r="AJ157" t="n">
-        <v>1.771122288359791</v>
+        <v>1.77112228835979</v>
       </c>
       <c r="AK157" t="n">
-        <v>-0.3111222883597906</v>
+        <v>-0.3111222883597904</v>
       </c>
       <c r="AL157" t="n">
-        <v>0.3111222883597906</v>
+        <v>0.3111222883597904</v>
       </c>
       <c r="AM157" t="n">
-        <v>21.30974577806785</v>
+        <v>21.30974577806784</v>
       </c>
     </row>
     <row r="158">
@@ -22696,13 +22698,13 @@
         <v>18.88632325637325</v>
       </c>
       <c r="AK160" t="n">
-        <v>-0.9863232563732502</v>
+        <v>-0.9863232563732467</v>
       </c>
       <c r="AL160" t="n">
-        <v>0.9863232563732502</v>
+        <v>0.9863232563732467</v>
       </c>
       <c r="AM160" t="n">
-        <v>5.510185789794694</v>
+        <v>5.510185789794675</v>
       </c>
     </row>
     <row r="161">
@@ -22830,16 +22832,16 @@
         <v>1</v>
       </c>
       <c r="AJ161" t="n">
-        <v>3.305775439560438</v>
+        <v>3.305775439560436</v>
       </c>
       <c r="AK161" t="n">
-        <v>0.1542245604395625</v>
+        <v>0.1542245604395642</v>
       </c>
       <c r="AL161" t="n">
-        <v>0.1542245604395625</v>
+        <v>0.1542245604395642</v>
       </c>
       <c r="AM161" t="n">
-        <v>4.457357238137643</v>
+        <v>4.457357238137694</v>
       </c>
     </row>
     <row r="162">
@@ -23244,13 +23246,13 @@
         <v>1.750718161838161</v>
       </c>
       <c r="AK164" t="n">
-        <v>0.1592818381618393</v>
+        <v>0.1592818381618391</v>
       </c>
       <c r="AL164" t="n">
-        <v>0.1592818381618393</v>
+        <v>0.1592818381618391</v>
       </c>
       <c r="AM164" t="n">
-        <v>8.339363254546559</v>
+        <v>8.339363254546548</v>
       </c>
     </row>
     <row r="165">
@@ -23378,16 +23380,16 @@
         <v>1</v>
       </c>
       <c r="AJ165" t="n">
-        <v>2.095998730158729</v>
+        <v>2.09599873015873</v>
       </c>
       <c r="AK165" t="n">
-        <v>-0.2759987301587292</v>
+        <v>-0.2759987301587301</v>
       </c>
       <c r="AL165" t="n">
-        <v>0.2759987301587292</v>
+        <v>0.2759987301587301</v>
       </c>
       <c r="AM165" t="n">
-        <v>15.16476539333677</v>
+        <v>15.16476539333682</v>
       </c>
     </row>
     <row r="166">
@@ -23515,16 +23517,16 @@
         <v>1</v>
       </c>
       <c r="AJ166" t="n">
-        <v>2.095998730158729</v>
+        <v>2.09599873015873</v>
       </c>
       <c r="AK166" t="n">
-        <v>-0.3259987301587293</v>
+        <v>-0.3259987301587302</v>
       </c>
       <c r="AL166" t="n">
-        <v>0.3259987301587293</v>
+        <v>0.3259987301587302</v>
       </c>
       <c r="AM166" t="n">
-        <v>18.41800735360052</v>
+        <v>18.41800735360057</v>
       </c>
     </row>
     <row r="167">
@@ -23652,16 +23654,16 @@
         <v>1</v>
       </c>
       <c r="AJ167" t="n">
-        <v>1.229434763107264</v>
+        <v>1.229434763107263</v>
       </c>
       <c r="AK167" t="n">
-        <v>-0.1594347631072637</v>
+        <v>-0.1594347631072632</v>
       </c>
       <c r="AL167" t="n">
-        <v>0.1594347631072637</v>
+        <v>0.1594347631072632</v>
       </c>
       <c r="AM167" t="n">
-        <v>14.90044515021156</v>
+        <v>14.90044515021152</v>
       </c>
     </row>
     <row r="168">
@@ -23789,16 +23791,16 @@
         <v>1</v>
       </c>
       <c r="AJ168" t="n">
-        <v>1.209398823953824</v>
+        <v>1.209398823953823</v>
       </c>
       <c r="AK168" t="n">
-        <v>-0.2493988239538236</v>
+        <v>-0.2493988239538232</v>
       </c>
       <c r="AL168" t="n">
-        <v>0.2493988239538236</v>
+        <v>0.2493988239538232</v>
       </c>
       <c r="AM168" t="n">
-        <v>25.97904416185663</v>
+        <v>25.97904416185659</v>
       </c>
     </row>
     <row r="169">
@@ -23926,16 +23928,16 @@
         <v>1</v>
       </c>
       <c r="AJ169" t="n">
-        <v>1.209398823953824</v>
+        <v>1.209398823953823</v>
       </c>
       <c r="AK169" t="n">
-        <v>0.3206011760461764</v>
+        <v>0.3206011760461769</v>
       </c>
       <c r="AL169" t="n">
-        <v>0.3206011760461764</v>
+        <v>0.3206011760461769</v>
       </c>
       <c r="AM169" t="n">
-        <v>20.95432523177624</v>
+        <v>20.95432523177627</v>
       </c>
     </row>
     <row r="170">
@@ -24063,16 +24065,16 @@
         <v>1</v>
       </c>
       <c r="AJ170" t="n">
-        <v>4.55075705026455</v>
+        <v>4.550757050264552</v>
       </c>
       <c r="AK170" t="n">
-        <v>0.2692429497354505</v>
+        <v>0.2692429497354487</v>
       </c>
       <c r="AL170" t="n">
-        <v>0.2692429497354505</v>
+        <v>0.2692429497354487</v>
       </c>
       <c r="AM170" t="n">
-        <v>5.585953314013495</v>
+        <v>5.585953314013459</v>
       </c>
     </row>
     <row r="171">
@@ -24337,16 +24339,16 @@
         <v>1</v>
       </c>
       <c r="AJ172" t="n">
-        <v>2.197485582473081</v>
+        <v>2.197485582473083</v>
       </c>
       <c r="AK172" t="n">
-        <v>-0.3174855824730809</v>
+        <v>-0.3174855824730827</v>
       </c>
       <c r="AL172" t="n">
-        <v>0.3174855824730809</v>
+        <v>0.3174855824730827</v>
       </c>
       <c r="AM172" t="n">
-        <v>16.88753098261069</v>
+        <v>16.88753098261078</v>
       </c>
     </row>
     <row r="173">
@@ -24477,13 +24479,13 @@
         <v>3.756032486772487</v>
       </c>
       <c r="AK173" t="n">
-        <v>0.533967513227513</v>
+        <v>0.5339675132275126</v>
       </c>
       <c r="AL173" t="n">
-        <v>0.533967513227513</v>
+        <v>0.5339675132275126</v>
       </c>
       <c r="AM173" t="n">
-        <v>12.44679518012851</v>
+        <v>12.4467951801285</v>
       </c>
     </row>
     <row r="174">
@@ -24614,13 +24616,13 @@
         <v>1.750718161838161</v>
       </c>
       <c r="AK174" t="n">
-        <v>-0.8407181618381606</v>
+        <v>-0.8407181618381608</v>
       </c>
       <c r="AL174" t="n">
-        <v>0.8407181618381606</v>
+        <v>0.8407181618381608</v>
       </c>
       <c r="AM174" t="n">
-        <v>92.38661119100666</v>
+        <v>92.38661119100668</v>
       </c>
     </row>
     <row r="175">
@@ -24748,16 +24750,16 @@
         <v>1</v>
       </c>
       <c r="AJ175" t="n">
-        <v>2.111659973544974</v>
+        <v>2.111659973544975</v>
       </c>
       <c r="AK175" t="n">
-        <v>3.638340026455026</v>
+        <v>3.638340026455025</v>
       </c>
       <c r="AL175" t="n">
-        <v>3.638340026455026</v>
+        <v>3.638340026455025</v>
       </c>
       <c r="AM175" t="n">
-        <v>63.27547872095697</v>
+        <v>63.27547872095695</v>
       </c>
     </row>
     <row r="176">
@@ -24888,10 +24890,10 @@
         <v>1.750718161838161</v>
       </c>
       <c r="AK176" t="n">
-        <v>-0.9007181618381607</v>
+        <v>-0.9007181618381609</v>
       </c>
       <c r="AL176" t="n">
-        <v>0.9007181618381607</v>
+        <v>0.9007181618381609</v>
       </c>
       <c r="AM176" t="n">
         <v>105.9668425691954</v>
@@ -25022,16 +25024,16 @@
         <v>1</v>
       </c>
       <c r="AJ177" t="n">
-        <v>2.111659973544974</v>
+        <v>2.111659973544975</v>
       </c>
       <c r="AK177" t="n">
-        <v>-1.051659973544974</v>
+        <v>-1.051659973544975</v>
       </c>
       <c r="AL177" t="n">
-        <v>1.051659973544974</v>
+        <v>1.051659973544975</v>
       </c>
       <c r="AM177" t="n">
-        <v>99.21320505141267</v>
+        <v>99.21320505141271</v>
       </c>
     </row>
     <row r="178">
@@ -25162,13 +25164,13 @@
         <v>1.176682670755171</v>
       </c>
       <c r="AK178" t="n">
-        <v>-0.0966826707551709</v>
+        <v>-0.09668267075517067</v>
       </c>
       <c r="AL178" t="n">
-        <v>0.0966826707551709</v>
+        <v>0.09668267075517067</v>
       </c>
       <c r="AM178" t="n">
-        <v>8.952099143997305</v>
+        <v>8.952099143997284</v>
       </c>
     </row>
     <row r="179">
@@ -25440,13 +25442,13 @@
         <v>1.931007235449734</v>
       </c>
       <c r="AK180" t="n">
-        <v>-0.9610072354497337</v>
+        <v>-0.9610072354497341</v>
       </c>
       <c r="AL180" t="n">
-        <v>0.9610072354497337</v>
+        <v>0.9610072354497341</v>
       </c>
       <c r="AM180" t="n">
-        <v>99.07291087110657</v>
+        <v>99.07291087110661</v>
       </c>
     </row>
     <row r="181">
@@ -25574,16 +25576,16 @@
         <v>1</v>
       </c>
       <c r="AJ181" t="n">
-        <v>1.843757288359787</v>
+        <v>1.843757288359788</v>
       </c>
       <c r="AK181" t="n">
-        <v>-0.1837572883597876</v>
+        <v>-0.1837572883597882</v>
       </c>
       <c r="AL181" t="n">
-        <v>0.1837572883597876</v>
+        <v>0.1837572883597882</v>
       </c>
       <c r="AM181" t="n">
-        <v>11.06971616625226</v>
+        <v>11.0697161662523</v>
       </c>
     </row>
     <row r="182">
@@ -25711,16 +25713,16 @@
         <v>1</v>
       </c>
       <c r="AJ182" t="n">
-        <v>1.567480460557962</v>
+        <v>1.567480460557961</v>
       </c>
       <c r="AK182" t="n">
-        <v>-0.1074804605579616</v>
+        <v>-0.1074804605579613</v>
       </c>
       <c r="AL182" t="n">
-        <v>0.1074804605579616</v>
+        <v>0.1074804605579613</v>
       </c>
       <c r="AM182" t="n">
-        <v>7.361675380682299</v>
+        <v>7.361675380682284</v>
       </c>
     </row>
     <row r="183">
@@ -25848,16 +25850,16 @@
         <v>1</v>
       </c>
       <c r="AJ183" t="n">
-        <v>1.855668742183744</v>
+        <v>1.855668742183745</v>
       </c>
       <c r="AK183" t="n">
-        <v>-0.4556687421837444</v>
+        <v>-0.4556687421837449</v>
       </c>
       <c r="AL183" t="n">
-        <v>0.4556687421837444</v>
+        <v>0.4556687421837449</v>
       </c>
       <c r="AM183" t="n">
-        <v>32.54776729883889</v>
+        <v>32.54776729883892</v>
       </c>
     </row>
     <row r="184">
@@ -25985,16 +25987,16 @@
         <v>1</v>
       </c>
       <c r="AJ184" t="n">
-        <v>1.855668742183744</v>
+        <v>1.855668742183745</v>
       </c>
       <c r="AK184" t="n">
-        <v>3.144331257816256</v>
+        <v>3.144331257816255</v>
       </c>
       <c r="AL184" t="n">
-        <v>3.144331257816256</v>
+        <v>3.144331257816255</v>
       </c>
       <c r="AM184" t="n">
-        <v>62.88662515632512</v>
+        <v>62.8866251563251</v>
       </c>
     </row>
     <row r="185">
@@ -26122,16 +26124,16 @@
         <v>1</v>
       </c>
       <c r="AJ185" t="n">
-        <v>1.970568846801346</v>
+        <v>1.970568846801347</v>
       </c>
       <c r="AK185" t="n">
-        <v>-0.02056884680134652</v>
+        <v>-0.02056884680134696</v>
       </c>
       <c r="AL185" t="n">
-        <v>0.02056884680134652</v>
+        <v>0.02056884680134696</v>
       </c>
       <c r="AM185" t="n">
-        <v>1.054812656479309</v>
+        <v>1.054812656479331</v>
       </c>
     </row>
     <row r="186">
@@ -26402,16 +26404,16 @@
         <v>1</v>
       </c>
       <c r="AJ187" t="n">
-        <v>2.653703002645503</v>
+        <v>2.653703002645502</v>
       </c>
       <c r="AK187" t="n">
-        <v>-0.3837030026455026</v>
+        <v>-0.3837030026455022</v>
       </c>
       <c r="AL187" t="n">
-        <v>0.3837030026455026</v>
+        <v>0.3837030026455022</v>
       </c>
       <c r="AM187" t="n">
-        <v>16.9032159755728</v>
+        <v>16.90321597557278</v>
       </c>
     </row>
     <row r="188">
@@ -26545,16 +26547,16 @@
         <v>1</v>
       </c>
       <c r="AJ188" t="n">
-        <v>1.240725565175564</v>
+        <v>1.240725565175565</v>
       </c>
       <c r="AK188" t="n">
-        <v>-0.0007255651755644354</v>
+        <v>-0.0007255651755646575</v>
       </c>
       <c r="AL188" t="n">
-        <v>0.0007255651755644354</v>
+        <v>0.0007255651755646575</v>
       </c>
       <c r="AM188" t="n">
-        <v>0.05851332061003511</v>
+        <v>0.05851332061005302</v>
       </c>
     </row>
     <row r="189">
@@ -26682,16 +26684,16 @@
         <v>1</v>
       </c>
       <c r="AJ189" t="n">
-        <v>4.029927830687833</v>
+        <v>4.029927830687834</v>
       </c>
       <c r="AK189" t="n">
-        <v>1.840072169312167</v>
+        <v>1.840072169312166</v>
       </c>
       <c r="AL189" t="n">
-        <v>1.840072169312167</v>
+        <v>1.840072169312166</v>
       </c>
       <c r="AM189" t="n">
-        <v>31.3470556952669</v>
+        <v>31.34705569526689</v>
       </c>
     </row>
     <row r="190">
@@ -26831,16 +26833,16 @@
         <v>0</v>
       </c>
       <c r="AJ190" t="n">
-        <v>8.295651379638885</v>
+        <v>8.295651379638883</v>
       </c>
       <c r="AK190" t="n">
-        <v>-0.5856513796388851</v>
+        <v>-0.5856513796388834</v>
       </c>
       <c r="AL190" t="n">
-        <v>0.5856513796388851</v>
+        <v>0.5856513796388834</v>
       </c>
       <c r="AM190" t="n">
-        <v>7.595997141879185</v>
+        <v>7.595997141879161</v>
       </c>
     </row>
     <row r="191">
@@ -26968,16 +26970,16 @@
         <v>1</v>
       </c>
       <c r="AJ191" t="n">
-        <v>1.043723615921116</v>
+        <v>1.043723615921117</v>
       </c>
       <c r="AK191" t="n">
-        <v>0.2162763840788842</v>
+        <v>0.2162763840788835</v>
       </c>
       <c r="AL191" t="n">
-        <v>0.2162763840788842</v>
+        <v>0.2162763840788835</v>
       </c>
       <c r="AM191" t="n">
-        <v>17.16479238721303</v>
+        <v>17.16479238721298</v>
       </c>
     </row>
     <row r="192">
@@ -27111,16 +27113,16 @@
         <v>0</v>
       </c>
       <c r="AJ192" t="n">
-        <v>19.060563997114</v>
+        <v>19.06056399711399</v>
       </c>
       <c r="AK192" t="n">
-        <v>0.7394360028860056</v>
+        <v>0.7394360028860092</v>
       </c>
       <c r="AL192" t="n">
-        <v>0.7394360028860056</v>
+        <v>0.7394360028860092</v>
       </c>
       <c r="AM192" t="n">
-        <v>3.734525267101038</v>
+        <v>3.734525267101056</v>
       </c>
     </row>
     <row r="193">
@@ -27251,13 +27253,13 @@
         <v>1.52625942881193</v>
       </c>
       <c r="AK193" t="n">
-        <v>-0.01625942881193021</v>
+        <v>-0.01625942881192999</v>
       </c>
       <c r="AL193" t="n">
-        <v>0.01625942881193021</v>
+        <v>0.01625942881192999</v>
       </c>
       <c r="AM193" t="n">
-        <v>1.076783365028491</v>
+        <v>1.076783365028476</v>
       </c>
     </row>
     <row r="194">
@@ -27805,13 +27807,13 @@
         <v>1.254465631313131</v>
       </c>
       <c r="AK197" t="n">
-        <v>0.005534368686868962</v>
+        <v>0.00553436868686874</v>
       </c>
       <c r="AL197" t="n">
-        <v>0.005534368686868962</v>
+        <v>0.00553436868686874</v>
       </c>
       <c r="AM197" t="n">
-        <v>0.4392356100689653</v>
+        <v>0.4392356100689477</v>
       </c>
     </row>
     <row r="198">
@@ -27939,16 +27941,16 @@
         <v>1</v>
       </c>
       <c r="AJ198" t="n">
-        <v>1.043723615921116</v>
+        <v>1.043723615921117</v>
       </c>
       <c r="AK198" t="n">
-        <v>-0.5937236159211159</v>
+        <v>-0.5937236159211166</v>
       </c>
       <c r="AL198" t="n">
-        <v>0.5937236159211159</v>
+        <v>0.5937236159211166</v>
       </c>
       <c r="AM198" t="n">
-        <v>131.9385813158035</v>
+        <v>131.9385813158037</v>
       </c>
     </row>
     <row r="199">
@@ -28356,16 +28358,16 @@
         <v>1</v>
       </c>
       <c r="AJ201" t="n">
-        <v>2.712283858826357</v>
+        <v>2.712283858826356</v>
       </c>
       <c r="AK201" t="n">
-        <v>2.077716141173643</v>
+        <v>2.077716141173644</v>
       </c>
       <c r="AL201" t="n">
-        <v>2.077716141173643</v>
+        <v>2.077716141173644</v>
       </c>
       <c r="AM201" t="n">
-        <v>43.37611985748732</v>
+        <v>43.37611985748734</v>
       </c>
     </row>
     <row r="202">
@@ -28651,13 +28653,13 @@
         <v>16.08811147186147</v>
       </c>
       <c r="AK203" t="n">
-        <v>-0.08811147186146684</v>
+        <v>-0.08811147186147394</v>
       </c>
       <c r="AL203" t="n">
-        <v>0.08811147186146684</v>
+        <v>0.08811147186147394</v>
       </c>
       <c r="AM203" t="n">
-        <v>0.5506966991341677</v>
+        <v>0.5506966991342122</v>
       </c>
     </row>
     <row r="204">
@@ -28794,7 +28796,7 @@
         <v>2.003241043956047</v>
       </c>
       <c r="AM204" t="n">
-        <v>39.82586568501088</v>
+        <v>39.82586568501087</v>
       </c>
     </row>
     <row r="205">
@@ -28920,16 +28922,16 @@
         <v>0</v>
       </c>
       <c r="AJ205" t="n">
-        <v>2.575417800625301</v>
+        <v>2.5754178006253</v>
       </c>
       <c r="AK205" t="n">
-        <v>-0.5254178006253007</v>
+        <v>-0.5254178006253003</v>
       </c>
       <c r="AL205" t="n">
-        <v>0.5254178006253007</v>
+        <v>0.5254178006253003</v>
       </c>
       <c r="AM205" t="n">
-        <v>25.63013661586833</v>
+        <v>25.63013661586831</v>
       </c>
     </row>
     <row r="206">
@@ -29340,13 +29342,13 @@
         <v>15.50899071789322</v>
       </c>
       <c r="AK208" t="n">
-        <v>4.891009282106777</v>
+        <v>4.891009282106781</v>
       </c>
       <c r="AL208" t="n">
-        <v>4.891009282106777</v>
+        <v>4.891009282106781</v>
       </c>
       <c r="AM208" t="n">
-        <v>23.97553569660185</v>
+        <v>23.97553569660187</v>
       </c>
     </row>
     <row r="209">
@@ -29483,13 +29485,13 @@
         <v>1.178994282106782</v>
       </c>
       <c r="AK209" t="n">
-        <v>-0.1589942821067818</v>
+        <v>-0.158994282106782</v>
       </c>
       <c r="AL209" t="n">
-        <v>0.1589942821067818</v>
+        <v>0.158994282106782</v>
       </c>
       <c r="AM209" t="n">
-        <v>15.58767471635115</v>
+        <v>15.58767471635118</v>
       </c>
     </row>
     <row r="210">
@@ -30302,16 +30304,16 @@
         <v>1</v>
       </c>
       <c r="AJ215" t="n">
-        <v>2.753202037499535</v>
+        <v>2.753202037499534</v>
       </c>
       <c r="AK215" t="n">
-        <v>1.886797962500465</v>
+        <v>1.886797962500466</v>
       </c>
       <c r="AL215" t="n">
-        <v>1.886797962500465</v>
+        <v>1.886797962500466</v>
       </c>
       <c r="AM215" t="n">
-        <v>40.66374919182037</v>
+        <v>40.66374919182038</v>
       </c>
     </row>
     <row r="216">
@@ -30442,13 +30444,13 @@
         <v>1.931007235449734</v>
       </c>
       <c r="AK216" t="n">
-        <v>0.2189927645502663</v>
+        <v>0.2189927645502658</v>
       </c>
       <c r="AL216" t="n">
-        <v>0.2189927645502663</v>
+        <v>0.2189927645502658</v>
       </c>
       <c r="AM216" t="n">
-        <v>10.18570997908215</v>
+        <v>10.18570997908213</v>
       </c>
     </row>
     <row r="217">
@@ -30999,16 +31001,16 @@
         <v>1</v>
       </c>
       <c r="AJ220" t="n">
-        <v>2.115648032708032</v>
+        <v>2.115648032708033</v>
       </c>
       <c r="AK220" t="n">
-        <v>-0.09564803270803246</v>
+        <v>-0.0956480327080329</v>
       </c>
       <c r="AL220" t="n">
-        <v>0.09564803270803246</v>
+        <v>0.0956480327080329</v>
       </c>
       <c r="AM220" t="n">
-        <v>4.735051124160022</v>
+        <v>4.735051124160044</v>
       </c>
     </row>
     <row r="221">
@@ -31136,16 +31138,16 @@
         <v>1</v>
       </c>
       <c r="AJ221" t="n">
-        <v>1.9272923015873</v>
+        <v>1.927292301587301</v>
       </c>
       <c r="AK221" t="n">
-        <v>-0.02729230158730056</v>
+        <v>-0.027292301587301</v>
       </c>
       <c r="AL221" t="n">
-        <v>0.02729230158730056</v>
+        <v>0.027292301587301</v>
       </c>
       <c r="AM221" t="n">
-        <v>1.436436925647398</v>
+        <v>1.436436925647421</v>
       </c>
     </row>
     <row r="222">
@@ -31830,13 +31832,13 @@
         <v>1.178994282106782</v>
       </c>
       <c r="AK226" t="n">
-        <v>-0.0589942821067817</v>
+        <v>-0.05899428210678193</v>
       </c>
       <c r="AL226" t="n">
-        <v>0.0589942821067817</v>
+        <v>0.05899428210678193</v>
       </c>
       <c r="AM226" t="n">
-        <v>5.267346616676937</v>
+        <v>5.267346616676957</v>
       </c>
     </row>
     <row r="227">
@@ -32104,13 +32106,13 @@
         <v>1.122731129148629</v>
       </c>
       <c r="AK228" t="n">
-        <v>0.127268870851371</v>
+        <v>0.1272688708513712</v>
       </c>
       <c r="AL228" t="n">
-        <v>0.127268870851371</v>
+        <v>0.1272688708513712</v>
       </c>
       <c r="AM228" t="n">
-        <v>10.18150966810968</v>
+        <v>10.18150966810969</v>
       </c>
     </row>
     <row r="229">
@@ -32247,13 +32249,13 @@
         <v>24.16819563492062</v>
       </c>
       <c r="AK229" t="n">
-        <v>-1.668195634920618</v>
+        <v>-1.668195634920622</v>
       </c>
       <c r="AL229" t="n">
-        <v>1.668195634920618</v>
+        <v>1.668195634920622</v>
       </c>
       <c r="AM229" t="n">
-        <v>7.414202821869415</v>
+        <v>7.41420282186943</v>
       </c>
     </row>
     <row r="230">
@@ -32941,16 +32943,16 @@
         <v>1</v>
       </c>
       <c r="AJ234" t="n">
-        <v>2.111659973544974</v>
+        <v>2.111659973544975</v>
       </c>
       <c r="AK234" t="n">
-        <v>2.308340026455026</v>
+        <v>2.308340026455025</v>
       </c>
       <c r="AL234" t="n">
-        <v>2.308340026455026</v>
+        <v>2.308340026455025</v>
       </c>
       <c r="AM234" t="n">
-        <v>52.22488747635805</v>
+        <v>52.22488747635804</v>
       </c>
     </row>
     <row r="235">
@@ -33227,16 +33229,16 @@
         <v>0</v>
       </c>
       <c r="AJ236" t="n">
-        <v>11.49662575433825</v>
+        <v>11.49662575433826</v>
       </c>
       <c r="AK236" t="n">
-        <v>-2.096625754338254</v>
+        <v>-2.096625754338255</v>
       </c>
       <c r="AL236" t="n">
-        <v>2.096625754338254</v>
+        <v>2.096625754338255</v>
       </c>
       <c r="AM236" t="n">
-        <v>22.30452930147078</v>
+        <v>22.3045293014708</v>
       </c>
     </row>
     <row r="237">
@@ -33367,13 +33369,13 @@
         <v>1.245809785954787</v>
       </c>
       <c r="AK237" t="n">
-        <v>0.01419021404521326</v>
+        <v>0.01419021404521348</v>
       </c>
       <c r="AL237" t="n">
-        <v>0.01419021404521326</v>
+        <v>0.01419021404521348</v>
       </c>
       <c r="AM237" t="n">
-        <v>1.126207463905814</v>
+        <v>1.126207463905831</v>
       </c>
     </row>
     <row r="238">
@@ -33501,16 +33503,16 @@
         <v>1</v>
       </c>
       <c r="AJ238" t="n">
-        <v>1.397737615440116</v>
+        <v>1.397737615440115</v>
       </c>
       <c r="AK238" t="n">
-        <v>0.2922623845598844</v>
+        <v>0.2922623845598848</v>
       </c>
       <c r="AL238" t="n">
-        <v>0.2922623845598844</v>
+        <v>0.2922623845598848</v>
       </c>
       <c r="AM238" t="n">
-        <v>17.29363222247837</v>
+        <v>17.29363222247839</v>
       </c>
     </row>
     <row r="239">
@@ -33641,13 +33643,13 @@
         <v>3.573573283475785</v>
       </c>
       <c r="AK239" t="n">
-        <v>0.05642671652421516</v>
+        <v>0.05642671652421472</v>
       </c>
       <c r="AL239" t="n">
-        <v>0.05642671652421516</v>
+        <v>0.05642671652421472</v>
       </c>
       <c r="AM239" t="n">
-        <v>1.554455000667084</v>
+        <v>1.554455000667072</v>
       </c>
     </row>
     <row r="240">
@@ -33778,13 +33780,13 @@
         <v>1.454185542328041</v>
       </c>
       <c r="AK240" t="n">
-        <v>0.8558144576719589</v>
+        <v>0.8558144576719586</v>
       </c>
       <c r="AL240" t="n">
-        <v>0.8558144576719589</v>
+        <v>0.8558144576719586</v>
       </c>
       <c r="AM240" t="n">
-        <v>37.04824492086402</v>
+        <v>37.04824492086401</v>
       </c>
     </row>
     <row r="241">
@@ -34740,16 +34742,16 @@
         <v>0</v>
       </c>
       <c r="AJ247" t="n">
-        <v>20.26365303030302</v>
+        <v>20.26365303030303</v>
       </c>
       <c r="AK247" t="n">
-        <v>-4.263653030303018</v>
+        <v>-4.263653030303029</v>
       </c>
       <c r="AL247" t="n">
-        <v>4.263653030303018</v>
+        <v>4.263653030303029</v>
       </c>
       <c r="AM247" t="n">
-        <v>26.64783143939387</v>
+        <v>26.64783143939393</v>
       </c>
     </row>
     <row r="248">
@@ -35014,16 +35016,16 @@
         <v>1</v>
       </c>
       <c r="AJ249" t="n">
-        <v>1.945346357346356</v>
+        <v>1.945346357346357</v>
       </c>
       <c r="AK249" t="n">
-        <v>0.5846536426536437</v>
+        <v>0.5846536426536431</v>
       </c>
       <c r="AL249" t="n">
-        <v>0.5846536426536437</v>
+        <v>0.5846536426536431</v>
       </c>
       <c r="AM249" t="n">
-        <v>23.10883963057881</v>
+        <v>23.10883963057878</v>
       </c>
     </row>
     <row r="250">
@@ -35291,13 +35293,13 @@
         <v>2.749246547619047</v>
       </c>
       <c r="AK251" t="n">
-        <v>0.3507534523809528</v>
+        <v>0.3507534523809532</v>
       </c>
       <c r="AL251" t="n">
-        <v>0.3507534523809528</v>
+        <v>0.3507534523809532</v>
       </c>
       <c r="AM251" t="n">
-        <v>11.31462749615977</v>
+        <v>11.31462749615978</v>
       </c>
     </row>
     <row r="252">
@@ -35425,16 +35427,16 @@
         <v>1</v>
       </c>
       <c r="AJ252" t="n">
-        <v>1.952123363812112</v>
+        <v>1.952123363812113</v>
       </c>
       <c r="AK252" t="n">
-        <v>1.477876636187888</v>
+        <v>1.477876636187887</v>
       </c>
       <c r="AL252" t="n">
-        <v>1.477876636187888</v>
+        <v>1.477876636187887</v>
       </c>
       <c r="AM252" t="n">
-        <v>43.08678239614833</v>
+        <v>43.08678239614831</v>
       </c>
     </row>
     <row r="253">
@@ -35568,16 +35570,16 @@
         <v>0</v>
       </c>
       <c r="AJ253" t="n">
-        <v>8.860108703703707</v>
+        <v>8.860108703703705</v>
       </c>
       <c r="AK253" t="n">
-        <v>0.9498912962962933</v>
+        <v>0.9498912962962951</v>
       </c>
       <c r="AL253" t="n">
-        <v>0.9498912962962933</v>
+        <v>0.9498912962962951</v>
       </c>
       <c r="AM253" t="n">
-        <v>9.682887831766497</v>
+        <v>9.682887831766514</v>
       </c>
     </row>
     <row r="254">
@@ -35842,16 +35844,16 @@
         <v>1</v>
       </c>
       <c r="AJ255" t="n">
-        <v>3.504752225274725</v>
+        <v>3.504752225274726</v>
       </c>
       <c r="AK255" t="n">
-        <v>-0.2447522252747256</v>
+        <v>-0.2447522252747265</v>
       </c>
       <c r="AL255" t="n">
-        <v>0.2447522252747256</v>
+        <v>0.2447522252747265</v>
       </c>
       <c r="AM255" t="n">
-        <v>7.507736971617351</v>
+        <v>7.507736971617378</v>
       </c>
     </row>
     <row r="256">
@@ -36399,13 +36401,13 @@
         <v>3.573573283475785</v>
       </c>
       <c r="AK259" t="n">
-        <v>-0.4535732834757846</v>
+        <v>-0.4535732834757851</v>
       </c>
       <c r="AL259" t="n">
-        <v>0.4535732834757846</v>
+        <v>0.4535732834757851</v>
       </c>
       <c r="AM259" t="n">
-        <v>14.53760523960848</v>
+        <v>14.53760523960849</v>
       </c>
     </row>
     <row r="260">
@@ -36536,13 +36538,13 @@
         <v>1.454185542328041</v>
       </c>
       <c r="AK260" t="n">
-        <v>0.0458144576719588</v>
+        <v>0.04581445767195857</v>
       </c>
       <c r="AL260" t="n">
-        <v>0.0458144576719588</v>
+        <v>0.04581445767195857</v>
       </c>
       <c r="AM260" t="n">
-        <v>3.054297178130587</v>
+        <v>3.054297178130572</v>
       </c>
     </row>
     <row r="261">
@@ -36810,13 +36812,13 @@
         <v>3.545207354497353</v>
       </c>
       <c r="AK262" t="n">
-        <v>-0.4652073544973527</v>
+        <v>-0.4652073544973532</v>
       </c>
       <c r="AL262" t="n">
-        <v>0.4652073544973527</v>
+        <v>0.4652073544973532</v>
       </c>
       <c r="AM262" t="n">
-        <v>15.10413488627769</v>
+        <v>15.1041348862777</v>
       </c>
     </row>
     <row r="263">
@@ -36943,13 +36945,13 @@
         <v>1.970527156084655</v>
       </c>
       <c r="AK263" t="n">
-        <v>-0.4305271560846549</v>
+        <v>-0.4305271560846551</v>
       </c>
       <c r="AL263" t="n">
-        <v>0.4305271560846549</v>
+        <v>0.4305271560846551</v>
       </c>
       <c r="AM263" t="n">
-        <v>27.9563088366659</v>
+        <v>27.95630883666592</v>
       </c>
     </row>
     <row r="264">
@@ -37089,16 +37091,16 @@
         <v>0</v>
       </c>
       <c r="AJ264" t="n">
-        <v>8.810385328652826</v>
+        <v>8.810385328652828</v>
       </c>
       <c r="AK264" t="n">
-        <v>-2.380385328652826</v>
+        <v>-2.380385328652828</v>
       </c>
       <c r="AL264" t="n">
-        <v>2.380385328652826</v>
+        <v>2.380385328652828</v>
       </c>
       <c r="AM264" t="n">
-        <v>37.01998955914193</v>
+        <v>37.01998955914196</v>
       </c>
     </row>
     <row r="265">
@@ -37238,16 +37240,16 @@
         <v>0</v>
       </c>
       <c r="AJ265" t="n">
-        <v>2.625779105339105</v>
+        <v>2.625779105339106</v>
       </c>
       <c r="AK265" t="n">
-        <v>-1.615779105339105</v>
+        <v>-1.615779105339106</v>
       </c>
       <c r="AL265" t="n">
-        <v>1.615779105339105</v>
+        <v>1.615779105339106</v>
       </c>
       <c r="AM265" t="n">
-        <v>159.9781292414955</v>
+        <v>159.9781292414957</v>
       </c>
     </row>
     <row r="266">
@@ -37527,13 +37529,13 @@
         <v>1.634873779461279</v>
       </c>
       <c r="AK267" t="n">
-        <v>-0.3748737794612786</v>
+        <v>-0.3748737794612789</v>
       </c>
       <c r="AL267" t="n">
-        <v>0.3748737794612786</v>
+        <v>0.3748737794612789</v>
       </c>
       <c r="AM267" t="n">
-        <v>29.75188725883164</v>
+        <v>29.75188725883165</v>
       </c>
     </row>
     <row r="268">
@@ -38081,13 +38083,13 @@
         <v>20.05331731601731</v>
       </c>
       <c r="AK271" t="n">
-        <v>0.9466826839826936</v>
+        <v>0.9466826839826865</v>
       </c>
       <c r="AL271" t="n">
-        <v>0.9466826839826936</v>
+        <v>0.9466826839826865</v>
       </c>
       <c r="AM271" t="n">
-        <v>4.508012780869969</v>
+        <v>4.508012780869936</v>
       </c>
     </row>
     <row r="272">
@@ -38372,16 +38374,16 @@
         <v>1</v>
       </c>
       <c r="AJ273" t="n">
-        <v>2.665485965608463</v>
+        <v>2.665485965608462</v>
       </c>
       <c r="AK273" t="n">
-        <v>0.6845140343915372</v>
+        <v>0.6845140343915381</v>
       </c>
       <c r="AL273" t="n">
-        <v>0.6845140343915372</v>
+        <v>0.6845140343915381</v>
       </c>
       <c r="AM273" t="n">
-        <v>20.43325475795633</v>
+        <v>20.43325475795636</v>
       </c>
     </row>
     <row r="274">
@@ -38515,16 +38517,16 @@
         <v>0</v>
       </c>
       <c r="AJ274" t="n">
-        <v>20.76966877104376</v>
+        <v>20.76966877104377</v>
       </c>
       <c r="AK274" t="n">
-        <v>0.4303312289562378</v>
+        <v>0.4303312289562342</v>
       </c>
       <c r="AL274" t="n">
-        <v>0.4303312289562378</v>
+        <v>0.4303312289562342</v>
       </c>
       <c r="AM274" t="n">
-        <v>2.029864287529424</v>
+        <v>2.029864287529407</v>
       </c>
     </row>
     <row r="275">
@@ -38938,16 +38940,16 @@
         <v>1</v>
       </c>
       <c r="AJ277" t="n">
-        <v>1.952123363812112</v>
+        <v>1.952123363812113</v>
       </c>
       <c r="AK277" t="n">
-        <v>-0.5121233638121123</v>
+        <v>-0.5121233638121132</v>
       </c>
       <c r="AL277" t="n">
-        <v>0.5121233638121123</v>
+        <v>0.5121233638121132</v>
       </c>
       <c r="AM277" t="n">
-        <v>35.56412248695224</v>
+        <v>35.56412248695231</v>
       </c>
     </row>
     <row r="278">
@@ -39075,16 +39077,16 @@
         <v>1</v>
       </c>
       <c r="AJ278" t="n">
-        <v>2.146390200216452</v>
+        <v>2.146390200216451</v>
       </c>
       <c r="AK278" t="n">
-        <v>-0.6163902002164516</v>
+        <v>-0.6163902002164512</v>
       </c>
       <c r="AL278" t="n">
-        <v>0.6163902002164516</v>
+        <v>0.6163902002164512</v>
       </c>
       <c r="AM278" t="n">
-        <v>40.28694119061775</v>
+        <v>40.28694119061772</v>
       </c>
     </row>
     <row r="279">
@@ -39212,16 +39214,16 @@
         <v>1</v>
       </c>
       <c r="AJ279" t="n">
-        <v>2.115906521164021</v>
+        <v>2.11590652116402</v>
       </c>
       <c r="AK279" t="n">
-        <v>-0.6359065211640207</v>
+        <v>-0.6359065211640202</v>
       </c>
       <c r="AL279" t="n">
-        <v>0.6359065211640207</v>
+        <v>0.6359065211640202</v>
       </c>
       <c r="AM279" t="n">
-        <v>42.9666568354068</v>
+        <v>42.96665683540677</v>
       </c>
     </row>
     <row r="280">
@@ -39349,16 +39351,16 @@
         <v>1</v>
       </c>
       <c r="AJ280" t="n">
-        <v>3.416999100529102</v>
+        <v>3.416999100529101</v>
       </c>
       <c r="AK280" t="n">
-        <v>-0.4269991005291018</v>
+        <v>-0.426999100529101</v>
       </c>
       <c r="AL280" t="n">
-        <v>0.4269991005291018</v>
+        <v>0.426999100529101</v>
       </c>
       <c r="AM280" t="n">
-        <v>14.28090637221076</v>
+        <v>14.28090637221073</v>
       </c>
     </row>
     <row r="281">
@@ -39790,16 +39792,16 @@
         <v>1</v>
       </c>
       <c r="AJ283" t="n">
-        <v>3.504752225274725</v>
+        <v>3.504752225274726</v>
       </c>
       <c r="AK283" t="n">
-        <v>-0.1547522252747253</v>
+        <v>-0.1547522252747262</v>
       </c>
       <c r="AL283" t="n">
-        <v>0.1547522252747253</v>
+        <v>0.1547522252747262</v>
       </c>
       <c r="AM283" t="n">
-        <v>4.61946941118583</v>
+        <v>4.619469411185857</v>
       </c>
     </row>
     <row r="284">
@@ -40076,16 +40078,16 @@
         <v>1</v>
       </c>
       <c r="AJ285" t="n">
-        <v>2.018190687830686</v>
+        <v>2.018190687830687</v>
       </c>
       <c r="AK285" t="n">
-        <v>-0.03819068783068635</v>
+        <v>-0.0381906878306868</v>
       </c>
       <c r="AL285" t="n">
-        <v>0.03819068783068635</v>
+        <v>0.0381906878306868</v>
       </c>
       <c r="AM285" t="n">
-        <v>1.928822617711432</v>
+        <v>1.928822617711454</v>
       </c>
     </row>
     <row r="286">
@@ -40487,16 +40489,16 @@
         <v>1</v>
       </c>
       <c r="AJ288" t="n">
-        <v>4.114252129629628</v>
+        <v>4.114252129629631</v>
       </c>
       <c r="AK288" t="n">
-        <v>-0.5542521296296283</v>
+        <v>-0.554252129629631</v>
       </c>
       <c r="AL288" t="n">
-        <v>0.5542521296296283</v>
+        <v>0.554252129629631</v>
       </c>
       <c r="AM288" t="n">
-        <v>15.56888004577608</v>
+        <v>15.56888004577615</v>
       </c>
     </row>
     <row r="289">
@@ -40627,13 +40629,13 @@
         <v>1.589712946590448</v>
       </c>
       <c r="AK289" t="n">
-        <v>0.650287053409552</v>
+        <v>0.6502870534095524</v>
       </c>
       <c r="AL289" t="n">
-        <v>0.650287053409552</v>
+        <v>0.6502870534095524</v>
       </c>
       <c r="AM289" t="n">
-        <v>29.03067202721214</v>
+        <v>29.03067202721216</v>
       </c>
     </row>
     <row r="290">
@@ -40764,13 +40766,13 @@
         <v>1.589712946590448</v>
       </c>
       <c r="AK290" t="n">
-        <v>0.1902870534095518</v>
+        <v>0.1902870534095522</v>
       </c>
       <c r="AL290" t="n">
-        <v>0.1902870534095518</v>
+        <v>0.1902870534095522</v>
       </c>
       <c r="AM290" t="n">
-        <v>10.69028389941302</v>
+        <v>10.69028389941305</v>
       </c>
     </row>
     <row r="291">
@@ -40901,13 +40903,13 @@
         <v>4.132082976190476</v>
       </c>
       <c r="AK291" t="n">
-        <v>0.4979170238095243</v>
+        <v>0.4979170238095234</v>
       </c>
       <c r="AL291" t="n">
-        <v>0.4979170238095243</v>
+        <v>0.4979170238095234</v>
       </c>
       <c r="AM291" t="n">
-        <v>10.75414738249513</v>
+        <v>10.75414738249511</v>
       </c>
     </row>
     <row r="292">
@@ -41035,16 +41037,16 @@
         <v>1</v>
       </c>
       <c r="AJ292" t="n">
-        <v>2.495758687469939</v>
+        <v>2.49575868746994</v>
       </c>
       <c r="AK292" t="n">
-        <v>-0.3257586874699392</v>
+        <v>-0.3257586874699396</v>
       </c>
       <c r="AL292" t="n">
-        <v>0.3257586874699392</v>
+        <v>0.3257586874699396</v>
       </c>
       <c r="AM292" t="n">
-        <v>15.01192108156402</v>
+        <v>15.01192108156404</v>
       </c>
     </row>
     <row r="293">
@@ -41172,16 +41174,16 @@
         <v>1</v>
       </c>
       <c r="AJ293" t="n">
-        <v>3.901334247881751</v>
+        <v>3.90133424788175</v>
       </c>
       <c r="AK293" t="n">
-        <v>1.388665752118249</v>
+        <v>1.38866575211825</v>
       </c>
       <c r="AL293" t="n">
-        <v>1.388665752118249</v>
+        <v>1.38866575211825</v>
       </c>
       <c r="AM293" t="n">
-        <v>26.25077036140358</v>
+        <v>26.2507703614036</v>
       </c>
     </row>
     <row r="294">
@@ -41309,16 +41311,16 @@
         <v>1</v>
       </c>
       <c r="AJ294" t="n">
-        <v>4.24408261904762</v>
+        <v>4.244082619047622</v>
       </c>
       <c r="AK294" t="n">
-        <v>4.90591738095238</v>
+        <v>4.905917380952379</v>
       </c>
       <c r="AL294" t="n">
-        <v>4.90591738095238</v>
+        <v>4.905917380952379</v>
       </c>
       <c r="AM294" t="n">
-        <v>53.61658339838667</v>
+        <v>53.61658339838665</v>
       </c>
     </row>
     <row r="295">
@@ -41446,16 +41448,16 @@
         <v>1</v>
       </c>
       <c r="AJ295" t="n">
-        <v>2.52895521164021</v>
+        <v>2.528955211640211</v>
       </c>
       <c r="AK295" t="n">
-        <v>-0.2889552116402099</v>
+        <v>-0.2889552116402103</v>
       </c>
       <c r="AL295" t="n">
-        <v>0.2889552116402099</v>
+        <v>0.2889552116402103</v>
       </c>
       <c r="AM295" t="n">
-        <v>12.89978623393794</v>
+        <v>12.89978623393796</v>
       </c>
     </row>
     <row r="296">
@@ -41583,16 +41585,16 @@
         <v>1</v>
       </c>
       <c r="AJ296" t="n">
-        <v>2.309938091029341</v>
+        <v>2.309938091029343</v>
       </c>
       <c r="AK296" t="n">
-        <v>0.3100619089706589</v>
+        <v>0.3100619089706576</v>
       </c>
       <c r="AL296" t="n">
-        <v>0.3100619089706589</v>
+        <v>0.3100619089706576</v>
       </c>
       <c r="AM296" t="n">
-        <v>11.8344240065137</v>
+        <v>11.83442400651365</v>
       </c>
     </row>
     <row r="297">
@@ -42006,16 +42008,16 @@
         <v>1</v>
       </c>
       <c r="AJ299" t="n">
-        <v>1.451088594276094</v>
+        <v>1.451088594276095</v>
       </c>
       <c r="AK299" t="n">
-        <v>0.1089114057239058</v>
+        <v>0.1089114057239053</v>
       </c>
       <c r="AL299" t="n">
-        <v>0.1089114057239058</v>
+        <v>0.1089114057239053</v>
       </c>
       <c r="AM299" t="n">
-        <v>6.981500366917038</v>
+        <v>6.981500366917009</v>
       </c>
     </row>
     <row r="300">
@@ -42143,16 +42145,16 @@
         <v>1</v>
       </c>
       <c r="AJ300" t="n">
-        <v>1.952123363812112</v>
+        <v>1.952123363812113</v>
       </c>
       <c r="AK300" t="n">
-        <v>-0.8021233638121124</v>
+        <v>-0.8021233638121132</v>
       </c>
       <c r="AL300" t="n">
-        <v>0.8021233638121124</v>
+        <v>0.8021233638121132</v>
       </c>
       <c r="AM300" t="n">
-        <v>69.74985772279238</v>
+        <v>69.74985772279247</v>
       </c>
     </row>
     <row r="301">
@@ -42280,16 +42282,16 @@
         <v>1</v>
       </c>
       <c r="AJ301" t="n">
-        <v>1.952123363812112</v>
+        <v>1.952123363812113</v>
       </c>
       <c r="AK301" t="n">
-        <v>-0.4021233638121122</v>
+        <v>-0.4021233638121131</v>
       </c>
       <c r="AL301" t="n">
-        <v>0.4021233638121122</v>
+        <v>0.4021233638121131</v>
       </c>
       <c r="AM301" t="n">
-        <v>25.94344282658789</v>
+        <v>25.94344282658794</v>
       </c>
     </row>
     <row r="302">
@@ -42554,16 +42556,16 @@
         <v>1</v>
       </c>
       <c r="AJ303" t="n">
-        <v>1.977615396825396</v>
+        <v>1.977615396825397</v>
       </c>
       <c r="AK303" t="n">
-        <v>-0.03761539682539605</v>
+        <v>-0.03761539682539672</v>
       </c>
       <c r="AL303" t="n">
-        <v>0.03761539682539605</v>
+        <v>0.03761539682539672</v>
       </c>
       <c r="AM303" t="n">
-        <v>1.938937980690518</v>
+        <v>1.938937980690553</v>
       </c>
     </row>
     <row r="304">
@@ -42831,10 +42833,10 @@
         <v>1.705189927248676</v>
       </c>
       <c r="AK305" t="n">
-        <v>-0.8951899272486759</v>
+        <v>-0.8951899272486761</v>
       </c>
       <c r="AL305" t="n">
-        <v>0.8951899272486759</v>
+        <v>0.8951899272486761</v>
       </c>
       <c r="AM305" t="n">
         <v>110.5172749689723</v>
@@ -42968,13 +42970,13 @@
         <v>1.811084348244348</v>
       </c>
       <c r="AK306" t="n">
-        <v>0.2889156517556521</v>
+        <v>0.2889156517556517</v>
       </c>
       <c r="AL306" t="n">
-        <v>0.2889156517556521</v>
+        <v>0.2889156517556517</v>
       </c>
       <c r="AM306" t="n">
-        <v>13.75788817884058</v>
+        <v>13.75788817884056</v>
       </c>
     </row>
     <row r="307">
@@ -43102,16 +43104,16 @@
         <v>1</v>
       </c>
       <c r="AJ307" t="n">
-        <v>1.952123363812112</v>
+        <v>1.952123363812113</v>
       </c>
       <c r="AK307" t="n">
-        <v>-0.4821233638121123</v>
+        <v>-0.4821233638121132</v>
       </c>
       <c r="AL307" t="n">
-        <v>0.4821233638121123</v>
+        <v>0.4821233638121132</v>
       </c>
       <c r="AM307" t="n">
-        <v>32.79750774232056</v>
+        <v>32.79750774232063</v>
       </c>
     </row>
     <row r="308">
@@ -43239,16 +43241,16 @@
         <v>1</v>
       </c>
       <c r="AJ308" t="n">
-        <v>1.952123363812112</v>
+        <v>1.952123363812113</v>
       </c>
       <c r="AK308" t="n">
-        <v>0.6878766361878879</v>
+        <v>0.687876636187887</v>
       </c>
       <c r="AL308" t="n">
-        <v>0.6878766361878879</v>
+        <v>0.687876636187887</v>
       </c>
       <c r="AM308" t="n">
-        <v>26.05593318893514</v>
+        <v>26.05593318893511</v>
       </c>
     </row>
     <row r="309">
@@ -43379,13 +43381,13 @@
         <v>5.107552433862431</v>
       </c>
       <c r="AK309" t="n">
-        <v>2.37244756613757</v>
+        <v>2.372447566137569</v>
       </c>
       <c r="AL309" t="n">
-        <v>2.37244756613757</v>
+        <v>2.372447566137569</v>
       </c>
       <c r="AM309" t="n">
-        <v>31.71721345103703</v>
+        <v>31.71721345103702</v>
       </c>
     </row>
     <row r="310">
@@ -43513,16 +43515,16 @@
         <v>1</v>
       </c>
       <c r="AJ310" t="n">
-        <v>1.952123363812112</v>
+        <v>1.952123363812113</v>
       </c>
       <c r="AK310" t="n">
-        <v>-0.4521233638121123</v>
+        <v>-0.4521233638121132</v>
       </c>
       <c r="AL310" t="n">
-        <v>0.4521233638121123</v>
+        <v>0.4521233638121132</v>
       </c>
       <c r="AM310" t="n">
-        <v>30.14155758747415</v>
+        <v>30.14155758747421</v>
       </c>
     </row>
     <row r="311">
@@ -43659,13 +43661,13 @@
         <v>22.39961822991821</v>
       </c>
       <c r="AK311" t="n">
-        <v>2.500381770081784</v>
+        <v>2.500381770081788</v>
       </c>
       <c r="AL311" t="n">
-        <v>2.500381770081784</v>
+        <v>2.500381770081788</v>
       </c>
       <c r="AM311" t="n">
-        <v>10.04169385575014</v>
+        <v>10.04169385575015</v>
       </c>
     </row>
     <row r="312">
@@ -43802,13 +43804,13 @@
         <v>24.81999178691677</v>
       </c>
       <c r="AK312" t="n">
-        <v>3.68000821308323</v>
+        <v>3.680008213083234</v>
       </c>
       <c r="AL312" t="n">
-        <v>3.68000821308323</v>
+        <v>3.680008213083234</v>
       </c>
       <c r="AM312" t="n">
-        <v>12.91230951959028</v>
+        <v>12.91230951959029</v>
       </c>
     </row>
     <row r="313">
@@ -44222,16 +44224,16 @@
         <v>0</v>
       </c>
       <c r="AJ315" t="n">
-        <v>9.294051242183746</v>
+        <v>9.294051242183748</v>
       </c>
       <c r="AK315" t="n">
-        <v>-0.4940512421837457</v>
+        <v>-0.4940512421837475</v>
       </c>
       <c r="AL315" t="n">
-        <v>0.4940512421837457</v>
+        <v>0.4940512421837475</v>
       </c>
       <c r="AM315" t="n">
-        <v>5.614218661178929</v>
+        <v>5.614218661178948</v>
       </c>
     </row>
     <row r="316">
@@ -44365,16 +44367,16 @@
         <v>0</v>
       </c>
       <c r="AJ316" t="n">
-        <v>9.475523900913901</v>
+        <v>9.475523900913899</v>
       </c>
       <c r="AK316" t="n">
-        <v>-0.1055239009139015</v>
+        <v>-0.1055239009138997</v>
       </c>
       <c r="AL316" t="n">
-        <v>0.1055239009139015</v>
+        <v>0.1055239009138997</v>
       </c>
       <c r="AM316" t="n">
-        <v>1.12618891050055</v>
+        <v>1.126188910500531</v>
       </c>
     </row>
     <row r="317">
@@ -44654,13 +44656,13 @@
         <v>12.12339782106782</v>
       </c>
       <c r="AK318" t="n">
-        <v>1.276602178932183</v>
+        <v>1.276602178932185</v>
       </c>
       <c r="AL318" t="n">
-        <v>1.276602178932183</v>
+        <v>1.276602178932185</v>
       </c>
       <c r="AM318" t="n">
-        <v>9.526881932329726</v>
+        <v>9.52688193232974</v>
       </c>
     </row>
     <row r="319">
@@ -44794,16 +44796,16 @@
         <v>0</v>
       </c>
       <c r="AJ319" t="n">
-        <v>20.25131606060604</v>
+        <v>20.25131606060605</v>
       </c>
       <c r="AK319" t="n">
-        <v>1.348683939393958</v>
+        <v>1.348683939393954</v>
       </c>
       <c r="AL319" t="n">
-        <v>1.348683939393958</v>
+        <v>1.348683939393954</v>
       </c>
       <c r="AM319" t="n">
-        <v>6.243907126823877</v>
+        <v>6.243907126823861</v>
       </c>
     </row>
     <row r="320">
@@ -44940,13 +44942,13 @@
         <v>23.25589309764309</v>
       </c>
       <c r="AK320" t="n">
-        <v>-2.455893097643084</v>
+        <v>-2.455893097643088</v>
       </c>
       <c r="AL320" t="n">
-        <v>2.455893097643084</v>
+        <v>2.455893097643088</v>
       </c>
       <c r="AM320" t="n">
-        <v>11.80717835405329</v>
+        <v>11.80717835405331</v>
       </c>
     </row>
     <row r="321">
@@ -45226,13 +45228,13 @@
         <v>24.94216216931217</v>
       </c>
       <c r="AK322" t="n">
-        <v>3.057837830687827</v>
+        <v>3.057837830687831</v>
       </c>
       <c r="AL322" t="n">
-        <v>3.057837830687827</v>
+        <v>3.057837830687831</v>
       </c>
       <c r="AM322" t="n">
-        <v>10.92084939531367</v>
+        <v>10.92084939531368</v>
       </c>
     </row>
     <row r="323">
@@ -45365,13 +45367,13 @@
         <v>11.08924290043289</v>
       </c>
       <c r="AK323" t="n">
-        <v>1.01075709956711</v>
+        <v>1.010757099567108</v>
       </c>
       <c r="AL323" t="n">
-        <v>1.01075709956711</v>
+        <v>1.010757099567108</v>
       </c>
       <c r="AM323" t="n">
-        <v>8.353364459232314</v>
+        <v>8.353364459232299</v>
       </c>
     </row>
     <row r="324">
@@ -45504,13 +45506,13 @@
         <v>11.08924290043289</v>
       </c>
       <c r="AK324" t="n">
-        <v>-0.98924290043289</v>
+        <v>-0.9892429004328918</v>
       </c>
       <c r="AL324" t="n">
-        <v>0.98924290043289</v>
+        <v>0.9892429004328918</v>
       </c>
       <c r="AM324" t="n">
-        <v>9.794484162701881</v>
+        <v>9.794484162701899</v>
       </c>
     </row>
     <row r="325">
@@ -45643,13 +45645,13 @@
         <v>14.8331473015873</v>
       </c>
       <c r="AK325" t="n">
-        <v>-2.733147301587303</v>
+        <v>-2.733147301587305</v>
       </c>
       <c r="AL325" t="n">
-        <v>2.733147301587303</v>
+        <v>2.733147301587305</v>
       </c>
       <c r="AM325" t="n">
-        <v>22.58799422799424</v>
+        <v>22.58799422799426</v>
       </c>
     </row>
     <row r="326">
@@ -45776,13 +45778,13 @@
         <v>13.10025892857142</v>
       </c>
       <c r="AK326" t="n">
-        <v>-1.000258928571421</v>
+        <v>-1.000258928571419</v>
       </c>
       <c r="AL326" t="n">
-        <v>1.000258928571421</v>
+        <v>1.000258928571419</v>
       </c>
       <c r="AM326" t="n">
-        <v>8.266602715466291</v>
+        <v>8.266602715466275</v>
       </c>
     </row>
     <row r="327">
@@ -46331,16 +46333,16 @@
         <v>0</v>
       </c>
       <c r="AJ330" t="n">
-        <v>7.352562631072616</v>
+        <v>7.352562631072614</v>
       </c>
       <c r="AK330" t="n">
-        <v>2.747437368927383</v>
+        <v>2.747437368927386</v>
       </c>
       <c r="AL330" t="n">
-        <v>2.747437368927383</v>
+        <v>2.747437368927386</v>
       </c>
       <c r="AM330" t="n">
-        <v>27.20235018739984</v>
+        <v>27.20235018739987</v>
       </c>
     </row>
     <row r="331">
@@ -46474,16 +46476,16 @@
         <v>1</v>
       </c>
       <c r="AJ331" t="n">
-        <v>5.550206095478607</v>
+        <v>5.550206095478606</v>
       </c>
       <c r="AK331" t="n">
-        <v>2.549793904521393</v>
+        <v>2.549793904521394</v>
       </c>
       <c r="AL331" t="n">
-        <v>2.549793904521393</v>
+        <v>2.549793904521394</v>
       </c>
       <c r="AM331" t="n">
-        <v>31.47893709285671</v>
+        <v>31.47893709285672</v>
       </c>
     </row>
     <row r="332">
@@ -46617,16 +46619,16 @@
         <v>0</v>
       </c>
       <c r="AJ332" t="n">
-        <v>9.044257275132241</v>
+        <v>9.044257275132242</v>
       </c>
       <c r="AK332" t="n">
-        <v>0.05574272486775911</v>
+        <v>0.05574272486775733</v>
       </c>
       <c r="AL332" t="n">
-        <v>0.05574272486775911</v>
+        <v>0.05574272486775733</v>
       </c>
       <c r="AM332" t="n">
-        <v>0.612557416129221</v>
+        <v>0.6125574161292014</v>
       </c>
     </row>
     <row r="333">
@@ -46754,16 +46756,16 @@
         <v>1</v>
       </c>
       <c r="AJ333" t="n">
-        <v>3.741571042568544</v>
+        <v>3.741571042568545</v>
       </c>
       <c r="AK333" t="n">
-        <v>0.7784289574314558</v>
+        <v>0.7784289574314549</v>
       </c>
       <c r="AL333" t="n">
-        <v>0.7784289574314558</v>
+        <v>0.7784289574314549</v>
       </c>
       <c r="AM333" t="n">
-        <v>17.2218795891915</v>
+        <v>17.22187958919148</v>
       </c>
     </row>
     <row r="334">
@@ -46891,16 +46893,16 @@
         <v>1</v>
       </c>
       <c r="AJ334" t="n">
-        <v>3.559268476430977</v>
+        <v>3.559268476430978</v>
       </c>
       <c r="AK334" t="n">
-        <v>0.03073152356902309</v>
+        <v>0.0307315235690222</v>
       </c>
       <c r="AL334" t="n">
-        <v>0.03073152356902309</v>
+        <v>0.0307315235690222</v>
       </c>
       <c r="AM334" t="n">
-        <v>0.8560312971872727</v>
+        <v>0.856031297187248</v>
       </c>
     </row>
     <row r="335">
@@ -47462,13 +47464,13 @@
         <v>10.543219510582</v>
       </c>
       <c r="AK338" t="n">
-        <v>-1.443219510582001</v>
+        <v>-1.443219510582002</v>
       </c>
       <c r="AL338" t="n">
-        <v>1.443219510582001</v>
+        <v>1.443219510582002</v>
       </c>
       <c r="AM338" t="n">
-        <v>15.85955506134067</v>
+        <v>15.85955506134069</v>
       </c>
     </row>
     <row r="339">
@@ -47741,16 +47743,16 @@
         <v>0</v>
       </c>
       <c r="AJ340" t="n">
-        <v>9.26082410052909</v>
+        <v>9.260824100529089</v>
       </c>
       <c r="AK340" t="n">
-        <v>0.8391758994709093</v>
+        <v>0.8391758994709111</v>
       </c>
       <c r="AL340" t="n">
-        <v>0.8391758994709093</v>
+        <v>0.8391758994709111</v>
       </c>
       <c r="AM340" t="n">
-        <v>8.308672271989201</v>
+        <v>8.308672271989218</v>
       </c>
     </row>
     <row r="341">
@@ -49016,16 +49018,16 @@
         <v>1</v>
       </c>
       <c r="AJ349" t="n">
-        <v>5.519346095478606</v>
+        <v>5.519346095478604</v>
       </c>
       <c r="AK349" t="n">
-        <v>-3.629346095478606</v>
+        <v>-3.629346095478605</v>
       </c>
       <c r="AL349" t="n">
-        <v>3.629346095478606</v>
+        <v>3.629346095478605</v>
       </c>
       <c r="AM349" t="n">
-        <v>192.028893940667</v>
+        <v>192.0288939406669</v>
       </c>
     </row>
     <row r="350">
@@ -49159,16 +49161,16 @@
         <v>1</v>
       </c>
       <c r="AJ350" t="n">
-        <v>5.550206095478607</v>
+        <v>5.550206095478606</v>
       </c>
       <c r="AK350" t="n">
-        <v>2.549793904521393</v>
+        <v>2.549793904521394</v>
       </c>
       <c r="AL350" t="n">
-        <v>2.549793904521393</v>
+        <v>2.549793904521394</v>
       </c>
       <c r="AM350" t="n">
-        <v>31.47893709285671</v>
+        <v>31.47893709285672</v>
       </c>
     </row>
     <row r="351">
@@ -49302,16 +49304,16 @@
         <v>0</v>
       </c>
       <c r="AJ351" t="n">
-        <v>6.379763346560839</v>
+        <v>6.379763346560841</v>
       </c>
       <c r="AK351" t="n">
-        <v>-5.27976334656084</v>
+        <v>-5.279763346560841</v>
       </c>
       <c r="AL351" t="n">
-        <v>5.27976334656084</v>
+        <v>5.279763346560841</v>
       </c>
       <c r="AM351" t="n">
-        <v>479.9784860509853</v>
+        <v>479.9784860509855</v>
       </c>
     </row>
     <row r="352">
@@ -49445,16 +49447,16 @@
         <v>0</v>
       </c>
       <c r="AJ352" t="n">
-        <v>7.049299325396805</v>
+        <v>7.049299325396803</v>
       </c>
       <c r="AK352" t="n">
-        <v>2.050700674603195</v>
+        <v>2.050700674603196</v>
       </c>
       <c r="AL352" t="n">
-        <v>2.050700674603195</v>
+        <v>2.050700674603196</v>
       </c>
       <c r="AM352" t="n">
-        <v>22.53517224838676</v>
+        <v>22.53517224838678</v>
       </c>
     </row>
     <row r="353">
@@ -49582,16 +49584,16 @@
         <v>1</v>
       </c>
       <c r="AJ353" t="n">
-        <v>5.508832405002415</v>
+        <v>5.508832405002413</v>
       </c>
       <c r="AK353" t="n">
-        <v>-0.828832405002415</v>
+        <v>-0.8288324050024132</v>
       </c>
       <c r="AL353" t="n">
-        <v>0.828832405002415</v>
+        <v>0.8288324050024132</v>
       </c>
       <c r="AM353" t="n">
-        <v>17.71009412398323</v>
+        <v>17.71009412398319</v>
       </c>
     </row>
     <row r="354">
@@ -50001,16 +50003,16 @@
         <v>1</v>
       </c>
       <c r="AJ356" t="n">
-        <v>4.221653516113517</v>
+        <v>4.221653516113515</v>
       </c>
       <c r="AK356" t="n">
-        <v>-2.191653516113517</v>
+        <v>-2.191653516113516</v>
       </c>
       <c r="AL356" t="n">
-        <v>2.191653516113517</v>
+        <v>2.191653516113516</v>
       </c>
       <c r="AM356" t="n">
-        <v>107.9632273947546</v>
+        <v>107.9632273947545</v>
       </c>
     </row>
     <row r="357">
@@ -50138,16 +50140,16 @@
         <v>1</v>
       </c>
       <c r="AJ357" t="n">
-        <v>3.395111891534392</v>
+        <v>3.395111891534393</v>
       </c>
       <c r="AK357" t="n">
-        <v>4.514888108465609</v>
+        <v>4.514888108465607</v>
       </c>
       <c r="AL357" t="n">
-        <v>4.514888108465609</v>
+        <v>4.514888108465607</v>
       </c>
       <c r="AM357" t="n">
-        <v>57.07823145974221</v>
+        <v>57.07823145974219</v>
       </c>
     </row>
     <row r="358">
@@ -50420,16 +50422,16 @@
         <v>0</v>
       </c>
       <c r="AJ359" t="n">
-        <v>12.72519722222223</v>
+        <v>12.72519722222222</v>
       </c>
       <c r="AK359" t="n">
-        <v>-2.625197222222226</v>
+        <v>-2.625197222222223</v>
       </c>
       <c r="AL359" t="n">
-        <v>2.625197222222226</v>
+        <v>2.625197222222223</v>
       </c>
       <c r="AM359" t="n">
-        <v>25.99205170517056</v>
+        <v>25.99205170517053</v>
       </c>
     </row>
     <row r="360">
@@ -50980,16 +50982,16 @@
         <v>0</v>
       </c>
       <c r="AJ363" t="n">
-        <v>9.219275767195757</v>
+        <v>9.219275767195755</v>
       </c>
       <c r="AK363" t="n">
-        <v>0.8807242328042424</v>
+        <v>0.8807242328042442</v>
       </c>
       <c r="AL363" t="n">
-        <v>0.8807242328042424</v>
+        <v>0.8807242328042442</v>
       </c>
       <c r="AM363" t="n">
-        <v>8.720041908952895</v>
+        <v>8.720041908952913</v>
       </c>
     </row>
     <row r="364">
@@ -51547,13 +51549,13 @@
         <v>12.21094519841269</v>
       </c>
       <c r="AK367" t="n">
-        <v>-2.110945198412695</v>
+        <v>-2.110945198412693</v>
       </c>
       <c r="AL367" t="n">
-        <v>2.110945198412695</v>
+        <v>2.110945198412693</v>
       </c>
       <c r="AM367" t="n">
-        <v>20.90044750903659</v>
+        <v>20.90044750903657</v>
       </c>
     </row>
     <row r="368">
@@ -51820,16 +51822,16 @@
         <v>1</v>
       </c>
       <c r="AJ369" t="n">
-        <v>3.742076730399229</v>
+        <v>3.74207673039923</v>
       </c>
       <c r="AK369" t="n">
-        <v>-1.552076730399229</v>
+        <v>-1.55207673039923</v>
       </c>
       <c r="AL369" t="n">
-        <v>1.552076730399229</v>
+        <v>1.55207673039923</v>
       </c>
       <c r="AM369" t="n">
-        <v>70.87108357987347</v>
+        <v>70.87108357987351</v>
       </c>
     </row>
     <row r="370">
@@ -51962,13 +51964,13 @@
         <v>16.33909140211642</v>
       </c>
       <c r="AK370" t="n">
-        <v>-4.23909140211642</v>
+        <v>-4.239091402116424</v>
       </c>
       <c r="AL370" t="n">
-        <v>4.23909140211642</v>
+        <v>4.239091402116424</v>
       </c>
       <c r="AM370" t="n">
-        <v>35.03381324063157</v>
+        <v>35.03381324063161</v>
       </c>
     </row>
     <row r="371">
@@ -52101,13 +52103,13 @@
         <v>11.32594603174602</v>
       </c>
       <c r="AK371" t="n">
-        <v>0.774053968253984</v>
+        <v>0.7740539682539787</v>
       </c>
       <c r="AL371" t="n">
-        <v>0.774053968253984</v>
+        <v>0.7740539682539787</v>
       </c>
       <c r="AM371" t="n">
-        <v>6.397140233504</v>
+        <v>6.397140233503956</v>
       </c>
     </row>
     <row r="372">
@@ -52235,16 +52237,16 @@
         <v>1</v>
       </c>
       <c r="AJ372" t="n">
-        <v>3.395111891534392</v>
+        <v>3.395111891534393</v>
       </c>
       <c r="AK372" t="n">
-        <v>-0.4351118915343917</v>
+        <v>-0.4351118915343926</v>
       </c>
       <c r="AL372" t="n">
-        <v>0.4351118915343917</v>
+        <v>0.4351118915343926</v>
       </c>
       <c r="AM372" t="n">
-        <v>14.69972606535107</v>
+        <v>14.6997260653511</v>
       </c>
     </row>
     <row r="373">
@@ -52378,16 +52380,16 @@
         <v>0</v>
       </c>
       <c r="AJ373" t="n">
-        <v>18.23858425925927</v>
+        <v>18.23858425925926</v>
       </c>
       <c r="AK373" t="n">
-        <v>-1.438584259259269</v>
+        <v>-1.438584259259262</v>
       </c>
       <c r="AL373" t="n">
-        <v>1.438584259259269</v>
+        <v>1.438584259259262</v>
       </c>
       <c r="AM373" t="n">
-        <v>8.563001543209934</v>
+        <v>8.563001543209889</v>
       </c>
     </row>
     <row r="374">
@@ -52518,13 +52520,13 @@
         <v>2.653346839086836</v>
       </c>
       <c r="AK374" t="n">
-        <v>-0.633346839086836</v>
+        <v>-0.6333468390868364</v>
       </c>
       <c r="AL374" t="n">
-        <v>0.633346839086836</v>
+        <v>0.6333468390868364</v>
       </c>
       <c r="AM374" t="n">
-        <v>31.3538039151899</v>
+        <v>31.35380391518992</v>
       </c>
     </row>
     <row r="375">
@@ -52926,16 +52928,16 @@
         <v>1</v>
       </c>
       <c r="AJ377" t="n">
-        <v>3.504596642061642</v>
+        <v>3.504596642061641</v>
       </c>
       <c r="AK377" t="n">
-        <v>-0.6545966420616423</v>
+        <v>-0.6545966420616414</v>
       </c>
       <c r="AL377" t="n">
-        <v>0.6545966420616423</v>
+        <v>0.6545966420616414</v>
       </c>
       <c r="AM377" t="n">
-        <v>22.96830323023306</v>
+        <v>22.96830323023303</v>
       </c>
     </row>
     <row r="378">
@@ -53200,16 +53202,16 @@
         <v>1</v>
       </c>
       <c r="AJ379" t="n">
-        <v>3.416999100529102</v>
+        <v>3.416999100529101</v>
       </c>
       <c r="AK379" t="n">
-        <v>0.143000899470898</v>
+        <v>0.1430008994708989</v>
       </c>
       <c r="AL379" t="n">
-        <v>0.143000899470898</v>
+        <v>0.1430008994708989</v>
       </c>
       <c r="AM379" t="n">
-        <v>4.016879198620731</v>
+        <v>4.016879198620756</v>
       </c>
     </row>
   </sheetData>
@@ -53301,7 +53303,7 @@
         <v>0.9553295680188567</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7526584438834246</v>
+        <v>0.7526584438834245</v>
       </c>
       <c r="D4" t="n">
         <v>1.195513565439799</v>
@@ -53321,99 +53323,183 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>feature</t>
+          <t>fold</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>importance</t>
+          <t>n_train</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n_test</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>rmse</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>power_kw</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7619898178846325</v>
+        <v>302</v>
+      </c>
+      <c r="C2" t="n">
+        <v>76</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9114203537686103</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.078764537672366</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.607680121080666</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1154732062532702</v>
+        <v>302</v>
+      </c>
+      <c r="C3" t="n">
+        <v>76</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8670645029277204</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8532864631384697</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.286435979352856</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>machinery_type_code</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.05307564486013724</v>
+        <v>302</v>
+      </c>
+      <c r="C4" t="n">
+        <v>76</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9056817688088141</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.207965340946823</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.88519429088325</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>machinery_family_code</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02537477952079661</v>
+        <v>303</v>
+      </c>
+      <c r="C5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.907160491652069</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.00744591808141</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.7901183800397</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>abemis_total_count</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02103764184007033</v>
+        <v>303</v>
+      </c>
+      <c r="C6" t="n">
+        <v>75</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8846697888720605</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.256193440672909</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.255965146947756</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>abemis_dominant_region_share</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01298761565031201</v>
+        <v>302.4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8951993812058548</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.080731140102396</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.765078783660845</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>analysis_subset_code</t>
+          <t>std</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00950217733473724</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>abemis_region_breadth</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.0005591166560439159</v>
+        <v>0.5477225575051662</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5477225575051661</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.01883157092682535</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1613081160055384</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3570355063649154</v>
       </c>
     </row>
   </sheetData>
@@ -53427,159 +53513,294 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>machinery_type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mean_actual</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>mean_pred</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>mean_residual</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>rmse</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Combine Harvester</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3.230714285714285</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.704632547848977</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5260817378653087</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.099089519237376</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.692413811577557</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Four-Wheel Tractor</t>
+          <t>Water Pump</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.996923076923077</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.678188339146609</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3187347377764684</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.695791010278895</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.019693877961644</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hand Tractor</t>
+          <t>Four-Wheel Tractor</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="C4" t="n">
+        <v>14.75272727272727</v>
+      </c>
+      <c r="D4" t="n">
+        <v>15.22896389424548</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.4762366215182034</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.053511155822292</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.315805355639539</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mechanical Dryer</t>
+          <t>Thresher</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2.518888888888889</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.003944396478007</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.4850555075891187</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7448139480786697</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.043216451133418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rice Mill</t>
+          <t>Hand Tractor</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.564</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.679606409331409</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.1156064093314089</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2390705656565656</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2961220615031392</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rice Transplanter</t>
+          <t>Sheller</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.057521987433862</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2724780125661384</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.570418295153921</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6147604594875876</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rotary Tiller</t>
+          <t>Seeder</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10.23034835537918</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.1303483553791794</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.276948443562614</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.406648617009358</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Seeder</t>
+          <t>Combine Harvester</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8.062742510822488</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-4.962742510822489</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.962742510822489</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.962742510822489</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sheller</t>
+          <t>Rice Transplanter</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.230945525493025</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1.420945525493025</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.420945525493025</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.420945525493025</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Walking-Type Agricultural Tractor</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sprayer</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Thresher</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Walking-Type Agricultural Tractor</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Water Pump</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.050791944444395</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0492080555556047</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0492080555556047</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0492080555556047</v>
       </c>
     </row>
   </sheetData>
@@ -53593,59 +53814,99 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>feature</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>importance</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Harvest Machinery</t>
+          <t>power_kw</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.7619898178846325</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mobile Field Machinery</t>
+          <t>year</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.1154732062532702</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Postharvest / Processing</t>
+          <t>machinery_type_code</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>0.05307564486013724</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Stationary Engine / Irrigation</t>
+          <t>machinery_family_code</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>0.02537477952079661</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>abemis_total_count</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.02103764184007033</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>abemis_dominant_region_share</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.01298761565031201</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>analysis_subset_code</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.00950217733473724</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>abemis_region_breadth</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0005591166560439159</v>
       </c>
     </row>
   </sheetData>
@@ -53659,6 +53920,238 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Combine Harvester</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Four-Wheel Tractor</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Hand Tractor</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mechanical Dryer</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rice Mill</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rice Transplanter</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Rotary Tiller</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Seeder</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sheller</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Small Engine</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sprayer</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Thresher</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Walking-Type Agricultural Tractor</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Water Pump</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Harvest Machinery</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mobile Field Machinery</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Postharvest / Processing</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Stationary Engine / Irrigation</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/Mini-Project/Agricultural Machinery Inventory from ABEMIS/Regression Parameters Output V3/RF_Predictions.xlsx
+++ b/Mini-Project/Agricultural Machinery Inventory from ABEMIS/Regression Parameters Output V3/RF_Predictions.xlsx
@@ -748,13 +748,13 @@
         <v>1.523347182539683</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.3566528174603165</v>
+        <v>0.3566528174603172</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.3566528174603165</v>
+        <v>0.3566528174603172</v>
       </c>
       <c r="AM2" t="n">
-        <v>18.97089454576152</v>
+        <v>18.97089454576156</v>
       </c>
     </row>
     <row r="3">
@@ -882,16 +882,16 @@
         <v>1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.137224229196729</v>
+        <v>2.13722422919673</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.2572242291967295</v>
+        <v>-0.2572242291967299</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.2572242291967295</v>
+        <v>0.2572242291967299</v>
       </c>
       <c r="AM3" t="n">
-        <v>13.68213985088987</v>
+        <v>13.68213985088989</v>
       </c>
     </row>
     <row r="4">
@@ -1019,7 +1019,7 @@
         <v>1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.066793339345838</v>
+        <v>3.066793339345837</v>
       </c>
       <c r="AK4" t="n">
         <v>1.863206660654162</v>
@@ -1028,7 +1028,7 @@
         <v>1.863206660654162</v>
       </c>
       <c r="AM4" t="n">
-        <v>37.79323855282275</v>
+        <v>37.79323855282276</v>
       </c>
     </row>
     <row r="5">
@@ -1156,16 +1156,16 @@
         <v>1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.260812592592594</v>
+        <v>2.260812592592592</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.2408125925925937</v>
+        <v>-0.2408125925925924</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.2408125925925937</v>
+        <v>0.2408125925925924</v>
       </c>
       <c r="AM5" t="n">
-        <v>11.92141547488088</v>
+        <v>11.92141547488081</v>
       </c>
     </row>
     <row r="6">
@@ -1305,16 +1305,16 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>8.177128125670629</v>
+        <v>8.177128125670633</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.3971281256706289</v>
+        <v>-0.3971281256706325</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.3971281256706289</v>
+        <v>0.3971281256706325</v>
       </c>
       <c r="AM6" t="n">
-        <v>5.104474623015796</v>
+        <v>5.104474623015841</v>
       </c>
     </row>
     <row r="7">
@@ -1457,13 +1457,13 @@
         <v>1.886966587764087</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.2930334122359133</v>
+        <v>0.2930334122359131</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.2930334122359133</v>
+        <v>0.2930334122359131</v>
       </c>
       <c r="AM7" t="n">
-        <v>13.44189964384923</v>
+        <v>13.44189964384922</v>
       </c>
     </row>
     <row r="8">
@@ -1606,13 +1606,13 @@
         <v>1.398657764550264</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.378657764550264</v>
+        <v>-0.3786577645502638</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.378657764550264</v>
+        <v>0.3786577645502638</v>
       </c>
       <c r="AM8" t="n">
-        <v>37.12331025002588</v>
+        <v>37.12331025002586</v>
       </c>
     </row>
     <row r="9">
@@ -1740,13 +1740,13 @@
         <v>1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.514341825396825</v>
+        <v>1.514341825396826</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.7943418253968255</v>
+        <v>-0.7943418253968257</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.7943418253968255</v>
+        <v>0.7943418253968257</v>
       </c>
       <c r="AM9" t="n">
         <v>110.3252535273369</v>
@@ -1883,16 +1883,16 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17.0488765873016</v>
+        <v>17.04887658730161</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.7511234126983979</v>
+        <v>0.7511234126983943</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.7511234126983979</v>
+        <v>0.7511234126983943</v>
       </c>
       <c r="AM10" t="n">
-        <v>4.219794453361786</v>
+        <v>4.219794453361766</v>
       </c>
     </row>
     <row r="11">
@@ -2020,16 +2020,16 @@
         <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.610884571909572</v>
+        <v>3.61458457190957</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.430884571909572</v>
+        <v>-0.43458457190957</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.430884571909572</v>
+        <v>0.43458457190957</v>
       </c>
       <c r="AM11" t="n">
-        <v>13.54982930533245</v>
+        <v>13.66618150659025</v>
       </c>
     </row>
     <row r="12">
@@ -2157,16 +2157,16 @@
         <v>1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.698877890812892</v>
+        <v>1.698877890812891</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.2988778908128917</v>
+        <v>-0.2988778908128913</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.2988778908128917</v>
+        <v>0.2988778908128913</v>
       </c>
       <c r="AM12" t="n">
-        <v>21.34842077234941</v>
+        <v>21.34842077234938</v>
       </c>
     </row>
     <row r="13">
@@ -2294,16 +2294,16 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.698877890812892</v>
+        <v>1.698877890812891</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.4988778908128917</v>
+        <v>-0.4988778908128912</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.4988778908128917</v>
+        <v>0.4988778908128912</v>
       </c>
       <c r="AM13" t="n">
-        <v>41.57315756774098</v>
+        <v>41.57315756774094</v>
       </c>
     </row>
     <row r="14">
@@ -2431,16 +2431,16 @@
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.627470894660895</v>
+        <v>3.627470894660893</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0.6074708946608949</v>
+        <v>-0.6074708946608931</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.6074708946608949</v>
+        <v>0.6074708946608931</v>
       </c>
       <c r="AM14" t="n">
-        <v>20.1149302867846</v>
+        <v>20.11493028678454</v>
       </c>
     </row>
     <row r="15">
@@ -2568,16 +2568,16 @@
         <v>1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.627470894660895</v>
+        <v>3.627470894660893</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.3625291053391053</v>
+        <v>0.3625291053391071</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.3625291053391053</v>
+        <v>0.3625291053391071</v>
       </c>
       <c r="AM15" t="n">
-        <v>9.085942489701887</v>
+        <v>9.085942489701932</v>
       </c>
     </row>
     <row r="16">
@@ -2991,7 +2991,7 @@
         <v>1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.605089015151516</v>
+        <v>2.605089015151517</v>
       </c>
       <c r="AK18" t="n">
         <v>-1.785089015151517</v>
@@ -3000,7 +3000,7 @@
         <v>1.785089015151517</v>
       </c>
       <c r="AM18" t="n">
-        <v>217.6937823355508</v>
+        <v>217.6937823355509</v>
       </c>
     </row>
     <row r="19">
@@ -3131,13 +3131,13 @@
         <v>2.520259576719578</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.3597404232804222</v>
+        <v>0.3597404232804218</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.3597404232804222</v>
+        <v>0.3597404232804218</v>
       </c>
       <c r="AM19" t="n">
-        <v>12.49098691945911</v>
+        <v>12.49098691945909</v>
       </c>
     </row>
     <row r="20">
@@ -3265,16 +3265,16 @@
         <v>1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3.688955656565656</v>
+        <v>3.688955656565655</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.1610443434343445</v>
+        <v>0.1610443434343454</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.1610443434343445</v>
+        <v>0.1610443434343454</v>
       </c>
       <c r="AM20" t="n">
-        <v>4.182969959333622</v>
+        <v>4.182969959333646</v>
       </c>
     </row>
     <row r="21">
@@ -3405,13 +3405,13 @@
         <v>1.523347182539683</v>
       </c>
       <c r="AK21" t="n">
-        <v>-0.5033471825396834</v>
+        <v>-0.5033471825396827</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.5033471825396834</v>
+        <v>0.5033471825396827</v>
       </c>
       <c r="AM21" t="n">
-        <v>49.3477629940866</v>
+        <v>49.34776299408654</v>
       </c>
     </row>
     <row r="22">
@@ -3816,13 +3816,13 @@
         <v>1.245543742183742</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.2444562578162583</v>
+        <v>0.2444562578162581</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.2444562578162583</v>
+        <v>0.2444562578162581</v>
       </c>
       <c r="AM24" t="n">
-        <v>16.40646025612472</v>
+        <v>16.40646025612471</v>
       </c>
     </row>
     <row r="25">
@@ -3948,16 +3948,16 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.483596145983647</v>
+        <v>3.483596145983646</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.2235961459836475</v>
+        <v>-0.2235961459836466</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.2235961459836475</v>
+        <v>0.2235961459836466</v>
       </c>
       <c r="AM25" t="n">
-        <v>6.858777484160967</v>
+        <v>6.85877748416094</v>
       </c>
     </row>
     <row r="26">
@@ -4088,13 +4088,13 @@
         <v>1.174051801346801</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.09594819865319937</v>
+        <v>0.09594819865319915</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.09594819865319937</v>
+        <v>0.09594819865319915</v>
       </c>
       <c r="AM26" t="n">
-        <v>7.554976271905462</v>
+        <v>7.554976271905445</v>
       </c>
     </row>
     <row r="27">
@@ -4357,16 +4357,16 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3.483596145983647</v>
+        <v>3.483596145983646</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.4835961459836473</v>
+        <v>-0.4835961459836464</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.4835961459836473</v>
+        <v>0.4835961459836464</v>
       </c>
       <c r="AM28" t="n">
-        <v>16.11987153278825</v>
+        <v>16.11987153278821</v>
       </c>
     </row>
     <row r="29">
@@ -4637,16 +4637,16 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>12.8215764983165</v>
+        <v>12.82157649831649</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0.4215764983164956</v>
+        <v>-0.4215764983164938</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.4215764983164956</v>
+        <v>0.4215764983164938</v>
       </c>
       <c r="AM30" t="n">
-        <v>3.399810470294319</v>
+        <v>3.399810470294304</v>
       </c>
     </row>
     <row r="31">
@@ -4786,16 +4786,16 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>8.723547365689871</v>
+        <v>8.723547365689864</v>
       </c>
       <c r="AK31" t="n">
-        <v>-1.063547365689871</v>
+        <v>-1.063547365689864</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.063547365689871</v>
+        <v>1.063547365689864</v>
       </c>
       <c r="AM31" t="n">
-        <v>13.88443036148657</v>
+        <v>13.88443036148647</v>
       </c>
     </row>
     <row r="32">
@@ -4923,16 +4923,16 @@
         <v>1</v>
       </c>
       <c r="AJ32" t="n">
-        <v>3.610884571909572</v>
+        <v>3.61458457190957</v>
       </c>
       <c r="AK32" t="n">
-        <v>-1.950884571909572</v>
+        <v>-1.95458457190957</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.950884571909572</v>
+        <v>1.95458457190957</v>
       </c>
       <c r="AM32" t="n">
-        <v>117.5231669825044</v>
+        <v>117.7460585487693</v>
       </c>
     </row>
     <row r="33">
@@ -5060,16 +5060,16 @@
         <v>1</v>
       </c>
       <c r="AJ33" t="n">
-        <v>3.610884571909572</v>
+        <v>3.61458457190957</v>
       </c>
       <c r="AK33" t="n">
-        <v>-2.140884571909572</v>
+        <v>-2.14458457190957</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.140884571909572</v>
+        <v>2.14458457190957</v>
       </c>
       <c r="AM33" t="n">
-        <v>145.6384062523518</v>
+        <v>145.8901069326238</v>
       </c>
     </row>
     <row r="34">
@@ -5334,16 +5334,16 @@
         <v>1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.837548237133235</v>
+        <v>1.840138951418951</v>
       </c>
       <c r="AK35" t="n">
-        <v>-0.2175482371332353</v>
+        <v>-0.2201389514189505</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.2175482371332353</v>
+        <v>0.2201389514189505</v>
       </c>
       <c r="AM35" t="n">
-        <v>13.42890352674292</v>
+        <v>13.58882416166361</v>
       </c>
     </row>
     <row r="36">
@@ -5483,16 +5483,16 @@
         <v>1</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.179063588263588</v>
+        <v>2.179063588263589</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.1909364117364118</v>
+        <v>0.1909364117364114</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.1909364117364118</v>
+        <v>0.1909364117364114</v>
       </c>
       <c r="AM36" t="n">
-        <v>8.056388680861259</v>
+        <v>8.056388680861239</v>
       </c>
     </row>
     <row r="37">
@@ -5616,16 +5616,16 @@
         <v>1</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.779066433381433</v>
+        <v>1.778319052429051</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.1209335666185674</v>
+        <v>0.1216809475709486</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.1209335666185674</v>
+        <v>0.1216809475709486</v>
       </c>
       <c r="AM37" t="n">
-        <v>6.364924558871967</v>
+        <v>6.404260398470979</v>
       </c>
     </row>
     <row r="38">
@@ -5890,16 +5890,16 @@
         <v>1</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.636376863876863</v>
+        <v>1.635237816257815</v>
       </c>
       <c r="AK39" t="n">
-        <v>-0.1463768638768634</v>
+        <v>-0.1452378162578154</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.1463768638768634</v>
+        <v>0.1452378162578154</v>
       </c>
       <c r="AM39" t="n">
-        <v>9.823950595762646</v>
+        <v>9.747504446833249</v>
       </c>
     </row>
     <row r="40">
@@ -6176,16 +6176,16 @@
         <v>1</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.363555513468013</v>
+        <v>1.366558211880711</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.8364444865319873</v>
+        <v>0.8334417881192888</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.8364444865319873</v>
+        <v>0.8334417881192888</v>
       </c>
       <c r="AM41" t="n">
-        <v>38.02020393327215</v>
+        <v>37.88371764178585</v>
       </c>
     </row>
     <row r="42">
@@ -6309,16 +6309,16 @@
         <v>1</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.360641961279461</v>
+        <v>1.357303866041366</v>
       </c>
       <c r="AK42" t="n">
-        <v>-0.1306419612794611</v>
+        <v>-0.1273038660413657</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.1306419612794611</v>
+        <v>0.1273038660413657</v>
       </c>
       <c r="AM42" t="n">
-        <v>10.62129766499684</v>
+        <v>10.34990780824111</v>
       </c>
     </row>
     <row r="43">
@@ -6442,16 +6442,16 @@
         <v>1</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.360641961279461</v>
+        <v>1.357303866041366</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.0593580387205388</v>
+        <v>0.06269613395863427</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.0593580387205388</v>
+        <v>0.06269613395863427</v>
       </c>
       <c r="AM43" t="n">
-        <v>4.180143571868929</v>
+        <v>4.415220701312273</v>
       </c>
     </row>
     <row r="44">
@@ -6986,16 +6986,16 @@
         <v>1</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.010180886243386</v>
+        <v>2.010180886243385</v>
       </c>
       <c r="AK47" t="n">
-        <v>-0.7501808862433859</v>
+        <v>-0.7501808862433854</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.7501808862433859</v>
+        <v>0.7501808862433854</v>
       </c>
       <c r="AM47" t="n">
-        <v>59.53816557487189</v>
+        <v>59.53816557487186</v>
       </c>
     </row>
     <row r="48">
@@ -7119,16 +7119,16 @@
         <v>1</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.010180886243386</v>
+        <v>2.010180886243385</v>
       </c>
       <c r="AK48" t="n">
-        <v>-0.5201808862433859</v>
+        <v>-0.5201808862433854</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.5201808862433859</v>
+        <v>0.5201808862433854</v>
       </c>
       <c r="AM48" t="n">
-        <v>34.91146887539502</v>
+        <v>34.91146887539499</v>
       </c>
     </row>
     <row r="49">
@@ -7256,16 +7256,16 @@
         <v>1</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.49621626984127</v>
+        <v>1.496216269841269</v>
       </c>
       <c r="AK49" t="n">
-        <v>0.04378373015873049</v>
+        <v>0.04378373015873072</v>
       </c>
       <c r="AL49" t="n">
-        <v>0.04378373015873049</v>
+        <v>0.04378373015873072</v>
       </c>
       <c r="AM49" t="n">
-        <v>2.843099360956526</v>
+        <v>2.84309936095654</v>
       </c>
     </row>
     <row r="50">
@@ -7393,16 +7393,16 @@
         <v>1</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.054023315295813</v>
+        <v>2.054023315295812</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.655976684704187</v>
+        <v>0.6559766847041879</v>
       </c>
       <c r="AL50" t="n">
-        <v>0.655976684704187</v>
+        <v>0.6559766847041879</v>
       </c>
       <c r="AM50" t="n">
-        <v>24.20578172340173</v>
+        <v>24.20578172340177</v>
       </c>
     </row>
     <row r="51">
@@ -7533,13 +7533,13 @@
         <v>1.608741855459354</v>
       </c>
       <c r="AK51" t="n">
-        <v>-0.9487418554593535</v>
+        <v>-0.948741855459354</v>
       </c>
       <c r="AL51" t="n">
-        <v>0.9487418554593535</v>
+        <v>0.948741855459354</v>
       </c>
       <c r="AM51" t="n">
-        <v>143.7487659786899</v>
+        <v>143.74876597869</v>
       </c>
     </row>
     <row r="52">
@@ -7673,16 +7673,16 @@
         <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>21.85481334776334</v>
+        <v>21.85005779220779</v>
       </c>
       <c r="AK52" t="n">
-        <v>-0.4548133477633449</v>
+        <v>-0.4500577922077902</v>
       </c>
       <c r="AL52" t="n">
-        <v>0.4548133477633449</v>
+        <v>0.4500577922077902</v>
       </c>
       <c r="AM52" t="n">
-        <v>2.125296017585724</v>
+        <v>2.103073795363506</v>
       </c>
     </row>
     <row r="53">
@@ -7816,16 +7816,16 @@
         <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>16.89638751322752</v>
+        <v>16.89638751322753</v>
       </c>
       <c r="AK53" t="n">
-        <v>-0.0963875132275227</v>
+        <v>-0.09638751322752981</v>
       </c>
       <c r="AL53" t="n">
-        <v>0.0963875132275227</v>
+        <v>0.09638751322752981</v>
       </c>
       <c r="AM53" t="n">
-        <v>0.5737351977828732</v>
+        <v>0.5737351977829155</v>
       </c>
     </row>
     <row r="54">
@@ -7962,13 +7962,13 @@
         <v>23.20752248677247</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.692477513227526</v>
+        <v>1.69247751322753</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.692477513227526</v>
+        <v>1.69247751322753</v>
       </c>
       <c r="AM54" t="n">
-        <v>6.797098446696894</v>
+        <v>6.797098446696909</v>
       </c>
     </row>
     <row r="55">
@@ -8245,16 +8245,16 @@
         <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>2.936877585377585</v>
+        <v>2.936877585377584</v>
       </c>
       <c r="AK56" t="n">
-        <v>-0.5468775853775845</v>
+        <v>-0.5468775853775836</v>
       </c>
       <c r="AL56" t="n">
-        <v>0.5468775853775845</v>
+        <v>0.5468775853775836</v>
       </c>
       <c r="AM56" t="n">
-        <v>22.88190733797424</v>
+        <v>22.88190733797421</v>
       </c>
     </row>
     <row r="57">
@@ -8546,13 +8546,13 @@
         <v>1.478863716931216</v>
       </c>
       <c r="AK58" t="n">
-        <v>0.1411362830687839</v>
+        <v>0.1411362830687841</v>
       </c>
       <c r="AL58" t="n">
-        <v>0.1411362830687839</v>
+        <v>0.1411362830687841</v>
       </c>
       <c r="AM58" t="n">
-        <v>8.71211623881382</v>
+        <v>8.712116238813834</v>
       </c>
     </row>
     <row r="59">
@@ -8954,16 +8954,16 @@
         <v>1</v>
       </c>
       <c r="AJ61" t="n">
-        <v>4.012119516594518</v>
+        <v>4.012119516594516</v>
       </c>
       <c r="AK61" t="n">
-        <v>0.3178804834054825</v>
+        <v>0.3178804834054842</v>
       </c>
       <c r="AL61" t="n">
-        <v>0.3178804834054825</v>
+        <v>0.3178804834054842</v>
       </c>
       <c r="AM61" t="n">
-        <v>7.341350656015762</v>
+        <v>7.341350656015802</v>
       </c>
     </row>
     <row r="62">
@@ -9094,13 +9094,13 @@
         <v>1.538962955007954</v>
       </c>
       <c r="AK62" t="n">
-        <v>-0.3389629550079536</v>
+        <v>-0.3389629550079538</v>
       </c>
       <c r="AL62" t="n">
-        <v>0.3389629550079536</v>
+        <v>0.3389629550079538</v>
       </c>
       <c r="AM62" t="n">
-        <v>28.24691291732947</v>
+        <v>28.24691291732949</v>
       </c>
     </row>
     <row r="63">
@@ -9231,13 +9231,13 @@
         <v>1.538962955007954</v>
       </c>
       <c r="AK63" t="n">
-        <v>-0.4389629550079535</v>
+        <v>-0.4389629550079537</v>
       </c>
       <c r="AL63" t="n">
-        <v>0.4389629550079535</v>
+        <v>0.4389629550079537</v>
       </c>
       <c r="AM63" t="n">
-        <v>39.90572318254122</v>
+        <v>39.90572318254124</v>
       </c>
     </row>
     <row r="64">
@@ -9364,13 +9364,13 @@
         <v>2.231474066859065</v>
       </c>
       <c r="AK64" t="n">
-        <v>-0.9014740668590653</v>
+        <v>-0.9014740668590648</v>
       </c>
       <c r="AL64" t="n">
-        <v>0.9014740668590653</v>
+        <v>0.9014740668590648</v>
       </c>
       <c r="AM64" t="n">
-        <v>67.78000502699739</v>
+        <v>67.78000502699734</v>
       </c>
     </row>
     <row r="65">
@@ -9497,13 +9497,13 @@
         <v>1.891756534854036</v>
       </c>
       <c r="AK65" t="n">
-        <v>-0.4817565348540362</v>
+        <v>-0.481756534854036</v>
       </c>
       <c r="AL65" t="n">
-        <v>0.4817565348540362</v>
+        <v>0.481756534854036</v>
       </c>
       <c r="AM65" t="n">
-        <v>34.16713013149194</v>
+        <v>34.16713013149192</v>
       </c>
     </row>
     <row r="66">
@@ -10316,16 +10316,16 @@
         <v>1</v>
       </c>
       <c r="AJ71" t="n">
-        <v>3.610884571909572</v>
+        <v>3.61458457190957</v>
       </c>
       <c r="AK71" t="n">
-        <v>-0.6708845719095722</v>
+        <v>-0.6745845719095702</v>
       </c>
       <c r="AL71" t="n">
-        <v>0.6708845719095722</v>
+        <v>0.6745845719095702</v>
       </c>
       <c r="AM71" t="n">
-        <v>22.81920312617592</v>
+        <v>22.94505346631191</v>
       </c>
     </row>
     <row r="72">
@@ -10452,13 +10452,13 @@
         <v>2.22507146103896</v>
       </c>
       <c r="AK72" t="n">
-        <v>-0.7450714610389602</v>
+        <v>-0.7450714610389597</v>
       </c>
       <c r="AL72" t="n">
-        <v>0.7450714610389602</v>
+        <v>0.7450714610389597</v>
       </c>
       <c r="AM72" t="n">
-        <v>50.34266628641623</v>
+        <v>50.34266628641619</v>
       </c>
     </row>
     <row r="73">
@@ -10586,16 +10586,16 @@
         <v>1</v>
       </c>
       <c r="AJ73" t="n">
-        <v>1.852534378306879</v>
+        <v>1.85253437830688</v>
       </c>
       <c r="AK73" t="n">
-        <v>-0.03253437830687922</v>
+        <v>-0.03253437830687966</v>
       </c>
       <c r="AL73" t="n">
-        <v>0.03253437830687922</v>
+        <v>0.03253437830687966</v>
       </c>
       <c r="AM73" t="n">
-        <v>1.787603203674683</v>
+        <v>1.787603203674707</v>
       </c>
     </row>
     <row r="74">
@@ -10719,16 +10719,16 @@
         <v>1</v>
       </c>
       <c r="AJ74" t="n">
-        <v>2.093057682040182</v>
+        <v>2.093057682040181</v>
       </c>
       <c r="AK74" t="n">
-        <v>0.04694231795981851</v>
+        <v>0.04694231795981896</v>
       </c>
       <c r="AL74" t="n">
-        <v>0.04694231795981851</v>
+        <v>0.04694231795981896</v>
       </c>
       <c r="AM74" t="n">
-        <v>2.193566259804603</v>
+        <v>2.193566259804624</v>
       </c>
     </row>
     <row r="75">
@@ -10856,16 +10856,16 @@
         <v>1</v>
       </c>
       <c r="AJ75" t="n">
-        <v>2.151781865079367</v>
+        <v>2.151781865079366</v>
       </c>
       <c r="AK75" t="n">
-        <v>0.598218134920633</v>
+        <v>0.5982181349206339</v>
       </c>
       <c r="AL75" t="n">
-        <v>0.598218134920633</v>
+        <v>0.5982181349206339</v>
       </c>
       <c r="AM75" t="n">
-        <v>21.75338672438665</v>
+        <v>21.75338672438669</v>
       </c>
     </row>
     <row r="76">
@@ -11132,16 +11132,16 @@
         <v>0</v>
       </c>
       <c r="AJ77" t="n">
-        <v>8.194272632275132</v>
+        <v>8.183505965608468</v>
       </c>
       <c r="AK77" t="n">
-        <v>0.05572736772486842</v>
+        <v>0.0664940343915319</v>
       </c>
       <c r="AL77" t="n">
-        <v>0.05572736772486842</v>
+        <v>0.0664940343915319</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.6754832451499202</v>
+        <v>0.8059882956549321</v>
       </c>
     </row>
     <row r="78">
@@ -11269,16 +11269,16 @@
         <v>1</v>
       </c>
       <c r="AJ78" t="n">
-        <v>4.073140752765754</v>
+        <v>4.073140752765753</v>
       </c>
       <c r="AK78" t="n">
-        <v>0.5768592472342462</v>
+        <v>0.5768592472342471</v>
       </c>
       <c r="AL78" t="n">
-        <v>0.5768592472342462</v>
+        <v>0.5768592472342471</v>
       </c>
       <c r="AM78" t="n">
-        <v>12.40557520933863</v>
+        <v>12.40557520933864</v>
       </c>
     </row>
     <row r="79">
@@ -11415,13 +11415,13 @@
         <v>23.43143624338623</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.868563756613771</v>
+        <v>1.868563756613774</v>
       </c>
       <c r="AL79" t="n">
-        <v>1.868563756613771</v>
+        <v>1.868563756613774</v>
       </c>
       <c r="AM79" t="n">
-        <v>7.385627496497118</v>
+        <v>7.385627496497131</v>
       </c>
     </row>
     <row r="80">
@@ -11686,16 +11686,16 @@
         <v>1</v>
       </c>
       <c r="AJ81" t="n">
-        <v>4.073140752765754</v>
+        <v>4.073140752765753</v>
       </c>
       <c r="AK81" t="n">
-        <v>0.1768592472342458</v>
+        <v>0.1768592472342467</v>
       </c>
       <c r="AL81" t="n">
-        <v>0.1768592472342458</v>
+        <v>0.1768592472342467</v>
       </c>
       <c r="AM81" t="n">
-        <v>4.161394052570491</v>
+        <v>4.161394052570511</v>
       </c>
     </row>
     <row r="82">
@@ -12237,13 +12237,13 @@
         <v>1.878263488455987</v>
       </c>
       <c r="AK85" t="n">
-        <v>0.621736511544013</v>
+        <v>0.6217365115440125</v>
       </c>
       <c r="AL85" t="n">
-        <v>0.621736511544013</v>
+        <v>0.6217365115440125</v>
       </c>
       <c r="AM85" t="n">
-        <v>24.86946046176052</v>
+        <v>24.8694604617605</v>
       </c>
     </row>
     <row r="86">
@@ -12517,13 +12517,13 @@
         <v>4.189303067580568</v>
       </c>
       <c r="AK87" t="n">
-        <v>-0.1993030675805674</v>
+        <v>-0.1993030675805683</v>
       </c>
       <c r="AL87" t="n">
-        <v>0.1993030675805674</v>
+        <v>0.1993030675805683</v>
       </c>
       <c r="AM87" t="n">
-        <v>4.99506435039016</v>
+        <v>4.995064350390182</v>
       </c>
     </row>
     <row r="88">
@@ -12654,13 +12654,13 @@
         <v>1.640803971861473</v>
       </c>
       <c r="AK88" t="n">
-        <v>-0.5408039718614732</v>
+        <v>-0.5408039718614726</v>
       </c>
       <c r="AL88" t="n">
-        <v>0.5408039718614732</v>
+        <v>0.5408039718614726</v>
       </c>
       <c r="AM88" t="n">
-        <v>49.16399744195211</v>
+        <v>49.16399744195205</v>
       </c>
     </row>
     <row r="89">
@@ -13476,13 +13476,13 @@
         <v>2.1477751984127</v>
       </c>
       <c r="AK94" t="n">
-        <v>0.4522248015872998</v>
+        <v>0.4522248015873003</v>
       </c>
       <c r="AL94" t="n">
-        <v>0.4522248015872998</v>
+        <v>0.4522248015873003</v>
       </c>
       <c r="AM94" t="n">
-        <v>17.39326159951153</v>
+        <v>17.39326159951155</v>
       </c>
     </row>
     <row r="95">
@@ -13613,13 +13613,13 @@
         <v>1.759485185185185</v>
       </c>
       <c r="AK95" t="n">
-        <v>0.01051481481481531</v>
+        <v>0.01051481481481509</v>
       </c>
       <c r="AL95" t="n">
-        <v>0.01051481481481531</v>
+        <v>0.01051481481481509</v>
       </c>
       <c r="AM95" t="n">
-        <v>0.5940573341703564</v>
+        <v>0.5940573341703439</v>
       </c>
     </row>
     <row r="96">
@@ -13747,16 +13747,16 @@
         <v>1</v>
       </c>
       <c r="AJ96" t="n">
-        <v>4.171668719336217</v>
+        <v>4.171668719336219</v>
       </c>
       <c r="AK96" t="n">
-        <v>-0.3916687193362169</v>
+        <v>-0.3916687193362196</v>
       </c>
       <c r="AL96" t="n">
-        <v>0.3916687193362169</v>
+        <v>0.3916687193362196</v>
       </c>
       <c r="AM96" t="n">
-        <v>10.36160633164595</v>
+        <v>10.36160633164602</v>
       </c>
     </row>
     <row r="97">
@@ -13884,16 +13884,16 @@
         <v>1</v>
       </c>
       <c r="AJ97" t="n">
-        <v>1.643746044973545</v>
+        <v>1.643746044973546</v>
       </c>
       <c r="AK97" t="n">
-        <v>0.1762539550264546</v>
+        <v>0.1762539550264544</v>
       </c>
       <c r="AL97" t="n">
-        <v>0.1762539550264546</v>
+        <v>0.1762539550264544</v>
       </c>
       <c r="AM97" t="n">
-        <v>9.684283243211791</v>
+        <v>9.684283243211777</v>
       </c>
     </row>
     <row r="98">
@@ -14021,16 +14021,16 @@
         <v>1</v>
       </c>
       <c r="AJ98" t="n">
-        <v>4.246050954785961</v>
+        <v>4.24605095478596</v>
       </c>
       <c r="AK98" t="n">
-        <v>2.383949045214039</v>
+        <v>2.38394904521404</v>
       </c>
       <c r="AL98" t="n">
-        <v>2.383949045214039</v>
+        <v>2.38394904521404</v>
       </c>
       <c r="AM98" t="n">
-        <v>35.95699917366575</v>
+        <v>35.95699917366576</v>
       </c>
     </row>
     <row r="99">
@@ -14161,13 +14161,13 @@
         <v>1.20945357984608</v>
       </c>
       <c r="AK99" t="n">
-        <v>-0.1394535798460799</v>
+        <v>-0.1394535798460801</v>
       </c>
       <c r="AL99" t="n">
-        <v>0.1394535798460799</v>
+        <v>0.1394535798460801</v>
       </c>
       <c r="AM99" t="n">
-        <v>13.03304484542802</v>
+        <v>13.03304484542805</v>
       </c>
     </row>
     <row r="100">
@@ -14843,16 +14843,16 @@
         <v>1</v>
       </c>
       <c r="AJ104" t="n">
-        <v>2.84634773809524</v>
+        <v>2.846347738095239</v>
       </c>
       <c r="AK104" t="n">
-        <v>2.40365226190476</v>
+        <v>2.403652261904761</v>
       </c>
       <c r="AL104" t="n">
-        <v>2.40365226190476</v>
+        <v>2.403652261904761</v>
       </c>
       <c r="AM104" t="n">
-        <v>45.78385260770972</v>
+        <v>45.78385260770973</v>
       </c>
     </row>
     <row r="105">
@@ -14980,16 +14980,16 @@
         <v>1</v>
       </c>
       <c r="AJ105" t="n">
-        <v>3.818820851139601</v>
+        <v>3.818820851139602</v>
       </c>
       <c r="AK105" t="n">
-        <v>2.191179148860399</v>
+        <v>2.191179148860398</v>
       </c>
       <c r="AL105" t="n">
-        <v>2.191179148860399</v>
+        <v>2.191179148860398</v>
       </c>
       <c r="AM105" t="n">
-        <v>36.45888766822627</v>
+        <v>36.45888766822626</v>
       </c>
     </row>
     <row r="106">
@@ -15257,13 +15257,13 @@
         <v>1.640803971861473</v>
       </c>
       <c r="AK107" t="n">
-        <v>-0.9908039718614733</v>
+        <v>-0.9908039718614726</v>
       </c>
       <c r="AL107" t="n">
-        <v>0.9908039718614733</v>
+        <v>0.9908039718614726</v>
       </c>
       <c r="AM107" t="n">
-        <v>152.4313802863805</v>
+        <v>152.4313802863804</v>
       </c>
     </row>
     <row r="108">
@@ -15391,16 +15391,16 @@
         <v>1</v>
       </c>
       <c r="AJ108" t="n">
-        <v>1.858971534391536</v>
+        <v>1.858971534391535</v>
       </c>
       <c r="AK108" t="n">
-        <v>-0.7889715343915358</v>
+        <v>-0.7889715343915349</v>
       </c>
       <c r="AL108" t="n">
-        <v>0.7889715343915358</v>
+        <v>0.7889715343915349</v>
       </c>
       <c r="AM108" t="n">
-        <v>73.73565741976969</v>
+        <v>73.73565741976961</v>
       </c>
     </row>
     <row r="109">
@@ -15677,16 +15677,16 @@
         <v>1</v>
       </c>
       <c r="AJ110" t="n">
-        <v>4.073140752765754</v>
+        <v>4.073140752765753</v>
       </c>
       <c r="AK110" t="n">
-        <v>0.02685924723424549</v>
+        <v>0.02685924723424638</v>
       </c>
       <c r="AL110" t="n">
-        <v>0.02685924723424549</v>
+        <v>0.02685924723424638</v>
       </c>
       <c r="AM110" t="n">
-        <v>0.6551035910791583</v>
+        <v>0.6551035910791799</v>
       </c>
     </row>
     <row r="111">
@@ -15963,16 +15963,16 @@
         <v>0</v>
       </c>
       <c r="AJ112" t="n">
-        <v>1.889458119288121</v>
+        <v>1.88945811928812</v>
       </c>
       <c r="AK112" t="n">
-        <v>-0.5594581192881207</v>
+        <v>-0.5594581192881203</v>
       </c>
       <c r="AL112" t="n">
-        <v>0.5594581192881207</v>
+        <v>0.5594581192881203</v>
       </c>
       <c r="AM112" t="n">
-        <v>42.06452024722712</v>
+        <v>42.06452024722709</v>
       </c>
     </row>
     <row r="113">
@@ -16115,13 +16115,13 @@
         <v>1.478863716931216</v>
       </c>
       <c r="AK113" t="n">
-        <v>-0.06886371693121629</v>
+        <v>-0.06886371693121607</v>
       </c>
       <c r="AL113" t="n">
-        <v>0.06886371693121629</v>
+        <v>0.06886371693121607</v>
       </c>
       <c r="AM113" t="n">
-        <v>4.883951555405411</v>
+        <v>4.883951555405395</v>
       </c>
     </row>
     <row r="114">
@@ -16249,16 +16249,16 @@
         <v>1</v>
       </c>
       <c r="AJ114" t="n">
-        <v>4.171668719336217</v>
+        <v>4.171668719336219</v>
       </c>
       <c r="AK114" t="n">
-        <v>0.2083312806637831</v>
+        <v>0.2083312806637805</v>
       </c>
       <c r="AL114" t="n">
-        <v>0.2083312806637831</v>
+        <v>0.2083312806637805</v>
       </c>
       <c r="AM114" t="n">
-        <v>4.756421932963086</v>
+        <v>4.756421932963026</v>
       </c>
     </row>
     <row r="115">
@@ -16389,13 +16389,13 @@
         <v>2.234771305916304</v>
       </c>
       <c r="AK115" t="n">
-        <v>0.2052286940836963</v>
+        <v>0.2052286940836958</v>
       </c>
       <c r="AL115" t="n">
-        <v>0.2052286940836963</v>
+        <v>0.2052286940836958</v>
       </c>
       <c r="AM115" t="n">
-        <v>8.411012052610504</v>
+        <v>8.411012052610484</v>
       </c>
     </row>
     <row r="116">
@@ -16797,16 +16797,16 @@
         <v>1</v>
       </c>
       <c r="AJ118" t="n">
-        <v>4.246050954785961</v>
+        <v>4.24605095478596</v>
       </c>
       <c r="AK118" t="n">
-        <v>-1.256050954785961</v>
+        <v>-1.25605095478596</v>
       </c>
       <c r="AL118" t="n">
-        <v>1.256050954785961</v>
+        <v>1.25605095478596</v>
       </c>
       <c r="AM118" t="n">
-        <v>42.0083931366542</v>
+        <v>42.00839313665417</v>
       </c>
     </row>
     <row r="119">
@@ -16934,16 +16934,16 @@
         <v>1</v>
       </c>
       <c r="AJ119" t="n">
-        <v>3.93807941077441</v>
+        <v>3.938079410774409</v>
       </c>
       <c r="AK119" t="n">
-        <v>0.1419205892255899</v>
+        <v>0.1419205892255908</v>
       </c>
       <c r="AL119" t="n">
-        <v>0.1419205892255899</v>
+        <v>0.1419205892255908</v>
       </c>
       <c r="AM119" t="n">
-        <v>3.478445814352694</v>
+        <v>3.478445814352716</v>
       </c>
     </row>
     <row r="120">
@@ -17074,13 +17074,13 @@
         <v>2.676362099567099</v>
       </c>
       <c r="AK120" t="n">
-        <v>-0.2963620995670992</v>
+        <v>-0.2963620995670988</v>
       </c>
       <c r="AL120" t="n">
-        <v>0.2963620995670992</v>
+        <v>0.2963620995670988</v>
       </c>
       <c r="AM120" t="n">
-        <v>12.45218905744115</v>
+        <v>12.45218905744113</v>
       </c>
     </row>
     <row r="121">
@@ -17208,16 +17208,16 @@
         <v>1</v>
       </c>
       <c r="AJ121" t="n">
-        <v>4.171668719336217</v>
+        <v>4.171668719336219</v>
       </c>
       <c r="AK121" t="n">
-        <v>0.2083312806637831</v>
+        <v>0.2083312806637805</v>
       </c>
       <c r="AL121" t="n">
-        <v>0.2083312806637831</v>
+        <v>0.2083312806637805</v>
       </c>
       <c r="AM121" t="n">
-        <v>4.756421932963086</v>
+        <v>4.756421932963026</v>
       </c>
     </row>
     <row r="122">
@@ -17348,13 +17348,13 @@
         <v>1.538962955007954</v>
       </c>
       <c r="AK122" t="n">
-        <v>0.8610370449920464</v>
+        <v>0.8610370449920461</v>
       </c>
       <c r="AL122" t="n">
-        <v>0.8610370449920464</v>
+        <v>0.8610370449920461</v>
       </c>
       <c r="AM122" t="n">
-        <v>35.87654354133527</v>
+        <v>35.87654354133526</v>
       </c>
     </row>
     <row r="123">
@@ -17488,16 +17488,16 @@
         <v>0</v>
       </c>
       <c r="AJ123" t="n">
-        <v>9.138460515873023</v>
+        <v>9.138460515873019</v>
       </c>
       <c r="AK123" t="n">
-        <v>0.3415394841269777</v>
+        <v>0.3415394841269812</v>
       </c>
       <c r="AL123" t="n">
-        <v>0.3415394841269777</v>
+        <v>0.3415394841269812</v>
       </c>
       <c r="AM123" t="n">
-        <v>3.602737174335207</v>
+        <v>3.602737174335244</v>
       </c>
     </row>
     <row r="124">
@@ -17625,16 +17625,16 @@
         <v>1</v>
       </c>
       <c r="AJ124" t="n">
-        <v>1.937888163780665</v>
+        <v>1.937888163780664</v>
       </c>
       <c r="AK124" t="n">
-        <v>-1.397888163780665</v>
+        <v>-1.397888163780664</v>
       </c>
       <c r="AL124" t="n">
-        <v>1.397888163780665</v>
+        <v>1.397888163780664</v>
       </c>
       <c r="AM124" t="n">
-        <v>258.868178477901</v>
+        <v>258.8681784779008</v>
       </c>
     </row>
     <row r="125">
@@ -17768,16 +17768,16 @@
         <v>0</v>
       </c>
       <c r="AJ125" t="n">
-        <v>17.64464351851852</v>
+        <v>17.64464351851853</v>
       </c>
       <c r="AK125" t="n">
-        <v>-0.9446435185185251</v>
+        <v>-0.9446435185185322</v>
       </c>
       <c r="AL125" t="n">
-        <v>0.9446435185185251</v>
+        <v>0.9446435185185322</v>
       </c>
       <c r="AM125" t="n">
-        <v>5.65654801508099</v>
+        <v>5.656548015081031</v>
       </c>
     </row>
     <row r="126">
@@ -17911,16 +17911,16 @@
         <v>0</v>
       </c>
       <c r="AJ126" t="n">
-        <v>6.321415555555554</v>
+        <v>6.310648888888887</v>
       </c>
       <c r="AK126" t="n">
-        <v>1.158584444444446</v>
+        <v>1.169351111111114</v>
       </c>
       <c r="AL126" t="n">
-        <v>1.158584444444446</v>
+        <v>1.169351111111114</v>
       </c>
       <c r="AM126" t="n">
-        <v>15.48909685086157</v>
+        <v>15.63303624480099</v>
       </c>
     </row>
     <row r="127">
@@ -18057,13 +18057,13 @@
         <v>1.172928170995671</v>
       </c>
       <c r="AK127" t="n">
-        <v>-0.3629281709956713</v>
+        <v>-0.3629281709956709</v>
       </c>
       <c r="AL127" t="n">
-        <v>0.3629281709956713</v>
+        <v>0.3629281709956709</v>
       </c>
       <c r="AM127" t="n">
-        <v>44.80594703650263</v>
+        <v>44.80594703650257</v>
       </c>
     </row>
     <row r="128">
@@ -18200,13 +18200,13 @@
         <v>12.37218268879269</v>
       </c>
       <c r="AK128" t="n">
-        <v>-1.07218268879269</v>
+        <v>-1.072182688792687</v>
       </c>
       <c r="AL128" t="n">
-        <v>1.07218268879269</v>
+        <v>1.072182688792687</v>
       </c>
       <c r="AM128" t="n">
-        <v>9.488342378696373</v>
+        <v>9.488342378696341</v>
       </c>
     </row>
     <row r="129">
@@ -18349,13 +18349,13 @@
         <v>2.676362099567099</v>
       </c>
       <c r="AK129" t="n">
-        <v>0.3236379004329009</v>
+        <v>0.3236379004329013</v>
       </c>
       <c r="AL129" t="n">
-        <v>0.3236379004329009</v>
+        <v>0.3236379004329013</v>
       </c>
       <c r="AM129" t="n">
-        <v>10.78793001443003</v>
+        <v>10.78793001443004</v>
       </c>
     </row>
     <row r="130">
@@ -18495,16 +18495,16 @@
         <v>1</v>
       </c>
       <c r="AJ130" t="n">
-        <v>1.858971534391536</v>
+        <v>1.858971534391535</v>
       </c>
       <c r="AK130" t="n">
-        <v>-0.1889715343915359</v>
+        <v>-0.188971534391535</v>
       </c>
       <c r="AL130" t="n">
-        <v>0.1889715343915359</v>
+        <v>0.188971534391535</v>
       </c>
       <c r="AM130" t="n">
-        <v>11.31566074200814</v>
+        <v>11.31566074200808</v>
       </c>
     </row>
     <row r="131">
@@ -18915,7 +18915,7 @@
         <v>1.409196028138527</v>
       </c>
       <c r="AM133" t="n">
-        <v>46.20314846355825</v>
+        <v>46.20314846355827</v>
       </c>
     </row>
     <row r="134">
@@ -19186,16 +19186,16 @@
         <v>0</v>
       </c>
       <c r="AJ135" t="n">
-        <v>14.97462283429535</v>
+        <v>14.99332283429535</v>
       </c>
       <c r="AK135" t="n">
-        <v>-0.6746228342953504</v>
+        <v>-0.693322834295353</v>
       </c>
       <c r="AL135" t="n">
-        <v>0.6746228342953504</v>
+        <v>0.693322834295353</v>
       </c>
       <c r="AM135" t="n">
-        <v>4.717642197869583</v>
+        <v>4.848411428638832</v>
       </c>
     </row>
     <row r="136">
@@ -19460,7 +19460,7 @@
         <v>1</v>
       </c>
       <c r="AJ137" t="n">
-        <v>3.850082833092833</v>
+        <v>3.850082833092834</v>
       </c>
       <c r="AK137" t="n">
         <v>-1.090082833092834</v>
@@ -19469,7 +19469,7 @@
         <v>1.090082833092834</v>
       </c>
       <c r="AM137" t="n">
-        <v>39.49575482220412</v>
+        <v>39.49575482220415</v>
       </c>
     </row>
     <row r="138">
@@ -19606,13 +19606,13 @@
         <v>23.43143624338623</v>
       </c>
       <c r="AK138" t="n">
-        <v>-1.331436243386229</v>
+        <v>-1.331436243386225</v>
       </c>
       <c r="AL138" t="n">
-        <v>1.331436243386229</v>
+        <v>1.331436243386225</v>
       </c>
       <c r="AM138" t="n">
-        <v>6.024598386363024</v>
+        <v>6.024598386363008</v>
       </c>
     </row>
     <row r="139">
@@ -19743,13 +19743,13 @@
         <v>2.231474066859065</v>
       </c>
       <c r="AK139" t="n">
-        <v>0.6285259331409345</v>
+        <v>0.628525933140935</v>
       </c>
       <c r="AL139" t="n">
-        <v>0.6285259331409345</v>
+        <v>0.628525933140935</v>
       </c>
       <c r="AM139" t="n">
-        <v>21.976431228704</v>
+        <v>21.97643122870402</v>
       </c>
     </row>
     <row r="140">
@@ -20190,13 +20190,13 @@
         <v>2.676362099567099</v>
       </c>
       <c r="AK142" t="n">
-        <v>-0.3963620995670993</v>
+        <v>-0.3963620995670989</v>
       </c>
       <c r="AL142" t="n">
-        <v>0.3963620995670993</v>
+        <v>0.3963620995670989</v>
       </c>
       <c r="AM142" t="n">
-        <v>17.38430261259208</v>
+        <v>17.38430261259206</v>
       </c>
     </row>
     <row r="143">
@@ -20339,13 +20339,13 @@
         <v>2.676362099567099</v>
       </c>
       <c r="AK143" t="n">
-        <v>0.9136379004329007</v>
+        <v>0.9136379004329012</v>
       </c>
       <c r="AL143" t="n">
-        <v>0.9136379004329007</v>
+        <v>0.9136379004329012</v>
       </c>
       <c r="AM143" t="n">
-        <v>25.44952368893874</v>
+        <v>25.44952368893875</v>
       </c>
     </row>
     <row r="144">
@@ -20473,16 +20473,16 @@
         <v>1</v>
       </c>
       <c r="AJ144" t="n">
-        <v>3.590833862433862</v>
+        <v>3.586067195767195</v>
       </c>
       <c r="AK144" t="n">
-        <v>0.04916613756613852</v>
+        <v>0.05393280423280533</v>
       </c>
       <c r="AL144" t="n">
-        <v>0.04916613756613852</v>
+        <v>0.05393280423280533</v>
       </c>
       <c r="AM144" t="n">
-        <v>1.350718065003806</v>
+        <v>1.48167044595619</v>
       </c>
     </row>
     <row r="145">
@@ -20896,16 +20896,16 @@
         <v>0</v>
       </c>
       <c r="AJ147" t="n">
-        <v>1.922985945165945</v>
+        <v>1.922985945165944</v>
       </c>
       <c r="AK147" t="n">
-        <v>-0.2729859451659449</v>
+        <v>-0.2729859451659442</v>
       </c>
       <c r="AL147" t="n">
-        <v>0.2729859451659449</v>
+        <v>0.2729859451659442</v>
       </c>
       <c r="AM147" t="n">
-        <v>16.54460273733</v>
+        <v>16.54460273732995</v>
       </c>
     </row>
     <row r="148">
@@ -21033,16 +21033,16 @@
         <v>1</v>
       </c>
       <c r="AJ148" t="n">
-        <v>1.858971534391536</v>
+        <v>1.858971534391535</v>
       </c>
       <c r="AK148" t="n">
-        <v>0.3310284656084641</v>
+        <v>0.331028465608465</v>
       </c>
       <c r="AL148" t="n">
-        <v>0.3310284656084641</v>
+        <v>0.331028465608465</v>
       </c>
       <c r="AM148" t="n">
-        <v>15.1154550506148</v>
+        <v>15.11545505061484</v>
       </c>
     </row>
     <row r="149">
@@ -21170,16 +21170,16 @@
         <v>1</v>
       </c>
       <c r="AJ149" t="n">
-        <v>4.524030925925928</v>
+        <v>4.524030925925926</v>
       </c>
       <c r="AK149" t="n">
-        <v>-0.3940309259259278</v>
+        <v>-0.394030925925926</v>
       </c>
       <c r="AL149" t="n">
-        <v>0.3940309259259278</v>
+        <v>0.394030925925926</v>
       </c>
       <c r="AM149" t="n">
-        <v>9.540700385615686</v>
+        <v>9.540700385615644</v>
       </c>
     </row>
     <row r="150">
@@ -21307,16 +21307,16 @@
         <v>1</v>
       </c>
       <c r="AJ150" t="n">
-        <v>1.898265805675808</v>
+        <v>1.898265805675809</v>
       </c>
       <c r="AK150" t="n">
-        <v>-0.8582658056758081</v>
+        <v>-0.8582658056758086</v>
       </c>
       <c r="AL150" t="n">
-        <v>0.8582658056758081</v>
+        <v>0.8582658056758086</v>
       </c>
       <c r="AM150" t="n">
-        <v>82.52555823805847</v>
+        <v>82.52555823805852</v>
       </c>
     </row>
     <row r="151">
@@ -21724,16 +21724,16 @@
         <v>0</v>
       </c>
       <c r="AJ153" t="n">
-        <v>18.96333425925925</v>
+        <v>18.96333425925926</v>
       </c>
       <c r="AK153" t="n">
-        <v>1.136665740740753</v>
+        <v>1.136665740740746</v>
       </c>
       <c r="AL153" t="n">
-        <v>1.136665740740753</v>
+        <v>1.136665740740746</v>
       </c>
       <c r="AM153" t="n">
-        <v>5.655053436521159</v>
+        <v>5.655053436521124</v>
       </c>
     </row>
     <row r="154">
@@ -22001,13 +22001,13 @@
         <v>1.462229996392497</v>
       </c>
       <c r="AK155" t="n">
-        <v>-0.2022299963924965</v>
+        <v>-0.2022299963924967</v>
       </c>
       <c r="AL155" t="n">
-        <v>0.2022299963924965</v>
+        <v>0.2022299963924967</v>
       </c>
       <c r="AM155" t="n">
-        <v>16.0499997136902</v>
+        <v>16.04999971369022</v>
       </c>
     </row>
     <row r="156">
@@ -22832,16 +22832,16 @@
         <v>1</v>
       </c>
       <c r="AJ161" t="n">
-        <v>3.305775439560436</v>
+        <v>3.305775439560437</v>
       </c>
       <c r="AK161" t="n">
-        <v>0.1542245604395642</v>
+        <v>0.1542245604395633</v>
       </c>
       <c r="AL161" t="n">
-        <v>0.1542245604395642</v>
+        <v>0.1542245604395633</v>
       </c>
       <c r="AM161" t="n">
-        <v>4.457357238137694</v>
+        <v>4.457357238137669</v>
       </c>
     </row>
     <row r="162">
@@ -22972,13 +22972,13 @@
         <v>1.45273863932364</v>
       </c>
       <c r="AK162" t="n">
-        <v>-0.3627386393236403</v>
+        <v>-0.36273863932364</v>
       </c>
       <c r="AL162" t="n">
-        <v>0.3627386393236403</v>
+        <v>0.36273863932364</v>
       </c>
       <c r="AM162" t="n">
-        <v>33.27877424987525</v>
+        <v>33.27877424987523</v>
       </c>
     </row>
     <row r="163">
@@ -23109,13 +23109,13 @@
         <v>1.711668888888889</v>
       </c>
       <c r="AK163" t="n">
-        <v>0.2783311111111111</v>
+        <v>0.2783311111111106</v>
       </c>
       <c r="AL163" t="n">
-        <v>0.2783311111111111</v>
+        <v>0.2783311111111106</v>
       </c>
       <c r="AM163" t="n">
-        <v>13.98648799553322</v>
+        <v>13.9864879955332</v>
       </c>
     </row>
     <row r="164">
@@ -23654,16 +23654,16 @@
         <v>1</v>
       </c>
       <c r="AJ167" t="n">
-        <v>1.229434763107263</v>
+        <v>1.229434763107264</v>
       </c>
       <c r="AK167" t="n">
-        <v>-0.1594347631072632</v>
+        <v>-0.1594347631072635</v>
       </c>
       <c r="AL167" t="n">
-        <v>0.1594347631072632</v>
+        <v>0.1594347631072635</v>
       </c>
       <c r="AM167" t="n">
-        <v>14.90044515021152</v>
+        <v>14.90044515021154</v>
       </c>
     </row>
     <row r="168">
@@ -23791,16 +23791,16 @@
         <v>1</v>
       </c>
       <c r="AJ168" t="n">
-        <v>1.209398823953823</v>
+        <v>1.209398823953824</v>
       </c>
       <c r="AK168" t="n">
-        <v>-0.2493988239538232</v>
+        <v>-0.2493988239538236</v>
       </c>
       <c r="AL168" t="n">
-        <v>0.2493988239538232</v>
+        <v>0.2493988239538236</v>
       </c>
       <c r="AM168" t="n">
-        <v>25.97904416185659</v>
+        <v>25.97904416185663</v>
       </c>
     </row>
     <row r="169">
@@ -23928,16 +23928,16 @@
         <v>1</v>
       </c>
       <c r="AJ169" t="n">
-        <v>1.209398823953823</v>
+        <v>1.209398823953824</v>
       </c>
       <c r="AK169" t="n">
-        <v>0.3206011760461769</v>
+        <v>0.3206011760461764</v>
       </c>
       <c r="AL169" t="n">
-        <v>0.3206011760461769</v>
+        <v>0.3206011760461764</v>
       </c>
       <c r="AM169" t="n">
-        <v>20.95432523177627</v>
+        <v>20.95432523177624</v>
       </c>
     </row>
     <row r="170">
@@ -24065,16 +24065,16 @@
         <v>1</v>
       </c>
       <c r="AJ170" t="n">
-        <v>4.550757050264552</v>
+        <v>4.55075705026455</v>
       </c>
       <c r="AK170" t="n">
-        <v>0.2692429497354487</v>
+        <v>0.2692429497354505</v>
       </c>
       <c r="AL170" t="n">
-        <v>0.2692429497354487</v>
+        <v>0.2692429497354505</v>
       </c>
       <c r="AM170" t="n">
-        <v>5.585953314013459</v>
+        <v>5.585953314013495</v>
       </c>
     </row>
     <row r="171">
@@ -24202,16 +24202,16 @@
         <v>1</v>
       </c>
       <c r="AJ171" t="n">
-        <v>2.297097665945164</v>
+        <v>2.297097665945165</v>
       </c>
       <c r="AK171" t="n">
-        <v>0.0829023340548356</v>
+        <v>0.08290233405483516</v>
       </c>
       <c r="AL171" t="n">
-        <v>0.0829023340548356</v>
+        <v>0.08290233405483516</v>
       </c>
       <c r="AM171" t="n">
-        <v>3.483291346841833</v>
+        <v>3.483291346841814</v>
       </c>
     </row>
     <row r="172">
@@ -24339,16 +24339,16 @@
         <v>1</v>
       </c>
       <c r="AJ172" t="n">
-        <v>2.197485582473083</v>
+        <v>2.197485582473081</v>
       </c>
       <c r="AK172" t="n">
-        <v>-0.3174855824730827</v>
+        <v>-0.3174855824730809</v>
       </c>
       <c r="AL172" t="n">
-        <v>0.3174855824730827</v>
+        <v>0.3174855824730809</v>
       </c>
       <c r="AM172" t="n">
-        <v>16.88753098261078</v>
+        <v>16.88753098261069</v>
       </c>
     </row>
     <row r="173">
@@ -24479,13 +24479,13 @@
         <v>3.756032486772487</v>
       </c>
       <c r="AK173" t="n">
-        <v>0.5339675132275126</v>
+        <v>0.533967513227513</v>
       </c>
       <c r="AL173" t="n">
-        <v>0.5339675132275126</v>
+        <v>0.533967513227513</v>
       </c>
       <c r="AM173" t="n">
-        <v>12.4467951801285</v>
+        <v>12.44679518012851</v>
       </c>
     </row>
     <row r="174">
@@ -25033,7 +25033,7 @@
         <v>1.051659973544975</v>
       </c>
       <c r="AM177" t="n">
-        <v>99.21320505141271</v>
+        <v>99.21320505141274</v>
       </c>
     </row>
     <row r="178">
@@ -25302,16 +25302,16 @@
         <v>0</v>
       </c>
       <c r="AJ179" t="n">
-        <v>2.230945525493025</v>
+        <v>2.254448303270802</v>
       </c>
       <c r="AK179" t="n">
-        <v>-1.420945525493025</v>
+        <v>-1.444448303270802</v>
       </c>
       <c r="AL179" t="n">
-        <v>1.420945525493025</v>
+        <v>1.444448303270802</v>
       </c>
       <c r="AM179" t="n">
-        <v>175.4253735176574</v>
+        <v>178.3269510210867</v>
       </c>
     </row>
     <row r="180">
@@ -25713,16 +25713,16 @@
         <v>1</v>
       </c>
       <c r="AJ182" t="n">
-        <v>1.567480460557961</v>
+        <v>1.567480460557962</v>
       </c>
       <c r="AK182" t="n">
-        <v>-0.1074804605579613</v>
+        <v>-0.1074804605579616</v>
       </c>
       <c r="AL182" t="n">
-        <v>0.1074804605579613</v>
+        <v>0.1074804605579616</v>
       </c>
       <c r="AM182" t="n">
-        <v>7.361675380682284</v>
+        <v>7.361675380682299</v>
       </c>
     </row>
     <row r="183">
@@ -25853,13 +25853,13 @@
         <v>1.855668742183745</v>
       </c>
       <c r="AK183" t="n">
-        <v>-0.4556687421837449</v>
+        <v>-0.4556687421837453</v>
       </c>
       <c r="AL183" t="n">
-        <v>0.4556687421837449</v>
+        <v>0.4556687421837453</v>
       </c>
       <c r="AM183" t="n">
-        <v>32.54776729883892</v>
+        <v>32.54776729883896</v>
       </c>
     </row>
     <row r="184">
@@ -26124,16 +26124,16 @@
         <v>1</v>
       </c>
       <c r="AJ185" t="n">
-        <v>1.970568846801347</v>
+        <v>1.970568846801346</v>
       </c>
       <c r="AK185" t="n">
-        <v>-0.02056884680134696</v>
+        <v>-0.02056884680134652</v>
       </c>
       <c r="AL185" t="n">
-        <v>0.02056884680134696</v>
+        <v>0.02056884680134652</v>
       </c>
       <c r="AM185" t="n">
-        <v>1.054812656479331</v>
+        <v>1.054812656479309</v>
       </c>
     </row>
     <row r="186">
@@ -26684,16 +26684,16 @@
         <v>1</v>
       </c>
       <c r="AJ189" t="n">
-        <v>4.029927830687834</v>
+        <v>4.029927830687833</v>
       </c>
       <c r="AK189" t="n">
-        <v>1.840072169312166</v>
+        <v>1.840072169312167</v>
       </c>
       <c r="AL189" t="n">
-        <v>1.840072169312166</v>
+        <v>1.840072169312167</v>
       </c>
       <c r="AM189" t="n">
-        <v>31.34705569526689</v>
+        <v>31.3470556952669</v>
       </c>
     </row>
     <row r="190">
@@ -26833,16 +26833,16 @@
         <v>0</v>
       </c>
       <c r="AJ190" t="n">
-        <v>8.295651379638883</v>
+        <v>8.295651379638885</v>
       </c>
       <c r="AK190" t="n">
-        <v>-0.5856513796388834</v>
+        <v>-0.5856513796388851</v>
       </c>
       <c r="AL190" t="n">
-        <v>0.5856513796388834</v>
+        <v>0.5856513796388851</v>
       </c>
       <c r="AM190" t="n">
-        <v>7.595997141879161</v>
+        <v>7.595997141879185</v>
       </c>
     </row>
     <row r="191">
@@ -26973,13 +26973,13 @@
         <v>1.043723615921117</v>
       </c>
       <c r="AK191" t="n">
-        <v>0.2162763840788835</v>
+        <v>0.2162763840788833</v>
       </c>
       <c r="AL191" t="n">
-        <v>0.2162763840788835</v>
+        <v>0.2162763840788833</v>
       </c>
       <c r="AM191" t="n">
-        <v>17.16479238721298</v>
+        <v>17.16479238721296</v>
       </c>
     </row>
     <row r="192">
@@ -27113,16 +27113,16 @@
         <v>0</v>
       </c>
       <c r="AJ192" t="n">
-        <v>19.06056399711399</v>
+        <v>19.060563997114</v>
       </c>
       <c r="AK192" t="n">
-        <v>0.7394360028860092</v>
+        <v>0.7394360028860056</v>
       </c>
       <c r="AL192" t="n">
-        <v>0.7394360028860092</v>
+        <v>0.7394360028860056</v>
       </c>
       <c r="AM192" t="n">
-        <v>3.734525267101056</v>
+        <v>3.734525267101038</v>
       </c>
     </row>
     <row r="193">
@@ -27253,13 +27253,13 @@
         <v>1.52625942881193</v>
       </c>
       <c r="AK193" t="n">
-        <v>-0.01625942881192999</v>
+        <v>-0.01625942881193021</v>
       </c>
       <c r="AL193" t="n">
-        <v>0.01625942881192999</v>
+        <v>0.01625942881193021</v>
       </c>
       <c r="AM193" t="n">
-        <v>1.076783365028476</v>
+        <v>1.076783365028491</v>
       </c>
     </row>
     <row r="194">
@@ -27944,10 +27944,10 @@
         <v>1.043723615921117</v>
       </c>
       <c r="AK198" t="n">
-        <v>-0.5937236159211166</v>
+        <v>-0.5937236159211168</v>
       </c>
       <c r="AL198" t="n">
-        <v>0.5937236159211166</v>
+        <v>0.5937236159211168</v>
       </c>
       <c r="AM198" t="n">
         <v>131.9385813158037</v>
@@ -28087,13 +28087,13 @@
         <v>17.77196257936509</v>
       </c>
       <c r="AK199" t="n">
-        <v>0.8280374206349137</v>
+        <v>0.8280374206349066</v>
       </c>
       <c r="AL199" t="n">
-        <v>0.8280374206349137</v>
+        <v>0.8280374206349066</v>
       </c>
       <c r="AM199" t="n">
-        <v>4.45181408943502</v>
+        <v>4.451814089434982</v>
       </c>
     </row>
     <row r="200">
@@ -28358,16 +28358,16 @@
         <v>1</v>
       </c>
       <c r="AJ201" t="n">
-        <v>2.712283858826356</v>
+        <v>2.712283858826357</v>
       </c>
       <c r="AK201" t="n">
-        <v>2.077716141173644</v>
+        <v>2.077716141173643</v>
       </c>
       <c r="AL201" t="n">
-        <v>2.077716141173644</v>
+        <v>2.077716141173643</v>
       </c>
       <c r="AM201" t="n">
-        <v>43.37611985748734</v>
+        <v>43.37611985748732</v>
       </c>
     </row>
     <row r="202">
@@ -28650,16 +28650,16 @@
         <v>0</v>
       </c>
       <c r="AJ203" t="n">
-        <v>16.08811147186147</v>
+        <v>16.10681147186147</v>
       </c>
       <c r="AK203" t="n">
-        <v>-0.08811147186147394</v>
+        <v>-0.1068114718614694</v>
       </c>
       <c r="AL203" t="n">
-        <v>0.08811147186147394</v>
+        <v>0.1068114718614694</v>
       </c>
       <c r="AM203" t="n">
-        <v>0.5506966991342122</v>
+        <v>0.667571699134184</v>
       </c>
     </row>
     <row r="204">
@@ -28787,16 +28787,16 @@
         <v>1</v>
       </c>
       <c r="AJ204" t="n">
-        <v>3.026758956043953</v>
+        <v>3.026758956043954</v>
       </c>
       <c r="AK204" t="n">
-        <v>2.003241043956047</v>
+        <v>2.003241043956046</v>
       </c>
       <c r="AL204" t="n">
-        <v>2.003241043956047</v>
+        <v>2.003241043956046</v>
       </c>
       <c r="AM204" t="n">
-        <v>39.82586568501087</v>
+        <v>39.82586568501086</v>
       </c>
     </row>
     <row r="205">
@@ -28922,16 +28922,16 @@
         <v>0</v>
       </c>
       <c r="AJ205" t="n">
-        <v>2.5754178006253</v>
+        <v>2.5818553006253</v>
       </c>
       <c r="AK205" t="n">
-        <v>-0.5254178006253003</v>
+        <v>-0.5318553006253004</v>
       </c>
       <c r="AL205" t="n">
-        <v>0.5254178006253003</v>
+        <v>0.5318553006253004</v>
       </c>
       <c r="AM205" t="n">
-        <v>25.63013661586831</v>
+        <v>25.94416100611221</v>
       </c>
     </row>
     <row r="206">
@@ -29199,13 +29199,13 @@
         <v>2.765967324434822</v>
       </c>
       <c r="AK207" t="n">
-        <v>-0.2059673244348215</v>
+        <v>-0.2059673244348219</v>
       </c>
       <c r="AL207" t="n">
-        <v>0.2059673244348215</v>
+        <v>0.2059673244348219</v>
       </c>
       <c r="AM207" t="n">
-        <v>8.045598610735214</v>
+        <v>8.04559861073523</v>
       </c>
     </row>
     <row r="208">
@@ -29342,13 +29342,13 @@
         <v>15.50899071789322</v>
       </c>
       <c r="AK208" t="n">
-        <v>4.891009282106781</v>
+        <v>4.891009282106777</v>
       </c>
       <c r="AL208" t="n">
-        <v>4.891009282106781</v>
+        <v>4.891009282106777</v>
       </c>
       <c r="AM208" t="n">
-        <v>23.97553569660187</v>
+        <v>23.97553569660185</v>
       </c>
     </row>
     <row r="209">
@@ -29485,13 +29485,13 @@
         <v>1.178994282106782</v>
       </c>
       <c r="AK209" t="n">
-        <v>-0.158994282106782</v>
+        <v>-0.1589942821067816</v>
       </c>
       <c r="AL209" t="n">
-        <v>0.158994282106782</v>
+        <v>0.1589942821067816</v>
       </c>
       <c r="AM209" t="n">
-        <v>15.58767471635118</v>
+        <v>15.58767471635113</v>
       </c>
     </row>
     <row r="210">
@@ -29756,16 +29756,16 @@
         <v>1</v>
       </c>
       <c r="AJ211" t="n">
-        <v>2.380796277056277</v>
+        <v>2.380796277056276</v>
       </c>
       <c r="AK211" t="n">
-        <v>-0.03079627705627663</v>
+        <v>-0.03079627705627619</v>
       </c>
       <c r="AL211" t="n">
-        <v>0.03079627705627663</v>
+        <v>0.03079627705627619</v>
       </c>
       <c r="AM211" t="n">
-        <v>1.310479874735176</v>
+        <v>1.310479874735157</v>
       </c>
     </row>
     <row r="212">
@@ -29896,13 +29896,13 @@
         <v>1.711668888888889</v>
       </c>
       <c r="AK212" t="n">
-        <v>0.3883311111111112</v>
+        <v>0.3883311111111107</v>
       </c>
       <c r="AL212" t="n">
-        <v>0.3883311111111112</v>
+        <v>0.3883311111111107</v>
       </c>
       <c r="AM212" t="n">
-        <v>18.49195767195767</v>
+        <v>18.49195767195765</v>
       </c>
     </row>
     <row r="213">
@@ -30033,13 +30033,13 @@
         <v>1.714413121693123</v>
       </c>
       <c r="AK213" t="n">
-        <v>-0.2844131216931229</v>
+        <v>-0.2844131216931227</v>
       </c>
       <c r="AL213" t="n">
-        <v>0.2844131216931229</v>
+        <v>0.2844131216931227</v>
       </c>
       <c r="AM213" t="n">
-        <v>19.88902948902958</v>
+        <v>19.88902948902956</v>
       </c>
     </row>
     <row r="214">
@@ -30578,16 +30578,16 @@
         <v>1</v>
       </c>
       <c r="AJ217" t="n">
-        <v>2.095254527417027</v>
+        <v>2.095254527417026</v>
       </c>
       <c r="AK217" t="n">
-        <v>0.4647454725829734</v>
+        <v>0.4647454725829738</v>
       </c>
       <c r="AL217" t="n">
-        <v>0.4647454725829734</v>
+        <v>0.4647454725829738</v>
       </c>
       <c r="AM217" t="n">
-        <v>18.1541200227724</v>
+        <v>18.15412002277242</v>
       </c>
     </row>
     <row r="218">
@@ -31001,16 +31001,16 @@
         <v>1</v>
       </c>
       <c r="AJ220" t="n">
-        <v>2.115648032708033</v>
+        <v>2.115648032708032</v>
       </c>
       <c r="AK220" t="n">
-        <v>-0.0956480327080329</v>
+        <v>-0.09564803270803202</v>
       </c>
       <c r="AL220" t="n">
-        <v>0.0956480327080329</v>
+        <v>0.09564803270803202</v>
       </c>
       <c r="AM220" t="n">
-        <v>4.735051124160044</v>
+        <v>4.735051124160001</v>
       </c>
     </row>
     <row r="221">
@@ -31412,16 +31412,16 @@
         <v>1</v>
       </c>
       <c r="AJ223" t="n">
-        <v>2.831645569245566</v>
+        <v>2.831645569245567</v>
       </c>
       <c r="AK223" t="n">
-        <v>-0.151645569245566</v>
+        <v>-0.1516455692455665</v>
       </c>
       <c r="AL223" t="n">
-        <v>0.151645569245566</v>
+        <v>0.1516455692455665</v>
       </c>
       <c r="AM223" t="n">
-        <v>5.658416762894255</v>
+        <v>5.658416762894271</v>
       </c>
     </row>
     <row r="224">
@@ -31552,13 +31552,13 @@
         <v>1.711668888888889</v>
       </c>
       <c r="AK224" t="n">
-        <v>-0.3416688888888888</v>
+        <v>-0.3416688888888892</v>
       </c>
       <c r="AL224" t="n">
-        <v>0.3416688888888888</v>
+        <v>0.3416688888888892</v>
       </c>
       <c r="AM224" t="n">
-        <v>24.93933495539334</v>
+        <v>24.93933495539337</v>
       </c>
     </row>
     <row r="225">
@@ -31832,13 +31832,13 @@
         <v>1.178994282106782</v>
       </c>
       <c r="AK226" t="n">
-        <v>-0.05899428210678193</v>
+        <v>-0.05899428210678148</v>
       </c>
       <c r="AL226" t="n">
-        <v>0.05899428210678193</v>
+        <v>0.05899428210678148</v>
       </c>
       <c r="AM226" t="n">
-        <v>5.267346616676957</v>
+        <v>5.267346616676917</v>
       </c>
     </row>
     <row r="227">
@@ -32526,16 +32526,16 @@
         <v>0</v>
       </c>
       <c r="AJ231" t="n">
-        <v>8.742334682539685</v>
+        <v>8.731568015873021</v>
       </c>
       <c r="AK231" t="n">
-        <v>-2.242334682539685</v>
+        <v>-2.231568015873021</v>
       </c>
       <c r="AL231" t="n">
-        <v>2.242334682539685</v>
+        <v>2.231568015873021</v>
       </c>
       <c r="AM231" t="n">
-        <v>34.49745665445668</v>
+        <v>34.33181562881572</v>
       </c>
     </row>
     <row r="232">
@@ -32952,7 +32952,7 @@
         <v>2.308340026455025</v>
       </c>
       <c r="AM234" t="n">
-        <v>52.22488747635804</v>
+        <v>52.22488747635803</v>
       </c>
     </row>
     <row r="235">
@@ -33229,16 +33229,16 @@
         <v>0</v>
       </c>
       <c r="AJ236" t="n">
-        <v>11.49662575433826</v>
+        <v>11.48200908767159</v>
       </c>
       <c r="AK236" t="n">
-        <v>-2.096625754338255</v>
+        <v>-2.082009087671587</v>
       </c>
       <c r="AL236" t="n">
-        <v>2.096625754338255</v>
+        <v>2.082009087671587</v>
       </c>
       <c r="AM236" t="n">
-        <v>22.3045293014708</v>
+        <v>22.14903284757007</v>
       </c>
     </row>
     <row r="237">
@@ -33506,13 +33506,13 @@
         <v>1.397737615440115</v>
       </c>
       <c r="AK238" t="n">
-        <v>0.2922623845598848</v>
+        <v>0.2922623845598846</v>
       </c>
       <c r="AL238" t="n">
-        <v>0.2922623845598848</v>
+        <v>0.2922623845598846</v>
       </c>
       <c r="AM238" t="n">
-        <v>17.29363222247839</v>
+        <v>17.29363222247838</v>
       </c>
     </row>
     <row r="239">
@@ -33643,13 +33643,13 @@
         <v>3.573573283475785</v>
       </c>
       <c r="AK239" t="n">
-        <v>0.05642671652421472</v>
+        <v>0.05642671652421516</v>
       </c>
       <c r="AL239" t="n">
-        <v>0.05642671652421472</v>
+        <v>0.05642671652421516</v>
       </c>
       <c r="AM239" t="n">
-        <v>1.554455000667072</v>
+        <v>1.554455000667084</v>
       </c>
     </row>
     <row r="240">
@@ -33780,13 +33780,13 @@
         <v>1.454185542328041</v>
       </c>
       <c r="AK240" t="n">
-        <v>0.8558144576719586</v>
+        <v>0.8558144576719589</v>
       </c>
       <c r="AL240" t="n">
-        <v>0.8558144576719586</v>
+        <v>0.8558144576719589</v>
       </c>
       <c r="AM240" t="n">
-        <v>37.04824492086401</v>
+        <v>37.04824492086402</v>
       </c>
     </row>
     <row r="241">
@@ -33914,16 +33914,16 @@
         <v>1</v>
       </c>
       <c r="AJ241" t="n">
-        <v>3.267171522181522</v>
+        <v>3.267171522181521</v>
       </c>
       <c r="AK241" t="n">
-        <v>-0.1571715221815224</v>
+        <v>-0.1571715221815206</v>
       </c>
       <c r="AL241" t="n">
-        <v>0.1571715221815224</v>
+        <v>0.1571715221815206</v>
       </c>
       <c r="AM241" t="n">
-        <v>5.053746693939628</v>
+        <v>5.05374669393957</v>
       </c>
     </row>
     <row r="242">
@@ -34742,16 +34742,16 @@
         <v>0</v>
       </c>
       <c r="AJ247" t="n">
-        <v>20.26365303030303</v>
+        <v>20.25210303030302</v>
       </c>
       <c r="AK247" t="n">
-        <v>-4.263653030303029</v>
+        <v>-4.252103030303022</v>
       </c>
       <c r="AL247" t="n">
-        <v>4.263653030303029</v>
+        <v>4.252103030303022</v>
       </c>
       <c r="AM247" t="n">
-        <v>26.64783143939393</v>
+        <v>26.57564393939389</v>
       </c>
     </row>
     <row r="248">
@@ -35016,16 +35016,16 @@
         <v>1</v>
       </c>
       <c r="AJ249" t="n">
-        <v>1.945346357346357</v>
+        <v>1.945346357346356</v>
       </c>
       <c r="AK249" t="n">
-        <v>0.5846536426536431</v>
+        <v>0.5846536426536437</v>
       </c>
       <c r="AL249" t="n">
-        <v>0.5846536426536431</v>
+        <v>0.5846536426536437</v>
       </c>
       <c r="AM249" t="n">
-        <v>23.10883963057878</v>
+        <v>23.10883963057881</v>
       </c>
     </row>
     <row r="250">
@@ -35153,16 +35153,16 @@
         <v>1</v>
       </c>
       <c r="AJ250" t="n">
-        <v>2.710087878186631</v>
+        <v>2.71008787818663</v>
       </c>
       <c r="AK250" t="n">
-        <v>0.389912121813369</v>
+        <v>0.3899121218133699</v>
       </c>
       <c r="AL250" t="n">
-        <v>0.389912121813369</v>
+        <v>0.3899121218133699</v>
       </c>
       <c r="AM250" t="n">
-        <v>12.57781038107642</v>
+        <v>12.57781038107645</v>
       </c>
     </row>
     <row r="251">
@@ -35293,13 +35293,13 @@
         <v>2.749246547619047</v>
       </c>
       <c r="AK251" t="n">
-        <v>0.3507534523809532</v>
+        <v>0.3507534523809528</v>
       </c>
       <c r="AL251" t="n">
-        <v>0.3507534523809532</v>
+        <v>0.3507534523809528</v>
       </c>
       <c r="AM251" t="n">
-        <v>11.31462749615978</v>
+        <v>11.31462749615977</v>
       </c>
     </row>
     <row r="252">
@@ -35427,16 +35427,16 @@
         <v>1</v>
       </c>
       <c r="AJ252" t="n">
-        <v>1.952123363812113</v>
+        <v>1.952123363812112</v>
       </c>
       <c r="AK252" t="n">
-        <v>1.477876636187887</v>
+        <v>1.477876636187888</v>
       </c>
       <c r="AL252" t="n">
-        <v>1.477876636187887</v>
+        <v>1.477876636187888</v>
       </c>
       <c r="AM252" t="n">
-        <v>43.08678239614831</v>
+        <v>43.08678239614833</v>
       </c>
     </row>
     <row r="253">
@@ -35570,16 +35570,16 @@
         <v>0</v>
       </c>
       <c r="AJ253" t="n">
-        <v>8.860108703703705</v>
+        <v>8.849342037037042</v>
       </c>
       <c r="AK253" t="n">
-        <v>0.9498912962962951</v>
+        <v>0.9606579629629586</v>
       </c>
       <c r="AL253" t="n">
-        <v>0.9498912962962951</v>
+        <v>0.9606579629629586</v>
       </c>
       <c r="AM253" t="n">
-        <v>9.682887831766514</v>
+        <v>9.792639785555131</v>
       </c>
     </row>
     <row r="254">
@@ -35844,16 +35844,16 @@
         <v>1</v>
       </c>
       <c r="AJ255" t="n">
-        <v>3.504752225274726</v>
+        <v>3.504752225274725</v>
       </c>
       <c r="AK255" t="n">
-        <v>-0.2447522252747265</v>
+        <v>-0.2447522252747256</v>
       </c>
       <c r="AL255" t="n">
-        <v>0.2447522252747265</v>
+        <v>0.2447522252747256</v>
       </c>
       <c r="AM255" t="n">
-        <v>7.507736971617378</v>
+        <v>7.507736971617351</v>
       </c>
     </row>
     <row r="256">
@@ -35987,16 +35987,16 @@
         <v>0</v>
       </c>
       <c r="AJ256" t="n">
-        <v>18.14363935305437</v>
+        <v>18.16233935305437</v>
       </c>
       <c r="AK256" t="n">
-        <v>2.556360646945627</v>
+        <v>2.537660646945628</v>
       </c>
       <c r="AL256" t="n">
-        <v>2.556360646945627</v>
+        <v>2.537660646945628</v>
       </c>
       <c r="AM256" t="n">
-        <v>12.3495683427325</v>
+        <v>12.2592301784813</v>
       </c>
     </row>
     <row r="257">
@@ -36261,16 +36261,16 @@
         <v>1</v>
       </c>
       <c r="AJ258" t="n">
-        <v>3.560809312169314</v>
+        <v>3.560809312169315</v>
       </c>
       <c r="AK258" t="n">
-        <v>0.5691906878306856</v>
+        <v>0.5691906878306847</v>
       </c>
       <c r="AL258" t="n">
-        <v>0.5691906878306856</v>
+        <v>0.5691906878306847</v>
       </c>
       <c r="AM258" t="n">
-        <v>13.78185684820062</v>
+        <v>13.7818568482006</v>
       </c>
     </row>
     <row r="259">
@@ -36401,13 +36401,13 @@
         <v>3.573573283475785</v>
       </c>
       <c r="AK259" t="n">
-        <v>-0.4535732834757851</v>
+        <v>-0.4535732834757846</v>
       </c>
       <c r="AL259" t="n">
-        <v>0.4535732834757851</v>
+        <v>0.4535732834757846</v>
       </c>
       <c r="AM259" t="n">
-        <v>14.53760523960849</v>
+        <v>14.53760523960848</v>
       </c>
     </row>
     <row r="260">
@@ -36538,13 +36538,13 @@
         <v>1.454185542328041</v>
       </c>
       <c r="AK260" t="n">
-        <v>0.04581445767195857</v>
+        <v>0.0458144576719588</v>
       </c>
       <c r="AL260" t="n">
-        <v>0.04581445767195857</v>
+        <v>0.0458144576719588</v>
       </c>
       <c r="AM260" t="n">
-        <v>3.054297178130572</v>
+        <v>3.054297178130587</v>
       </c>
     </row>
     <row r="261">
@@ -36812,13 +36812,13 @@
         <v>3.545207354497353</v>
       </c>
       <c r="AK262" t="n">
-        <v>-0.4652073544973532</v>
+        <v>-0.4652073544973527</v>
       </c>
       <c r="AL262" t="n">
-        <v>0.4652073544973532</v>
+        <v>0.4652073544973527</v>
       </c>
       <c r="AM262" t="n">
-        <v>15.1041348862777</v>
+        <v>15.10413488627769</v>
       </c>
     </row>
     <row r="263">
@@ -36942,16 +36942,16 @@
         <v>1</v>
       </c>
       <c r="AJ263" t="n">
-        <v>1.970527156084655</v>
+        <v>1.970527156084654</v>
       </c>
       <c r="AK263" t="n">
-        <v>-0.4305271560846551</v>
+        <v>-0.4305271560846544</v>
       </c>
       <c r="AL263" t="n">
-        <v>0.4305271560846551</v>
+        <v>0.4305271560846544</v>
       </c>
       <c r="AM263" t="n">
-        <v>27.95630883666592</v>
+        <v>27.95630883666587</v>
       </c>
     </row>
     <row r="264">
@@ -37091,16 +37091,16 @@
         <v>0</v>
       </c>
       <c r="AJ264" t="n">
-        <v>8.810385328652828</v>
+        <v>8.810385328652824</v>
       </c>
       <c r="AK264" t="n">
-        <v>-2.380385328652828</v>
+        <v>-2.380385328652824</v>
       </c>
       <c r="AL264" t="n">
-        <v>2.380385328652828</v>
+        <v>2.380385328652824</v>
       </c>
       <c r="AM264" t="n">
-        <v>37.01998955914196</v>
+        <v>37.01998955914191</v>
       </c>
     </row>
     <row r="265">
@@ -37240,16 +37240,16 @@
         <v>0</v>
       </c>
       <c r="AJ265" t="n">
-        <v>2.625779105339106</v>
+        <v>2.625779105339105</v>
       </c>
       <c r="AK265" t="n">
-        <v>-1.615779105339106</v>
+        <v>-1.615779105339105</v>
       </c>
       <c r="AL265" t="n">
-        <v>1.615779105339106</v>
+        <v>1.615779105339105</v>
       </c>
       <c r="AM265" t="n">
-        <v>159.9781292414957</v>
+        <v>159.9781292414955</v>
       </c>
     </row>
     <row r="266">
@@ -37940,13 +37940,13 @@
         <v>1.751517017195767</v>
       </c>
       <c r="AK270" t="n">
-        <v>0.248482982804233</v>
+        <v>0.2484829828042325</v>
       </c>
       <c r="AL270" t="n">
-        <v>0.248482982804233</v>
+        <v>0.2484829828042325</v>
       </c>
       <c r="AM270" t="n">
-        <v>12.42414914021165</v>
+        <v>12.42414914021163</v>
       </c>
     </row>
     <row r="271">
@@ -38083,13 +38083,13 @@
         <v>20.05331731601731</v>
       </c>
       <c r="AK271" t="n">
-        <v>0.9466826839826865</v>
+        <v>0.9466826839826901</v>
       </c>
       <c r="AL271" t="n">
-        <v>0.9466826839826865</v>
+        <v>0.9466826839826901</v>
       </c>
       <c r="AM271" t="n">
-        <v>4.508012780869936</v>
+        <v>4.508012780869953</v>
       </c>
     </row>
     <row r="272">
@@ -38229,16 +38229,16 @@
         <v>0</v>
       </c>
       <c r="AJ272" t="n">
-        <v>8.121899977522475</v>
+        <v>8.103199977522477</v>
       </c>
       <c r="AK272" t="n">
-        <v>-0.1818999775224741</v>
+        <v>-0.1631999775224768</v>
       </c>
       <c r="AL272" t="n">
-        <v>0.1818999775224741</v>
+        <v>0.1631999775224768</v>
       </c>
       <c r="AM272" t="n">
-        <v>2.290931706832168</v>
+        <v>2.055415334036232</v>
       </c>
     </row>
     <row r="273">
@@ -38517,16 +38517,16 @@
         <v>0</v>
       </c>
       <c r="AJ274" t="n">
-        <v>20.76966877104377</v>
+        <v>20.75811877104377</v>
       </c>
       <c r="AK274" t="n">
-        <v>0.4303312289562342</v>
+        <v>0.4418812289562304</v>
       </c>
       <c r="AL274" t="n">
-        <v>0.4303312289562342</v>
+        <v>0.4418812289562304</v>
       </c>
       <c r="AM274" t="n">
-        <v>2.029864287529407</v>
+        <v>2.084345419604861</v>
       </c>
     </row>
     <row r="275">
@@ -38657,13 +38657,13 @@
         <v>1.448121853054352</v>
       </c>
       <c r="AK275" t="n">
-        <v>-0.4881218530543521</v>
+        <v>-0.4881218530543519</v>
       </c>
       <c r="AL275" t="n">
-        <v>0.4881218530543521</v>
+        <v>0.4881218530543519</v>
       </c>
       <c r="AM275" t="n">
-        <v>50.84602635982834</v>
+        <v>50.84602635982832</v>
       </c>
     </row>
     <row r="276">
@@ -38940,16 +38940,16 @@
         <v>1</v>
       </c>
       <c r="AJ277" t="n">
-        <v>1.952123363812113</v>
+        <v>1.952123363812112</v>
       </c>
       <c r="AK277" t="n">
-        <v>-0.5121233638121132</v>
+        <v>-0.5121233638121123</v>
       </c>
       <c r="AL277" t="n">
-        <v>0.5121233638121132</v>
+        <v>0.5121233638121123</v>
       </c>
       <c r="AM277" t="n">
-        <v>35.56412248695231</v>
+        <v>35.56412248695224</v>
       </c>
     </row>
     <row r="278">
@@ -39351,16 +39351,16 @@
         <v>1</v>
       </c>
       <c r="AJ280" t="n">
-        <v>3.416999100529101</v>
+        <v>3.416999100529102</v>
       </c>
       <c r="AK280" t="n">
-        <v>-0.426999100529101</v>
+        <v>-0.4269991005291018</v>
       </c>
       <c r="AL280" t="n">
-        <v>0.426999100529101</v>
+        <v>0.4269991005291018</v>
       </c>
       <c r="AM280" t="n">
-        <v>14.28090637221073</v>
+        <v>14.28090637221076</v>
       </c>
     </row>
     <row r="281">
@@ -39494,16 +39494,16 @@
         <v>0</v>
       </c>
       <c r="AJ281" t="n">
-        <v>12.74770522847523</v>
+        <v>12.74770522847522</v>
       </c>
       <c r="AK281" t="n">
-        <v>0.1522947715247742</v>
+        <v>0.152294771524776</v>
       </c>
       <c r="AL281" t="n">
-        <v>0.1522947715247742</v>
+        <v>0.152294771524776</v>
       </c>
       <c r="AM281" t="n">
-        <v>1.180579624223056</v>
+        <v>1.18057962422307</v>
       </c>
     </row>
     <row r="282">
@@ -39643,16 +39643,16 @@
         <v>1</v>
       </c>
       <c r="AJ282" t="n">
-        <v>1.750035393680392</v>
+        <v>1.750035393680393</v>
       </c>
       <c r="AK282" t="n">
-        <v>-3.539368039207069e-05</v>
+        <v>-3.539368039251478e-05</v>
       </c>
       <c r="AL282" t="n">
-        <v>3.539368039207069e-05</v>
+        <v>3.539368039251478e-05</v>
       </c>
       <c r="AM282" t="n">
-        <v>0.002022496022404039</v>
+        <v>0.002022496022429416</v>
       </c>
     </row>
     <row r="283">
@@ -39792,16 +39792,16 @@
         <v>1</v>
       </c>
       <c r="AJ283" t="n">
-        <v>3.504752225274726</v>
+        <v>3.504752225274725</v>
       </c>
       <c r="AK283" t="n">
-        <v>-0.1547522252747262</v>
+        <v>-0.1547522252747253</v>
       </c>
       <c r="AL283" t="n">
-        <v>0.1547522252747262</v>
+        <v>0.1547522252747253</v>
       </c>
       <c r="AM283" t="n">
-        <v>4.619469411185857</v>
+        <v>4.61946941118583</v>
       </c>
     </row>
     <row r="284">
@@ -40078,16 +40078,16 @@
         <v>1</v>
       </c>
       <c r="AJ285" t="n">
-        <v>2.018190687830687</v>
+        <v>2.018190687830686</v>
       </c>
       <c r="AK285" t="n">
-        <v>-0.0381906878306868</v>
+        <v>-0.03819068783068635</v>
       </c>
       <c r="AL285" t="n">
-        <v>0.0381906878306868</v>
+        <v>0.03819068783068635</v>
       </c>
       <c r="AM285" t="n">
-        <v>1.928822617711454</v>
+        <v>1.928822617711432</v>
       </c>
     </row>
     <row r="286">
@@ -40218,13 +40218,13 @@
         <v>2.104858174603174</v>
       </c>
       <c r="AK286" t="n">
-        <v>-0.05485817460317399</v>
+        <v>-0.05485817460317444</v>
       </c>
       <c r="AL286" t="n">
-        <v>0.05485817460317399</v>
+        <v>0.05485817460317444</v>
       </c>
       <c r="AM286" t="n">
-        <v>2.676008517228</v>
+        <v>2.676008517228021</v>
       </c>
     </row>
     <row r="287">
@@ -40489,16 +40489,16 @@
         <v>1</v>
       </c>
       <c r="AJ288" t="n">
-        <v>4.114252129629631</v>
+        <v>4.114252129629628</v>
       </c>
       <c r="AK288" t="n">
-        <v>-0.554252129629631</v>
+        <v>-0.5542521296296283</v>
       </c>
       <c r="AL288" t="n">
-        <v>0.554252129629631</v>
+        <v>0.5542521296296283</v>
       </c>
       <c r="AM288" t="n">
-        <v>15.56888004577615</v>
+        <v>15.56888004577608</v>
       </c>
     </row>
     <row r="289">
@@ -40900,16 +40900,16 @@
         <v>1</v>
       </c>
       <c r="AJ291" t="n">
-        <v>4.132082976190476</v>
+        <v>4.132082976190475</v>
       </c>
       <c r="AK291" t="n">
-        <v>0.4979170238095234</v>
+        <v>0.4979170238095252</v>
       </c>
       <c r="AL291" t="n">
-        <v>0.4979170238095234</v>
+        <v>0.4979170238095252</v>
       </c>
       <c r="AM291" t="n">
-        <v>10.75414738249511</v>
+        <v>10.75414738249514</v>
       </c>
     </row>
     <row r="292">
@@ -41037,16 +41037,16 @@
         <v>1</v>
       </c>
       <c r="AJ292" t="n">
-        <v>2.49575868746994</v>
+        <v>2.495758687469939</v>
       </c>
       <c r="AK292" t="n">
-        <v>-0.3257586874699396</v>
+        <v>-0.3257586874699392</v>
       </c>
       <c r="AL292" t="n">
-        <v>0.3257586874699396</v>
+        <v>0.3257586874699392</v>
       </c>
       <c r="AM292" t="n">
-        <v>15.01192108156404</v>
+        <v>15.01192108156402</v>
       </c>
     </row>
     <row r="293">
@@ -41174,16 +41174,16 @@
         <v>1</v>
       </c>
       <c r="AJ293" t="n">
-        <v>3.90133424788175</v>
+        <v>3.901334247881751</v>
       </c>
       <c r="AK293" t="n">
-        <v>1.38866575211825</v>
+        <v>1.388665752118249</v>
       </c>
       <c r="AL293" t="n">
-        <v>1.38866575211825</v>
+        <v>1.388665752118249</v>
       </c>
       <c r="AM293" t="n">
-        <v>26.2507703614036</v>
+        <v>26.25077036140357</v>
       </c>
     </row>
     <row r="294">
@@ -41311,16 +41311,16 @@
         <v>1</v>
       </c>
       <c r="AJ294" t="n">
-        <v>4.244082619047622</v>
+        <v>4.244082619047621</v>
       </c>
       <c r="AK294" t="n">
-        <v>4.905917380952379</v>
+        <v>4.90591738095238</v>
       </c>
       <c r="AL294" t="n">
-        <v>4.905917380952379</v>
+        <v>4.90591738095238</v>
       </c>
       <c r="AM294" t="n">
-        <v>53.61658339838665</v>
+        <v>53.61658339838667</v>
       </c>
     </row>
     <row r="295">
@@ -41737,13 +41737,13 @@
         <v>1.79116132996633</v>
       </c>
       <c r="AK297" t="n">
-        <v>0.008838670033670448</v>
+        <v>0.008838670033670004</v>
       </c>
       <c r="AL297" t="n">
-        <v>0.008838670033670448</v>
+        <v>0.008838670033670004</v>
       </c>
       <c r="AM297" t="n">
-        <v>0.4910372240928026</v>
+        <v>0.491037224092778</v>
       </c>
     </row>
     <row r="298">
@@ -42145,16 +42145,16 @@
         <v>1</v>
       </c>
       <c r="AJ300" t="n">
-        <v>1.952123363812113</v>
+        <v>1.952123363812112</v>
       </c>
       <c r="AK300" t="n">
-        <v>-0.8021233638121132</v>
+        <v>-0.8021233638121124</v>
       </c>
       <c r="AL300" t="n">
-        <v>0.8021233638121132</v>
+        <v>0.8021233638121124</v>
       </c>
       <c r="AM300" t="n">
-        <v>69.74985772279247</v>
+        <v>69.74985772279238</v>
       </c>
     </row>
     <row r="301">
@@ -42282,16 +42282,16 @@
         <v>1</v>
       </c>
       <c r="AJ301" t="n">
-        <v>1.952123363812113</v>
+        <v>1.952123363812112</v>
       </c>
       <c r="AK301" t="n">
-        <v>-0.4021233638121131</v>
+        <v>-0.4021233638121122</v>
       </c>
       <c r="AL301" t="n">
-        <v>0.4021233638121131</v>
+        <v>0.4021233638121122</v>
       </c>
       <c r="AM301" t="n">
-        <v>25.94344282658794</v>
+        <v>25.94344282658789</v>
       </c>
     </row>
     <row r="302">
@@ -42556,16 +42556,16 @@
         <v>1</v>
       </c>
       <c r="AJ303" t="n">
-        <v>1.977615396825397</v>
+        <v>1.977615396825396</v>
       </c>
       <c r="AK303" t="n">
-        <v>-0.03761539682539672</v>
+        <v>-0.03761539682539605</v>
       </c>
       <c r="AL303" t="n">
-        <v>0.03761539682539672</v>
+        <v>0.03761539682539605</v>
       </c>
       <c r="AM303" t="n">
-        <v>1.938937980690553</v>
+        <v>1.938937980690518</v>
       </c>
     </row>
     <row r="304">
@@ -42833,10 +42833,10 @@
         <v>1.705189927248676</v>
       </c>
       <c r="AK305" t="n">
-        <v>-0.8951899272486761</v>
+        <v>-0.8951899272486759</v>
       </c>
       <c r="AL305" t="n">
-        <v>0.8951899272486761</v>
+        <v>0.8951899272486759</v>
       </c>
       <c r="AM305" t="n">
         <v>110.5172749689723</v>
@@ -42970,13 +42970,13 @@
         <v>1.811084348244348</v>
       </c>
       <c r="AK306" t="n">
-        <v>0.2889156517556517</v>
+        <v>0.2889156517556521</v>
       </c>
       <c r="AL306" t="n">
-        <v>0.2889156517556517</v>
+        <v>0.2889156517556521</v>
       </c>
       <c r="AM306" t="n">
-        <v>13.75788817884056</v>
+        <v>13.75788817884058</v>
       </c>
     </row>
     <row r="307">
@@ -43104,16 +43104,16 @@
         <v>1</v>
       </c>
       <c r="AJ307" t="n">
-        <v>1.952123363812113</v>
+        <v>1.952123363812112</v>
       </c>
       <c r="AK307" t="n">
-        <v>-0.4821233638121132</v>
+        <v>-0.4821233638121123</v>
       </c>
       <c r="AL307" t="n">
-        <v>0.4821233638121132</v>
+        <v>0.4821233638121123</v>
       </c>
       <c r="AM307" t="n">
-        <v>32.79750774232063</v>
+        <v>32.79750774232056</v>
       </c>
     </row>
     <row r="308">
@@ -43241,16 +43241,16 @@
         <v>1</v>
       </c>
       <c r="AJ308" t="n">
-        <v>1.952123363812113</v>
+        <v>1.952123363812112</v>
       </c>
       <c r="AK308" t="n">
-        <v>0.687876636187887</v>
+        <v>0.6878766361878879</v>
       </c>
       <c r="AL308" t="n">
-        <v>0.687876636187887</v>
+        <v>0.6878766361878879</v>
       </c>
       <c r="AM308" t="n">
-        <v>26.05593318893511</v>
+        <v>26.05593318893514</v>
       </c>
     </row>
     <row r="309">
@@ -43381,13 +43381,13 @@
         <v>5.107552433862431</v>
       </c>
       <c r="AK309" t="n">
-        <v>2.372447566137569</v>
+        <v>2.37244756613757</v>
       </c>
       <c r="AL309" t="n">
-        <v>2.372447566137569</v>
+        <v>2.37244756613757</v>
       </c>
       <c r="AM309" t="n">
-        <v>31.71721345103702</v>
+        <v>31.71721345103703</v>
       </c>
     </row>
     <row r="310">
@@ -43515,16 +43515,16 @@
         <v>1</v>
       </c>
       <c r="AJ310" t="n">
-        <v>1.952123363812113</v>
+        <v>1.952123363812112</v>
       </c>
       <c r="AK310" t="n">
-        <v>-0.4521233638121132</v>
+        <v>-0.4521233638121123</v>
       </c>
       <c r="AL310" t="n">
-        <v>0.4521233638121132</v>
+        <v>0.4521233638121123</v>
       </c>
       <c r="AM310" t="n">
-        <v>30.14155758747421</v>
+        <v>30.14155758747415</v>
       </c>
     </row>
     <row r="311">
@@ -43658,16 +43658,16 @@
         <v>0</v>
       </c>
       <c r="AJ311" t="n">
-        <v>22.39961822991821</v>
+        <v>22.38806822991822</v>
       </c>
       <c r="AK311" t="n">
-        <v>2.500381770081788</v>
+        <v>2.51193177008178</v>
       </c>
       <c r="AL311" t="n">
-        <v>2.500381770081788</v>
+        <v>2.51193177008178</v>
       </c>
       <c r="AM311" t="n">
-        <v>10.04169385575015</v>
+        <v>10.0880793979188</v>
       </c>
     </row>
     <row r="312">
@@ -43801,16 +43801,16 @@
         <v>0</v>
       </c>
       <c r="AJ312" t="n">
-        <v>24.81999178691677</v>
+        <v>24.83341400913899</v>
       </c>
       <c r="AK312" t="n">
-        <v>3.680008213083234</v>
+        <v>3.666585990861005</v>
       </c>
       <c r="AL312" t="n">
-        <v>3.680008213083234</v>
+        <v>3.666585990861005</v>
       </c>
       <c r="AM312" t="n">
-        <v>12.91230951959029</v>
+        <v>12.86521400302107</v>
       </c>
     </row>
     <row r="313">
@@ -43944,16 +43944,16 @@
         <v>0</v>
       </c>
       <c r="AJ313" t="n">
-        <v>24.03676069023569</v>
+        <v>24.03835116642617</v>
       </c>
       <c r="AK313" t="n">
-        <v>4.163239309764311</v>
+        <v>4.161648833573832</v>
       </c>
       <c r="AL313" t="n">
-        <v>4.163239309764311</v>
+        <v>4.161648833573832</v>
       </c>
       <c r="AM313" t="n">
-        <v>14.76325996370323</v>
+        <v>14.75761997721217</v>
       </c>
     </row>
     <row r="314">
@@ -44224,16 +44224,16 @@
         <v>0</v>
       </c>
       <c r="AJ315" t="n">
-        <v>9.294051242183748</v>
+        <v>9.294051242183745</v>
       </c>
       <c r="AK315" t="n">
-        <v>-0.4940512421837475</v>
+        <v>-0.494051242183744</v>
       </c>
       <c r="AL315" t="n">
-        <v>0.4940512421837475</v>
+        <v>0.494051242183744</v>
       </c>
       <c r="AM315" t="n">
-        <v>5.614218661178948</v>
+        <v>5.614218661178908</v>
       </c>
     </row>
     <row r="316">
@@ -44510,16 +44510,16 @@
         <v>0</v>
       </c>
       <c r="AJ317" t="n">
-        <v>9.998398983886487</v>
+        <v>9.998398983886485</v>
       </c>
       <c r="AK317" t="n">
-        <v>1.001601016113513</v>
+        <v>1.001601016113515</v>
       </c>
       <c r="AL317" t="n">
-        <v>1.001601016113513</v>
+        <v>1.001601016113515</v>
       </c>
       <c r="AM317" t="n">
-        <v>9.105463782850119</v>
+        <v>9.105463782850135</v>
       </c>
     </row>
     <row r="318">
@@ -44653,16 +44653,16 @@
         <v>0</v>
       </c>
       <c r="AJ318" t="n">
-        <v>12.12339782106782</v>
+        <v>12.12048115440115</v>
       </c>
       <c r="AK318" t="n">
-        <v>1.276602178932185</v>
+        <v>1.279518845598853</v>
       </c>
       <c r="AL318" t="n">
-        <v>1.276602178932185</v>
+        <v>1.279518845598853</v>
       </c>
       <c r="AM318" t="n">
-        <v>9.52688193232974</v>
+        <v>9.548648101483975</v>
       </c>
     </row>
     <row r="319">
@@ -44796,16 +44796,16 @@
         <v>0</v>
       </c>
       <c r="AJ319" t="n">
-        <v>20.25131606060605</v>
+        <v>20.23976606060605</v>
       </c>
       <c r="AK319" t="n">
-        <v>1.348683939393954</v>
+        <v>1.360233939393954</v>
       </c>
       <c r="AL319" t="n">
-        <v>1.348683939393954</v>
+        <v>1.360233939393954</v>
       </c>
       <c r="AM319" t="n">
-        <v>6.243907126823861</v>
+        <v>6.297379349046082</v>
       </c>
     </row>
     <row r="320">
@@ -44939,16 +44939,16 @@
         <v>0</v>
       </c>
       <c r="AJ320" t="n">
-        <v>23.25589309764309</v>
+        <v>23.25748357383357</v>
       </c>
       <c r="AK320" t="n">
-        <v>-2.455893097643088</v>
+        <v>-2.457483573833567</v>
       </c>
       <c r="AL320" t="n">
-        <v>2.455893097643088</v>
+        <v>2.457483573833567</v>
       </c>
       <c r="AM320" t="n">
-        <v>11.80717835405331</v>
+        <v>11.81482487419984</v>
       </c>
     </row>
     <row r="321">
@@ -45085,13 +45085,13 @@
         <v>25.4296988095238</v>
       </c>
       <c r="AK321" t="n">
-        <v>2.570301190476201</v>
+        <v>2.570301190476197</v>
       </c>
       <c r="AL321" t="n">
-        <v>2.570301190476201</v>
+        <v>2.570301190476197</v>
       </c>
       <c r="AM321" t="n">
-        <v>9.179647108843573</v>
+        <v>9.179647108843561</v>
       </c>
     </row>
     <row r="322">
@@ -45228,13 +45228,13 @@
         <v>24.94216216931217</v>
       </c>
       <c r="AK322" t="n">
-        <v>3.057837830687831</v>
+        <v>3.057837830687827</v>
       </c>
       <c r="AL322" t="n">
-        <v>3.057837830687831</v>
+        <v>3.057837830687827</v>
       </c>
       <c r="AM322" t="n">
-        <v>10.92084939531368</v>
+        <v>10.92084939531367</v>
       </c>
     </row>
     <row r="323">
@@ -45367,13 +45367,13 @@
         <v>11.08924290043289</v>
       </c>
       <c r="AK323" t="n">
-        <v>1.010757099567108</v>
+        <v>1.01075709956711</v>
       </c>
       <c r="AL323" t="n">
-        <v>1.010757099567108</v>
+        <v>1.01075709956711</v>
       </c>
       <c r="AM323" t="n">
-        <v>8.353364459232299</v>
+        <v>8.353364459232314</v>
       </c>
     </row>
     <row r="324">
@@ -45506,13 +45506,13 @@
         <v>11.08924290043289</v>
       </c>
       <c r="AK324" t="n">
-        <v>-0.9892429004328918</v>
+        <v>-0.98924290043289</v>
       </c>
       <c r="AL324" t="n">
-        <v>0.9892429004328918</v>
+        <v>0.98924290043289</v>
       </c>
       <c r="AM324" t="n">
-        <v>9.794484162701899</v>
+        <v>9.794484162701881</v>
       </c>
     </row>
     <row r="325">
@@ -45642,16 +45642,16 @@
         <v>0</v>
       </c>
       <c r="AJ325" t="n">
-        <v>14.8331473015873</v>
+        <v>14.82159730158731</v>
       </c>
       <c r="AK325" t="n">
-        <v>-2.733147301587305</v>
+        <v>-2.721597301587305</v>
       </c>
       <c r="AL325" t="n">
-        <v>2.733147301587305</v>
+        <v>2.721597301587305</v>
       </c>
       <c r="AM325" t="n">
-        <v>22.58799422799426</v>
+        <v>22.49253968253971</v>
       </c>
     </row>
     <row r="326">
@@ -45775,16 +45775,16 @@
         <v>0</v>
       </c>
       <c r="AJ326" t="n">
-        <v>13.10025892857142</v>
+        <v>13.08870892857142</v>
       </c>
       <c r="AK326" t="n">
-        <v>-1.000258928571419</v>
+        <v>-0.9887089285714179</v>
       </c>
       <c r="AL326" t="n">
-        <v>1.000258928571419</v>
+        <v>0.9887089285714179</v>
       </c>
       <c r="AM326" t="n">
-        <v>8.266602715466275</v>
+        <v>8.171148170011719</v>
       </c>
     </row>
     <row r="327">
@@ -45912,16 +45912,16 @@
         <v>0</v>
       </c>
       <c r="AJ327" t="n">
-        <v>11.72361488095236</v>
+        <v>11.71206488095236</v>
       </c>
       <c r="AK327" t="n">
-        <v>0.3763851190476366</v>
+        <v>0.3879351190476399</v>
       </c>
       <c r="AL327" t="n">
-        <v>0.3763851190476366</v>
+        <v>0.3879351190476399</v>
       </c>
       <c r="AM327" t="n">
-        <v>3.110620818575509</v>
+        <v>3.206075364030082</v>
       </c>
     </row>
     <row r="328">
@@ -46051,16 +46051,16 @@
         <v>0</v>
       </c>
       <c r="AJ328" t="n">
-        <v>13.11792719576719</v>
+        <v>13.10637719576718</v>
       </c>
       <c r="AK328" t="n">
-        <v>-2.017927195767186</v>
+        <v>-2.006377195767183</v>
       </c>
       <c r="AL328" t="n">
-        <v>2.017927195767186</v>
+        <v>2.006377195767183</v>
       </c>
       <c r="AM328" t="n">
-        <v>18.17952428619087</v>
+        <v>18.07547023213678</v>
       </c>
     </row>
     <row r="329">
@@ -46333,16 +46333,16 @@
         <v>0</v>
       </c>
       <c r="AJ330" t="n">
-        <v>7.352562631072614</v>
+        <v>7.353840964405948</v>
       </c>
       <c r="AK330" t="n">
-        <v>2.747437368927386</v>
+        <v>2.746159035594052</v>
       </c>
       <c r="AL330" t="n">
-        <v>2.747437368927386</v>
+        <v>2.746159035594052</v>
       </c>
       <c r="AM330" t="n">
-        <v>27.20235018739987</v>
+        <v>27.18969342172329</v>
       </c>
     </row>
     <row r="331">
@@ -46759,13 +46759,13 @@
         <v>3.741571042568545</v>
       </c>
       <c r="AK333" t="n">
-        <v>0.7784289574314549</v>
+        <v>0.7784289574314545</v>
       </c>
       <c r="AL333" t="n">
-        <v>0.7784289574314549</v>
+        <v>0.7784289574314545</v>
       </c>
       <c r="AM333" t="n">
-        <v>17.22187958919148</v>
+        <v>17.22187958919147</v>
       </c>
     </row>
     <row r="334">
@@ -46893,16 +46893,16 @@
         <v>1</v>
       </c>
       <c r="AJ334" t="n">
-        <v>3.559268476430978</v>
+        <v>3.559268476430977</v>
       </c>
       <c r="AK334" t="n">
-        <v>0.0307315235690222</v>
+        <v>0.03073152356902309</v>
       </c>
       <c r="AL334" t="n">
-        <v>0.0307315235690222</v>
+        <v>0.03073152356902309</v>
       </c>
       <c r="AM334" t="n">
-        <v>0.856031297187248</v>
+        <v>0.8560312971872727</v>
       </c>
     </row>
     <row r="335">
@@ -47179,16 +47179,16 @@
         <v>0</v>
       </c>
       <c r="AJ336" t="n">
-        <v>7.604364880952362</v>
+        <v>7.620659325396804</v>
       </c>
       <c r="AK336" t="n">
-        <v>1.495635119047638</v>
+        <v>1.479340674603195</v>
       </c>
       <c r="AL336" t="n">
-        <v>1.495635119047638</v>
+        <v>1.479340674603195</v>
       </c>
       <c r="AM336" t="n">
-        <v>16.43555075876525</v>
+        <v>16.25649092970544</v>
       </c>
     </row>
     <row r="337">
@@ -47461,16 +47461,16 @@
         <v>0</v>
       </c>
       <c r="AJ338" t="n">
-        <v>10.543219510582</v>
+        <v>10.554769510582</v>
       </c>
       <c r="AK338" t="n">
-        <v>-1.443219510582002</v>
+        <v>-1.454769510582</v>
       </c>
       <c r="AL338" t="n">
-        <v>1.443219510582002</v>
+        <v>1.454769510582</v>
       </c>
       <c r="AM338" t="n">
-        <v>15.85955506134069</v>
+        <v>15.98647813826374</v>
       </c>
     </row>
     <row r="339">
@@ -47743,16 +47743,16 @@
         <v>0</v>
       </c>
       <c r="AJ340" t="n">
-        <v>9.260824100529089</v>
+        <v>9.25807687830687</v>
       </c>
       <c r="AK340" t="n">
-        <v>0.8391758994709111</v>
+        <v>0.8419231216931298</v>
       </c>
       <c r="AL340" t="n">
-        <v>0.8391758994709111</v>
+        <v>0.8419231216931298</v>
       </c>
       <c r="AM340" t="n">
-        <v>8.308672271989218</v>
+        <v>8.335872492011186</v>
       </c>
     </row>
     <row r="341">
@@ -48455,13 +48455,13 @@
         <v>3.744278172198173</v>
       </c>
       <c r="AK345" t="n">
-        <v>-0.3342781721981734</v>
+        <v>-0.3342781721981729</v>
       </c>
       <c r="AL345" t="n">
-        <v>0.3342781721981734</v>
+        <v>0.3342781721981729</v>
       </c>
       <c r="AM345" t="n">
-        <v>9.80287895009306</v>
+        <v>9.802878950093048</v>
       </c>
     </row>
     <row r="346">
@@ -49018,16 +49018,16 @@
         <v>1</v>
       </c>
       <c r="AJ349" t="n">
-        <v>5.519346095478604</v>
+        <v>5.519346095478606</v>
       </c>
       <c r="AK349" t="n">
-        <v>-3.629346095478605</v>
+        <v>-3.629346095478606</v>
       </c>
       <c r="AL349" t="n">
-        <v>3.629346095478605</v>
+        <v>3.629346095478606</v>
       </c>
       <c r="AM349" t="n">
-        <v>192.0288939406669</v>
+        <v>192.028893940667</v>
       </c>
     </row>
     <row r="350">
@@ -49304,16 +49304,16 @@
         <v>0</v>
       </c>
       <c r="AJ351" t="n">
-        <v>6.379763346560841</v>
+        <v>6.389655013227507</v>
       </c>
       <c r="AK351" t="n">
-        <v>-5.279763346560841</v>
+        <v>-5.289655013227506</v>
       </c>
       <c r="AL351" t="n">
-        <v>5.279763346560841</v>
+        <v>5.289655013227506</v>
       </c>
       <c r="AM351" t="n">
-        <v>479.9784860509855</v>
+        <v>480.8777284752278</v>
       </c>
     </row>
     <row r="352">
@@ -49447,16 +49447,16 @@
         <v>0</v>
       </c>
       <c r="AJ352" t="n">
-        <v>7.049299325396803</v>
+        <v>7.033499325396805</v>
       </c>
       <c r="AK352" t="n">
-        <v>2.050700674603196</v>
+        <v>2.066500674603195</v>
       </c>
       <c r="AL352" t="n">
-        <v>2.050700674603196</v>
+        <v>2.066500674603195</v>
       </c>
       <c r="AM352" t="n">
-        <v>22.53517224838678</v>
+        <v>22.70879862201313</v>
       </c>
     </row>
     <row r="353">
@@ -49584,16 +49584,16 @@
         <v>1</v>
       </c>
       <c r="AJ353" t="n">
-        <v>5.508832405002413</v>
+        <v>5.508832405002414</v>
       </c>
       <c r="AK353" t="n">
-        <v>-0.8288324050024132</v>
+        <v>-0.8288324050024141</v>
       </c>
       <c r="AL353" t="n">
-        <v>0.8288324050024132</v>
+        <v>0.8288324050024141</v>
       </c>
       <c r="AM353" t="n">
-        <v>17.71009412398319</v>
+        <v>17.71009412398321</v>
       </c>
     </row>
     <row r="354">
@@ -50003,16 +50003,16 @@
         <v>1</v>
       </c>
       <c r="AJ356" t="n">
-        <v>4.221653516113515</v>
+        <v>4.221653516113517</v>
       </c>
       <c r="AK356" t="n">
-        <v>-2.191653516113516</v>
+        <v>-2.191653516113517</v>
       </c>
       <c r="AL356" t="n">
-        <v>2.191653516113516</v>
+        <v>2.191653516113517</v>
       </c>
       <c r="AM356" t="n">
-        <v>107.9632273947545</v>
+        <v>107.9632273947546</v>
       </c>
     </row>
     <row r="357">
@@ -50283,16 +50283,16 @@
         <v>0</v>
       </c>
       <c r="AJ358" t="n">
-        <v>9.046245238095198</v>
+        <v>9.046195238095198</v>
       </c>
       <c r="AK358" t="n">
-        <v>0.053754761904802</v>
+        <v>0.05380476190480188</v>
       </c>
       <c r="AL358" t="n">
-        <v>0.053754761904802</v>
+        <v>0.05380476190480188</v>
       </c>
       <c r="AM358" t="n">
-        <v>0.5907116692835385</v>
+        <v>0.5912611198329877</v>
       </c>
     </row>
     <row r="359">
@@ -50564,13 +50564,13 @@
         <v>10.00132397787397</v>
       </c>
       <c r="AK360" t="n">
-        <v>0.09867602212603188</v>
+        <v>0.09867602212603366</v>
       </c>
       <c r="AL360" t="n">
-        <v>0.09867602212603188</v>
+        <v>0.09867602212603366</v>
       </c>
       <c r="AM360" t="n">
-        <v>0.9769903180795236</v>
+        <v>0.9769903180795412</v>
       </c>
     </row>
     <row r="361">
@@ -50703,13 +50703,13 @@
         <v>10.00132397787397</v>
       </c>
       <c r="AK361" t="n">
-        <v>-0.9013239778739681</v>
+        <v>-0.9013239778739663</v>
       </c>
       <c r="AL361" t="n">
-        <v>0.9013239778739681</v>
+        <v>0.9013239778739663</v>
       </c>
       <c r="AM361" t="n">
-        <v>9.904659097516133</v>
+        <v>9.904659097516113</v>
       </c>
     </row>
     <row r="362">
@@ -50843,16 +50843,16 @@
         <v>0</v>
       </c>
       <c r="AJ362" t="n">
-        <v>8.062742510822488</v>
+        <v>8.096703820346299</v>
       </c>
       <c r="AK362" t="n">
-        <v>-4.962742510822489</v>
+        <v>-4.996703820346299</v>
       </c>
       <c r="AL362" t="n">
-        <v>4.962742510822489</v>
+        <v>4.996703820346299</v>
       </c>
       <c r="AM362" t="n">
-        <v>160.088468091048</v>
+        <v>161.1839942047193</v>
       </c>
     </row>
     <row r="363">
@@ -50982,16 +50982,16 @@
         <v>0</v>
       </c>
       <c r="AJ363" t="n">
-        <v>9.219275767195755</v>
+        <v>9.216528544973537</v>
       </c>
       <c r="AK363" t="n">
-        <v>0.8807242328042442</v>
+        <v>0.8834714550264628</v>
       </c>
       <c r="AL363" t="n">
-        <v>0.8807242328042442</v>
+        <v>0.8834714550264628</v>
       </c>
       <c r="AM363" t="n">
-        <v>8.720041908952913</v>
+        <v>8.747242128974881</v>
       </c>
     </row>
     <row r="364">
@@ -51549,13 +51549,13 @@
         <v>12.21094519841269</v>
       </c>
       <c r="AK367" t="n">
-        <v>-2.110945198412693</v>
+        <v>-2.110945198412692</v>
       </c>
       <c r="AL367" t="n">
-        <v>2.110945198412693</v>
+        <v>2.110945198412692</v>
       </c>
       <c r="AM367" t="n">
-        <v>20.90044750903657</v>
+        <v>20.90044750903655</v>
       </c>
     </row>
     <row r="368">
@@ -51822,16 +51822,16 @@
         <v>1</v>
       </c>
       <c r="AJ369" t="n">
-        <v>3.74207673039923</v>
+        <v>3.742076730399231</v>
       </c>
       <c r="AK369" t="n">
-        <v>-1.55207673039923</v>
+        <v>-1.552076730399231</v>
       </c>
       <c r="AL369" t="n">
-        <v>1.55207673039923</v>
+        <v>1.552076730399231</v>
       </c>
       <c r="AM369" t="n">
-        <v>70.87108357987351</v>
+        <v>70.87108357987356</v>
       </c>
     </row>
     <row r="370">
@@ -52103,13 +52103,13 @@
         <v>11.32594603174602</v>
       </c>
       <c r="AK371" t="n">
-        <v>0.7740539682539787</v>
+        <v>0.7740539682539822</v>
       </c>
       <c r="AL371" t="n">
-        <v>0.7740539682539787</v>
+        <v>0.7740539682539822</v>
       </c>
       <c r="AM371" t="n">
-        <v>6.397140233503956</v>
+        <v>6.397140233503985</v>
       </c>
     </row>
     <row r="372">
@@ -52240,13 +52240,13 @@
         <v>3.395111891534393</v>
       </c>
       <c r="AK372" t="n">
-        <v>-0.4351118915343926</v>
+        <v>-0.435111891534393</v>
       </c>
       <c r="AL372" t="n">
-        <v>0.4351118915343926</v>
+        <v>0.435111891534393</v>
       </c>
       <c r="AM372" t="n">
-        <v>14.6997260653511</v>
+        <v>14.69972606535111</v>
       </c>
     </row>
     <row r="373">
@@ -52380,16 +52380,16 @@
         <v>0</v>
       </c>
       <c r="AJ373" t="n">
-        <v>18.23858425925926</v>
+        <v>18.23858425925927</v>
       </c>
       <c r="AK373" t="n">
-        <v>-1.438584259259262</v>
+        <v>-1.438584259259269</v>
       </c>
       <c r="AL373" t="n">
-        <v>1.438584259259262</v>
+        <v>1.438584259259269</v>
       </c>
       <c r="AM373" t="n">
-        <v>8.563001543209889</v>
+        <v>8.563001543209934</v>
       </c>
     </row>
     <row r="374">
@@ -52791,16 +52791,16 @@
         <v>1</v>
       </c>
       <c r="AJ376" t="n">
-        <v>3.745857619047621</v>
+        <v>3.745857619047622</v>
       </c>
       <c r="AK376" t="n">
-        <v>1.494142380952379</v>
+        <v>1.494142380952378</v>
       </c>
       <c r="AL376" t="n">
-        <v>1.494142380952379</v>
+        <v>1.494142380952378</v>
       </c>
       <c r="AM376" t="n">
-        <v>28.51416757542708</v>
+        <v>28.51416757542706</v>
       </c>
     </row>
     <row r="377">
@@ -52928,16 +52928,16 @@
         <v>1</v>
       </c>
       <c r="AJ377" t="n">
-        <v>3.504596642061641</v>
+        <v>3.504596642061642</v>
       </c>
       <c r="AK377" t="n">
-        <v>-0.6545966420616414</v>
+        <v>-0.6545966420616423</v>
       </c>
       <c r="AL377" t="n">
-        <v>0.6545966420616414</v>
+        <v>0.6545966420616423</v>
       </c>
       <c r="AM377" t="n">
-        <v>22.96830323023303</v>
+        <v>22.96830323023306</v>
       </c>
     </row>
     <row r="378">
@@ -53202,16 +53202,16 @@
         <v>1</v>
       </c>
       <c r="AJ379" t="n">
-        <v>3.416999100529101</v>
+        <v>3.416999100529102</v>
       </c>
       <c r="AK379" t="n">
-        <v>0.1430008994708989</v>
+        <v>0.143000899470898</v>
       </c>
       <c r="AL379" t="n">
-        <v>0.1430008994708989</v>
+        <v>0.143000899470898</v>
       </c>
       <c r="AM379" t="n">
-        <v>4.016879198620756</v>
+        <v>4.016879198620731</v>
       </c>
     </row>
   </sheetData>
@@ -53262,13 +53262,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9652330983813701</v>
+        <v>0.9652206434734942</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6677231338988465</v>
+        <v>0.6679583739650716</v>
       </c>
       <c r="D2" t="n">
-        <v>1.066058776279091</v>
+        <v>1.066249711828346</v>
       </c>
       <c r="E2" t="n">
         <v>302</v>
@@ -53281,13 +53281,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9111462395227746</v>
+        <v>0.911090964433246</v>
       </c>
       <c r="C3" t="n">
-        <v>1.090164544085301</v>
+        <v>1.09053942555982</v>
       </c>
       <c r="D3" t="n">
-        <v>1.610165723791115</v>
+        <v>1.610666480408105</v>
       </c>
       <c r="E3" t="n">
         <v>76</v>
@@ -53300,13 +53300,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9553295680188567</v>
+        <v>0.9553092666217726</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7526584438834245</v>
+        <v>0.7529217599999946</v>
       </c>
       <c r="D4" t="n">
-        <v>1.195513565439799</v>
+        <v>1.195785197452226</v>
       </c>
       <c r="E4" t="n">
         <v>378</v>
@@ -53369,13 +53369,13 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9114203537686103</v>
+        <v>0.9112846905439373</v>
       </c>
       <c r="E2" t="n">
-        <v>1.078764537672366</v>
+        <v>1.079248238069192</v>
       </c>
       <c r="F2" t="n">
-        <v>1.607680121080666</v>
+        <v>1.608910762849211</v>
       </c>
     </row>
     <row r="3">
@@ -53389,13 +53389,13 @@
         <v>76</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8670645029277204</v>
+        <v>0.8670810341201258</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8532864631384697</v>
+        <v>0.8537763910833318</v>
       </c>
       <c r="F3" t="n">
-        <v>1.286435979352856</v>
+        <v>1.286355989499338</v>
       </c>
     </row>
     <row r="4">
@@ -53409,13 +53409,13 @@
         <v>76</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9056817688088141</v>
+        <v>0.9056765901938679</v>
       </c>
       <c r="E4" t="n">
-        <v>1.207965340946823</v>
+        <v>1.208047266768321</v>
       </c>
       <c r="F4" t="n">
-        <v>1.88519429088325</v>
+        <v>1.885246044193319</v>
       </c>
     </row>
     <row r="5">
@@ -53429,13 +53429,13 @@
         <v>75</v>
       </c>
       <c r="D5" t="n">
-        <v>0.907160491652069</v>
+        <v>0.9069522622141418</v>
       </c>
       <c r="E5" t="n">
-        <v>1.00744591808141</v>
+        <v>1.008337484218976</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7901183800397</v>
+        <v>1.792124781042105</v>
       </c>
     </row>
     <row r="6">
@@ -53449,13 +53449,13 @@
         <v>75</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8846697888720605</v>
+        <v>0.8845944456339582</v>
       </c>
       <c r="E6" t="n">
-        <v>1.256193440672909</v>
+        <v>1.256538949667618</v>
       </c>
       <c r="F6" t="n">
-        <v>2.255965146947756</v>
+        <v>2.256701918201015</v>
       </c>
     </row>
     <row r="7">
@@ -53471,13 +53471,13 @@
         <v>75.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8951993812058548</v>
+        <v>0.8951178045412063</v>
       </c>
       <c r="E7" t="n">
-        <v>1.080731140102396</v>
+        <v>1.081189665961488</v>
       </c>
       <c r="F7" t="n">
-        <v>1.765078783660845</v>
+        <v>1.765867899156997</v>
       </c>
     </row>
     <row r="8">
@@ -53493,13 +53493,13 @@
         <v>0.5477225575051661</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01883157092682535</v>
+        <v>0.01877306663968216</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1613081160055384</v>
+        <v>0.1611429716869708</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3570355063649154</v>
+        <v>0.3572204549542974</v>
       </c>
     </row>
   </sheetData>
@@ -53594,7 +53594,7 @@
         <v>1.678188339146609</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3187347377764684</v>
+        <v>0.3187347377764682</v>
       </c>
       <c r="F3" t="n">
         <v>0.695791010278895</v>
@@ -53616,16 +53616,16 @@
         <v>14.75272727272727</v>
       </c>
       <c r="D4" t="n">
-        <v>15.22896389424548</v>
+        <v>15.22481136899295</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4762366215182034</v>
+        <v>-0.4720840962656787</v>
       </c>
       <c r="F4" t="n">
-        <v>2.053511155822292</v>
+        <v>2.049406105317241</v>
       </c>
       <c r="G4" t="n">
-        <v>2.315805355639539</v>
+        <v>2.30947459036602</v>
       </c>
     </row>
     <row r="5">
@@ -53641,16 +53641,16 @@
         <v>2.518888888888889</v>
       </c>
       <c r="D5" t="n">
-        <v>3.003944396478007</v>
+        <v>3.005465586954198</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4850555075891187</v>
+        <v>-0.4865766980653092</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7448139480786697</v>
+        <v>0.7463351385548604</v>
       </c>
       <c r="G5" t="n">
-        <v>1.043216451133418</v>
+        <v>1.045059684908372</v>
       </c>
     </row>
     <row r="6">
@@ -53669,13 +53669,13 @@
         <v>1.679606409331409</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1156064093314089</v>
+        <v>-0.1156064093314087</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2390705656565656</v>
+        <v>0.2390705656565655</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2961220615031392</v>
+        <v>0.2961220615031391</v>
       </c>
     </row>
     <row r="7">
@@ -53691,16 +53691,16 @@
         <v>2.33</v>
       </c>
       <c r="D7" t="n">
-        <v>2.057521987433862</v>
+        <v>2.058272662037036</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2724780125661384</v>
+        <v>0.2717273379629641</v>
       </c>
       <c r="F7" t="n">
-        <v>0.570418295153921</v>
+        <v>0.5696676205507463</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6147604594875876</v>
+        <v>0.6137400763619885</v>
       </c>
     </row>
     <row r="8">
@@ -53716,16 +53716,16 @@
         <v>10.1</v>
       </c>
       <c r="D8" t="n">
-        <v>10.23034835537918</v>
+        <v>10.2285168738977</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1303483553791794</v>
+        <v>-0.1285168738976979</v>
       </c>
       <c r="F8" t="n">
-        <v>1.276948443562614</v>
+        <v>1.278779925044097</v>
       </c>
       <c r="G8" t="n">
-        <v>1.406648617009358</v>
+        <v>1.407769629045615</v>
       </c>
     </row>
     <row r="9">
@@ -53741,16 +53741,16 @@
         <v>3.1</v>
       </c>
       <c r="D9" t="n">
-        <v>8.062742510822488</v>
+        <v>8.096703820346297</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.962742510822489</v>
+        <v>-4.996703820346298</v>
       </c>
       <c r="F9" t="n">
-        <v>4.962742510822489</v>
+        <v>4.996703820346298</v>
       </c>
       <c r="G9" t="n">
-        <v>4.962742510822489</v>
+        <v>4.996703820346298</v>
       </c>
     </row>
     <row r="10">
@@ -53766,16 +53766,16 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>2.230945525493025</v>
+        <v>2.254448303270802</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.420945525493025</v>
+        <v>-1.444448303270802</v>
       </c>
       <c r="F10" t="n">
-        <v>1.420945525493025</v>
+        <v>1.444448303270802</v>
       </c>
       <c r="G10" t="n">
-        <v>1.420945525493025</v>
+        <v>1.444448303270802</v>
       </c>
     </row>
     <row r="11">
@@ -53836,7 +53836,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7619898178846325</v>
+        <v>0.7619767811410728</v>
       </c>
     </row>
     <row r="3">
@@ -53846,7 +53846,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1154732062532702</v>
+        <v>0.11545716214391</v>
       </c>
     </row>
     <row r="4">
@@ -53856,7 +53856,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05307564486013724</v>
+        <v>0.05308979526261556</v>
       </c>
     </row>
     <row r="5">
@@ -53866,7 +53866,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02537477952079661</v>
+        <v>0.02535556099097978</v>
       </c>
     </row>
     <row r="6">
@@ -53876,7 +53876,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02103764184007033</v>
+        <v>0.02073886324438766</v>
       </c>
     </row>
     <row r="7">
@@ -53886,7 +53886,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01298761565031201</v>
+        <v>0.01324918840943131</v>
       </c>
     </row>
     <row r="8">
@@ -53896,7 +53896,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00950217733473724</v>
+        <v>0.009579161091771565</v>
       </c>
     </row>
     <row r="9">
@@ -53906,7 +53906,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0005591166560439159</v>
+        <v>0.0005534877158314565</v>
       </c>
     </row>
   </sheetData>

--- a/Mini-Project/Agricultural Machinery Inventory from ABEMIS/Regression Parameters Output V3/RF_Predictions.xlsx
+++ b/Mini-Project/Agricultural Machinery Inventory from ABEMIS/Regression Parameters Output V3/RF_Predictions.xlsx
@@ -885,13 +885,13 @@
         <v>1.872129098124096</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.007870901875904002</v>
+        <v>0.007870901875903558</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.007870901875904002</v>
+        <v>0.007870901875903558</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.4186649933991491</v>
+        <v>0.4186649933991254</v>
       </c>
     </row>
     <row r="4">
@@ -1159,13 +1159,13 @@
         <v>2.291416005291006</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.2714160052910057</v>
+        <v>-0.2714160052910062</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.2714160052910057</v>
+        <v>0.2714160052910062</v>
       </c>
       <c r="AM5" t="n">
-        <v>13.43643590549533</v>
+        <v>13.43643590549536</v>
       </c>
     </row>
     <row r="6">
@@ -1606,13 +1606,13 @@
         <v>1.36020867003367</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.3402086700336697</v>
+        <v>-0.3402086700336702</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.3402086700336697</v>
+        <v>0.3402086700336702</v>
       </c>
       <c r="AM8" t="n">
-        <v>33.35379117977154</v>
+        <v>33.35379117977158</v>
       </c>
     </row>
     <row r="9">
@@ -1743,10 +1743,10 @@
         <v>1.608327652717652</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.8883276527176525</v>
+        <v>-0.8883276527176522</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.8883276527176525</v>
+        <v>0.8883276527176522</v>
       </c>
       <c r="AM9" t="n">
         <v>123.3788406552295</v>
@@ -1886,13 +1886,13 @@
         <v>17.25910338383839</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.5408966161616071</v>
+        <v>0.5408966161616107</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.5408966161616071</v>
+        <v>0.5408966161616107</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.03874503461577</v>
+        <v>3.03874503461579</v>
       </c>
     </row>
     <row r="11">
@@ -2023,13 +2023,13 @@
         <v>3.3111507984608</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.1311507984608</v>
+        <v>-0.1311507984607996</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.1311507984608</v>
+        <v>0.1311507984607996</v>
       </c>
       <c r="AM11" t="n">
-        <v>4.124238945308177</v>
+        <v>4.124238945308162</v>
       </c>
     </row>
     <row r="12">
@@ -2431,16 +2431,16 @@
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.563822354497352</v>
+        <v>3.563822354497354</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0.5438223544973524</v>
+        <v>-0.5438223544973537</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.5438223544973524</v>
+        <v>0.5438223544973537</v>
       </c>
       <c r="AM14" t="n">
-        <v>18.00736273170041</v>
+        <v>18.00736273170045</v>
       </c>
     </row>
     <row r="15">
@@ -2568,16 +2568,16 @@
         <v>1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.563822354497352</v>
+        <v>3.563822354497354</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.4261776455026478</v>
+        <v>0.4261776455026465</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.4261776455026478</v>
+        <v>0.4261776455026465</v>
       </c>
       <c r="AM15" t="n">
-        <v>10.68114399756009</v>
+        <v>10.68114399756006</v>
       </c>
     </row>
     <row r="16">
@@ -2854,16 +2854,16 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.398510482202983</v>
+        <v>1.398510482202982</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.04851048220298271</v>
+        <v>-0.04851048220298226</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.04851048220298271</v>
+        <v>0.04851048220298226</v>
       </c>
       <c r="AM17" t="n">
-        <v>3.593369052072793</v>
+        <v>3.59336905207276</v>
       </c>
     </row>
     <row r="18">
@@ -2991,16 +2991,16 @@
         <v>1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.384319591149592</v>
+        <v>2.384319591149591</v>
       </c>
       <c r="AK18" t="n">
-        <v>-1.564319591149592</v>
+        <v>-1.564319591149591</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.564319591149592</v>
+        <v>1.564319591149591</v>
       </c>
       <c r="AM18" t="n">
-        <v>190.7706818475112</v>
+        <v>190.7706818475111</v>
       </c>
     </row>
     <row r="19">
@@ -3539,16 +3539,16 @@
         <v>1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.194808014670516</v>
+        <v>1.194808014670515</v>
       </c>
       <c r="AK22" t="n">
-        <v>-0.1348080146705155</v>
+        <v>-0.1348080146705153</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.1348080146705155</v>
+        <v>0.1348080146705153</v>
       </c>
       <c r="AM22" t="n">
-        <v>12.7177372330675</v>
+        <v>12.71773723306748</v>
       </c>
     </row>
     <row r="23">
@@ -3816,13 +3816,13 @@
         <v>1.131082374939875</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.3589176250601247</v>
+        <v>0.3589176250601251</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.3589176250601247</v>
+        <v>0.3589176250601251</v>
       </c>
       <c r="AM24" t="n">
-        <v>24.08843121208891</v>
+        <v>24.08843121208894</v>
       </c>
     </row>
     <row r="25">
@@ -3948,16 +3948,16 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.433488492063493</v>
+        <v>3.433488492063492</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.1734884920634934</v>
+        <v>-0.1734884920634925</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.1734884920634934</v>
+        <v>0.1734884920634925</v>
       </c>
       <c r="AM25" t="n">
-        <v>5.321732885383232</v>
+        <v>5.321732885383206</v>
       </c>
     </row>
     <row r="26">
@@ -4088,13 +4088,13 @@
         <v>1.177954191919192</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.09204580808080798</v>
+        <v>0.0920458080808082</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.09204580808080798</v>
+        <v>0.0920458080808082</v>
       </c>
       <c r="AM26" t="n">
-        <v>7.247701423685668</v>
+        <v>7.247701423685685</v>
       </c>
     </row>
     <row r="27">
@@ -4357,16 +4357,16 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3.433488492063493</v>
+        <v>3.433488492063492</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.4334884920634932</v>
+        <v>-0.4334884920634923</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.4334884920634932</v>
+        <v>0.4334884920634923</v>
       </c>
       <c r="AM28" t="n">
-        <v>14.44961640211644</v>
+        <v>14.44961640211641</v>
       </c>
     </row>
     <row r="29">
@@ -4497,13 +4497,13 @@
         <v>1.680054920634921</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.8799450793650792</v>
+        <v>0.8799450793650789</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.8799450793650792</v>
+        <v>0.8799450793650789</v>
       </c>
       <c r="AM29" t="n">
-        <v>34.3728546626984</v>
+        <v>34.37285466269839</v>
       </c>
     </row>
     <row r="30">
@@ -4640,13 +4640,13 @@
         <v>12.81563244107743</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0.4156324410774328</v>
+        <v>-0.415632441077431</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.4156324410774328</v>
+        <v>0.415632441077431</v>
       </c>
       <c r="AM30" t="n">
-        <v>3.351874524818006</v>
+        <v>3.351874524817992</v>
       </c>
     </row>
     <row r="31">
@@ -4932,7 +4932,7 @@
         <v>1.6511507984608</v>
       </c>
       <c r="AM32" t="n">
-        <v>99.46691556992772</v>
+        <v>99.46691556992771</v>
       </c>
     </row>
     <row r="33">
@@ -5483,16 +5483,16 @@
         <v>1</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.952504604377106</v>
+        <v>1.952504604377107</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.4174953956228942</v>
+        <v>0.4174953956228933</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.4174953956228942</v>
+        <v>0.4174953956228933</v>
       </c>
       <c r="AM36" t="n">
-        <v>17.61583947775924</v>
+        <v>17.61583947775921</v>
       </c>
     </row>
     <row r="37">
@@ -5616,16 +5616,16 @@
         <v>1</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.71599557979058</v>
+        <v>1.715995579790579</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.1840044202094198</v>
+        <v>0.1840044202094204</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.1840044202094198</v>
+        <v>0.1840044202094204</v>
       </c>
       <c r="AM37" t="n">
-        <v>9.684443168916831</v>
+        <v>9.684443168916864</v>
       </c>
     </row>
     <row r="38">
@@ -5753,16 +5753,16 @@
         <v>1</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.752549600769601</v>
+        <v>1.7525496007696</v>
       </c>
       <c r="AK38" t="n">
-        <v>-0.2125496007696006</v>
+        <v>-0.2125496007695995</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.2125496007696006</v>
+        <v>0.2125496007695995</v>
       </c>
       <c r="AM38" t="n">
-        <v>13.80192212789614</v>
+        <v>13.80192212789607</v>
       </c>
     </row>
     <row r="39">
@@ -6179,13 +6179,13 @@
         <v>1.329980904280905</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.8700190957190956</v>
+        <v>0.8700190957190954</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.8700190957190956</v>
+        <v>0.8700190957190954</v>
       </c>
       <c r="AM41" t="n">
-        <v>39.54632253268616</v>
+        <v>39.54632253268615</v>
       </c>
     </row>
     <row r="42">
@@ -6716,16 +6716,16 @@
         <v>1</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.305137467532468</v>
+        <v>1.305137467532467</v>
       </c>
       <c r="AK45" t="n">
-        <v>-0.1451374675324677</v>
+        <v>-0.1451374675324675</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.1451374675324677</v>
+        <v>0.1451374675324675</v>
       </c>
       <c r="AM45" t="n">
-        <v>12.51185064935066</v>
+        <v>12.51185064935065</v>
       </c>
     </row>
     <row r="46">
@@ -6853,16 +6853,16 @@
         <v>1</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.305137467532468</v>
+        <v>1.305137467532467</v>
       </c>
       <c r="AK46" t="n">
-        <v>-0.5051374675324676</v>
+        <v>-0.5051374675324674</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.5051374675324676</v>
+        <v>0.5051374675324674</v>
       </c>
       <c r="AM46" t="n">
-        <v>63.14218344155844</v>
+        <v>63.14218344155842</v>
       </c>
     </row>
     <row r="47">
@@ -6986,16 +6986,16 @@
         <v>1</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.12428224867725</v>
+        <v>2.124282248677249</v>
       </c>
       <c r="AK47" t="n">
-        <v>-0.8642822486772499</v>
+        <v>-0.8642822486772495</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.8642822486772499</v>
+        <v>0.8642822486772495</v>
       </c>
       <c r="AM47" t="n">
-        <v>68.5938292600992</v>
+        <v>68.59382926009916</v>
       </c>
     </row>
     <row r="48">
@@ -7119,16 +7119,16 @@
         <v>1</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.12428224867725</v>
+        <v>2.124282248677249</v>
       </c>
       <c r="AK48" t="n">
-        <v>-0.6342822486772499</v>
+        <v>-0.6342822486772495</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.6342822486772499</v>
+        <v>0.6342822486772495</v>
       </c>
       <c r="AM48" t="n">
-        <v>42.56927843471476</v>
+        <v>42.56927843471473</v>
       </c>
     </row>
     <row r="49">
@@ -7530,16 +7530,16 @@
         <v>1</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.775440017852518</v>
+        <v>1.775440017852517</v>
       </c>
       <c r="AK51" t="n">
-        <v>-1.115440017852518</v>
+        <v>-1.115440017852517</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.115440017852518</v>
+        <v>1.115440017852517</v>
       </c>
       <c r="AM51" t="n">
-        <v>169.0060633109875</v>
+        <v>169.0060633109874</v>
       </c>
     </row>
     <row r="52">
@@ -7676,13 +7676,13 @@
         <v>21.95408591871092</v>
       </c>
       <c r="AK52" t="n">
-        <v>-0.5540859187109177</v>
+        <v>-0.5540859187109213</v>
       </c>
       <c r="AL52" t="n">
-        <v>0.5540859187109177</v>
+        <v>0.5540859187109213</v>
       </c>
       <c r="AM52" t="n">
-        <v>2.589186536032326</v>
+        <v>2.589186536032343</v>
       </c>
     </row>
     <row r="53">
@@ -8096,16 +8096,16 @@
         <v>1</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.781646646814514</v>
+        <v>1.781646646814515</v>
       </c>
       <c r="AK55" t="n">
-        <v>-0.4116466468145137</v>
+        <v>-0.4116466468145146</v>
       </c>
       <c r="AL55" t="n">
-        <v>0.4116466468145137</v>
+        <v>0.4116466468145146</v>
       </c>
       <c r="AM55" t="n">
-        <v>30.04720049740975</v>
+        <v>30.04720049740982</v>
       </c>
     </row>
     <row r="56">
@@ -8245,16 +8245,16 @@
         <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>2.652166902356903</v>
+        <v>2.652166902356904</v>
       </c>
       <c r="AK56" t="n">
-        <v>-0.2621669023569031</v>
+        <v>-0.2621669023569035</v>
       </c>
       <c r="AL56" t="n">
-        <v>0.2621669023569031</v>
+        <v>0.2621669023569035</v>
       </c>
       <c r="AM56" t="n">
-        <v>10.96932645844783</v>
+        <v>10.96932645844785</v>
       </c>
     </row>
     <row r="57">
@@ -8397,13 +8397,13 @@
         <v>1.554997757335257</v>
       </c>
       <c r="AK57" t="n">
-        <v>0.3150022426647432</v>
+        <v>0.315002242664743</v>
       </c>
       <c r="AL57" t="n">
-        <v>0.3150022426647432</v>
+        <v>0.315002242664743</v>
       </c>
       <c r="AM57" t="n">
-        <v>16.84503971469215</v>
+        <v>16.84503971469214</v>
       </c>
     </row>
     <row r="58">
@@ -8683,13 +8683,13 @@
         <v>1.176639416786918</v>
       </c>
       <c r="AK59" t="n">
-        <v>-0.5466394167869179</v>
+        <v>-0.5466394167869176</v>
       </c>
       <c r="AL59" t="n">
-        <v>0.5466394167869179</v>
+        <v>0.5466394167869176</v>
       </c>
       <c r="AM59" t="n">
-        <v>86.76816139474887</v>
+        <v>86.76816139474883</v>
       </c>
     </row>
     <row r="60">
@@ -8820,13 +8820,13 @@
         <v>1.277094708994709</v>
       </c>
       <c r="AK60" t="n">
-        <v>-0.3070947089947091</v>
+        <v>-0.3070947089947087</v>
       </c>
       <c r="AL60" t="n">
-        <v>0.3070947089947091</v>
+        <v>0.3070947089947087</v>
       </c>
       <c r="AM60" t="n">
-        <v>31.65924834997001</v>
+        <v>31.65924834996997</v>
       </c>
     </row>
     <row r="61">
@@ -8957,13 +8957,13 @@
         <v>3.871689457671957</v>
       </c>
       <c r="AK61" t="n">
-        <v>0.4583105423280434</v>
+        <v>0.4583105423280429</v>
       </c>
       <c r="AL61" t="n">
-        <v>0.4583105423280434</v>
+        <v>0.4583105423280429</v>
       </c>
       <c r="AM61" t="n">
-        <v>10.58453908378853</v>
+        <v>10.58453908378852</v>
       </c>
     </row>
     <row r="62">
@@ -9364,13 +9364,13 @@
         <v>2.085705972823475</v>
       </c>
       <c r="AK64" t="n">
-        <v>-0.7557059728234745</v>
+        <v>-0.7557059728234754</v>
       </c>
       <c r="AL64" t="n">
-        <v>0.7557059728234745</v>
+        <v>0.7557059728234754</v>
       </c>
       <c r="AM64" t="n">
-        <v>56.81999795665222</v>
+        <v>56.81999795665228</v>
       </c>
     </row>
     <row r="65">
@@ -9494,16 +9494,16 @@
         <v>1</v>
       </c>
       <c r="AJ65" t="n">
-        <v>1.780929669312169</v>
+        <v>1.780929669312168</v>
       </c>
       <c r="AK65" t="n">
-        <v>-0.3709296693121686</v>
+        <v>-0.3709296693121682</v>
       </c>
       <c r="AL65" t="n">
-        <v>0.3709296693121686</v>
+        <v>0.3709296693121682</v>
       </c>
       <c r="AM65" t="n">
-        <v>26.30706874554388</v>
+        <v>26.30706874554384</v>
       </c>
     </row>
     <row r="66">
@@ -9640,7 +9640,7 @@
         <v>1.065705972823475</v>
       </c>
       <c r="AM66" t="n">
-        <v>104.4809777277916</v>
+        <v>104.4809777277917</v>
       </c>
     </row>
     <row r="67">
@@ -9768,16 +9768,16 @@
         <v>1</v>
       </c>
       <c r="AJ67" t="n">
-        <v>1.752549600769601</v>
+        <v>1.7525496007696</v>
       </c>
       <c r="AK67" t="n">
-        <v>0.5074503992303991</v>
+        <v>0.5074503992304003</v>
       </c>
       <c r="AL67" t="n">
-        <v>0.5074503992303991</v>
+        <v>0.5074503992304003</v>
       </c>
       <c r="AM67" t="n">
-        <v>22.45355748807076</v>
+        <v>22.45355748807081</v>
       </c>
     </row>
     <row r="68">
@@ -9908,13 +9908,13 @@
         <v>2.883526487493988</v>
       </c>
       <c r="AK68" t="n">
-        <v>-0.4435264874939882</v>
+        <v>-0.4435264874939877</v>
       </c>
       <c r="AL68" t="n">
-        <v>0.4435264874939882</v>
+        <v>0.4435264874939877</v>
       </c>
       <c r="AM68" t="n">
-        <v>18.17731506122902</v>
+        <v>18.17731506122901</v>
       </c>
     </row>
     <row r="69">
@@ -10042,16 +10042,16 @@
         <v>1</v>
       </c>
       <c r="AJ69" t="n">
-        <v>1.824216465848965</v>
+        <v>1.824216465848964</v>
       </c>
       <c r="AK69" t="n">
-        <v>0.3057835341510351</v>
+        <v>0.3057835341510355</v>
       </c>
       <c r="AL69" t="n">
-        <v>0.3057835341510351</v>
+        <v>0.3057835341510355</v>
       </c>
       <c r="AM69" t="n">
-        <v>14.35603446718475</v>
+        <v>14.35603446718477</v>
       </c>
     </row>
     <row r="70">
@@ -10182,13 +10182,13 @@
         <v>1.513129493931993</v>
       </c>
       <c r="AK70" t="n">
-        <v>-0.2231294939319932</v>
+        <v>-0.223129493931993</v>
       </c>
       <c r="AL70" t="n">
-        <v>0.2231294939319932</v>
+        <v>0.223129493931993</v>
       </c>
       <c r="AM70" t="n">
-        <v>17.29685999472816</v>
+        <v>17.29685999472814</v>
       </c>
     </row>
     <row r="71">
@@ -10722,13 +10722,13 @@
         <v>2.207789051226553</v>
       </c>
       <c r="AK74" t="n">
-        <v>0.5422109487734472</v>
+        <v>0.5422109487734468</v>
       </c>
       <c r="AL74" t="n">
-        <v>0.5422109487734472</v>
+        <v>0.5422109487734468</v>
       </c>
       <c r="AM74" t="n">
-        <v>19.7167617735799</v>
+        <v>19.71676177357988</v>
       </c>
     </row>
     <row r="75">
@@ -11132,16 +11132,16 @@
         <v>1</v>
       </c>
       <c r="AJ77" t="n">
-        <v>3.888647647907649</v>
+        <v>3.888647647907648</v>
       </c>
       <c r="AK77" t="n">
-        <v>0.7613523520923517</v>
+        <v>0.7613523520923526</v>
       </c>
       <c r="AL77" t="n">
-        <v>0.7613523520923517</v>
+        <v>0.7613523520923526</v>
       </c>
       <c r="AM77" t="n">
-        <v>16.37316886220111</v>
+        <v>16.37316886220113</v>
       </c>
     </row>
     <row r="78">
@@ -11415,13 +11415,13 @@
         <v>1.767020593018093</v>
       </c>
       <c r="AK79" t="n">
-        <v>0.3829794069819066</v>
+        <v>0.382979406981907</v>
       </c>
       <c r="AL79" t="n">
-        <v>0.3829794069819066</v>
+        <v>0.382979406981907</v>
       </c>
       <c r="AM79" t="n">
-        <v>17.81299567357705</v>
+        <v>17.81299567357707</v>
       </c>
     </row>
     <row r="80">
@@ -11549,16 +11549,16 @@
         <v>1</v>
       </c>
       <c r="AJ80" t="n">
-        <v>3.888647647907649</v>
+        <v>3.888647647907648</v>
       </c>
       <c r="AK80" t="n">
-        <v>0.3613523520923514</v>
+        <v>0.3613523520923523</v>
       </c>
       <c r="AL80" t="n">
-        <v>0.3613523520923514</v>
+        <v>0.3613523520923523</v>
       </c>
       <c r="AM80" t="n">
-        <v>8.502408284525915</v>
+        <v>8.502408284525936</v>
       </c>
     </row>
     <row r="81">
@@ -11826,13 +11826,13 @@
         <v>2.295999981962481</v>
       </c>
       <c r="AK82" t="n">
-        <v>-0.04599998196248123</v>
+        <v>-0.04599998196248078</v>
       </c>
       <c r="AL82" t="n">
-        <v>0.04599998196248123</v>
+        <v>0.04599998196248078</v>
       </c>
       <c r="AM82" t="n">
-        <v>2.044443642776943</v>
+        <v>2.044443642776923</v>
       </c>
     </row>
     <row r="83">
@@ -12106,7 +12106,7 @@
         <v>1.014595998075998</v>
       </c>
       <c r="AM84" t="n">
-        <v>40.58383992303994</v>
+        <v>40.58383992303992</v>
       </c>
     </row>
     <row r="85">
@@ -12377,16 +12377,16 @@
         <v>1</v>
       </c>
       <c r="AJ86" t="n">
-        <v>3.888647647907649</v>
+        <v>3.888647647907648</v>
       </c>
       <c r="AK86" t="n">
-        <v>0.1013523520923516</v>
+        <v>0.1013523520923525</v>
       </c>
       <c r="AL86" t="n">
-        <v>0.1013523520923516</v>
+        <v>0.1013523520923525</v>
       </c>
       <c r="AM86" t="n">
-        <v>2.540159200309564</v>
+        <v>2.540159200309586</v>
       </c>
     </row>
     <row r="87">
@@ -12517,13 +12517,13 @@
         <v>1.625353968253968</v>
       </c>
       <c r="AK87" t="n">
-        <v>-0.5253539682539676</v>
+        <v>-0.5253539682539681</v>
       </c>
       <c r="AL87" t="n">
-        <v>0.5253539682539676</v>
+        <v>0.5253539682539681</v>
       </c>
       <c r="AM87" t="n">
-        <v>47.7594516594516</v>
+        <v>47.75945165945164</v>
       </c>
     </row>
     <row r="88">
@@ -12654,13 +12654,13 @@
         <v>1.062992685185185</v>
       </c>
       <c r="AK88" t="n">
-        <v>-0.1329926851851854</v>
+        <v>-0.1329926851851851</v>
       </c>
       <c r="AL88" t="n">
-        <v>0.1329926851851854</v>
+        <v>0.1329926851851851</v>
       </c>
       <c r="AM88" t="n">
-        <v>14.30028872958983</v>
+        <v>14.3002887295898</v>
       </c>
     </row>
     <row r="89">
@@ -12788,13 +12788,13 @@
         <v>1</v>
       </c>
       <c r="AJ89" t="n">
-        <v>1.824216465848965</v>
+        <v>1.824216465848964</v>
       </c>
       <c r="AK89" t="n">
-        <v>-1.094216465848965</v>
+        <v>-1.094216465848964</v>
       </c>
       <c r="AL89" t="n">
-        <v>1.094216465848965</v>
+        <v>1.094216465848964</v>
       </c>
       <c r="AM89" t="n">
         <v>149.8926665546527</v>
@@ -13339,13 +13339,13 @@
         <v>2.208112014189516</v>
       </c>
       <c r="AK93" t="n">
-        <v>0.3918879858104845</v>
+        <v>0.391887985810484</v>
       </c>
       <c r="AL93" t="n">
-        <v>0.3918879858104845</v>
+        <v>0.391887985810484</v>
       </c>
       <c r="AM93" t="n">
-        <v>15.07261483886479</v>
+        <v>15.07261483886477</v>
       </c>
     </row>
     <row r="94">
@@ -13473,16 +13473,16 @@
         <v>1</v>
       </c>
       <c r="AJ94" t="n">
-        <v>1.716928452380951</v>
+        <v>1.716928452380952</v>
       </c>
       <c r="AK94" t="n">
-        <v>0.05307154761904864</v>
+        <v>0.0530715476190482</v>
       </c>
       <c r="AL94" t="n">
-        <v>0.05307154761904864</v>
+        <v>0.0530715476190482</v>
       </c>
       <c r="AM94" t="n">
-        <v>2.998392520850206</v>
+        <v>2.998392520850181</v>
       </c>
     </row>
     <row r="95">
@@ -13893,7 +13893,7 @@
         <v>2.744986084656089</v>
       </c>
       <c r="AM97" t="n">
-        <v>41.40250504760315</v>
+        <v>41.40250504760316</v>
       </c>
     </row>
     <row r="98">
@@ -14021,16 +14021,16 @@
         <v>1</v>
       </c>
       <c r="AJ98" t="n">
-        <v>1.083956402116402</v>
+        <v>1.083956402116403</v>
       </c>
       <c r="AK98" t="n">
-        <v>-0.01395640211640226</v>
+        <v>-0.01395640211640248</v>
       </c>
       <c r="AL98" t="n">
-        <v>0.01395640211640226</v>
+        <v>0.01395640211640248</v>
       </c>
       <c r="AM98" t="n">
-        <v>1.304336646392734</v>
+        <v>1.304336646392755</v>
       </c>
     </row>
     <row r="99">
@@ -14161,13 +14161,13 @@
         <v>1.54970369047619</v>
       </c>
       <c r="AK99" t="n">
-        <v>0.03029630952380979</v>
+        <v>0.03029630952381002</v>
       </c>
       <c r="AL99" t="n">
-        <v>0.03029630952380979</v>
+        <v>0.03029630952381002</v>
       </c>
       <c r="AM99" t="n">
-        <v>1.917487944544924</v>
+        <v>1.917487944544938</v>
       </c>
     </row>
     <row r="100">
@@ -14304,7 +14304,7 @@
         <v>2.220080687830686</v>
       </c>
       <c r="AM100" t="n">
-        <v>44.13679299862198</v>
+        <v>44.13679299862199</v>
       </c>
     </row>
     <row r="101">
@@ -14432,16 +14432,16 @@
         <v>1</v>
       </c>
       <c r="AJ101" t="n">
-        <v>3.750534656084656</v>
+        <v>3.750534656084655</v>
       </c>
       <c r="AK101" t="n">
-        <v>0.7294653439153449</v>
+        <v>0.7294653439153458</v>
       </c>
       <c r="AL101" t="n">
-        <v>0.7294653439153449</v>
+        <v>0.7294653439153458</v>
       </c>
       <c r="AM101" t="n">
-        <v>16.28270856953895</v>
+        <v>16.28270856953897</v>
       </c>
     </row>
     <row r="102">
@@ -14569,16 +14569,16 @@
         <v>1</v>
       </c>
       <c r="AJ102" t="n">
-        <v>3.787072552910052</v>
+        <v>3.787072552910053</v>
       </c>
       <c r="AK102" t="n">
-        <v>0.5629274470899475</v>
+        <v>0.5629274470899466</v>
       </c>
       <c r="AL102" t="n">
-        <v>0.5629274470899475</v>
+        <v>0.5629274470899466</v>
       </c>
       <c r="AM102" t="n">
-        <v>12.94086085264247</v>
+        <v>12.94086085264245</v>
       </c>
     </row>
     <row r="103">
@@ -14983,13 +14983,13 @@
         <v>1.513129493931993</v>
       </c>
       <c r="AK105" t="n">
-        <v>-0.2631294939319933</v>
+        <v>-0.263129493931993</v>
       </c>
       <c r="AL105" t="n">
-        <v>0.2631294939319933</v>
+        <v>0.263129493931993</v>
       </c>
       <c r="AM105" t="n">
-        <v>21.05035951455946</v>
+        <v>21.05035951455944</v>
       </c>
     </row>
     <row r="106">
@@ -15120,13 +15120,13 @@
         <v>1.625353968253968</v>
       </c>
       <c r="AK106" t="n">
-        <v>-0.9753539682539677</v>
+        <v>-0.9753539682539681</v>
       </c>
       <c r="AL106" t="n">
-        <v>0.9753539682539677</v>
+        <v>0.9753539682539681</v>
       </c>
       <c r="AM106" t="n">
-        <v>150.0544566544565</v>
+        <v>150.0544566544566</v>
       </c>
     </row>
     <row r="107">
@@ -15406,13 +15406,13 @@
         <v>2.341904846079846</v>
       </c>
       <c r="AK108" t="n">
-        <v>-0.4719048460798456</v>
+        <v>-0.4719048460798461</v>
       </c>
       <c r="AL108" t="n">
-        <v>0.4719048460798456</v>
+        <v>0.4719048460798461</v>
       </c>
       <c r="AM108" t="n">
-        <v>25.2355532663019</v>
+        <v>25.23555326630192</v>
       </c>
     </row>
     <row r="109">
@@ -15540,16 +15540,16 @@
         <v>1</v>
       </c>
       <c r="AJ109" t="n">
-        <v>3.888647647907649</v>
+        <v>3.888647647907648</v>
       </c>
       <c r="AK109" t="n">
-        <v>0.211352352092351</v>
+        <v>0.2113523520923519</v>
       </c>
       <c r="AL109" t="n">
-        <v>0.211352352092351</v>
+        <v>0.2113523520923519</v>
       </c>
       <c r="AM109" t="n">
-        <v>5.154935416886611</v>
+        <v>5.154935416886633</v>
       </c>
     </row>
     <row r="110">
@@ -15826,16 +15826,16 @@
         <v>0</v>
       </c>
       <c r="AJ111" t="n">
-        <v>1.751355132275132</v>
+        <v>1.751355132275133</v>
       </c>
       <c r="AK111" t="n">
-        <v>-0.4213551322751319</v>
+        <v>-0.4213551322751325</v>
       </c>
       <c r="AL111" t="n">
-        <v>0.4213551322751319</v>
+        <v>0.4213551322751325</v>
       </c>
       <c r="AM111" t="n">
-        <v>31.68083701316781</v>
+        <v>31.68083701316786</v>
       </c>
     </row>
     <row r="112">
@@ -16252,13 +16252,13 @@
         <v>2.297098793891295</v>
       </c>
       <c r="AK114" t="n">
-        <v>0.1429012061087049</v>
+        <v>0.1429012061087045</v>
       </c>
       <c r="AL114" t="n">
-        <v>0.1429012061087049</v>
+        <v>0.1429012061087045</v>
       </c>
       <c r="AM114" t="n">
-        <v>5.856606807733809</v>
+        <v>5.85660680773379</v>
       </c>
     </row>
     <row r="115">
@@ -16663,13 +16663,13 @@
         <v>3.885013915343911</v>
       </c>
       <c r="AK117" t="n">
-        <v>-0.8950139153439109</v>
+        <v>-0.8950139153439105</v>
       </c>
       <c r="AL117" t="n">
-        <v>0.8950139153439109</v>
+        <v>0.8950139153439105</v>
       </c>
       <c r="AM117" t="n">
-        <v>29.9335757640104</v>
+        <v>29.93357576401039</v>
       </c>
     </row>
     <row r="118">
@@ -16797,16 +16797,16 @@
         <v>1</v>
       </c>
       <c r="AJ118" t="n">
-        <v>3.877080449735449</v>
+        <v>3.87708044973545</v>
       </c>
       <c r="AK118" t="n">
-        <v>0.2029195502645509</v>
+        <v>0.20291955026455</v>
       </c>
       <c r="AL118" t="n">
-        <v>0.2029195502645509</v>
+        <v>0.20291955026455</v>
       </c>
       <c r="AM118" t="n">
-        <v>4.973518388837031</v>
+        <v>4.973518388837009</v>
       </c>
     </row>
     <row r="119">
@@ -16934,16 +16934,16 @@
         <v>1</v>
       </c>
       <c r="AJ119" t="n">
-        <v>2.476247015392015</v>
+        <v>2.476247015392014</v>
       </c>
       <c r="AK119" t="n">
-        <v>-0.09624701539201519</v>
+        <v>-0.0962470153920143</v>
       </c>
       <c r="AL119" t="n">
-        <v>0.09624701539201519</v>
+        <v>0.0962470153920143</v>
       </c>
       <c r="AM119" t="n">
-        <v>4.043992243361983</v>
+        <v>4.043992243361946</v>
       </c>
     </row>
     <row r="120">
@@ -17351,16 +17351,16 @@
         <v>0</v>
       </c>
       <c r="AJ122" t="n">
-        <v>9.093005812890807</v>
+        <v>9.093005812890805</v>
       </c>
       <c r="AK122" t="n">
-        <v>0.3869941871091935</v>
+        <v>0.3869941871091953</v>
       </c>
       <c r="AL122" t="n">
-        <v>0.3869941871091935</v>
+        <v>0.3869941871091953</v>
       </c>
       <c r="AM122" t="n">
-        <v>4.082217163599087</v>
+        <v>4.082217163599107</v>
       </c>
     </row>
     <row r="123">
@@ -17497,7 +17497,7 @@
         <v>1.013948785473787</v>
       </c>
       <c r="AM123" t="n">
-        <v>187.7682936062567</v>
+        <v>187.7682936062568</v>
       </c>
     </row>
     <row r="124">
@@ -17774,16 +17774,16 @@
         <v>0</v>
       </c>
       <c r="AJ125" t="n">
-        <v>7.055484298941801</v>
+        <v>7.055484298941805</v>
       </c>
       <c r="AK125" t="n">
-        <v>0.4245157010581995</v>
+        <v>0.4245157010581959</v>
       </c>
       <c r="AL125" t="n">
-        <v>0.4245157010581995</v>
+        <v>0.4245157010581959</v>
       </c>
       <c r="AM125" t="n">
-        <v>5.675343597034752</v>
+        <v>5.675343597034704</v>
       </c>
     </row>
     <row r="126">
@@ -18063,13 +18063,13 @@
         <v>12.50060474987974</v>
       </c>
       <c r="AK127" t="n">
-        <v>-1.200604749879737</v>
+        <v>-1.200604749879739</v>
       </c>
       <c r="AL127" t="n">
-        <v>1.200604749879737</v>
+        <v>1.200604749879739</v>
       </c>
       <c r="AM127" t="n">
-        <v>10.6248207953959</v>
+        <v>10.62482079539592</v>
       </c>
     </row>
     <row r="128">
@@ -18212,13 +18212,13 @@
         <v>2.629777041847041</v>
       </c>
       <c r="AK128" t="n">
-        <v>0.3702229581529592</v>
+        <v>0.3702229581529588</v>
       </c>
       <c r="AL128" t="n">
-        <v>0.3702229581529592</v>
+        <v>0.3702229581529588</v>
       </c>
       <c r="AM128" t="n">
-        <v>12.34076527176531</v>
+        <v>12.34076527176529</v>
       </c>
     </row>
     <row r="129">
@@ -18498,13 +18498,13 @@
         <v>1.811892325637327</v>
       </c>
       <c r="AK130" t="n">
-        <v>0.08810767436267253</v>
+        <v>0.08810767436267297</v>
       </c>
       <c r="AL130" t="n">
-        <v>0.08810767436267253</v>
+        <v>0.08810767436267297</v>
       </c>
       <c r="AM130" t="n">
-        <v>4.637246019088028</v>
+        <v>4.637246019088051</v>
       </c>
     </row>
     <row r="131">
@@ -18778,7 +18778,7 @@
         <v>1.424646031746032</v>
       </c>
       <c r="AM132" t="n">
-        <v>46.7097059588863</v>
+        <v>46.70970595888629</v>
       </c>
     </row>
     <row r="133">
@@ -19052,13 +19052,13 @@
         <v>15.72545809644059</v>
       </c>
       <c r="AK134" t="n">
-        <v>-1.425458096440593</v>
+        <v>-1.425458096440591</v>
       </c>
       <c r="AL134" t="n">
-        <v>1.425458096440593</v>
+        <v>1.425458096440591</v>
       </c>
       <c r="AM134" t="n">
-        <v>9.968238436647505</v>
+        <v>9.968238436647493</v>
       </c>
     </row>
     <row r="135">
@@ -19323,16 +19323,16 @@
         <v>1</v>
       </c>
       <c r="AJ136" t="n">
-        <v>3.641903664021164</v>
+        <v>3.641903664021162</v>
       </c>
       <c r="AK136" t="n">
-        <v>-0.8819036640211642</v>
+        <v>-0.8819036640211624</v>
       </c>
       <c r="AL136" t="n">
-        <v>0.8819036640211642</v>
+        <v>0.8819036640211624</v>
       </c>
       <c r="AM136" t="n">
-        <v>31.95303130511465</v>
+        <v>31.95303130511458</v>
       </c>
     </row>
     <row r="137">
@@ -19606,13 +19606,13 @@
         <v>2.085705972823475</v>
       </c>
       <c r="AK138" t="n">
-        <v>0.7742940271765253</v>
+        <v>0.7742940271765244</v>
       </c>
       <c r="AL138" t="n">
-        <v>0.7742940271765253</v>
+        <v>0.7742940271765244</v>
       </c>
       <c r="AM138" t="n">
-        <v>27.07321773344494</v>
+        <v>27.07321773344491</v>
       </c>
     </row>
     <row r="139">
@@ -19755,13 +19755,13 @@
         <v>2.362494923039923</v>
       </c>
       <c r="AK139" t="n">
-        <v>-0.1224949230399233</v>
+        <v>-0.1224949230399228</v>
       </c>
       <c r="AL139" t="n">
-        <v>0.1224949230399233</v>
+        <v>0.1224949230399228</v>
       </c>
       <c r="AM139" t="n">
-        <v>5.468523349996573</v>
+        <v>5.468523349996554</v>
       </c>
     </row>
     <row r="140">
@@ -19904,13 +19904,13 @@
         <v>2.629777041847041</v>
       </c>
       <c r="AK140" t="n">
-        <v>-0.3497770418470409</v>
+        <v>-0.3497770418470414</v>
       </c>
       <c r="AL140" t="n">
-        <v>0.3497770418470409</v>
+        <v>0.3497770418470414</v>
       </c>
       <c r="AM140" t="n">
-        <v>15.34109832662461</v>
+        <v>15.34109832662462</v>
       </c>
     </row>
     <row r="141">
@@ -20053,13 +20053,13 @@
         <v>2.629777041847041</v>
       </c>
       <c r="AK141" t="n">
-        <v>0.9602229581529591</v>
+        <v>0.9602229581529587</v>
       </c>
       <c r="AL141" t="n">
-        <v>0.9602229581529591</v>
+        <v>0.9602229581529587</v>
       </c>
       <c r="AM141" t="n">
-        <v>26.74715760871753</v>
+        <v>26.74715760871752</v>
       </c>
     </row>
     <row r="142">
@@ -20610,16 +20610,16 @@
         <v>0</v>
       </c>
       <c r="AJ145" t="n">
-        <v>1.583004741462242</v>
+        <v>1.583004741462241</v>
       </c>
       <c r="AK145" t="n">
-        <v>0.06699525853775801</v>
+        <v>0.06699525853775845</v>
       </c>
       <c r="AL145" t="n">
-        <v>0.06699525853775801</v>
+        <v>0.06699525853775845</v>
       </c>
       <c r="AM145" t="n">
-        <v>4.060318699258062</v>
+        <v>4.060318699258088</v>
       </c>
     </row>
     <row r="146">
@@ -20887,13 +20887,13 @@
         <v>4.69954681697932</v>
       </c>
       <c r="AK147" t="n">
-        <v>-0.5695468169793205</v>
+        <v>-0.5695468169793196</v>
       </c>
       <c r="AL147" t="n">
-        <v>0.5695468169793205</v>
+        <v>0.5695468169793196</v>
       </c>
       <c r="AM147" t="n">
-        <v>13.79047983000776</v>
+        <v>13.79047983000774</v>
       </c>
     </row>
     <row r="148">
@@ -21021,16 +21021,16 @@
         <v>1</v>
       </c>
       <c r="AJ148" t="n">
-        <v>2.032281642616644</v>
+        <v>2.032281642616643</v>
       </c>
       <c r="AK148" t="n">
-        <v>-0.9922816426166436</v>
+        <v>-0.9922816426166432</v>
       </c>
       <c r="AL148" t="n">
-        <v>0.9922816426166436</v>
+        <v>0.9922816426166432</v>
       </c>
       <c r="AM148" t="n">
-        <v>95.41169640544651</v>
+        <v>95.41169640544645</v>
       </c>
     </row>
     <row r="149">
@@ -21298,13 +21298,13 @@
         <v>3.450294206349207</v>
       </c>
       <c r="AK150" t="n">
-        <v>-0.5502942063492067</v>
+        <v>-0.5502942063492076</v>
       </c>
       <c r="AL150" t="n">
-        <v>0.5502942063492067</v>
+        <v>0.5502942063492076</v>
       </c>
       <c r="AM150" t="n">
-        <v>18.97566228790368</v>
+        <v>18.97566228790371</v>
       </c>
     </row>
     <row r="151">
@@ -21715,13 +21715,13 @@
         <v>1.514634576719576</v>
       </c>
       <c r="AK153" t="n">
-        <v>-0.2546345767195757</v>
+        <v>-0.2546345767195759</v>
       </c>
       <c r="AL153" t="n">
-        <v>0.2546345767195757</v>
+        <v>0.2546345767195759</v>
       </c>
       <c r="AM153" t="n">
-        <v>20.20909339044251</v>
+        <v>20.20909339044253</v>
       </c>
     </row>
     <row r="154">
@@ -21858,13 +21858,13 @@
         <v>19.13667849927849</v>
       </c>
       <c r="AK154" t="n">
-        <v>1.263321500721506</v>
+        <v>1.26332150072151</v>
       </c>
       <c r="AL154" t="n">
-        <v>1.263321500721506</v>
+        <v>1.26332150072151</v>
       </c>
       <c r="AM154" t="n">
-        <v>6.192752454517189</v>
+        <v>6.192752454517206</v>
       </c>
     </row>
     <row r="155">
@@ -21992,16 +21992,16 @@
         <v>1</v>
       </c>
       <c r="AJ155" t="n">
-        <v>1.8359732007807</v>
+        <v>1.835973200780701</v>
       </c>
       <c r="AK155" t="n">
-        <v>-0.3759732007807002</v>
+        <v>-0.3759732007807008</v>
       </c>
       <c r="AL155" t="n">
-        <v>0.3759732007807002</v>
+        <v>0.3759732007807008</v>
       </c>
       <c r="AM155" t="n">
-        <v>25.75158909456851</v>
+        <v>25.75158909456855</v>
       </c>
     </row>
     <row r="156">
@@ -22412,13 +22412,13 @@
         <v>19.13667849927849</v>
       </c>
       <c r="AK158" t="n">
-        <v>-1.236678499278494</v>
+        <v>-1.23667849927849</v>
       </c>
       <c r="AL158" t="n">
-        <v>1.236678499278494</v>
+        <v>1.23667849927849</v>
       </c>
       <c r="AM158" t="n">
-        <v>6.908818431723429</v>
+        <v>6.908818431723408</v>
       </c>
     </row>
     <row r="159">
@@ -22546,16 +22546,16 @@
         <v>1</v>
       </c>
       <c r="AJ159" t="n">
-        <v>3.44722753968254</v>
+        <v>3.447227539682541</v>
       </c>
       <c r="AK159" t="n">
-        <v>0.01277246031746015</v>
+        <v>0.01277246031745927</v>
       </c>
       <c r="AL159" t="n">
-        <v>0.01277246031746015</v>
+        <v>0.01277246031745927</v>
       </c>
       <c r="AM159" t="n">
-        <v>0.3691462519497155</v>
+        <v>0.3691462519496898</v>
       </c>
     </row>
     <row r="160">
@@ -22683,16 +22683,16 @@
         <v>1</v>
       </c>
       <c r="AJ160" t="n">
-        <v>1.738686216504085</v>
+        <v>1.738686216504084</v>
       </c>
       <c r="AK160" t="n">
-        <v>-0.6486862165040845</v>
+        <v>-0.6486862165040841</v>
       </c>
       <c r="AL160" t="n">
-        <v>0.6486862165040845</v>
+        <v>0.6486862165040841</v>
       </c>
       <c r="AM160" t="n">
-        <v>59.51249692698023</v>
+        <v>59.51249692698018</v>
       </c>
     </row>
     <row r="161">
@@ -22820,16 +22820,16 @@
         <v>1</v>
       </c>
       <c r="AJ161" t="n">
-        <v>1.95593419071669</v>
+        <v>1.955934190716691</v>
       </c>
       <c r="AK161" t="n">
-        <v>0.03406580928330971</v>
+        <v>0.03406580928330949</v>
       </c>
       <c r="AL161" t="n">
-        <v>0.03406580928330971</v>
+        <v>0.03406580928330949</v>
       </c>
       <c r="AM161" t="n">
-        <v>1.711849712729131</v>
+        <v>1.71184971272912</v>
       </c>
     </row>
     <row r="162">
@@ -23094,16 +23094,16 @@
         <v>1</v>
       </c>
       <c r="AJ163" t="n">
-        <v>1.971947158489659</v>
+        <v>1.971947158489658</v>
       </c>
       <c r="AK163" t="n">
-        <v>-0.151947158489659</v>
+        <v>-0.1519471584896583</v>
       </c>
       <c r="AL163" t="n">
-        <v>0.151947158489659</v>
+        <v>0.1519471584896583</v>
       </c>
       <c r="AM163" t="n">
-        <v>8.348744971959286</v>
+        <v>8.348744971959249</v>
       </c>
     </row>
     <row r="164">
@@ -23231,16 +23231,16 @@
         <v>1</v>
       </c>
       <c r="AJ164" t="n">
-        <v>1.971947158489659</v>
+        <v>1.971947158489658</v>
       </c>
       <c r="AK164" t="n">
-        <v>-0.2019471584896591</v>
+        <v>-0.2019471584896584</v>
       </c>
       <c r="AL164" t="n">
-        <v>0.2019471584896591</v>
+        <v>0.2019471584896584</v>
       </c>
       <c r="AM164" t="n">
-        <v>11.40944398246661</v>
+        <v>11.40944398246658</v>
       </c>
     </row>
     <row r="165">
@@ -24056,13 +24056,13 @@
         <v>1.732201150793649</v>
       </c>
       <c r="AK170" t="n">
-        <v>0.1477988492063509</v>
+        <v>0.1477988492063513</v>
       </c>
       <c r="AL170" t="n">
-        <v>0.1477988492063509</v>
+        <v>0.1477988492063513</v>
       </c>
       <c r="AM170" t="n">
-        <v>7.861640915231431</v>
+        <v>7.861640915231455</v>
       </c>
     </row>
     <row r="171">
@@ -24190,16 +24190,16 @@
         <v>1</v>
       </c>
       <c r="AJ171" t="n">
-        <v>4.402286764069265</v>
+        <v>4.402286764069266</v>
       </c>
       <c r="AK171" t="n">
-        <v>-0.1122867640692649</v>
+        <v>-0.1122867640692657</v>
       </c>
       <c r="AL171" t="n">
-        <v>0.1122867640692649</v>
+        <v>0.1122867640692657</v>
       </c>
       <c r="AM171" t="n">
-        <v>2.617407087861652</v>
+        <v>2.617407087861672</v>
       </c>
     </row>
     <row r="172">
@@ -24473,7 +24473,7 @@
         <v>2.057030981240978</v>
       </c>
       <c r="AM173" t="n">
-        <v>35.77445184766918</v>
+        <v>35.77445184766919</v>
       </c>
     </row>
     <row r="174">
@@ -24747,7 +24747,7 @@
         <v>2.632969018759022</v>
       </c>
       <c r="AM175" t="n">
-        <v>248.3933036565115</v>
+        <v>248.3933036565114</v>
       </c>
     </row>
     <row r="176">
@@ -25156,13 +25156,13 @@
         <v>1.705998516483517</v>
       </c>
       <c r="AK178" t="n">
-        <v>-0.7359985164835166</v>
+        <v>-0.735998516483517</v>
       </c>
       <c r="AL178" t="n">
-        <v>0.7359985164835166</v>
+        <v>0.735998516483517</v>
       </c>
       <c r="AM178" t="n">
-        <v>75.87613571995017</v>
+        <v>75.87613571995021</v>
       </c>
     </row>
     <row r="179">
@@ -25427,16 +25427,16 @@
         <v>1</v>
       </c>
       <c r="AJ180" t="n">
-        <v>1.678199214489214</v>
+        <v>1.678199214489215</v>
       </c>
       <c r="AK180" t="n">
-        <v>-0.2181992144892144</v>
+        <v>-0.2181992144892149</v>
       </c>
       <c r="AL180" t="n">
-        <v>0.2181992144892144</v>
+        <v>0.2181992144892149</v>
       </c>
       <c r="AM180" t="n">
-        <v>14.94515167734346</v>
+        <v>14.94515167734349</v>
       </c>
     </row>
     <row r="181">
@@ -25838,16 +25838,16 @@
         <v>1</v>
       </c>
       <c r="AJ183" t="n">
-        <v>2.267791860084361</v>
+        <v>2.26779186008436</v>
       </c>
       <c r="AK183" t="n">
-        <v>-0.3177918600843606</v>
+        <v>-0.3177918600843601</v>
       </c>
       <c r="AL183" t="n">
-        <v>0.3177918600843606</v>
+        <v>0.3177918600843601</v>
       </c>
       <c r="AM183" t="n">
-        <v>16.29701846586464</v>
+        <v>16.29701846586462</v>
       </c>
     </row>
     <row r="184">
@@ -25984,13 +25984,13 @@
         <v>20.75166097883599</v>
       </c>
       <c r="AK184" t="n">
-        <v>-1.551660978835994</v>
+        <v>-1.55166097883599</v>
       </c>
       <c r="AL184" t="n">
-        <v>1.551660978835994</v>
+        <v>1.55166097883599</v>
       </c>
       <c r="AM184" t="n">
-        <v>8.081567598104133</v>
+        <v>8.081567598104115</v>
       </c>
     </row>
     <row r="185">
@@ -26118,16 +26118,16 @@
         <v>1</v>
       </c>
       <c r="AJ185" t="n">
-        <v>4.268847777777779</v>
+        <v>4.268847777777781</v>
       </c>
       <c r="AK185" t="n">
-        <v>-1.998847777777779</v>
+        <v>-1.998847777777781</v>
       </c>
       <c r="AL185" t="n">
-        <v>1.998847777777779</v>
+        <v>1.998847777777781</v>
       </c>
       <c r="AM185" t="n">
-        <v>88.05496818404313</v>
+        <v>88.05496818404322</v>
       </c>
     </row>
     <row r="186">
@@ -26264,13 +26264,13 @@
         <v>1.443320615680615</v>
       </c>
       <c r="AK186" t="n">
-        <v>-0.2033206156806149</v>
+        <v>-0.2033206156806151</v>
       </c>
       <c r="AL186" t="n">
-        <v>0.2033206156806149</v>
+        <v>0.2033206156806151</v>
       </c>
       <c r="AM186" t="n">
-        <v>16.39682384521088</v>
+        <v>16.3968238452109</v>
       </c>
     </row>
     <row r="187">
@@ -26547,16 +26547,16 @@
         <v>0</v>
       </c>
       <c r="AJ188" t="n">
-        <v>8.209556750934253</v>
+        <v>8.209556750934251</v>
       </c>
       <c r="AK188" t="n">
-        <v>-0.4995567509342527</v>
+        <v>-0.4995567509342509</v>
       </c>
       <c r="AL188" t="n">
-        <v>0.4995567509342527</v>
+        <v>0.4995567509342509</v>
       </c>
       <c r="AM188" t="n">
-        <v>6.47933529097604</v>
+        <v>6.479335290976016</v>
       </c>
     </row>
     <row r="189">
@@ -26687,13 +26687,13 @@
         <v>1.025140964405964</v>
       </c>
       <c r="AK189" t="n">
-        <v>0.2348590355940359</v>
+        <v>0.2348590355940356</v>
       </c>
       <c r="AL189" t="n">
-        <v>0.2348590355940359</v>
+        <v>0.2348590355940356</v>
       </c>
       <c r="AM189" t="n">
-        <v>18.63960599952666</v>
+        <v>18.63960599952664</v>
       </c>
     </row>
     <row r="190">
@@ -26830,13 +26830,13 @@
         <v>19.46546778499278</v>
       </c>
       <c r="AK190" t="n">
-        <v>0.3345322150072221</v>
+        <v>0.3345322150072256</v>
       </c>
       <c r="AL190" t="n">
-        <v>0.3345322150072221</v>
+        <v>0.3345322150072256</v>
       </c>
       <c r="AM190" t="n">
-        <v>1.689556641450617</v>
+        <v>1.689556641450634</v>
       </c>
     </row>
     <row r="191">
@@ -26967,13 +26967,13 @@
         <v>1.728501367382618</v>
       </c>
       <c r="AK191" t="n">
-        <v>-0.2185013673826177</v>
+        <v>-0.2185013673826179</v>
       </c>
       <c r="AL191" t="n">
-        <v>0.2185013673826177</v>
+        <v>0.2185013673826179</v>
       </c>
       <c r="AM191" t="n">
-        <v>14.47028923063693</v>
+        <v>14.47028923063695</v>
       </c>
     </row>
     <row r="192">
@@ -27521,13 +27521,13 @@
         <v>1.577930933140932</v>
       </c>
       <c r="AK195" t="n">
-        <v>-0.3179309331409321</v>
+        <v>-0.3179309331409323</v>
       </c>
       <c r="AL195" t="n">
-        <v>0.3179309331409321</v>
+        <v>0.3179309331409323</v>
       </c>
       <c r="AM195" t="n">
-        <v>25.23261374134382</v>
+        <v>25.23261374134383</v>
       </c>
     </row>
     <row r="196">
@@ -27658,10 +27658,10 @@
         <v>1.025140964405964</v>
       </c>
       <c r="AK196" t="n">
-        <v>-0.5751409644059642</v>
+        <v>-0.5751409644059644</v>
       </c>
       <c r="AL196" t="n">
-        <v>0.5751409644059642</v>
+        <v>0.5751409644059644</v>
       </c>
       <c r="AM196" t="n">
         <v>127.8091032013254</v>
@@ -28636,16 +28636,16 @@
         <v>0</v>
       </c>
       <c r="AJ203" t="n">
-        <v>2.064314724627224</v>
+        <v>2.064314724627225</v>
       </c>
       <c r="AK203" t="n">
-        <v>-0.01431472462722461</v>
+        <v>-0.01431472462722505</v>
       </c>
       <c r="AL203" t="n">
-        <v>0.01431472462722461</v>
+        <v>0.01431472462722505</v>
       </c>
       <c r="AM203" t="n">
-        <v>0.6982792501085175</v>
+        <v>0.6982792501085391</v>
       </c>
     </row>
     <row r="204">
@@ -29053,16 +29053,16 @@
         <v>0</v>
       </c>
       <c r="AJ206" t="n">
-        <v>15.81384231601731</v>
+        <v>15.8138423160173</v>
       </c>
       <c r="AK206" t="n">
-        <v>4.586157683982687</v>
+        <v>4.586157683982695</v>
       </c>
       <c r="AL206" t="n">
-        <v>4.586157683982687</v>
+        <v>4.586157683982695</v>
       </c>
       <c r="AM206" t="n">
-        <v>22.48116511756219</v>
+        <v>22.48116511756223</v>
       </c>
     </row>
     <row r="207">
@@ -29607,16 +29607,16 @@
         <v>1</v>
       </c>
       <c r="AJ210" t="n">
-        <v>1.95593419071669</v>
+        <v>1.955934190716691</v>
       </c>
       <c r="AK210" t="n">
-        <v>0.1440658092833098</v>
+        <v>0.1440658092833096</v>
       </c>
       <c r="AL210" t="n">
-        <v>0.1440658092833098</v>
+        <v>0.1440658092833096</v>
       </c>
       <c r="AM210" t="n">
-        <v>6.860276632538562</v>
+        <v>6.860276632538552</v>
       </c>
     </row>
     <row r="211">
@@ -29744,16 +29744,16 @@
         <v>1</v>
       </c>
       <c r="AJ211" t="n">
-        <v>1.774524227994229</v>
+        <v>1.774524227994228</v>
       </c>
       <c r="AK211" t="n">
-        <v>-0.3445242279942291</v>
+        <v>-0.3445242279942284</v>
       </c>
       <c r="AL211" t="n">
-        <v>0.3445242279942291</v>
+        <v>0.3445242279942284</v>
       </c>
       <c r="AM211" t="n">
-        <v>24.0926033562398</v>
+        <v>24.09260335623975</v>
       </c>
     </row>
     <row r="212">
@@ -30158,13 +30158,13 @@
         <v>1.705998516483517</v>
       </c>
       <c r="AK214" t="n">
-        <v>0.4440014835164834</v>
+        <v>0.4440014835164829</v>
       </c>
       <c r="AL214" t="n">
-        <v>0.4440014835164834</v>
+        <v>0.4440014835164829</v>
       </c>
       <c r="AM214" t="n">
-        <v>20.65123179146434</v>
+        <v>20.65123179146433</v>
       </c>
     </row>
     <row r="215">
@@ -30292,16 +30292,16 @@
         <v>1</v>
       </c>
       <c r="AJ215" t="n">
-        <v>2.122415334295333</v>
+        <v>2.122415334295334</v>
       </c>
       <c r="AK215" t="n">
-        <v>0.4375846657046667</v>
+        <v>0.4375846657046663</v>
       </c>
       <c r="AL215" t="n">
-        <v>0.4375846657046667</v>
+        <v>0.4375846657046663</v>
       </c>
       <c r="AM215" t="n">
-        <v>17.09315100408854</v>
+        <v>17.09315100408853</v>
       </c>
     </row>
     <row r="216">
@@ -30429,16 +30429,16 @@
         <v>1</v>
       </c>
       <c r="AJ216" t="n">
-        <v>1.980878304473305</v>
+        <v>1.980878304473304</v>
       </c>
       <c r="AK216" t="n">
-        <v>0.05912169552669533</v>
+        <v>0.05912169552669577</v>
       </c>
       <c r="AL216" t="n">
-        <v>0.05912169552669533</v>
+        <v>0.05912169552669577</v>
       </c>
       <c r="AM216" t="n">
-        <v>2.898122329739967</v>
+        <v>2.898122329739989</v>
       </c>
     </row>
     <row r="217">
@@ -30852,16 +30852,16 @@
         <v>1</v>
       </c>
       <c r="AJ219" t="n">
-        <v>1.939911293891295</v>
+        <v>1.939911293891294</v>
       </c>
       <c r="AK219" t="n">
-        <v>-0.03991129389129511</v>
+        <v>-0.039911293891294</v>
       </c>
       <c r="AL219" t="n">
-        <v>0.03991129389129511</v>
+        <v>0.039911293891294</v>
       </c>
       <c r="AM219" t="n">
-        <v>2.100594415331321</v>
+        <v>2.100594415331263</v>
       </c>
     </row>
     <row r="220">
@@ -30992,13 +30992,13 @@
         <v>3.456552593795091</v>
       </c>
       <c r="AK220" t="n">
-        <v>-0.8665525937950913</v>
+        <v>-0.8665525937950909</v>
       </c>
       <c r="AL220" t="n">
-        <v>0.8665525937950913</v>
+        <v>0.8665525937950909</v>
       </c>
       <c r="AM220" t="n">
-        <v>33.45762910405758</v>
+        <v>33.45762910405756</v>
       </c>
     </row>
     <row r="221">
@@ -31263,16 +31263,16 @@
         <v>1</v>
       </c>
       <c r="AJ222" t="n">
-        <v>1.95593419071669</v>
+        <v>1.955934190716691</v>
       </c>
       <c r="AK222" t="n">
-        <v>-0.5859341907166902</v>
+        <v>-0.5859341907166904</v>
       </c>
       <c r="AL222" t="n">
-        <v>0.5859341907166902</v>
+        <v>0.5859341907166904</v>
       </c>
       <c r="AM222" t="n">
-        <v>42.76891903041534</v>
+        <v>42.76891903041535</v>
       </c>
     </row>
     <row r="223">
@@ -31403,13 +31403,13 @@
         <v>1.662716615699114</v>
       </c>
       <c r="AK223" t="n">
-        <v>0.03728338430088574</v>
+        <v>0.03728338430088551</v>
       </c>
       <c r="AL223" t="n">
-        <v>0.03728338430088574</v>
+        <v>0.03728338430088551</v>
       </c>
       <c r="AM223" t="n">
-        <v>2.193140252993279</v>
+        <v>2.193140252993266</v>
       </c>
     </row>
     <row r="224">
@@ -31820,13 +31820,13 @@
         <v>1.126945898268398</v>
       </c>
       <c r="AK226" t="n">
-        <v>0.1230541017316023</v>
+        <v>0.123054101731602</v>
       </c>
       <c r="AL226" t="n">
-        <v>0.1230541017316023</v>
+        <v>0.123054101731602</v>
       </c>
       <c r="AM226" t="n">
-        <v>9.84432813852818</v>
+        <v>9.844328138528162</v>
       </c>
     </row>
     <row r="227">
@@ -32240,16 +32240,16 @@
         <v>0</v>
       </c>
       <c r="AJ229" t="n">
-        <v>7.979872407407409</v>
+        <v>7.97987240740741</v>
       </c>
       <c r="AK229" t="n">
-        <v>-1.479872407407409</v>
+        <v>-1.47987240740741</v>
       </c>
       <c r="AL229" t="n">
-        <v>1.479872407407409</v>
+        <v>1.47987240740741</v>
       </c>
       <c r="AM229" t="n">
-        <v>22.76726780626784</v>
+        <v>22.76726780626785</v>
       </c>
     </row>
     <row r="230">
@@ -32383,16 +32383,16 @@
         <v>0</v>
       </c>
       <c r="AJ230" t="n">
-        <v>21.99735379990378</v>
+        <v>21.99735379990379</v>
       </c>
       <c r="AK230" t="n">
-        <v>-1.997353799903784</v>
+        <v>-1.997353799903788</v>
       </c>
       <c r="AL230" t="n">
-        <v>1.997353799903784</v>
+        <v>1.997353799903788</v>
       </c>
       <c r="AM230" t="n">
-        <v>9.986768999518922</v>
+        <v>9.98676899951894</v>
       </c>
     </row>
     <row r="231">
@@ -32660,13 +32660,13 @@
         <v>3.692969018759022</v>
       </c>
       <c r="AK232" t="n">
-        <v>0.7270309812409779</v>
+        <v>0.7270309812409783</v>
       </c>
       <c r="AL232" t="n">
-        <v>0.7270309812409779</v>
+        <v>0.7270309812409783</v>
       </c>
       <c r="AM232" t="n">
-        <v>16.44866473395878</v>
+        <v>16.44866473395879</v>
       </c>
     </row>
     <row r="233">
@@ -32794,16 +32794,16 @@
         <v>1</v>
       </c>
       <c r="AJ233" t="n">
-        <v>4.082377008177005</v>
+        <v>4.082377008177006</v>
       </c>
       <c r="AK233" t="n">
-        <v>-0.1823770081770051</v>
+        <v>-0.182377008177006</v>
       </c>
       <c r="AL233" t="n">
-        <v>0.1823770081770051</v>
+        <v>0.182377008177006</v>
       </c>
       <c r="AM233" t="n">
-        <v>4.67633354300013</v>
+        <v>4.676333543000153</v>
       </c>
     </row>
     <row r="234">
@@ -32943,16 +32943,16 @@
         <v>0</v>
       </c>
       <c r="AJ234" t="n">
-        <v>13.85569450937951</v>
+        <v>13.8556945093795</v>
       </c>
       <c r="AK234" t="n">
-        <v>-4.455694509379509</v>
+        <v>-4.455694509379503</v>
       </c>
       <c r="AL234" t="n">
-        <v>4.455694509379509</v>
+        <v>4.455694509379503</v>
       </c>
       <c r="AM234" t="n">
-        <v>47.40100541893094</v>
+        <v>47.40100541893089</v>
       </c>
     </row>
     <row r="235">
@@ -33220,13 +33220,13 @@
         <v>1.29416414021164</v>
       </c>
       <c r="AK236" t="n">
-        <v>0.3958358597883598</v>
+        <v>0.3958358597883596</v>
       </c>
       <c r="AL236" t="n">
-        <v>0.3958358597883598</v>
+        <v>0.3958358597883596</v>
       </c>
       <c r="AM236" t="n">
-        <v>23.4222402241633</v>
+        <v>23.42224022416329</v>
       </c>
     </row>
     <row r="237">
@@ -33628,16 +33628,16 @@
         <v>1</v>
       </c>
       <c r="AJ239" t="n">
-        <v>3.285731184463683</v>
+        <v>3.285731184463682</v>
       </c>
       <c r="AK239" t="n">
-        <v>-0.1757311844636829</v>
+        <v>-0.1757311844636824</v>
       </c>
       <c r="AL239" t="n">
-        <v>0.1757311844636829</v>
+        <v>0.1757311844636824</v>
       </c>
       <c r="AM239" t="n">
-        <v>5.650520400761507</v>
+        <v>5.650520400761493</v>
       </c>
     </row>
     <row r="240">
@@ -33765,16 +33765,16 @@
         <v>1</v>
       </c>
       <c r="AJ240" t="n">
-        <v>3.595104338624339</v>
+        <v>3.59510433862434</v>
       </c>
       <c r="AK240" t="n">
-        <v>1.064895661375661</v>
+        <v>1.06489566137566</v>
       </c>
       <c r="AL240" t="n">
-        <v>1.064895661375661</v>
+        <v>1.06489566137566</v>
       </c>
       <c r="AM240" t="n">
-        <v>22.85183822694552</v>
+        <v>22.85183822694549</v>
       </c>
     </row>
     <row r="241">
@@ -33905,13 +33905,13 @@
         <v>1.975936002886003</v>
       </c>
       <c r="AK241" t="n">
-        <v>0.07406399711399647</v>
+        <v>0.07406399711399692</v>
       </c>
       <c r="AL241" t="n">
-        <v>0.07406399711399647</v>
+        <v>0.07406399711399692</v>
       </c>
       <c r="AM241" t="n">
-        <v>3.612877907999828</v>
+        <v>3.61287790799985</v>
       </c>
     </row>
     <row r="242">
@@ -34179,13 +34179,13 @@
         <v>2.114847995245496</v>
       </c>
       <c r="AK243" t="n">
-        <v>0.2151520047545041</v>
+        <v>0.2151520047545037</v>
       </c>
       <c r="AL243" t="n">
-        <v>0.2151520047545041</v>
+        <v>0.2151520047545037</v>
       </c>
       <c r="AM243" t="n">
-        <v>9.233991620364984</v>
+        <v>9.233991620364964</v>
       </c>
     </row>
     <row r="244">
@@ -34316,13 +34316,13 @@
         <v>2.114847995245496</v>
       </c>
       <c r="AK244" t="n">
-        <v>0.2151520047545041</v>
+        <v>0.2151520047545037</v>
       </c>
       <c r="AL244" t="n">
-        <v>0.2151520047545041</v>
+        <v>0.2151520047545037</v>
       </c>
       <c r="AM244" t="n">
-        <v>9.233991620364984</v>
+        <v>9.233991620364964</v>
       </c>
     </row>
     <row r="245">
@@ -34459,13 +34459,13 @@
         <v>18.98870588929589</v>
       </c>
       <c r="AK245" t="n">
-        <v>-2.988705889295893</v>
+        <v>-2.98870588929589</v>
       </c>
       <c r="AL245" t="n">
-        <v>2.988705889295893</v>
+        <v>2.98870588929589</v>
       </c>
       <c r="AM245" t="n">
-        <v>18.67941180809933</v>
+        <v>18.67941180809931</v>
       </c>
     </row>
     <row r="246">
@@ -34596,13 +34596,13 @@
         <v>1.975936002886003</v>
       </c>
       <c r="AK246" t="n">
-        <v>-0.005936002886003378</v>
+        <v>-0.005936002886002933</v>
       </c>
       <c r="AL246" t="n">
-        <v>0.005936002886003378</v>
+        <v>0.005936002886002933</v>
       </c>
       <c r="AM246" t="n">
-        <v>0.3013199434519481</v>
+        <v>0.3013199434519255</v>
       </c>
     </row>
     <row r="247">
@@ -34730,16 +34730,16 @@
         <v>1</v>
       </c>
       <c r="AJ247" t="n">
-        <v>1.898226243144111</v>
+        <v>1.89822624314411</v>
       </c>
       <c r="AK247" t="n">
-        <v>0.6317737568558885</v>
+        <v>0.6317737568558897</v>
       </c>
       <c r="AL247" t="n">
-        <v>0.6317737568558885</v>
+        <v>0.6317737568558897</v>
       </c>
       <c r="AM247" t="n">
-        <v>24.9712947373869</v>
+        <v>24.97129473738694</v>
       </c>
     </row>
     <row r="248">
@@ -34870,13 +34870,13 @@
         <v>2.301065386002884</v>
       </c>
       <c r="AK248" t="n">
-        <v>0.7989346139971163</v>
+        <v>0.7989346139971159</v>
       </c>
       <c r="AL248" t="n">
-        <v>0.7989346139971163</v>
+        <v>0.7989346139971159</v>
       </c>
       <c r="AM248" t="n">
-        <v>25.77208432248762</v>
+        <v>25.77208432248761</v>
       </c>
     </row>
     <row r="249">
@@ -35144,13 +35144,13 @@
         <v>1.878365063212931</v>
       </c>
       <c r="AK250" t="n">
-        <v>1.551634936787069</v>
+        <v>1.55163493678707</v>
       </c>
       <c r="AL250" t="n">
-        <v>1.551634936787069</v>
+        <v>1.55163493678707</v>
       </c>
       <c r="AM250" t="n">
-        <v>45.23717016871921</v>
+        <v>45.23717016871923</v>
       </c>
     </row>
     <row r="251">
@@ -35421,16 +35421,16 @@
         <v>1</v>
       </c>
       <c r="AJ252" t="n">
-        <v>3.936066553713171</v>
+        <v>3.936066553713172</v>
       </c>
       <c r="AK252" t="n">
-        <v>0.473933446286829</v>
+        <v>0.4739334462868285</v>
       </c>
       <c r="AL252" t="n">
-        <v>0.473933446286829</v>
+        <v>0.4739334462868285</v>
       </c>
       <c r="AM252" t="n">
-        <v>10.74679016523422</v>
+        <v>10.74679016523421</v>
       </c>
     </row>
     <row r="253">
@@ -35838,16 +35838,16 @@
         <v>1</v>
       </c>
       <c r="AJ255" t="n">
-        <v>3.409065198412697</v>
+        <v>3.409065198412696</v>
       </c>
       <c r="AK255" t="n">
-        <v>0.6509348015873031</v>
+        <v>0.6509348015873035</v>
       </c>
       <c r="AL255" t="n">
-        <v>0.6509348015873031</v>
+        <v>0.6509348015873035</v>
       </c>
       <c r="AM255" t="n">
-        <v>16.03287688638678</v>
+        <v>16.03287688638679</v>
       </c>
     </row>
     <row r="256">
@@ -35975,16 +35975,16 @@
         <v>1</v>
       </c>
       <c r="AJ256" t="n">
-        <v>3.383508062770562</v>
+        <v>3.383508062770561</v>
       </c>
       <c r="AK256" t="n">
-        <v>0.7464919372294383</v>
+        <v>0.7464919372294392</v>
       </c>
       <c r="AL256" t="n">
-        <v>0.7464919372294383</v>
+        <v>0.7464919372294392</v>
       </c>
       <c r="AM256" t="n">
-        <v>18.07486530821885</v>
+        <v>18.07486530821887</v>
       </c>
     </row>
     <row r="257">
@@ -36112,16 +36112,16 @@
         <v>1</v>
       </c>
       <c r="AJ257" t="n">
-        <v>3.388499576719576</v>
+        <v>3.388499576719577</v>
       </c>
       <c r="AK257" t="n">
-        <v>-0.2684995767195764</v>
+        <v>-0.2684995767195768</v>
       </c>
       <c r="AL257" t="n">
-        <v>0.2684995767195764</v>
+        <v>0.2684995767195768</v>
       </c>
       <c r="AM257" t="n">
-        <v>8.605755664088987</v>
+        <v>8.605755664089001</v>
       </c>
     </row>
     <row r="258">
@@ -36386,16 +36386,16 @@
         <v>1</v>
       </c>
       <c r="AJ259" t="n">
-        <v>2.655179078884079</v>
+        <v>2.655179078884078</v>
       </c>
       <c r="AK259" t="n">
-        <v>0.2848209211159212</v>
+        <v>0.2848209211159221</v>
       </c>
       <c r="AL259" t="n">
-        <v>0.2848209211159212</v>
+        <v>0.2848209211159221</v>
       </c>
       <c r="AM259" t="n">
-        <v>9.687786432514326</v>
+        <v>9.687786432514356</v>
       </c>
     </row>
     <row r="260">
@@ -36659,13 +36659,13 @@
         <v>2.012029355459354</v>
       </c>
       <c r="AK261" t="n">
-        <v>-0.472029355459354</v>
+        <v>-0.4720293554593535</v>
       </c>
       <c r="AL261" t="n">
-        <v>0.472029355459354</v>
+        <v>0.4720293554593535</v>
       </c>
       <c r="AM261" t="n">
-        <v>30.65125684801</v>
+        <v>30.65125684800997</v>
       </c>
     </row>
     <row r="262">
@@ -36805,16 +36805,16 @@
         <v>0</v>
       </c>
       <c r="AJ262" t="n">
-        <v>9.190078893791402</v>
+        <v>9.190078893791403</v>
       </c>
       <c r="AK262" t="n">
-        <v>-2.760078893791402</v>
+        <v>-2.760078893791404</v>
       </c>
       <c r="AL262" t="n">
-        <v>2.760078893791402</v>
+        <v>2.760078893791404</v>
       </c>
       <c r="AM262" t="n">
-        <v>42.92502167638261</v>
+        <v>42.92502167638264</v>
       </c>
     </row>
     <row r="263">
@@ -36954,16 +36954,16 @@
         <v>0</v>
       </c>
       <c r="AJ263" t="n">
-        <v>3.914962510822513</v>
+        <v>3.914962510822512</v>
       </c>
       <c r="AK263" t="n">
-        <v>-2.904962510822513</v>
+        <v>-2.904962510822512</v>
       </c>
       <c r="AL263" t="n">
-        <v>2.904962510822513</v>
+        <v>2.904962510822512</v>
       </c>
       <c r="AM263" t="n">
-        <v>287.6200505764865</v>
+        <v>287.6200505764863</v>
       </c>
     </row>
     <row r="264">
@@ -37243,13 +37243,13 @@
         <v>1.638850002405003</v>
       </c>
       <c r="AK265" t="n">
-        <v>-0.378850002405003</v>
+        <v>-0.3788500024050028</v>
       </c>
       <c r="AL265" t="n">
-        <v>0.378850002405003</v>
+        <v>0.3788500024050028</v>
       </c>
       <c r="AM265" t="n">
-        <v>30.06746050833357</v>
+        <v>30.06746050833355</v>
       </c>
     </row>
     <row r="266">
@@ -37943,16 +37943,16 @@
         <v>0</v>
       </c>
       <c r="AJ270" t="n">
-        <v>8.527872221019727</v>
+        <v>8.527872221019726</v>
       </c>
       <c r="AK270" t="n">
-        <v>-0.5878722210197269</v>
+        <v>-0.5878722210197251</v>
       </c>
       <c r="AL270" t="n">
-        <v>0.5878722210197269</v>
+        <v>0.5878722210197251</v>
       </c>
       <c r="AM270" t="n">
-        <v>7.40393225465651</v>
+        <v>7.403932254656488</v>
       </c>
     </row>
     <row r="271">
@@ -38234,13 +38234,13 @@
         <v>21.13365673585673</v>
       </c>
       <c r="AK272" t="n">
-        <v>0.06634326414327063</v>
+        <v>0.06634326414326708</v>
       </c>
       <c r="AL272" t="n">
-        <v>0.06634326414327063</v>
+        <v>0.06634326414326708</v>
       </c>
       <c r="AM272" t="n">
-        <v>0.3129399252041067</v>
+        <v>0.31293992520409</v>
       </c>
     </row>
     <row r="273">
@@ -38520,13 +38520,13 @@
         <v>1.460113564213564</v>
       </c>
       <c r="AK274" t="n">
-        <v>-0.8201135642135639</v>
+        <v>-0.8201135642135643</v>
       </c>
       <c r="AL274" t="n">
-        <v>0.8201135642135639</v>
+        <v>0.8201135642135643</v>
       </c>
       <c r="AM274" t="n">
-        <v>128.1427444083693</v>
+        <v>128.1427444083694</v>
       </c>
     </row>
     <row r="275">
@@ -38657,13 +38657,13 @@
         <v>1.878365063212931</v>
       </c>
       <c r="AK275" t="n">
-        <v>-0.4383650632129312</v>
+        <v>-0.4383650632129306</v>
       </c>
       <c r="AL275" t="n">
-        <v>0.4383650632129312</v>
+        <v>0.4383650632129306</v>
       </c>
       <c r="AM275" t="n">
-        <v>30.44201827867578</v>
+        <v>30.44201827867574</v>
       </c>
     </row>
     <row r="276">
@@ -38794,13 +38794,13 @@
         <v>2.021782837902837</v>
       </c>
       <c r="AK276" t="n">
-        <v>-0.4917828379028373</v>
+        <v>-0.4917828379028368</v>
       </c>
       <c r="AL276" t="n">
-        <v>0.4917828379028373</v>
+        <v>0.4917828379028368</v>
       </c>
       <c r="AM276" t="n">
-        <v>32.14266914397629</v>
+        <v>32.14266914397626</v>
       </c>
     </row>
     <row r="277">
@@ -38931,13 +38931,13 @@
         <v>2.281959298941797</v>
       </c>
       <c r="AK277" t="n">
-        <v>-0.8019592989417972</v>
+        <v>-0.8019592989417967</v>
       </c>
       <c r="AL277" t="n">
-        <v>0.8019592989417972</v>
+        <v>0.8019592989417967</v>
       </c>
       <c r="AM277" t="n">
-        <v>54.186439117689</v>
+        <v>54.18643911768897</v>
       </c>
     </row>
     <row r="278">
@@ -39065,16 +39065,16 @@
         <v>1</v>
       </c>
       <c r="AJ278" t="n">
-        <v>3.395822896825398</v>
+        <v>3.395822896825397</v>
       </c>
       <c r="AK278" t="n">
-        <v>-0.4058228968253976</v>
+        <v>-0.4058228968253972</v>
       </c>
       <c r="AL278" t="n">
-        <v>0.4058228968253976</v>
+        <v>0.4058228968253972</v>
       </c>
       <c r="AM278" t="n">
-        <v>13.57267213462868</v>
+        <v>13.57267213462867</v>
       </c>
     </row>
     <row r="279">
@@ -39506,16 +39506,16 @@
         <v>1</v>
       </c>
       <c r="AJ281" t="n">
-        <v>3.306928637566137</v>
+        <v>3.306928637566138</v>
       </c>
       <c r="AK281" t="n">
-        <v>0.04307136243386278</v>
+        <v>0.04307136243386189</v>
       </c>
       <c r="AL281" t="n">
-        <v>0.04307136243386278</v>
+        <v>0.04307136243386189</v>
       </c>
       <c r="AM281" t="n">
-        <v>1.28571231145859</v>
+        <v>1.285712311458564</v>
       </c>
     </row>
     <row r="282">
@@ -39658,13 +39658,13 @@
         <v>3.153393373015871</v>
       </c>
       <c r="AK282" t="n">
-        <v>-0.4733933730158713</v>
+        <v>-0.4733933730158708</v>
       </c>
       <c r="AL282" t="n">
-        <v>0.4733933730158713</v>
+        <v>0.4733933730158708</v>
       </c>
       <c r="AM282" t="n">
-        <v>17.66393182895042</v>
+        <v>17.6639318289504</v>
       </c>
     </row>
     <row r="283">
@@ -39792,16 +39792,16 @@
         <v>1</v>
       </c>
       <c r="AJ283" t="n">
-        <v>1.983785465367965</v>
+        <v>1.983785465367964</v>
       </c>
       <c r="AK283" t="n">
-        <v>-0.00378546536796498</v>
+        <v>-0.003785465367963869</v>
       </c>
       <c r="AL283" t="n">
-        <v>0.00378546536796498</v>
+        <v>0.003785465367963869</v>
       </c>
       <c r="AM283" t="n">
-        <v>0.1911851195941909</v>
+        <v>0.1911851195941348</v>
       </c>
     </row>
     <row r="284">
@@ -39932,13 +39932,13 @@
         <v>2.109296645021645</v>
       </c>
       <c r="AK284" t="n">
-        <v>-0.05929664502164567</v>
+        <v>-0.05929664502164478</v>
       </c>
       <c r="AL284" t="n">
-        <v>0.05929664502164567</v>
+        <v>0.05929664502164478</v>
       </c>
       <c r="AM284" t="n">
-        <v>2.892519269348569</v>
+        <v>2.892519269348526</v>
       </c>
     </row>
     <row r="285">
@@ -40066,16 +40066,16 @@
         <v>1</v>
       </c>
       <c r="AJ285" t="n">
-        <v>2.016508297258296</v>
+        <v>2.016508297258295</v>
       </c>
       <c r="AK285" t="n">
-        <v>0.2134917027417043</v>
+        <v>0.2134917027417047</v>
       </c>
       <c r="AL285" t="n">
-        <v>0.2134917027417043</v>
+        <v>0.2134917027417047</v>
       </c>
       <c r="AM285" t="n">
-        <v>9.573618957027097</v>
+        <v>9.573618957027117</v>
       </c>
     </row>
     <row r="286">
@@ -40343,13 +40343,13 @@
         <v>1.799720318292818</v>
       </c>
       <c r="AK287" t="n">
-        <v>0.4402796817071823</v>
+        <v>0.4402796817071819</v>
       </c>
       <c r="AL287" t="n">
-        <v>0.4402796817071823</v>
+        <v>0.4402796817071819</v>
       </c>
       <c r="AM287" t="n">
-        <v>19.65534293335635</v>
+        <v>19.65534293335633</v>
       </c>
     </row>
     <row r="288">
@@ -40480,13 +40480,13 @@
         <v>1.799720318292818</v>
       </c>
       <c r="AK288" t="n">
-        <v>-0.01972031829281784</v>
+        <v>-0.01972031829281828</v>
       </c>
       <c r="AL288" t="n">
-        <v>0.01972031829281784</v>
+        <v>0.01972031829281828</v>
       </c>
       <c r="AM288" t="n">
-        <v>1.107883050158306</v>
+        <v>1.107883050158331</v>
       </c>
     </row>
     <row r="289">
@@ -40888,16 +40888,16 @@
         <v>1</v>
       </c>
       <c r="AJ291" t="n">
-        <v>3.868108915343911</v>
+        <v>3.868108915343913</v>
       </c>
       <c r="AK291" t="n">
-        <v>1.421891084656089</v>
+        <v>1.421891084656087</v>
       </c>
       <c r="AL291" t="n">
-        <v>1.421891084656089</v>
+        <v>1.421891084656087</v>
       </c>
       <c r="AM291" t="n">
-        <v>26.87884848121151</v>
+        <v>26.87884848121148</v>
       </c>
     </row>
     <row r="292">
@@ -41025,16 +41025,16 @@
         <v>1</v>
       </c>
       <c r="AJ292" t="n">
-        <v>3.59227044973545</v>
+        <v>3.592270449735451</v>
       </c>
       <c r="AK292" t="n">
-        <v>5.557729550264551</v>
+        <v>5.55772955026455</v>
       </c>
       <c r="AL292" t="n">
-        <v>5.557729550264551</v>
+        <v>5.55772955026455</v>
       </c>
       <c r="AM292" t="n">
-        <v>60.74021366409345</v>
+        <v>60.74021366409343</v>
       </c>
     </row>
     <row r="293">
@@ -41451,13 +41451,13 @@
         <v>1.701051937229436</v>
       </c>
       <c r="AK295" t="n">
-        <v>0.09894806277056389</v>
+        <v>0.09894806277056434</v>
       </c>
       <c r="AL295" t="n">
-        <v>0.09894806277056389</v>
+        <v>0.09894806277056434</v>
       </c>
       <c r="AM295" t="n">
-        <v>5.497114598364661</v>
+        <v>5.497114598364685</v>
       </c>
     </row>
     <row r="296">
@@ -41722,16 +41722,16 @@
         <v>1</v>
       </c>
       <c r="AJ297" t="n">
-        <v>1.578882447089947</v>
+        <v>1.578882447089946</v>
       </c>
       <c r="AK297" t="n">
-        <v>-0.01888244708994646</v>
+        <v>-0.01888244708994602</v>
       </c>
       <c r="AL297" t="n">
-        <v>0.01888244708994646</v>
+        <v>0.01888244708994602</v>
       </c>
       <c r="AM297" t="n">
-        <v>1.210413274996568</v>
+        <v>1.21041327499654</v>
       </c>
     </row>
     <row r="298">
@@ -41862,13 +41862,13 @@
         <v>1.878365063212931</v>
       </c>
       <c r="AK298" t="n">
-        <v>-0.7283650632129313</v>
+        <v>-0.7283650632129306</v>
       </c>
       <c r="AL298" t="n">
-        <v>0.7283650632129313</v>
+        <v>0.7283650632129306</v>
       </c>
       <c r="AM298" t="n">
-        <v>63.33609245329838</v>
+        <v>63.33609245329832</v>
       </c>
     </row>
     <row r="299">
@@ -41999,13 +41999,13 @@
         <v>1.878365063212931</v>
       </c>
       <c r="AK299" t="n">
-        <v>-0.3283650632129311</v>
+        <v>-0.3283650632129305</v>
       </c>
       <c r="AL299" t="n">
-        <v>0.3283650632129311</v>
+        <v>0.3283650632129305</v>
       </c>
       <c r="AM299" t="n">
-        <v>21.18484278793104</v>
+        <v>21.184842787931</v>
       </c>
     </row>
     <row r="300">
@@ -42270,16 +42270,16 @@
         <v>1</v>
       </c>
       <c r="AJ301" t="n">
-        <v>2.024347034632036</v>
+        <v>2.024347034632035</v>
       </c>
       <c r="AK301" t="n">
-        <v>-0.08434703463203563</v>
+        <v>-0.08434703463203519</v>
       </c>
       <c r="AL301" t="n">
-        <v>0.08434703463203563</v>
+        <v>0.08434703463203519</v>
       </c>
       <c r="AM301" t="n">
-        <v>4.347785290311116</v>
+        <v>4.347785290311093</v>
       </c>
     </row>
     <row r="302">
@@ -42681,16 +42681,16 @@
         <v>1</v>
       </c>
       <c r="AJ304" t="n">
-        <v>1.803988981481482</v>
+        <v>1.803988981481481</v>
       </c>
       <c r="AK304" t="n">
-        <v>0.2960110185185185</v>
+        <v>0.296011018518519</v>
       </c>
       <c r="AL304" t="n">
-        <v>0.2960110185185185</v>
+        <v>0.296011018518519</v>
       </c>
       <c r="AM304" t="n">
-        <v>14.09576278659612</v>
+        <v>14.09576278659614</v>
       </c>
     </row>
     <row r="305">
@@ -42821,13 +42821,13 @@
         <v>1.878365063212931</v>
       </c>
       <c r="AK305" t="n">
-        <v>-0.4083650632129312</v>
+        <v>-0.4083650632129305</v>
       </c>
       <c r="AL305" t="n">
-        <v>0.4083650632129312</v>
+        <v>0.4083650632129305</v>
       </c>
       <c r="AM305" t="n">
-        <v>27.77993627298852</v>
+        <v>27.77993627298847</v>
       </c>
     </row>
     <row r="306">
@@ -42958,13 +42958,13 @@
         <v>1.878365063212931</v>
       </c>
       <c r="AK306" t="n">
-        <v>0.761634936787069</v>
+        <v>0.7616349367870696</v>
       </c>
       <c r="AL306" t="n">
-        <v>0.761634936787069</v>
+        <v>0.7616349367870696</v>
       </c>
       <c r="AM306" t="n">
-        <v>28.8498082116314</v>
+        <v>28.84980821163142</v>
       </c>
     </row>
     <row r="307">
@@ -43092,16 +43092,16 @@
         <v>1</v>
       </c>
       <c r="AJ307" t="n">
-        <v>4.717393465608464</v>
+        <v>4.717393465608462</v>
       </c>
       <c r="AK307" t="n">
-        <v>2.762606534391536</v>
+        <v>2.762606534391538</v>
       </c>
       <c r="AL307" t="n">
-        <v>2.762606534391536</v>
+        <v>2.762606534391538</v>
       </c>
       <c r="AM307" t="n">
-        <v>36.93324243838952</v>
+        <v>36.93324243838955</v>
       </c>
     </row>
     <row r="308">
@@ -43232,13 +43232,13 @@
         <v>1.878365063212931</v>
       </c>
       <c r="AK308" t="n">
-        <v>-0.3783650632129312</v>
+        <v>-0.3783650632129305</v>
       </c>
       <c r="AL308" t="n">
-        <v>0.3783650632129312</v>
+        <v>0.3783650632129305</v>
       </c>
       <c r="AM308" t="n">
-        <v>25.22433754752875</v>
+        <v>25.2243375475287</v>
       </c>
     </row>
     <row r="309">
@@ -43372,16 +43372,16 @@
         <v>0</v>
       </c>
       <c r="AJ309" t="n">
-        <v>22.55823345543345</v>
+        <v>22.55823345543346</v>
       </c>
       <c r="AK309" t="n">
-        <v>2.341766544566546</v>
+        <v>2.341766544566539</v>
       </c>
       <c r="AL309" t="n">
-        <v>2.341766544566546</v>
+        <v>2.341766544566539</v>
       </c>
       <c r="AM309" t="n">
-        <v>9.404684917937937</v>
+        <v>9.40468491793791</v>
       </c>
     </row>
     <row r="310">
@@ -43515,16 +43515,16 @@
         <v>0</v>
       </c>
       <c r="AJ310" t="n">
-        <v>25.88769765512266</v>
+        <v>25.88769765512267</v>
       </c>
       <c r="AK310" t="n">
-        <v>2.612302344877335</v>
+        <v>2.612302344877328</v>
       </c>
       <c r="AL310" t="n">
-        <v>2.612302344877335</v>
+        <v>2.612302344877328</v>
       </c>
       <c r="AM310" t="n">
-        <v>9.165973139920474</v>
+        <v>9.16597313992045</v>
       </c>
     </row>
     <row r="311">
@@ -43661,13 +43661,13 @@
         <v>24.58219152421653</v>
       </c>
       <c r="AK311" t="n">
-        <v>3.61780847578347</v>
+        <v>3.617808475783466</v>
       </c>
       <c r="AL311" t="n">
-        <v>3.61780847578347</v>
+        <v>3.617808475783466</v>
       </c>
       <c r="AM311" t="n">
-        <v>12.82910807015415</v>
+        <v>12.82910807015413</v>
       </c>
     </row>
     <row r="312">
@@ -43795,16 +43795,16 @@
         <v>1</v>
       </c>
       <c r="AJ312" t="n">
-        <v>2.821245079365079</v>
+        <v>2.821245079365078</v>
       </c>
       <c r="AK312" t="n">
-        <v>-1.671245079365079</v>
+        <v>-1.671245079365078</v>
       </c>
       <c r="AL312" t="n">
-        <v>1.671245079365079</v>
+        <v>1.671245079365078</v>
       </c>
       <c r="AM312" t="n">
-        <v>145.3256590752243</v>
+        <v>145.3256590752242</v>
       </c>
     </row>
     <row r="313">
@@ -44081,16 +44081,16 @@
         <v>0</v>
       </c>
       <c r="AJ314" t="n">
-        <v>9.520466381673879</v>
+        <v>9.520466381673881</v>
       </c>
       <c r="AK314" t="n">
-        <v>-0.1504663816738798</v>
+        <v>-0.1504663816738816</v>
       </c>
       <c r="AL314" t="n">
-        <v>0.1504663816738798</v>
+        <v>0.1504663816738816</v>
       </c>
       <c r="AM314" t="n">
-        <v>1.605831181151332</v>
+        <v>1.605831181151351</v>
       </c>
     </row>
     <row r="315">
@@ -44227,13 +44227,13 @@
         <v>10.17074230880231</v>
       </c>
       <c r="AK315" t="n">
-        <v>0.8292576911976894</v>
+        <v>0.8292576911976877</v>
       </c>
       <c r="AL315" t="n">
-        <v>0.8292576911976894</v>
+        <v>0.8292576911976877</v>
       </c>
       <c r="AM315" t="n">
-        <v>7.538706283615358</v>
+        <v>7.538706283615343</v>
       </c>
     </row>
     <row r="316">
@@ -44796,16 +44796,16 @@
         <v>0</v>
       </c>
       <c r="AJ319" t="n">
-        <v>24.74713760221261</v>
+        <v>24.74713760221262</v>
       </c>
       <c r="AK319" t="n">
-        <v>3.252862397787389</v>
+        <v>3.252862397787382</v>
       </c>
       <c r="AL319" t="n">
-        <v>3.252862397787389</v>
+        <v>3.252862397787382</v>
       </c>
       <c r="AM319" t="n">
-        <v>11.61736570638353</v>
+        <v>11.61736570638351</v>
       </c>
     </row>
     <row r="320">
@@ -44939,16 +44939,16 @@
         <v>0</v>
       </c>
       <c r="AJ320" t="n">
-        <v>24.73443045935547</v>
+        <v>24.73443045935548</v>
       </c>
       <c r="AK320" t="n">
-        <v>3.265569540644531</v>
+        <v>3.265569540644524</v>
       </c>
       <c r="AL320" t="n">
-        <v>3.265569540644531</v>
+        <v>3.265569540644524</v>
       </c>
       <c r="AM320" t="n">
-        <v>11.66274835944475</v>
+        <v>11.66274835944473</v>
       </c>
     </row>
     <row r="321">
@@ -45359,13 +45359,13 @@
         <v>12.09491819606318</v>
       </c>
       <c r="AK323" t="n">
-        <v>0.005081803936821672</v>
+        <v>0.005081803936818119</v>
       </c>
       <c r="AL323" t="n">
-        <v>0.005081803936821672</v>
+        <v>0.005081803936818119</v>
       </c>
       <c r="AM323" t="n">
-        <v>0.04199837964315431</v>
+        <v>0.04199837964312495</v>
       </c>
     </row>
     <row r="324">
@@ -45489,16 +45489,16 @@
         <v>0</v>
       </c>
       <c r="AJ324" t="n">
-        <v>12.12427630351128</v>
+        <v>12.12427630351129</v>
       </c>
       <c r="AK324" t="n">
-        <v>-0.02427630351128407</v>
+        <v>-0.02427630351128585</v>
       </c>
       <c r="AL324" t="n">
-        <v>0.02427630351128407</v>
+        <v>0.02427630351128585</v>
       </c>
       <c r="AM324" t="n">
-        <v>0.2006306075312733</v>
+        <v>0.200630607531288</v>
       </c>
     </row>
     <row r="325">
@@ -45629,13 +45629,13 @@
         <v>11.07501061568061</v>
       </c>
       <c r="AK325" t="n">
-        <v>1.024989384319392</v>
+        <v>1.024989384319394</v>
       </c>
       <c r="AL325" t="n">
-        <v>1.024989384319392</v>
+        <v>1.024989384319394</v>
       </c>
       <c r="AM325" t="n">
-        <v>8.470986647267702</v>
+        <v>8.470986647267717</v>
       </c>
     </row>
     <row r="326">
@@ -45907,13 +45907,13 @@
         <v>10.00478754689754</v>
       </c>
       <c r="AK327" t="n">
-        <v>0.09521245310245696</v>
+        <v>0.09521245310245519</v>
       </c>
       <c r="AL327" t="n">
-        <v>0.09521245310245696</v>
+        <v>0.09521245310245519</v>
       </c>
       <c r="AM327" t="n">
-        <v>0.942697555469871</v>
+        <v>0.9426975554698535</v>
       </c>
     </row>
     <row r="328">
@@ -46333,16 +46333,16 @@
         <v>0</v>
       </c>
       <c r="AJ330" t="n">
-        <v>9.087663809523779</v>
+        <v>9.087663809523781</v>
       </c>
       <c r="AK330" t="n">
-        <v>0.01233619047622092</v>
+        <v>0.01233619047621914</v>
       </c>
       <c r="AL330" t="n">
-        <v>0.01233619047622092</v>
+        <v>0.01233619047621914</v>
       </c>
       <c r="AM330" t="n">
-        <v>0.1355625327057244</v>
+        <v>0.1355625327057049</v>
       </c>
     </row>
     <row r="331">
@@ -46470,16 +46470,16 @@
         <v>1</v>
       </c>
       <c r="AJ331" t="n">
-        <v>3.762659856902358</v>
+        <v>3.762659856902356</v>
       </c>
       <c r="AK331" t="n">
-        <v>0.7573401430976419</v>
+        <v>0.7573401430976436</v>
       </c>
       <c r="AL331" t="n">
-        <v>0.7573401430976419</v>
+        <v>0.7573401430976436</v>
       </c>
       <c r="AM331" t="n">
-        <v>16.75531290039031</v>
+        <v>16.75531290039035</v>
       </c>
     </row>
     <row r="332">
@@ -46610,13 +46610,13 @@
         <v>3.560121695526695</v>
       </c>
       <c r="AK332" t="n">
-        <v>0.02987830447330442</v>
+        <v>0.02987830447330531</v>
       </c>
       <c r="AL332" t="n">
-        <v>0.02987830447330442</v>
+        <v>0.02987830447330531</v>
       </c>
       <c r="AM332" t="n">
-        <v>0.8322647485600116</v>
+        <v>0.8322647485600364</v>
       </c>
     </row>
     <row r="333">
@@ -46893,13 +46893,13 @@
         <v>0</v>
       </c>
       <c r="AJ334" t="n">
-        <v>7.742596576479057</v>
+        <v>7.742596576479056</v>
       </c>
       <c r="AK334" t="n">
-        <v>1.357403423520942</v>
+        <v>1.357403423520943</v>
       </c>
       <c r="AL334" t="n">
-        <v>1.357403423520942</v>
+        <v>1.357403423520943</v>
       </c>
       <c r="AM334" t="n">
         <v>14.91652113759278</v>
@@ -47600,16 +47600,16 @@
         <v>0</v>
       </c>
       <c r="AJ339" t="n">
-        <v>9.089237950937909</v>
+        <v>9.089237950937907</v>
       </c>
       <c r="AK339" t="n">
-        <v>0.01076204906209099</v>
+        <v>0.01076204906209277</v>
       </c>
       <c r="AL339" t="n">
-        <v>0.01076204906209099</v>
+        <v>0.01076204906209277</v>
       </c>
       <c r="AM339" t="n">
-        <v>0.1182642754075933</v>
+        <v>0.1182642754076129</v>
       </c>
     </row>
     <row r="340">
@@ -48166,16 +48166,16 @@
         <v>1</v>
       </c>
       <c r="AJ343" t="n">
-        <v>3.620766801346799</v>
+        <v>3.620766801346798</v>
       </c>
       <c r="AK343" t="n">
-        <v>-0.2107668013467991</v>
+        <v>-0.2107668013467983</v>
       </c>
       <c r="AL343" t="n">
-        <v>0.2107668013467991</v>
+        <v>0.2107668013467983</v>
       </c>
       <c r="AM343" t="n">
-        <v>6.180844614275634</v>
+        <v>6.180844614275609</v>
       </c>
     </row>
     <row r="344">
@@ -48309,16 +48309,16 @@
         <v>0</v>
       </c>
       <c r="AJ344" t="n">
-        <v>9.089237950937909</v>
+        <v>9.089237950937907</v>
       </c>
       <c r="AK344" t="n">
-        <v>0.01076204906209099</v>
+        <v>0.01076204906209277</v>
       </c>
       <c r="AL344" t="n">
-        <v>0.01076204906209099</v>
+        <v>0.01076204906209277</v>
       </c>
       <c r="AM344" t="n">
-        <v>0.1182642754075933</v>
+        <v>0.1182642754076129</v>
       </c>
     </row>
     <row r="345">
@@ -48732,13 +48732,13 @@
         <v>1</v>
       </c>
       <c r="AJ347" t="n">
-        <v>5.341694126984129</v>
+        <v>5.341694126984128</v>
       </c>
       <c r="AK347" t="n">
-        <v>-3.45169412698413</v>
+        <v>-3.451694126984129</v>
       </c>
       <c r="AL347" t="n">
-        <v>3.45169412698413</v>
+        <v>3.451694126984129</v>
       </c>
       <c r="AM347" t="n">
         <v>182.6293188880492</v>
@@ -49298,16 +49298,16 @@
         <v>1</v>
       </c>
       <c r="AJ351" t="n">
-        <v>5.278808915343918</v>
+        <v>5.278808915343919</v>
       </c>
       <c r="AK351" t="n">
-        <v>-0.598808915343918</v>
+        <v>-0.5988089153439189</v>
       </c>
       <c r="AL351" t="n">
-        <v>0.598808915343918</v>
+        <v>0.5988089153439189</v>
       </c>
       <c r="AM351" t="n">
-        <v>12.79506229367346</v>
+        <v>12.79506229367348</v>
       </c>
     </row>
     <row r="352">
@@ -49854,16 +49854,16 @@
         <v>1</v>
       </c>
       <c r="AJ355" t="n">
-        <v>3.464777423039923</v>
+        <v>3.464777423039922</v>
       </c>
       <c r="AK355" t="n">
-        <v>4.445222576960077</v>
+        <v>4.445222576960078</v>
       </c>
       <c r="AL355" t="n">
-        <v>4.445222576960077</v>
+        <v>4.445222576960078</v>
       </c>
       <c r="AM355" t="n">
-        <v>56.19750413350287</v>
+        <v>56.19750413350288</v>
       </c>
     </row>
     <row r="356">
@@ -50136,16 +50136,16 @@
         <v>0</v>
       </c>
       <c r="AJ357" t="n">
-        <v>11.88187086802084</v>
+        <v>11.88187086802085</v>
       </c>
       <c r="AK357" t="n">
-        <v>-1.781870868020844</v>
+        <v>-1.781870868020846</v>
       </c>
       <c r="AL357" t="n">
-        <v>1.781870868020844</v>
+        <v>1.781870868020846</v>
       </c>
       <c r="AM357" t="n">
-        <v>17.64228582198856</v>
+        <v>17.64228582198857</v>
       </c>
     </row>
     <row r="358">
@@ -50696,16 +50696,16 @@
         <v>0</v>
       </c>
       <c r="AJ361" t="n">
-        <v>9.594542314814809</v>
+        <v>9.594542314814808</v>
       </c>
       <c r="AK361" t="n">
-        <v>0.5054576851851902</v>
+        <v>0.505457685185192</v>
       </c>
       <c r="AL361" t="n">
-        <v>0.5054576851851902</v>
+        <v>0.505457685185192</v>
       </c>
       <c r="AM361" t="n">
-        <v>5.004531536487032</v>
+        <v>5.00453153648705</v>
       </c>
     </row>
     <row r="362">
@@ -51536,16 +51536,16 @@
         <v>1</v>
       </c>
       <c r="AJ367" t="n">
-        <v>3.549325214045214</v>
+        <v>3.549325214045211</v>
       </c>
       <c r="AK367" t="n">
-        <v>-1.359325214045214</v>
+        <v>-1.359325214045211</v>
       </c>
       <c r="AL367" t="n">
-        <v>1.359325214045214</v>
+        <v>1.359325214045211</v>
       </c>
       <c r="AM367" t="n">
-        <v>62.06964447695039</v>
+        <v>62.06964447695029</v>
       </c>
     </row>
     <row r="368">
@@ -51678,13 +51678,13 @@
         <v>16.25151349668851</v>
       </c>
       <c r="AK368" t="n">
-        <v>-4.151513496688507</v>
+        <v>-4.15151349668851</v>
       </c>
       <c r="AL368" t="n">
-        <v>4.151513496688507</v>
+        <v>4.15151349668851</v>
       </c>
       <c r="AM368" t="n">
-        <v>34.31002889825212</v>
+        <v>34.31002889825216</v>
       </c>
     </row>
     <row r="369">
@@ -51817,13 +51817,13 @@
         <v>10.78000764050762</v>
       </c>
       <c r="AK369" t="n">
-        <v>1.31999235949238</v>
+        <v>1.319992359492378</v>
       </c>
       <c r="AL369" t="n">
-        <v>1.31999235949238</v>
+        <v>1.319992359492378</v>
       </c>
       <c r="AM369" t="n">
-        <v>10.90902776439983</v>
+        <v>10.90902776439982</v>
       </c>
     </row>
     <row r="370">
@@ -51951,16 +51951,16 @@
         <v>1</v>
       </c>
       <c r="AJ370" t="n">
-        <v>3.464777423039923</v>
+        <v>3.464777423039922</v>
       </c>
       <c r="AK370" t="n">
-        <v>-0.5047774230399233</v>
+        <v>-0.504777423039922</v>
       </c>
       <c r="AL370" t="n">
-        <v>0.5047774230399233</v>
+        <v>0.504777423039922</v>
       </c>
       <c r="AM370" t="n">
-        <v>17.05329131891633</v>
+        <v>17.05329131891628</v>
       </c>
     </row>
     <row r="371">
@@ -52368,16 +52368,16 @@
         <v>1</v>
       </c>
       <c r="AJ373" t="n">
-        <v>2.265549462481962</v>
+        <v>2.265549462481963</v>
       </c>
       <c r="AK373" t="n">
-        <v>0.2744505375180379</v>
+        <v>0.2744505375180375</v>
       </c>
       <c r="AL373" t="n">
-        <v>0.2744505375180379</v>
+        <v>0.2744505375180375</v>
       </c>
       <c r="AM373" t="n">
-        <v>10.8051392723637</v>
+        <v>10.80513927236368</v>
       </c>
     </row>
     <row r="374">
@@ -52505,16 +52505,16 @@
         <v>1</v>
       </c>
       <c r="AJ374" t="n">
-        <v>4.773025097402599</v>
+        <v>4.773025097402598</v>
       </c>
       <c r="AK374" t="n">
-        <v>0.4669749025974017</v>
+        <v>0.4669749025974026</v>
       </c>
       <c r="AL374" t="n">
-        <v>0.4669749025974017</v>
+        <v>0.4669749025974026</v>
       </c>
       <c r="AM374" t="n">
-        <v>8.911734782393161</v>
+        <v>8.911734782393179</v>
       </c>
     </row>
     <row r="375">
@@ -52779,16 +52779,16 @@
         <v>1</v>
       </c>
       <c r="AJ376" t="n">
-        <v>3.594786005291005</v>
+        <v>3.594786005291006</v>
       </c>
       <c r="AK376" t="n">
-        <v>-0.1747860052910051</v>
+        <v>-0.1747860052910064</v>
       </c>
       <c r="AL376" t="n">
-        <v>0.1747860052910051</v>
+        <v>0.1747860052910064</v>
       </c>
       <c r="AM376" t="n">
-        <v>5.110701909093716</v>
+        <v>5.110701909093755</v>
       </c>
     </row>
     <row r="377">
@@ -52916,16 +52916,16 @@
         <v>1</v>
       </c>
       <c r="AJ377" t="n">
-        <v>3.395822896825398</v>
+        <v>3.395822896825397</v>
       </c>
       <c r="AK377" t="n">
-        <v>0.1641771031746022</v>
+        <v>0.1641771031746027</v>
       </c>
       <c r="AL377" t="n">
-        <v>0.1641771031746022</v>
+        <v>0.1641771031746027</v>
       </c>
       <c r="AM377" t="n">
-        <v>4.61171638130905</v>
+        <v>4.611716381309063</v>
       </c>
     </row>
   </sheetData>
@@ -53001,7 +53001,7 @@
         <v>0.9503597492453506</v>
       </c>
       <c r="D3" t="n">
-        <v>1.534250105259319</v>
+        <v>1.53425010525932</v>
       </c>
       <c r="E3" t="n">
         <v>76</v>
@@ -53086,7 +53086,7 @@
         <v>0.9173219328662713</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9380886476863776</v>
+        <v>0.9380886476863779</v>
       </c>
       <c r="F2" t="n">
         <v>1.519185484812992</v>
@@ -53126,7 +53126,7 @@
         <v>0.8970942214372927</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9840948935138929</v>
+        <v>0.9840948935138931</v>
       </c>
       <c r="F4" t="n">
         <v>1.448944801952477</v>
@@ -53188,7 +53188,7 @@
         <v>0.8938521996287129</v>
       </c>
       <c r="E7" t="n">
-        <v>1.108699526743156</v>
+        <v>1.108699526743157</v>
       </c>
       <c r="F7" t="n">
         <v>1.783205266945985</v>
@@ -53210,7 +53210,7 @@
         <v>0.02277936671062199</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1646728521891828</v>
+        <v>0.1646728521891827</v>
       </c>
       <c r="F8" t="n">
         <v>0.3630553964789631</v>
@@ -53283,7 +53283,7 @@
         <v>2.731556544100619</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3532582707141964</v>
+        <v>0.353258270714196</v>
       </c>
       <c r="F2" t="n">
         <v>1.071974481232074</v>
@@ -53308,13 +53308,13 @@
         <v>1.63003504161704</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2011414289711955</v>
+        <v>0.2011414289711957</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6462820573422479</v>
+        <v>0.646282057342248</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9857099516268643</v>
+        <v>0.9857099516268644</v>
       </c>
     </row>
     <row r="4">
@@ -53333,13 +53333,13 @@
         <v>16.20494248750092</v>
       </c>
       <c r="E4" t="n">
-        <v>0.107557512499084</v>
+        <v>0.107557512499082</v>
       </c>
       <c r="F4" t="n">
-        <v>1.39476354695073</v>
+        <v>1.394763546950729</v>
       </c>
       <c r="G4" t="n">
-        <v>1.61185307413829</v>
+        <v>1.611853074138289</v>
       </c>
     </row>
     <row r="5">
@@ -53355,16 +53355,16 @@
         <v>2.808333333333334</v>
       </c>
       <c r="D5" t="n">
-        <v>3.021875515503015</v>
+        <v>3.021875515503016</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.213542182169682</v>
+        <v>-0.2135421821696827</v>
       </c>
       <c r="F5" t="n">
-        <v>0.495436885891886</v>
+        <v>0.4954368858918856</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7245451723665212</v>
+        <v>0.7245451723665211</v>
       </c>
     </row>
     <row r="6">
@@ -53380,16 +53380,16 @@
         <v>5.4975</v>
       </c>
       <c r="D6" t="n">
-        <v>8.650121040764786</v>
+        <v>8.650121040764787</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.152621040764785</v>
+        <v>-3.152621040764786</v>
       </c>
       <c r="F6" t="n">
-        <v>3.152621040764785</v>
+        <v>3.152621040764787</v>
       </c>
       <c r="G6" t="n">
-        <v>3.731294956979725</v>
+        <v>3.731294956979727</v>
       </c>
     </row>
     <row r="7">
@@ -53405,16 +53405,16 @@
         <v>1.5625</v>
       </c>
       <c r="D7" t="n">
-        <v>1.484282254689754</v>
+        <v>1.484282254689755</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0782177453102455</v>
+        <v>0.07821774531024533</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1433781812169316</v>
+        <v>0.1433781812169314</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1765681142133453</v>
+        <v>0.176568114213345</v>
       </c>
     </row>
     <row r="8">
@@ -53433,13 +53433,13 @@
         <v>1.984019016608392</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3384809833916083</v>
+        <v>0.3384809833916078</v>
       </c>
       <c r="F8" t="n">
         <v>0.4973769134337879</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6089917263372803</v>
+        <v>0.60899172633728</v>
       </c>
     </row>
     <row r="9">
@@ -53483,10 +53483,10 @@
         <v>10.55810120069744</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4581012006974365</v>
+        <v>-0.4581012006974357</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9178412932900368</v>
+        <v>0.9178412932900377</v>
       </c>
       <c r="G10" t="n">
         <v>1.025811556646132</v>

--- a/Mini-Project/Agricultural Machinery Inventory from ABEMIS/Regression Parameters Output V3/RF_Predictions.xlsx
+++ b/Mini-Project/Agricultural Machinery Inventory from ABEMIS/Regression Parameters Output V3/RF_Predictions.xlsx
@@ -10,11 +10,10 @@
     <sheet name="RF Predictions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metrics" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="CV Metrics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Per-Type Residuals" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Feature Importance" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Encoder machinery_type" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Encoder machinery_family" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Encoder analysis_subset" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Feature Importance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Encoder machinery_type" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Encoder machinery_family" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Encoder analysis_subset" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1156,16 +1155,16 @@
         <v>1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.291416005291006</v>
+        <v>2.291416005291007</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.2714160052910062</v>
+        <v>-0.2714160052910071</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.2714160052910062</v>
+        <v>0.2714160052910071</v>
       </c>
       <c r="AM5" t="n">
-        <v>13.43643590549536</v>
+        <v>13.4364359054954</v>
       </c>
     </row>
     <row r="6">
@@ -1305,16 +1304,16 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>8.113126374458876</v>
+        <v>8.113126374458872</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.3331263744588755</v>
+        <v>-0.3331263744588719</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.3331263744588755</v>
+        <v>0.3331263744588719</v>
       </c>
       <c r="AM6" t="n">
-        <v>4.281830005898143</v>
+        <v>4.281830005898097</v>
       </c>
     </row>
     <row r="7">
@@ -1457,13 +1456,13 @@
         <v>1.754740753968255</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.425259246031745</v>
+        <v>0.4252592460317448</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.425259246031745</v>
+        <v>0.4252592460317448</v>
       </c>
       <c r="AM7" t="n">
-        <v>19.50730486384151</v>
+        <v>19.5073048638415</v>
       </c>
     </row>
     <row r="8">
@@ -1606,13 +1605,13 @@
         <v>1.36020867003367</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.3402086700336702</v>
+        <v>-0.3402086700336699</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.3402086700336702</v>
+        <v>0.3402086700336699</v>
       </c>
       <c r="AM8" t="n">
-        <v>33.35379117977158</v>
+        <v>33.35379117977156</v>
       </c>
     </row>
     <row r="9">
@@ -1743,10 +1742,10 @@
         <v>1.608327652717652</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.8883276527176522</v>
+        <v>-0.888327652717652</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.8883276527176522</v>
+        <v>0.888327652717652</v>
       </c>
       <c r="AM9" t="n">
         <v>123.3788406552295</v>
@@ -1886,13 +1885,13 @@
         <v>17.25910338383839</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.5408966161616107</v>
+        <v>0.5408966161616071</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.5408966161616107</v>
+        <v>0.5408966161616071</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.03874503461579</v>
+        <v>3.03874503461577</v>
       </c>
     </row>
     <row r="11">
@@ -2160,13 +2159,13 @@
         <v>1.70895986171236</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.3089598617123603</v>
+        <v>-0.3089598617123599</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.3089598617123603</v>
+        <v>0.3089598617123599</v>
       </c>
       <c r="AM12" t="n">
-        <v>22.06856155088288</v>
+        <v>22.06856155088285</v>
       </c>
     </row>
     <row r="13">
@@ -2297,13 +2296,13 @@
         <v>1.70895986171236</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.5089598617123603</v>
+        <v>-0.5089598617123599</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.5089598617123603</v>
+        <v>0.5089598617123599</v>
       </c>
       <c r="AM13" t="n">
-        <v>42.41332180936336</v>
+        <v>42.41332180936332</v>
       </c>
     </row>
     <row r="14">
@@ -2708,13 +2707,13 @@
         <v>1.326383148148148</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.3836168518518521</v>
+        <v>0.3836168518518523</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.3836168518518521</v>
+        <v>0.3836168518518523</v>
       </c>
       <c r="AM16" t="n">
-        <v>22.4337340264241</v>
+        <v>22.43373402642412</v>
       </c>
     </row>
     <row r="17">
@@ -2854,16 +2853,16 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.398510482202982</v>
+        <v>1.398510482202983</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.04851048220298226</v>
+        <v>-0.04851048220298271</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.04851048220298226</v>
+        <v>0.04851048220298271</v>
       </c>
       <c r="AM17" t="n">
-        <v>3.59336905207276</v>
+        <v>3.593369052072793</v>
       </c>
     </row>
     <row r="18">
@@ -2991,16 +2990,16 @@
         <v>1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.384319591149591</v>
+        <v>2.384319591149592</v>
       </c>
       <c r="AK18" t="n">
-        <v>-1.564319591149591</v>
+        <v>-1.564319591149593</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.564319591149591</v>
+        <v>1.564319591149593</v>
       </c>
       <c r="AM18" t="n">
-        <v>190.7706818475111</v>
+        <v>190.7706818475113</v>
       </c>
     </row>
     <row r="19">
@@ -3265,16 +3264,16 @@
         <v>1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3.635028888888888</v>
+        <v>3.635028888888889</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.2149711111111121</v>
+        <v>0.2149711111111112</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.2149711111111121</v>
+        <v>0.2149711111111112</v>
       </c>
       <c r="AM20" t="n">
-        <v>5.58366522366525</v>
+        <v>5.583665223665227</v>
       </c>
     </row>
     <row r="21">
@@ -3948,16 +3947,16 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.433488492063492</v>
+        <v>3.433488492063493</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.1734884920634925</v>
+        <v>-0.1734884920634934</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.1734884920634925</v>
+        <v>0.1734884920634934</v>
       </c>
       <c r="AM25" t="n">
-        <v>5.321732885383206</v>
+        <v>5.321732885383232</v>
       </c>
     </row>
     <row r="26">
@@ -4088,13 +4087,13 @@
         <v>1.177954191919192</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.0920458080808082</v>
+        <v>0.09204580808080842</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.0920458080808082</v>
+        <v>0.09204580808080842</v>
       </c>
       <c r="AM26" t="n">
-        <v>7.247701423685685</v>
+        <v>7.247701423685703</v>
       </c>
     </row>
     <row r="27">
@@ -4222,16 +4221,16 @@
         <v>1</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.064450501443001</v>
+        <v>1.064450501443002</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.4755494985569986</v>
+        <v>0.4755494985569984</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.4755494985569986</v>
+        <v>0.4755494985569984</v>
       </c>
       <c r="AM27" t="n">
-        <v>30.87983756863627</v>
+        <v>30.87983756863625</v>
       </c>
     </row>
     <row r="28">
@@ -4357,16 +4356,16 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3.433488492063492</v>
+        <v>3.433488492063493</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.4334884920634923</v>
+        <v>-0.4334884920634932</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.4334884920634923</v>
+        <v>0.4334884920634932</v>
       </c>
       <c r="AM28" t="n">
-        <v>14.44961640211641</v>
+        <v>14.44961640211644</v>
       </c>
     </row>
     <row r="29">
@@ -4640,13 +4639,13 @@
         <v>12.81563244107743</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0.415632441077431</v>
+        <v>-0.4156324410774328</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.415632441077431</v>
+        <v>0.4156324410774328</v>
       </c>
       <c r="AM30" t="n">
-        <v>3.351874524817992</v>
+        <v>3.351874524818006</v>
       </c>
     </row>
     <row r="31">
@@ -5483,16 +5482,16 @@
         <v>1</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.952504604377107</v>
+        <v>1.952504604377106</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.4174953956228933</v>
+        <v>0.4174953956228937</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.4174953956228933</v>
+        <v>0.4174953956228937</v>
       </c>
       <c r="AM36" t="n">
-        <v>17.61583947775921</v>
+        <v>17.61583947775923</v>
       </c>
     </row>
     <row r="37">
@@ -5616,16 +5615,16 @@
         <v>1</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.715995579790579</v>
+        <v>1.71599557979058</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.1840044202094204</v>
+        <v>0.1840044202094202</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.1840044202094204</v>
+        <v>0.1840044202094202</v>
       </c>
       <c r="AM37" t="n">
-        <v>9.684443168916864</v>
+        <v>9.684443168916854</v>
       </c>
     </row>
     <row r="38">
@@ -5893,13 +5892,13 @@
         <v>1.603099958097458</v>
       </c>
       <c r="AK39" t="n">
-        <v>-0.1130999580974581</v>
+        <v>-0.1130999580974579</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.1130999580974581</v>
+        <v>0.1130999580974579</v>
       </c>
       <c r="AM39" t="n">
-        <v>7.590601214594503</v>
+        <v>7.590601214594489</v>
       </c>
     </row>
     <row r="40">
@@ -6312,13 +6311,13 @@
         <v>1.29550506012506</v>
       </c>
       <c r="AK42" t="n">
-        <v>-0.06550506012506041</v>
+        <v>-0.06550506012506019</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.06550506012506041</v>
+        <v>0.06550506012506019</v>
       </c>
       <c r="AM42" t="n">
-        <v>5.325614644313855</v>
+        <v>5.325614644313836</v>
       </c>
     </row>
     <row r="43">
@@ -6445,13 +6444,13 @@
         <v>1.29550506012506</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.1244949398749395</v>
+        <v>0.1244949398749398</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.1244949398749395</v>
+        <v>0.1244949398749398</v>
       </c>
       <c r="AM43" t="n">
-        <v>8.767249286967575</v>
+        <v>8.767249286967589</v>
       </c>
     </row>
     <row r="44">
@@ -6986,16 +6985,16 @@
         <v>1</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.124282248677249</v>
+        <v>2.12428224867725</v>
       </c>
       <c r="AK47" t="n">
-        <v>-0.8642822486772495</v>
+        <v>-0.8642822486772499</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.8642822486772495</v>
+        <v>0.8642822486772499</v>
       </c>
       <c r="AM47" t="n">
-        <v>68.59382926009916</v>
+        <v>68.5938292600992</v>
       </c>
     </row>
     <row r="48">
@@ -7119,16 +7118,16 @@
         <v>1</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.124282248677249</v>
+        <v>2.12428224867725</v>
       </c>
       <c r="AK48" t="n">
-        <v>-0.6342822486772495</v>
+        <v>-0.6342822486772499</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.6342822486772495</v>
+        <v>0.6342822486772499</v>
       </c>
       <c r="AM48" t="n">
-        <v>42.56927843471473</v>
+        <v>42.56927843471476</v>
       </c>
     </row>
     <row r="49">
@@ -7962,13 +7961,13 @@
         <v>23.30197622655122</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.598023773448777</v>
+        <v>1.59802377344878</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.598023773448777</v>
+        <v>1.59802377344878</v>
       </c>
       <c r="AM54" t="n">
-        <v>6.417766158428821</v>
+        <v>6.417766158428837</v>
       </c>
     </row>
     <row r="55">
@@ -8096,16 +8095,16 @@
         <v>1</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.781646646814515</v>
+        <v>1.781646646814514</v>
       </c>
       <c r="AK55" t="n">
-        <v>-0.4116466468145146</v>
+        <v>-0.4116466468145141</v>
       </c>
       <c r="AL55" t="n">
-        <v>0.4116466468145146</v>
+        <v>0.4116466468145141</v>
       </c>
       <c r="AM55" t="n">
-        <v>30.04720049740982</v>
+        <v>30.04720049740979</v>
       </c>
     </row>
     <row r="56">
@@ -8245,16 +8244,16 @@
         <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>2.652166902356904</v>
+        <v>2.652166902356903</v>
       </c>
       <c r="AK56" t="n">
-        <v>-0.2621669023569035</v>
+        <v>-0.2621669023569031</v>
       </c>
       <c r="AL56" t="n">
-        <v>0.2621669023569035</v>
+        <v>0.2621669023569031</v>
       </c>
       <c r="AM56" t="n">
-        <v>10.96932645844785</v>
+        <v>10.96932645844783</v>
       </c>
     </row>
     <row r="57">
@@ -8680,16 +8679,16 @@
         <v>1</v>
       </c>
       <c r="AJ59" t="n">
-        <v>1.176639416786918</v>
+        <v>1.176639416786917</v>
       </c>
       <c r="AK59" t="n">
-        <v>-0.5466394167869176</v>
+        <v>-0.5466394167869174</v>
       </c>
       <c r="AL59" t="n">
-        <v>0.5466394167869176</v>
+        <v>0.5466394167869174</v>
       </c>
       <c r="AM59" t="n">
-        <v>86.76816139474883</v>
+        <v>86.7681613947488</v>
       </c>
     </row>
     <row r="60">
@@ -8817,16 +8816,16 @@
         <v>1</v>
       </c>
       <c r="AJ60" t="n">
-        <v>1.277094708994709</v>
+        <v>1.277094708994708</v>
       </c>
       <c r="AK60" t="n">
-        <v>-0.3070947089947087</v>
+        <v>-0.3070947089947085</v>
       </c>
       <c r="AL60" t="n">
-        <v>0.3070947089947087</v>
+        <v>0.3070947089947085</v>
       </c>
       <c r="AM60" t="n">
-        <v>31.65924834996997</v>
+        <v>31.65924834996995</v>
       </c>
     </row>
     <row r="61">
@@ -8954,16 +8953,16 @@
         <v>1</v>
       </c>
       <c r="AJ61" t="n">
-        <v>3.871689457671957</v>
+        <v>3.871689457671956</v>
       </c>
       <c r="AK61" t="n">
-        <v>0.4583105423280429</v>
+        <v>0.4583105423280442</v>
       </c>
       <c r="AL61" t="n">
-        <v>0.4583105423280429</v>
+        <v>0.4583105423280442</v>
       </c>
       <c r="AM61" t="n">
-        <v>10.58453908378852</v>
+        <v>10.58453908378855</v>
       </c>
     </row>
     <row r="62">
@@ -9364,13 +9363,13 @@
         <v>2.085705972823475</v>
       </c>
       <c r="AK64" t="n">
-        <v>-0.7557059728234754</v>
+        <v>-0.7557059728234745</v>
       </c>
       <c r="AL64" t="n">
-        <v>0.7557059728234754</v>
+        <v>0.7557059728234745</v>
       </c>
       <c r="AM64" t="n">
-        <v>56.81999795665228</v>
+        <v>56.81999795665222</v>
       </c>
     </row>
     <row r="65">
@@ -9494,16 +9493,16 @@
         <v>1</v>
       </c>
       <c r="AJ65" t="n">
-        <v>1.780929669312168</v>
+        <v>1.780929669312169</v>
       </c>
       <c r="AK65" t="n">
-        <v>-0.3709296693121682</v>
+        <v>-0.3709296693121686</v>
       </c>
       <c r="AL65" t="n">
-        <v>0.3709296693121682</v>
+        <v>0.3709296693121686</v>
       </c>
       <c r="AM65" t="n">
-        <v>26.30706874554384</v>
+        <v>26.30706874554388</v>
       </c>
     </row>
     <row r="66">
@@ -9640,7 +9639,7 @@
         <v>1.065705972823475</v>
       </c>
       <c r="AM66" t="n">
-        <v>104.4809777277917</v>
+        <v>104.4809777277916</v>
       </c>
     </row>
     <row r="67">
@@ -9908,13 +9907,13 @@
         <v>2.883526487493988</v>
       </c>
       <c r="AK68" t="n">
-        <v>-0.4435264874939877</v>
+        <v>-0.4435264874939882</v>
       </c>
       <c r="AL68" t="n">
-        <v>0.4435264874939877</v>
+        <v>0.4435264874939882</v>
       </c>
       <c r="AM68" t="n">
-        <v>18.17731506122901</v>
+        <v>18.17731506122902</v>
       </c>
     </row>
     <row r="69">
@@ -10182,13 +10181,13 @@
         <v>1.513129493931993</v>
       </c>
       <c r="AK70" t="n">
-        <v>-0.223129493931993</v>
+        <v>-0.2231294939319928</v>
       </c>
       <c r="AL70" t="n">
-        <v>0.223129493931993</v>
+        <v>0.2231294939319928</v>
       </c>
       <c r="AM70" t="n">
-        <v>17.29685999472814</v>
+        <v>17.29685999472812</v>
       </c>
     </row>
     <row r="71">
@@ -10452,13 +10451,13 @@
         <v>1.90175482804233</v>
       </c>
       <c r="AK72" t="n">
-        <v>-0.08175482804232947</v>
+        <v>-0.08175482804232992</v>
       </c>
       <c r="AL72" t="n">
-        <v>0.08175482804232947</v>
+        <v>0.08175482804232992</v>
       </c>
       <c r="AM72" t="n">
-        <v>4.492023518809312</v>
+        <v>4.492023518809336</v>
       </c>
     </row>
     <row r="73">
@@ -10582,16 +10581,16 @@
         <v>1</v>
       </c>
       <c r="AJ73" t="n">
-        <v>2.041258558201058</v>
+        <v>2.041258558201059</v>
       </c>
       <c r="AK73" t="n">
-        <v>0.09874144179894184</v>
+        <v>0.09874144179894095</v>
       </c>
       <c r="AL73" t="n">
-        <v>0.09874144179894184</v>
+        <v>0.09874144179894095</v>
       </c>
       <c r="AM73" t="n">
-        <v>4.614086065371114</v>
+        <v>4.614086065371072</v>
       </c>
     </row>
     <row r="74">
@@ -11132,16 +11131,16 @@
         <v>1</v>
       </c>
       <c r="AJ77" t="n">
-        <v>3.888647647907648</v>
+        <v>3.888647647907647</v>
       </c>
       <c r="AK77" t="n">
-        <v>0.7613523520923526</v>
+        <v>0.7613523520923531</v>
       </c>
       <c r="AL77" t="n">
-        <v>0.7613523520923526</v>
+        <v>0.7613523520923531</v>
       </c>
       <c r="AM77" t="n">
-        <v>16.37316886220113</v>
+        <v>16.37316886220114</v>
       </c>
     </row>
     <row r="78">
@@ -11412,16 +11411,16 @@
         <v>1</v>
       </c>
       <c r="AJ79" t="n">
-        <v>1.767020593018093</v>
+        <v>1.767020593018094</v>
       </c>
       <c r="AK79" t="n">
-        <v>0.382979406981907</v>
+        <v>0.3829794069819061</v>
       </c>
       <c r="AL79" t="n">
-        <v>0.382979406981907</v>
+        <v>0.3829794069819061</v>
       </c>
       <c r="AM79" t="n">
-        <v>17.81299567357707</v>
+        <v>17.81299567357703</v>
       </c>
     </row>
     <row r="80">
@@ -11549,16 +11548,16 @@
         <v>1</v>
       </c>
       <c r="AJ80" t="n">
-        <v>3.888647647907648</v>
+        <v>3.888647647907647</v>
       </c>
       <c r="AK80" t="n">
-        <v>0.3613523520923523</v>
+        <v>0.3613523520923527</v>
       </c>
       <c r="AL80" t="n">
-        <v>0.3613523520923523</v>
+        <v>0.3613523520923527</v>
       </c>
       <c r="AM80" t="n">
-        <v>8.502408284525936</v>
+        <v>8.502408284525947</v>
       </c>
     </row>
     <row r="81">
@@ -11826,13 +11825,13 @@
         <v>2.295999981962481</v>
       </c>
       <c r="AK82" t="n">
-        <v>-0.04599998196248078</v>
+        <v>-0.04599998196248123</v>
       </c>
       <c r="AL82" t="n">
-        <v>0.04599998196248078</v>
+        <v>0.04599998196248123</v>
       </c>
       <c r="AM82" t="n">
-        <v>2.044443642776923</v>
+        <v>2.044443642776943</v>
       </c>
     </row>
     <row r="83">
@@ -12106,7 +12105,7 @@
         <v>1.014595998075998</v>
       </c>
       <c r="AM84" t="n">
-        <v>40.58383992303992</v>
+        <v>40.58383992303994</v>
       </c>
     </row>
     <row r="85">
@@ -12240,16 +12239,16 @@
         <v>0</v>
       </c>
       <c r="AJ85" t="n">
-        <v>9.630595151515156</v>
+        <v>9.630595151515152</v>
       </c>
       <c r="AK85" t="n">
-        <v>0.6694048484848452</v>
+        <v>0.6694048484848487</v>
       </c>
       <c r="AL85" t="n">
-        <v>0.6694048484848452</v>
+        <v>0.6694048484848487</v>
       </c>
       <c r="AM85" t="n">
-        <v>6.499076198881991</v>
+        <v>6.499076198882026</v>
       </c>
     </row>
     <row r="86">
@@ -12377,16 +12376,16 @@
         <v>1</v>
       </c>
       <c r="AJ86" t="n">
-        <v>3.888647647907648</v>
+        <v>3.888647647907647</v>
       </c>
       <c r="AK86" t="n">
-        <v>0.1013523520923525</v>
+        <v>0.1013523520923529</v>
       </c>
       <c r="AL86" t="n">
-        <v>0.1013523520923525</v>
+        <v>0.1013523520923529</v>
       </c>
       <c r="AM86" t="n">
-        <v>2.540159200309586</v>
+        <v>2.540159200309597</v>
       </c>
     </row>
     <row r="87">
@@ -12517,13 +12516,13 @@
         <v>1.625353968253968</v>
       </c>
       <c r="AK87" t="n">
-        <v>-0.5253539682539681</v>
+        <v>-0.5253539682539676</v>
       </c>
       <c r="AL87" t="n">
-        <v>0.5253539682539681</v>
+        <v>0.5253539682539676</v>
       </c>
       <c r="AM87" t="n">
-        <v>47.75945165945164</v>
+        <v>47.7594516594516</v>
       </c>
     </row>
     <row r="88">
@@ -12654,13 +12653,13 @@
         <v>1.062992685185185</v>
       </c>
       <c r="AK88" t="n">
-        <v>-0.1329926851851851</v>
+        <v>-0.1329926851851854</v>
       </c>
       <c r="AL88" t="n">
-        <v>0.1329926851851851</v>
+        <v>0.1329926851851854</v>
       </c>
       <c r="AM88" t="n">
-        <v>14.3002887295898</v>
+        <v>14.30028872958983</v>
       </c>
     </row>
     <row r="89">
@@ -13336,16 +13335,16 @@
         <v>1</v>
       </c>
       <c r="AJ93" t="n">
-        <v>2.208112014189516</v>
+        <v>2.208112014189517</v>
       </c>
       <c r="AK93" t="n">
-        <v>0.391887985810484</v>
+        <v>0.3918879858104836</v>
       </c>
       <c r="AL93" t="n">
-        <v>0.391887985810484</v>
+        <v>0.3918879858104836</v>
       </c>
       <c r="AM93" t="n">
-        <v>15.07261483886477</v>
+        <v>15.07261483886475</v>
       </c>
     </row>
     <row r="94">
@@ -13747,16 +13746,16 @@
         <v>1</v>
       </c>
       <c r="AJ96" t="n">
-        <v>1.89810628066378</v>
+        <v>1.898106280663781</v>
       </c>
       <c r="AK96" t="n">
-        <v>-0.07810628066378023</v>
+        <v>-0.07810628066378045</v>
       </c>
       <c r="AL96" t="n">
-        <v>0.07810628066378023</v>
+        <v>0.07810628066378045</v>
       </c>
       <c r="AM96" t="n">
-        <v>4.291553882625287</v>
+        <v>4.291553882625299</v>
       </c>
     </row>
     <row r="97">
@@ -13884,16 +13883,16 @@
         <v>1</v>
       </c>
       <c r="AJ97" t="n">
-        <v>3.885013915343911</v>
+        <v>3.885013915343912</v>
       </c>
       <c r="AK97" t="n">
-        <v>2.744986084656089</v>
+        <v>2.744986084656088</v>
       </c>
       <c r="AL97" t="n">
-        <v>2.744986084656089</v>
+        <v>2.744986084656088</v>
       </c>
       <c r="AM97" t="n">
-        <v>41.40250504760316</v>
+        <v>41.40250504760314</v>
       </c>
     </row>
     <row r="98">
@@ -14021,16 +14020,16 @@
         <v>1</v>
       </c>
       <c r="AJ98" t="n">
-        <v>1.083956402116403</v>
+        <v>1.083956402116402</v>
       </c>
       <c r="AK98" t="n">
-        <v>-0.01395640211640248</v>
+        <v>-0.01395640211640203</v>
       </c>
       <c r="AL98" t="n">
-        <v>0.01395640211640248</v>
+        <v>0.01395640211640203</v>
       </c>
       <c r="AM98" t="n">
-        <v>1.304336646392755</v>
+        <v>1.304336646392713</v>
       </c>
     </row>
     <row r="99">
@@ -14161,13 +14160,13 @@
         <v>1.54970369047619</v>
       </c>
       <c r="AK99" t="n">
-        <v>0.03029630952381002</v>
+        <v>0.03029630952380979</v>
       </c>
       <c r="AL99" t="n">
-        <v>0.03029630952381002</v>
+        <v>0.03029630952380979</v>
       </c>
       <c r="AM99" t="n">
-        <v>1.917487944544938</v>
+        <v>1.917487944544924</v>
       </c>
     </row>
     <row r="100">
@@ -14304,7 +14303,7 @@
         <v>2.220080687830686</v>
       </c>
       <c r="AM100" t="n">
-        <v>44.13679299862199</v>
+        <v>44.13679299862198</v>
       </c>
     </row>
     <row r="101">
@@ -14569,16 +14568,16 @@
         <v>1</v>
       </c>
       <c r="AJ102" t="n">
-        <v>3.787072552910053</v>
+        <v>3.787072552910051</v>
       </c>
       <c r="AK102" t="n">
-        <v>0.5629274470899466</v>
+        <v>0.5629274470899484</v>
       </c>
       <c r="AL102" t="n">
-        <v>0.5629274470899466</v>
+        <v>0.5629274470899484</v>
       </c>
       <c r="AM102" t="n">
-        <v>12.94086085264245</v>
+        <v>12.94086085264249</v>
       </c>
     </row>
     <row r="103">
@@ -14706,13 +14705,13 @@
         <v>1</v>
       </c>
       <c r="AJ103" t="n">
-        <v>1.806977870555369</v>
+        <v>1.80697787055537</v>
       </c>
       <c r="AK103" t="n">
-        <v>3.443022129444631</v>
+        <v>3.44302212944463</v>
       </c>
       <c r="AL103" t="n">
-        <v>3.443022129444631</v>
+        <v>3.44302212944463</v>
       </c>
       <c r="AM103" t="n">
         <v>65.58137389418344</v>
@@ -14846,13 +14845,13 @@
         <v>3.885589593821213</v>
       </c>
       <c r="AK104" t="n">
-        <v>2.124410406178787</v>
+        <v>2.124410406178786</v>
       </c>
       <c r="AL104" t="n">
-        <v>2.124410406178787</v>
+        <v>2.124410406178786</v>
       </c>
       <c r="AM104" t="n">
-        <v>35.34792689149396</v>
+        <v>35.34792689149395</v>
       </c>
     </row>
     <row r="105">
@@ -14983,13 +14982,13 @@
         <v>1.513129493931993</v>
       </c>
       <c r="AK105" t="n">
-        <v>-0.263129493931993</v>
+        <v>-0.2631294939319928</v>
       </c>
       <c r="AL105" t="n">
-        <v>0.263129493931993</v>
+        <v>0.2631294939319928</v>
       </c>
       <c r="AM105" t="n">
-        <v>21.05035951455944</v>
+        <v>21.05035951455942</v>
       </c>
     </row>
     <row r="106">
@@ -15120,13 +15119,13 @@
         <v>1.625353968253968</v>
       </c>
       <c r="AK106" t="n">
-        <v>-0.9753539682539681</v>
+        <v>-0.9753539682539677</v>
       </c>
       <c r="AL106" t="n">
-        <v>0.9753539682539681</v>
+        <v>0.9753539682539677</v>
       </c>
       <c r="AM106" t="n">
-        <v>150.0544566544566</v>
+        <v>150.0544566544565</v>
       </c>
     </row>
     <row r="107">
@@ -15540,16 +15539,16 @@
         <v>1</v>
       </c>
       <c r="AJ109" t="n">
-        <v>3.888647647907648</v>
+        <v>3.888647647907647</v>
       </c>
       <c r="AK109" t="n">
-        <v>0.2113523520923519</v>
+        <v>0.2113523520923524</v>
       </c>
       <c r="AL109" t="n">
-        <v>0.2113523520923519</v>
+        <v>0.2113523520923524</v>
       </c>
       <c r="AM109" t="n">
-        <v>5.154935416886633</v>
+        <v>5.154935416886643</v>
       </c>
     </row>
     <row r="110">
@@ -15826,16 +15825,16 @@
         <v>0</v>
       </c>
       <c r="AJ111" t="n">
-        <v>1.751355132275133</v>
+        <v>1.751355132275132</v>
       </c>
       <c r="AK111" t="n">
-        <v>-0.4213551322751325</v>
+        <v>-0.4213551322751323</v>
       </c>
       <c r="AL111" t="n">
-        <v>0.4213551322751325</v>
+        <v>0.4213551322751323</v>
       </c>
       <c r="AM111" t="n">
-        <v>31.68083701316786</v>
+        <v>31.68083701316785</v>
       </c>
     </row>
     <row r="112">
@@ -16252,13 +16251,13 @@
         <v>2.297098793891295</v>
       </c>
       <c r="AK114" t="n">
-        <v>0.1429012061087045</v>
+        <v>0.1429012061087049</v>
       </c>
       <c r="AL114" t="n">
-        <v>0.1429012061087045</v>
+        <v>0.1429012061087049</v>
       </c>
       <c r="AM114" t="n">
-        <v>5.85660680773379</v>
+        <v>5.856606807733809</v>
       </c>
     </row>
     <row r="115">
@@ -16660,16 +16659,16 @@
         <v>1</v>
       </c>
       <c r="AJ117" t="n">
-        <v>3.885013915343911</v>
+        <v>3.885013915343912</v>
       </c>
       <c r="AK117" t="n">
-        <v>-0.8950139153439105</v>
+        <v>-0.8950139153439118</v>
       </c>
       <c r="AL117" t="n">
-        <v>0.8950139153439105</v>
+        <v>0.8950139153439118</v>
       </c>
       <c r="AM117" t="n">
-        <v>29.93357576401039</v>
+        <v>29.93357576401043</v>
       </c>
     </row>
     <row r="118">
@@ -16797,16 +16796,16 @@
         <v>1</v>
       </c>
       <c r="AJ118" t="n">
-        <v>3.87708044973545</v>
+        <v>3.877080449735449</v>
       </c>
       <c r="AK118" t="n">
-        <v>0.20291955026455</v>
+        <v>0.2029195502645513</v>
       </c>
       <c r="AL118" t="n">
-        <v>0.20291955026455</v>
+        <v>0.2029195502645513</v>
       </c>
       <c r="AM118" t="n">
-        <v>4.973518388837009</v>
+        <v>4.973518388837042</v>
       </c>
     </row>
     <row r="119">
@@ -16934,16 +16933,16 @@
         <v>1</v>
       </c>
       <c r="AJ119" t="n">
-        <v>2.476247015392014</v>
+        <v>2.476247015392016</v>
       </c>
       <c r="AK119" t="n">
-        <v>-0.0962470153920143</v>
+        <v>-0.09624701539201608</v>
       </c>
       <c r="AL119" t="n">
-        <v>0.0962470153920143</v>
+        <v>0.09624701539201608</v>
       </c>
       <c r="AM119" t="n">
-        <v>4.043992243361946</v>
+        <v>4.043992243362021</v>
       </c>
     </row>
     <row r="120">
@@ -17634,13 +17633,13 @@
         <v>17.74503232804232</v>
       </c>
       <c r="AK124" t="n">
-        <v>-1.045032328042325</v>
+        <v>-1.045032328042321</v>
       </c>
       <c r="AL124" t="n">
-        <v>1.045032328042325</v>
+        <v>1.045032328042321</v>
       </c>
       <c r="AM124" t="n">
-        <v>6.257678611031886</v>
+        <v>6.257678611031864</v>
       </c>
     </row>
     <row r="125">
@@ -17774,16 +17773,16 @@
         <v>0</v>
       </c>
       <c r="AJ125" t="n">
-        <v>7.055484298941805</v>
+        <v>7.055484298941801</v>
       </c>
       <c r="AK125" t="n">
-        <v>0.4245157010581959</v>
+        <v>0.4245157010581995</v>
       </c>
       <c r="AL125" t="n">
-        <v>0.4245157010581959</v>
+        <v>0.4245157010581995</v>
       </c>
       <c r="AM125" t="n">
-        <v>5.675343597034704</v>
+        <v>5.675343597034752</v>
       </c>
     </row>
     <row r="126">
@@ -17920,13 +17919,13 @@
         <v>1.59185244107744</v>
       </c>
       <c r="AK126" t="n">
-        <v>-0.7818524410774397</v>
+        <v>-0.7818524410774399</v>
       </c>
       <c r="AL126" t="n">
-        <v>0.7818524410774397</v>
+        <v>0.7818524410774399</v>
       </c>
       <c r="AM126" t="n">
-        <v>96.52499272560982</v>
+        <v>96.52499272560986</v>
       </c>
     </row>
     <row r="127">
@@ -18063,13 +18062,13 @@
         <v>12.50060474987974</v>
       </c>
       <c r="AK127" t="n">
-        <v>-1.200604749879739</v>
+        <v>-1.200604749879737</v>
       </c>
       <c r="AL127" t="n">
-        <v>1.200604749879739</v>
+        <v>1.200604749879737</v>
       </c>
       <c r="AM127" t="n">
-        <v>10.62482079539592</v>
+        <v>10.6248207953959</v>
       </c>
     </row>
     <row r="128">
@@ -18212,13 +18211,13 @@
         <v>2.629777041847041</v>
       </c>
       <c r="AK128" t="n">
-        <v>0.3702229581529588</v>
+        <v>0.3702229581529592</v>
       </c>
       <c r="AL128" t="n">
-        <v>0.3702229581529588</v>
+        <v>0.3702229581529592</v>
       </c>
       <c r="AM128" t="n">
-        <v>12.34076527176529</v>
+        <v>12.34076527176531</v>
       </c>
     </row>
     <row r="129">
@@ -18498,13 +18497,13 @@
         <v>1.811892325637327</v>
       </c>
       <c r="AK130" t="n">
-        <v>0.08810767436267297</v>
+        <v>0.08810767436267253</v>
       </c>
       <c r="AL130" t="n">
-        <v>0.08810767436267297</v>
+        <v>0.08810767436267253</v>
       </c>
       <c r="AM130" t="n">
-        <v>4.637246019088051</v>
+        <v>4.637246019088028</v>
       </c>
     </row>
     <row r="131">
@@ -18778,7 +18777,7 @@
         <v>1.424646031746032</v>
       </c>
       <c r="AM132" t="n">
-        <v>46.70970595888629</v>
+        <v>46.7097059588863</v>
       </c>
     </row>
     <row r="133">
@@ -18906,16 +18905,16 @@
         <v>1</v>
       </c>
       <c r="AJ133" t="n">
-        <v>1.965098784271285</v>
+        <v>1.965098784271284</v>
       </c>
       <c r="AK133" t="n">
-        <v>-0.1850987842712846</v>
+        <v>-0.1850987842712841</v>
       </c>
       <c r="AL133" t="n">
-        <v>0.1850987842712846</v>
+        <v>0.1850987842712841</v>
       </c>
       <c r="AM133" t="n">
-        <v>10.39880810512835</v>
+        <v>10.39880810512832</v>
       </c>
     </row>
     <row r="134">
@@ -19052,13 +19051,13 @@
         <v>15.72545809644059</v>
       </c>
       <c r="AK134" t="n">
-        <v>-1.425458096440591</v>
+        <v>-1.425458096440588</v>
       </c>
       <c r="AL134" t="n">
-        <v>1.425458096440591</v>
+        <v>1.425458096440588</v>
       </c>
       <c r="AM134" t="n">
-        <v>9.968238436647493</v>
+        <v>9.968238436647466</v>
       </c>
     </row>
     <row r="135">
@@ -19186,16 +19185,16 @@
         <v>1</v>
       </c>
       <c r="AJ135" t="n">
-        <v>1.965098784271285</v>
+        <v>1.965098784271284</v>
       </c>
       <c r="AK135" t="n">
-        <v>-0.1350987842712845</v>
+        <v>-0.1350987842712841</v>
       </c>
       <c r="AL135" t="n">
-        <v>0.1350987842712845</v>
+        <v>0.1350987842712841</v>
       </c>
       <c r="AM135" t="n">
-        <v>7.382447227939045</v>
+        <v>7.382447227939021</v>
       </c>
     </row>
     <row r="136">
@@ -19323,16 +19322,16 @@
         <v>1</v>
       </c>
       <c r="AJ136" t="n">
-        <v>3.641903664021162</v>
+        <v>3.641903664021164</v>
       </c>
       <c r="AK136" t="n">
-        <v>-0.8819036640211624</v>
+        <v>-0.8819036640211642</v>
       </c>
       <c r="AL136" t="n">
-        <v>0.8819036640211624</v>
+        <v>0.8819036640211642</v>
       </c>
       <c r="AM136" t="n">
-        <v>31.95303130511458</v>
+        <v>31.95303130511465</v>
       </c>
     </row>
     <row r="137">
@@ -19606,13 +19605,13 @@
         <v>2.085705972823475</v>
       </c>
       <c r="AK138" t="n">
-        <v>0.7742940271765244</v>
+        <v>0.7742940271765253</v>
       </c>
       <c r="AL138" t="n">
-        <v>0.7742940271765244</v>
+        <v>0.7742940271765253</v>
       </c>
       <c r="AM138" t="n">
-        <v>27.07321773344491</v>
+        <v>27.07321773344494</v>
       </c>
     </row>
     <row r="139">
@@ -19755,13 +19754,13 @@
         <v>2.362494923039923</v>
       </c>
       <c r="AK139" t="n">
-        <v>-0.1224949230399228</v>
+        <v>-0.1224949230399233</v>
       </c>
       <c r="AL139" t="n">
-        <v>0.1224949230399228</v>
+        <v>0.1224949230399233</v>
       </c>
       <c r="AM139" t="n">
-        <v>5.468523349996554</v>
+        <v>5.468523349996573</v>
       </c>
     </row>
     <row r="140">
@@ -19904,13 +19903,13 @@
         <v>2.629777041847041</v>
       </c>
       <c r="AK140" t="n">
-        <v>-0.3497770418470414</v>
+        <v>-0.3497770418470409</v>
       </c>
       <c r="AL140" t="n">
-        <v>0.3497770418470414</v>
+        <v>0.3497770418470409</v>
       </c>
       <c r="AM140" t="n">
-        <v>15.34109832662462</v>
+        <v>15.34109832662461</v>
       </c>
     </row>
     <row r="141">
@@ -20053,13 +20052,13 @@
         <v>2.629777041847041</v>
       </c>
       <c r="AK141" t="n">
-        <v>0.9602229581529587</v>
+        <v>0.9602229581529591</v>
       </c>
       <c r="AL141" t="n">
-        <v>0.9602229581529587</v>
+        <v>0.9602229581529591</v>
       </c>
       <c r="AM141" t="n">
-        <v>26.74715760871752</v>
+        <v>26.74715760871753</v>
       </c>
     </row>
     <row r="142">
@@ -20324,16 +20323,16 @@
         <v>1</v>
       </c>
       <c r="AJ143" t="n">
-        <v>2.325889386724385</v>
+        <v>2.325889386724386</v>
       </c>
       <c r="AK143" t="n">
-        <v>0.5141106132756144</v>
+        <v>0.5141106132756139</v>
       </c>
       <c r="AL143" t="n">
-        <v>0.5141106132756144</v>
+        <v>0.5141106132756139</v>
       </c>
       <c r="AM143" t="n">
-        <v>18.10248638294417</v>
+        <v>18.10248638294415</v>
       </c>
     </row>
     <row r="144">
@@ -20610,16 +20609,16 @@
         <v>0</v>
       </c>
       <c r="AJ145" t="n">
-        <v>1.583004741462241</v>
+        <v>1.583004741462242</v>
       </c>
       <c r="AK145" t="n">
-        <v>0.06699525853775845</v>
+        <v>0.06699525853775823</v>
       </c>
       <c r="AL145" t="n">
-        <v>0.06699525853775845</v>
+        <v>0.06699525853775823</v>
       </c>
       <c r="AM145" t="n">
-        <v>4.060318699258088</v>
+        <v>4.060318699258074</v>
       </c>
     </row>
     <row r="146">
@@ -20887,13 +20886,13 @@
         <v>4.69954681697932</v>
       </c>
       <c r="AK147" t="n">
-        <v>-0.5695468169793196</v>
+        <v>-0.5695468169793205</v>
       </c>
       <c r="AL147" t="n">
-        <v>0.5695468169793196</v>
+        <v>0.5695468169793205</v>
       </c>
       <c r="AM147" t="n">
-        <v>13.79047983000774</v>
+        <v>13.79047983000776</v>
       </c>
     </row>
     <row r="148">
@@ -21021,16 +21020,16 @@
         <v>1</v>
       </c>
       <c r="AJ148" t="n">
-        <v>2.032281642616643</v>
+        <v>2.032281642616644</v>
       </c>
       <c r="AK148" t="n">
-        <v>-0.9922816426166432</v>
+        <v>-0.9922816426166436</v>
       </c>
       <c r="AL148" t="n">
-        <v>0.9922816426166432</v>
+        <v>0.9922816426166436</v>
       </c>
       <c r="AM148" t="n">
-        <v>95.41169640544645</v>
+        <v>95.41169640544651</v>
       </c>
     </row>
     <row r="149">
@@ -21161,13 +21160,13 @@
         <v>3.350020873015874</v>
       </c>
       <c r="AK149" t="n">
-        <v>-0.1800208730158741</v>
+        <v>-0.1800208730158745</v>
       </c>
       <c r="AL149" t="n">
-        <v>0.1800208730158741</v>
+        <v>0.1800208730158745</v>
       </c>
       <c r="AM149" t="n">
-        <v>5.67889189324524</v>
+        <v>5.678891893245254</v>
       </c>
     </row>
     <row r="150">
@@ -21298,13 +21297,13 @@
         <v>3.450294206349207</v>
       </c>
       <c r="AK150" t="n">
-        <v>-0.5502942063492076</v>
+        <v>-0.5502942063492067</v>
       </c>
       <c r="AL150" t="n">
-        <v>0.5502942063492076</v>
+        <v>0.5502942063492067</v>
       </c>
       <c r="AM150" t="n">
-        <v>18.97566228790371</v>
+        <v>18.97566228790368</v>
       </c>
     </row>
     <row r="151">
@@ -21575,16 +21574,16 @@
         <v>1</v>
       </c>
       <c r="AJ152" t="n">
-        <v>4.662638615921118</v>
+        <v>4.662638615921117</v>
       </c>
       <c r="AK152" t="n">
-        <v>0.1873613840788817</v>
+        <v>0.1873613840788826</v>
       </c>
       <c r="AL152" t="n">
-        <v>0.1873613840788817</v>
+        <v>0.1873613840788826</v>
       </c>
       <c r="AM152" t="n">
-        <v>3.863121321214056</v>
+        <v>3.863121321214074</v>
       </c>
     </row>
     <row r="153">
@@ -21715,13 +21714,13 @@
         <v>1.514634576719576</v>
       </c>
       <c r="AK153" t="n">
-        <v>-0.2546345767195759</v>
+        <v>-0.2546345767195757</v>
       </c>
       <c r="AL153" t="n">
-        <v>0.2546345767195759</v>
+        <v>0.2546345767195757</v>
       </c>
       <c r="AM153" t="n">
-        <v>20.20909339044253</v>
+        <v>20.20909339044251</v>
       </c>
     </row>
     <row r="154">
@@ -21992,16 +21991,16 @@
         <v>1</v>
       </c>
       <c r="AJ155" t="n">
-        <v>1.835973200780701</v>
+        <v>1.8359732007807</v>
       </c>
       <c r="AK155" t="n">
-        <v>-0.3759732007807008</v>
+        <v>-0.3759732007807004</v>
       </c>
       <c r="AL155" t="n">
-        <v>0.3759732007807008</v>
+        <v>0.3759732007807004</v>
       </c>
       <c r="AM155" t="n">
-        <v>25.75158909456855</v>
+        <v>25.75158909456852</v>
       </c>
     </row>
     <row r="156">
@@ -22132,13 +22131,13 @@
         <v>1.972924073889075</v>
       </c>
       <c r="AK156" t="n">
-        <v>0.2870759261109248</v>
+        <v>0.2870759261109253</v>
       </c>
       <c r="AL156" t="n">
-        <v>0.2870759261109248</v>
+        <v>0.2870759261109253</v>
       </c>
       <c r="AM156" t="n">
-        <v>12.70247460667809</v>
+        <v>12.70247460667811</v>
       </c>
     </row>
     <row r="157">
@@ -22269,13 +22268,13 @@
         <v>1.763893063880564</v>
       </c>
       <c r="AK157" t="n">
-        <v>-0.8838930638805637</v>
+        <v>-0.8838930638805641</v>
       </c>
       <c r="AL157" t="n">
-        <v>0.8838930638805637</v>
+        <v>0.8838930638805641</v>
       </c>
       <c r="AM157" t="n">
-        <v>100.4423936227913</v>
+        <v>100.4423936227914</v>
       </c>
     </row>
     <row r="158">
@@ -22683,16 +22682,16 @@
         <v>1</v>
       </c>
       <c r="AJ160" t="n">
-        <v>1.738686216504084</v>
+        <v>1.738686216504085</v>
       </c>
       <c r="AK160" t="n">
-        <v>-0.6486862165040841</v>
+        <v>-0.6486862165040845</v>
       </c>
       <c r="AL160" t="n">
-        <v>0.6486862165040841</v>
+        <v>0.6486862165040845</v>
       </c>
       <c r="AM160" t="n">
-        <v>59.51249692698018</v>
+        <v>59.51249692698023</v>
       </c>
     </row>
     <row r="161">
@@ -22960,13 +22959,13 @@
         <v>1.527651190476189</v>
       </c>
       <c r="AK162" t="n">
-        <v>0.382348809523811</v>
+        <v>0.3823488095238108</v>
       </c>
       <c r="AL162" t="n">
-        <v>0.382348809523811</v>
+        <v>0.3823488095238108</v>
       </c>
       <c r="AM162" t="n">
-        <v>20.01826227873356</v>
+        <v>20.01826227873355</v>
       </c>
     </row>
     <row r="163">
@@ -23094,16 +23093,16 @@
         <v>1</v>
       </c>
       <c r="AJ163" t="n">
-        <v>1.971947158489658</v>
+        <v>1.97194715848966</v>
       </c>
       <c r="AK163" t="n">
-        <v>-0.1519471584896583</v>
+        <v>-0.1519471584896595</v>
       </c>
       <c r="AL163" t="n">
-        <v>0.1519471584896583</v>
+        <v>0.1519471584896595</v>
       </c>
       <c r="AM163" t="n">
-        <v>8.348744971959249</v>
+        <v>8.348744971959309</v>
       </c>
     </row>
     <row r="164">
@@ -23231,16 +23230,16 @@
         <v>1</v>
       </c>
       <c r="AJ164" t="n">
-        <v>1.971947158489658</v>
+        <v>1.97194715848966</v>
       </c>
       <c r="AK164" t="n">
-        <v>-0.2019471584896584</v>
+        <v>-0.2019471584896595</v>
       </c>
       <c r="AL164" t="n">
-        <v>0.2019471584896584</v>
+        <v>0.2019471584896595</v>
       </c>
       <c r="AM164" t="n">
-        <v>11.40944398246658</v>
+        <v>11.40944398246664</v>
       </c>
     </row>
     <row r="165">
@@ -23368,16 +23367,16 @@
         <v>1</v>
       </c>
       <c r="AJ165" t="n">
-        <v>1.173315846560846</v>
+        <v>1.173315846560847</v>
       </c>
       <c r="AK165" t="n">
-        <v>-0.1033158465608461</v>
+        <v>-0.1033158465608466</v>
       </c>
       <c r="AL165" t="n">
-        <v>0.1033158465608461</v>
+        <v>0.1033158465608466</v>
       </c>
       <c r="AM165" t="n">
-        <v>9.6556865944716</v>
+        <v>9.655686594471643</v>
       </c>
     </row>
     <row r="166">
@@ -23919,13 +23918,13 @@
         <v>2.227234012746513</v>
       </c>
       <c r="AK169" t="n">
-        <v>0.152765987253487</v>
+        <v>0.1527659872534866</v>
       </c>
       <c r="AL169" t="n">
-        <v>0.152765987253487</v>
+        <v>0.1527659872534866</v>
       </c>
       <c r="AM169" t="n">
-        <v>6.418738960230547</v>
+        <v>6.418738960230527</v>
       </c>
     </row>
     <row r="170">
@@ -24056,13 +24055,13 @@
         <v>1.732201150793649</v>
       </c>
       <c r="AK170" t="n">
-        <v>0.1477988492063513</v>
+        <v>0.1477988492063504</v>
       </c>
       <c r="AL170" t="n">
-        <v>0.1477988492063513</v>
+        <v>0.1477988492063504</v>
       </c>
       <c r="AM170" t="n">
-        <v>7.861640915231455</v>
+        <v>7.861640915231408</v>
       </c>
     </row>
     <row r="171">
@@ -24190,16 +24189,16 @@
         <v>1</v>
       </c>
       <c r="AJ171" t="n">
-        <v>4.402286764069266</v>
+        <v>4.402286764069265</v>
       </c>
       <c r="AK171" t="n">
-        <v>-0.1122867640692657</v>
+        <v>-0.1122867640692649</v>
       </c>
       <c r="AL171" t="n">
-        <v>0.1122867640692657</v>
+        <v>0.1122867640692649</v>
       </c>
       <c r="AM171" t="n">
-        <v>2.617407087861672</v>
+        <v>2.617407087861652</v>
       </c>
     </row>
     <row r="172">
@@ -24330,13 +24329,13 @@
         <v>1.527651190476189</v>
       </c>
       <c r="AK172" t="n">
-        <v>-0.6176511904761889</v>
+        <v>-0.6176511904761891</v>
       </c>
       <c r="AL172" t="n">
-        <v>0.6176511904761889</v>
+        <v>0.6176511904761891</v>
       </c>
       <c r="AM172" t="n">
-        <v>67.87375719518559</v>
+        <v>67.87375719518562</v>
       </c>
     </row>
     <row r="173">
@@ -24604,13 +24603,13 @@
         <v>1.527651190476189</v>
       </c>
       <c r="AK174" t="n">
-        <v>-0.6776511904761889</v>
+        <v>-0.6776511904761892</v>
       </c>
       <c r="AL174" t="n">
-        <v>0.6776511904761889</v>
+        <v>0.6776511904761892</v>
       </c>
       <c r="AM174" t="n">
-        <v>79.72366946778693</v>
+        <v>79.72366946778696</v>
       </c>
     </row>
     <row r="175">
@@ -24875,16 +24874,16 @@
         <v>1</v>
       </c>
       <c r="AJ176" t="n">
-        <v>1.101588161375662</v>
+        <v>1.101588161375661</v>
       </c>
       <c r="AK176" t="n">
-        <v>-0.02158816137566144</v>
+        <v>-0.02158816137566122</v>
       </c>
       <c r="AL176" t="n">
-        <v>0.02158816137566144</v>
+        <v>0.02158816137566122</v>
       </c>
       <c r="AM176" t="n">
-        <v>1.998903831079763</v>
+        <v>1.998903831079742</v>
       </c>
     </row>
     <row r="177">
@@ -25019,13 +25018,13 @@
         <v>1.580150209235209</v>
       </c>
       <c r="AK177" t="n">
-        <v>-0.7701502092352086</v>
+        <v>-0.7701502092352088</v>
       </c>
       <c r="AL177" t="n">
-        <v>0.7701502092352086</v>
+        <v>0.7701502092352088</v>
       </c>
       <c r="AM177" t="n">
-        <v>95.08027274508748</v>
+        <v>95.0802727450875</v>
       </c>
     </row>
     <row r="178">
@@ -25156,13 +25155,13 @@
         <v>1.705998516483517</v>
       </c>
       <c r="AK178" t="n">
-        <v>-0.735998516483517</v>
+        <v>-0.7359985164835168</v>
       </c>
       <c r="AL178" t="n">
-        <v>0.735998516483517</v>
+        <v>0.7359985164835168</v>
       </c>
       <c r="AM178" t="n">
-        <v>75.87613571995021</v>
+        <v>75.87613571995018</v>
       </c>
     </row>
     <row r="179">
@@ -25430,13 +25429,13 @@
         <v>1.678199214489215</v>
       </c>
       <c r="AK180" t="n">
-        <v>-0.2181992144892149</v>
+        <v>-0.2181992144892146</v>
       </c>
       <c r="AL180" t="n">
-        <v>0.2181992144892149</v>
+        <v>0.2181992144892146</v>
       </c>
       <c r="AM180" t="n">
-        <v>14.94515167734349</v>
+        <v>14.94515167734347</v>
       </c>
     </row>
     <row r="181">
@@ -25567,13 +25566,13 @@
         <v>2.544738071188072</v>
       </c>
       <c r="AK181" t="n">
-        <v>-1.144738071188073</v>
+        <v>-1.144738071188072</v>
       </c>
       <c r="AL181" t="n">
-        <v>1.144738071188073</v>
+        <v>1.144738071188072</v>
       </c>
       <c r="AM181" t="n">
-        <v>81.76700508486233</v>
+        <v>81.7670050848623</v>
       </c>
     </row>
     <row r="182">
@@ -26118,16 +26117,16 @@
         <v>1</v>
       </c>
       <c r="AJ185" t="n">
-        <v>4.268847777777781</v>
+        <v>4.268847777777778</v>
       </c>
       <c r="AK185" t="n">
-        <v>-1.998847777777781</v>
+        <v>-1.998847777777778</v>
       </c>
       <c r="AL185" t="n">
-        <v>1.998847777777781</v>
+        <v>1.998847777777778</v>
       </c>
       <c r="AM185" t="n">
-        <v>88.05496818404322</v>
+        <v>88.05496818404309</v>
       </c>
     </row>
     <row r="186">
@@ -26264,13 +26263,13 @@
         <v>1.443320615680615</v>
       </c>
       <c r="AK186" t="n">
-        <v>-0.2033206156806151</v>
+        <v>-0.2033206156806149</v>
       </c>
       <c r="AL186" t="n">
-        <v>0.2033206156806151</v>
+        <v>0.2033206156806149</v>
       </c>
       <c r="AM186" t="n">
-        <v>16.3968238452109</v>
+        <v>16.39682384521088</v>
       </c>
     </row>
     <row r="187">
@@ -26547,16 +26546,16 @@
         <v>0</v>
       </c>
       <c r="AJ188" t="n">
-        <v>8.209556750934251</v>
+        <v>8.209556750934249</v>
       </c>
       <c r="AK188" t="n">
-        <v>-0.4995567509342509</v>
+        <v>-0.4995567509342491</v>
       </c>
       <c r="AL188" t="n">
-        <v>0.4995567509342509</v>
+        <v>0.4995567509342491</v>
       </c>
       <c r="AM188" t="n">
-        <v>6.479335290976016</v>
+        <v>6.479335290975993</v>
       </c>
     </row>
     <row r="189">
@@ -26830,13 +26829,13 @@
         <v>19.46546778499278</v>
       </c>
       <c r="AK190" t="n">
-        <v>0.3345322150072256</v>
+        <v>0.3345322150072221</v>
       </c>
       <c r="AL190" t="n">
-        <v>0.3345322150072256</v>
+        <v>0.3345322150072221</v>
       </c>
       <c r="AM190" t="n">
-        <v>1.689556641450634</v>
+        <v>1.689556641450617</v>
       </c>
     </row>
     <row r="191">
@@ -26964,16 +26963,16 @@
         <v>1</v>
       </c>
       <c r="AJ191" t="n">
-        <v>1.728501367382618</v>
+        <v>1.728501367382617</v>
       </c>
       <c r="AK191" t="n">
-        <v>-0.2185013673826179</v>
+        <v>-0.2185013673826173</v>
       </c>
       <c r="AL191" t="n">
-        <v>0.2185013673826179</v>
+        <v>0.2185013673826173</v>
       </c>
       <c r="AM191" t="n">
-        <v>14.47028923063695</v>
+        <v>14.4702892306369</v>
       </c>
     </row>
     <row r="192">
@@ -27241,13 +27240,13 @@
         <v>1.763893063880564</v>
       </c>
       <c r="AK193" t="n">
-        <v>-0.3238930638805637</v>
+        <v>-0.3238930638805642</v>
       </c>
       <c r="AL193" t="n">
-        <v>0.3238930638805637</v>
+        <v>0.3238930638805642</v>
       </c>
       <c r="AM193" t="n">
-        <v>22.4925738805947</v>
+        <v>22.49257388059473</v>
       </c>
     </row>
     <row r="194">
@@ -27378,13 +27377,13 @@
         <v>1.763893063880564</v>
       </c>
       <c r="AK194" t="n">
-        <v>0.4561069361194365</v>
+        <v>0.4561069361194361</v>
       </c>
       <c r="AL194" t="n">
-        <v>0.4561069361194365</v>
+        <v>0.4561069361194361</v>
       </c>
       <c r="AM194" t="n">
-        <v>20.5453574828575</v>
+        <v>20.54535748285748</v>
       </c>
     </row>
     <row r="195">
@@ -27938,13 +27937,13 @@
         <v>1.763893063880564</v>
       </c>
       <c r="AK198" t="n">
-        <v>-0.7938930638805637</v>
+        <v>-0.7938930638805641</v>
       </c>
       <c r="AL198" t="n">
-        <v>0.7938930638805637</v>
+        <v>0.7938930638805641</v>
       </c>
       <c r="AM198" t="n">
-        <v>81.84464576088286</v>
+        <v>81.84464576088291</v>
       </c>
     </row>
     <row r="199">
@@ -28367,13 +28366,13 @@
         <v>16.2315825999001</v>
       </c>
       <c r="AK201" t="n">
-        <v>-0.2315825999001007</v>
+        <v>-0.2315825999000971</v>
       </c>
       <c r="AL201" t="n">
-        <v>0.2315825999001007</v>
+        <v>0.2315825999000971</v>
       </c>
       <c r="AM201" t="n">
-        <v>1.447391249375629</v>
+        <v>1.447391249375607</v>
       </c>
     </row>
     <row r="202">
@@ -28776,13 +28775,13 @@
         <v>1.763893063880564</v>
       </c>
       <c r="AK204" t="n">
-        <v>-0.9438930638805637</v>
+        <v>-0.9438930638805642</v>
       </c>
       <c r="AL204" t="n">
-        <v>0.9438930638805637</v>
+        <v>0.9438930638805642</v>
       </c>
       <c r="AM204" t="n">
-        <v>115.108910229337</v>
+        <v>115.1089102293371</v>
       </c>
     </row>
     <row r="205">
@@ -29053,16 +29052,16 @@
         <v>0</v>
       </c>
       <c r="AJ206" t="n">
-        <v>15.8138423160173</v>
+        <v>15.81384231601731</v>
       </c>
       <c r="AK206" t="n">
-        <v>4.586157683982695</v>
+        <v>4.586157683982691</v>
       </c>
       <c r="AL206" t="n">
-        <v>4.586157683982695</v>
+        <v>4.586157683982691</v>
       </c>
       <c r="AM206" t="n">
-        <v>22.48116511756223</v>
+        <v>22.48116511756221</v>
       </c>
     </row>
     <row r="207">
@@ -29336,13 +29335,13 @@
         <v>1.763893063880564</v>
       </c>
       <c r="AK208" t="n">
-        <v>0.3561069361194364</v>
+        <v>0.356106936119436</v>
       </c>
       <c r="AL208" t="n">
-        <v>0.3561069361194364</v>
+        <v>0.356106936119436</v>
       </c>
       <c r="AM208" t="n">
-        <v>16.79749698676587</v>
+        <v>16.79749698676585</v>
       </c>
     </row>
     <row r="209">
@@ -29473,13 +29472,13 @@
         <v>2.4491772005772</v>
       </c>
       <c r="AK209" t="n">
-        <v>-0.09917720057719981</v>
+        <v>-0.09917720057720025</v>
       </c>
       <c r="AL209" t="n">
-        <v>0.09917720057719981</v>
+        <v>0.09917720057720025</v>
       </c>
       <c r="AM209" t="n">
-        <v>4.220306407540417</v>
+        <v>4.220306407540436</v>
       </c>
     </row>
     <row r="210">
@@ -29744,16 +29743,16 @@
         <v>1</v>
       </c>
       <c r="AJ211" t="n">
-        <v>1.774524227994228</v>
+        <v>1.774524227994229</v>
       </c>
       <c r="AK211" t="n">
-        <v>-0.3445242279942284</v>
+        <v>-0.3445242279942289</v>
       </c>
       <c r="AL211" t="n">
-        <v>0.3445242279942284</v>
+        <v>0.3445242279942289</v>
       </c>
       <c r="AM211" t="n">
-        <v>24.09260335623975</v>
+        <v>24.09260335623978</v>
       </c>
     </row>
     <row r="212">
@@ -29884,13 +29883,13 @@
         <v>2.448274422799422</v>
       </c>
       <c r="AK212" t="n">
-        <v>-0.3982744227994219</v>
+        <v>-0.3982744227994224</v>
       </c>
       <c r="AL212" t="n">
-        <v>0.3982744227994219</v>
+        <v>0.3982744227994224</v>
       </c>
       <c r="AM212" t="n">
-        <v>19.42802062436205</v>
+        <v>19.42802062436207</v>
       </c>
     </row>
     <row r="213">
@@ -30018,16 +30017,16 @@
         <v>1</v>
       </c>
       <c r="AJ213" t="n">
-        <v>1.732801150793649</v>
+        <v>1.73280115079365</v>
       </c>
       <c r="AK213" t="n">
-        <v>2.907198849206351</v>
+        <v>2.90719884920635</v>
       </c>
       <c r="AL213" t="n">
-        <v>2.907198849206351</v>
+        <v>2.90719884920635</v>
       </c>
       <c r="AM213" t="n">
-        <v>62.65514761220584</v>
+        <v>62.65514761220582</v>
       </c>
     </row>
     <row r="214">
@@ -30158,10 +30157,10 @@
         <v>1.705998516483517</v>
       </c>
       <c r="AK214" t="n">
-        <v>0.4440014835164829</v>
+        <v>0.4440014835164832</v>
       </c>
       <c r="AL214" t="n">
-        <v>0.4440014835164829</v>
+        <v>0.4440014835164832</v>
       </c>
       <c r="AM214" t="n">
         <v>20.65123179146433</v>
@@ -30429,16 +30428,16 @@
         <v>1</v>
       </c>
       <c r="AJ216" t="n">
-        <v>1.980878304473304</v>
+        <v>1.980878304473305</v>
       </c>
       <c r="AK216" t="n">
-        <v>0.05912169552669577</v>
+        <v>0.05912169552669488</v>
       </c>
       <c r="AL216" t="n">
-        <v>0.05912169552669577</v>
+        <v>0.05912169552669488</v>
       </c>
       <c r="AM216" t="n">
-        <v>2.898122329739989</v>
+        <v>2.898122329739945</v>
       </c>
     </row>
     <row r="217">
@@ -30855,13 +30854,13 @@
         <v>1.939911293891294</v>
       </c>
       <c r="AK219" t="n">
-        <v>-0.039911293891294</v>
+        <v>-0.03991129389129444</v>
       </c>
       <c r="AL219" t="n">
-        <v>0.039911293891294</v>
+        <v>0.03991129389129444</v>
       </c>
       <c r="AM219" t="n">
-        <v>2.100594415331263</v>
+        <v>2.100594415331286</v>
       </c>
     </row>
     <row r="220">
@@ -30992,13 +30991,13 @@
         <v>3.456552593795091</v>
       </c>
       <c r="AK220" t="n">
-        <v>-0.8665525937950909</v>
+        <v>-0.8665525937950913</v>
       </c>
       <c r="AL220" t="n">
-        <v>0.8665525937950909</v>
+        <v>0.8665525937950913</v>
       </c>
       <c r="AM220" t="n">
-        <v>33.45762910405756</v>
+        <v>33.45762910405758</v>
       </c>
     </row>
     <row r="221">
@@ -31683,13 +31682,13 @@
         <v>1.74858850181137</v>
       </c>
       <c r="AK225" t="n">
-        <v>-0.2985885018113705</v>
+        <v>-0.2985885018113701</v>
       </c>
       <c r="AL225" t="n">
-        <v>0.2985885018113705</v>
+        <v>0.2985885018113701</v>
       </c>
       <c r="AM225" t="n">
-        <v>20.59231046974969</v>
+        <v>20.59231046974966</v>
       </c>
     </row>
     <row r="226">
@@ -31820,13 +31819,13 @@
         <v>1.126945898268398</v>
       </c>
       <c r="AK226" t="n">
-        <v>0.123054101731602</v>
+        <v>0.1230541017316023</v>
       </c>
       <c r="AL226" t="n">
-        <v>0.123054101731602</v>
+        <v>0.1230541017316023</v>
       </c>
       <c r="AM226" t="n">
-        <v>9.844328138528162</v>
+        <v>9.84432813852818</v>
       </c>
     </row>
     <row r="227">
@@ -32100,13 +32099,13 @@
         <v>1.763893063880564</v>
       </c>
       <c r="AK228" t="n">
-        <v>0.4161069361194365</v>
+        <v>0.4161069361194361</v>
       </c>
       <c r="AL228" t="n">
-        <v>0.4161069361194365</v>
+        <v>0.4161069361194361</v>
       </c>
       <c r="AM228" t="n">
-        <v>19.08747413391911</v>
+        <v>19.08747413391908</v>
       </c>
     </row>
     <row r="229">
@@ -32240,16 +32239,16 @@
         <v>0</v>
       </c>
       <c r="AJ229" t="n">
-        <v>7.97987240740741</v>
+        <v>7.979872407407409</v>
       </c>
       <c r="AK229" t="n">
-        <v>-1.47987240740741</v>
+        <v>-1.479872407407409</v>
       </c>
       <c r="AL229" t="n">
-        <v>1.47987240740741</v>
+        <v>1.479872407407409</v>
       </c>
       <c r="AM229" t="n">
-        <v>22.76726780626785</v>
+        <v>22.76726780626784</v>
       </c>
     </row>
     <row r="230">
@@ -32383,16 +32382,16 @@
         <v>0</v>
       </c>
       <c r="AJ230" t="n">
-        <v>21.99735379990379</v>
+        <v>21.99735379990378</v>
       </c>
       <c r="AK230" t="n">
-        <v>-1.997353799903788</v>
+        <v>-1.997353799903784</v>
       </c>
       <c r="AL230" t="n">
-        <v>1.997353799903788</v>
+        <v>1.997353799903784</v>
       </c>
       <c r="AM230" t="n">
-        <v>9.98676899951894</v>
+        <v>9.986768999518922</v>
       </c>
     </row>
     <row r="231">
@@ -32523,13 +32522,13 @@
         <v>1.74858850181137</v>
       </c>
       <c r="AK231" t="n">
-        <v>-0.3385885018113706</v>
+        <v>-0.3385885018113701</v>
       </c>
       <c r="AL231" t="n">
-        <v>0.3385885018113706</v>
+        <v>0.3385885018113701</v>
       </c>
       <c r="AM231" t="n">
-        <v>24.01336892279224</v>
+        <v>24.01336892279221</v>
       </c>
     </row>
     <row r="232">
@@ -32794,16 +32793,16 @@
         <v>1</v>
       </c>
       <c r="AJ233" t="n">
-        <v>4.082377008177006</v>
+        <v>4.082377008177005</v>
       </c>
       <c r="AK233" t="n">
-        <v>-0.182377008177006</v>
+        <v>-0.1823770081770051</v>
       </c>
       <c r="AL233" t="n">
-        <v>0.182377008177006</v>
+        <v>0.1823770081770051</v>
       </c>
       <c r="AM233" t="n">
-        <v>4.676333543000153</v>
+        <v>4.67633354300013</v>
       </c>
     </row>
     <row r="234">
@@ -32943,16 +32942,16 @@
         <v>0</v>
       </c>
       <c r="AJ234" t="n">
-        <v>13.8556945093795</v>
+        <v>13.85569450937951</v>
       </c>
       <c r="AK234" t="n">
-        <v>-4.455694509379503</v>
+        <v>-4.455694509379505</v>
       </c>
       <c r="AL234" t="n">
-        <v>4.455694509379503</v>
+        <v>4.455694509379505</v>
       </c>
       <c r="AM234" t="n">
-        <v>47.40100541893089</v>
+        <v>47.4010054189309</v>
       </c>
     </row>
     <row r="235">
@@ -33217,16 +33216,16 @@
         <v>1</v>
       </c>
       <c r="AJ236" t="n">
-        <v>1.29416414021164</v>
+        <v>1.294164140211641</v>
       </c>
       <c r="AK236" t="n">
-        <v>0.3958358597883596</v>
+        <v>0.3958358597883593</v>
       </c>
       <c r="AL236" t="n">
-        <v>0.3958358597883596</v>
+        <v>0.3958358597883593</v>
       </c>
       <c r="AM236" t="n">
-        <v>23.42224022416329</v>
+        <v>23.42224022416328</v>
       </c>
     </row>
     <row r="237">
@@ -33494,13 +33493,13 @@
         <v>1.710446558441558</v>
       </c>
       <c r="AK238" t="n">
-        <v>0.599553441558442</v>
+        <v>0.5995534415584416</v>
       </c>
       <c r="AL238" t="n">
-        <v>0.599553441558442</v>
+        <v>0.5995534415584416</v>
       </c>
       <c r="AM238" t="n">
-        <v>25.9546944397594</v>
+        <v>25.95469443975937</v>
       </c>
     </row>
     <row r="239">
@@ -33628,16 +33627,16 @@
         <v>1</v>
       </c>
       <c r="AJ239" t="n">
-        <v>3.285731184463682</v>
+        <v>3.285731184463683</v>
       </c>
       <c r="AK239" t="n">
-        <v>-0.1757311844636824</v>
+        <v>-0.1757311844636829</v>
       </c>
       <c r="AL239" t="n">
-        <v>0.1757311844636824</v>
+        <v>0.1757311844636829</v>
       </c>
       <c r="AM239" t="n">
-        <v>5.650520400761493</v>
+        <v>5.650520400761507</v>
       </c>
     </row>
     <row r="240">
@@ -34176,16 +34175,16 @@
         <v>1</v>
       </c>
       <c r="AJ243" t="n">
-        <v>2.114847995245496</v>
+        <v>2.114847995245495</v>
       </c>
       <c r="AK243" t="n">
-        <v>0.2151520047545037</v>
+        <v>0.2151520047545046</v>
       </c>
       <c r="AL243" t="n">
-        <v>0.2151520047545037</v>
+        <v>0.2151520047545046</v>
       </c>
       <c r="AM243" t="n">
-        <v>9.233991620364964</v>
+        <v>9.233991620365003</v>
       </c>
     </row>
     <row r="244">
@@ -34313,16 +34312,16 @@
         <v>1</v>
       </c>
       <c r="AJ244" t="n">
-        <v>2.114847995245496</v>
+        <v>2.114847995245495</v>
       </c>
       <c r="AK244" t="n">
-        <v>0.2151520047545037</v>
+        <v>0.2151520047545046</v>
       </c>
       <c r="AL244" t="n">
-        <v>0.2151520047545037</v>
+        <v>0.2151520047545046</v>
       </c>
       <c r="AM244" t="n">
-        <v>9.233991620364964</v>
+        <v>9.233991620365003</v>
       </c>
     </row>
     <row r="245">
@@ -34459,13 +34458,13 @@
         <v>18.98870588929589</v>
       </c>
       <c r="AK245" t="n">
-        <v>-2.98870588929589</v>
+        <v>-2.988705889295893</v>
       </c>
       <c r="AL245" t="n">
-        <v>2.98870588929589</v>
+        <v>2.988705889295893</v>
       </c>
       <c r="AM245" t="n">
-        <v>18.67941180809931</v>
+        <v>18.67941180809933</v>
       </c>
     </row>
     <row r="246">
@@ -34730,16 +34729,16 @@
         <v>1</v>
       </c>
       <c r="AJ247" t="n">
-        <v>1.89822624314411</v>
+        <v>1.898226243144111</v>
       </c>
       <c r="AK247" t="n">
-        <v>0.6317737568558897</v>
+        <v>0.6317737568558885</v>
       </c>
       <c r="AL247" t="n">
-        <v>0.6317737568558897</v>
+        <v>0.6317737568558885</v>
       </c>
       <c r="AM247" t="n">
-        <v>24.97129473738694</v>
+        <v>24.9712947373869</v>
       </c>
     </row>
     <row r="248">
@@ -34870,13 +34869,13 @@
         <v>2.301065386002884</v>
       </c>
       <c r="AK248" t="n">
-        <v>0.7989346139971159</v>
+        <v>0.7989346139971163</v>
       </c>
       <c r="AL248" t="n">
-        <v>0.7989346139971159</v>
+        <v>0.7989346139971163</v>
       </c>
       <c r="AM248" t="n">
-        <v>25.77208432248761</v>
+        <v>25.77208432248762</v>
       </c>
     </row>
     <row r="249">
@@ -35144,13 +35143,13 @@
         <v>1.878365063212931</v>
       </c>
       <c r="AK250" t="n">
-        <v>1.55163493678707</v>
+        <v>1.551634936787069</v>
       </c>
       <c r="AL250" t="n">
-        <v>1.55163493678707</v>
+        <v>1.551634936787069</v>
       </c>
       <c r="AM250" t="n">
-        <v>45.23717016871923</v>
+        <v>45.23717016871921</v>
       </c>
     </row>
     <row r="251">
@@ -35558,16 +35557,16 @@
         <v>1</v>
       </c>
       <c r="AJ253" t="n">
-        <v>3.327885317460318</v>
+        <v>3.327885317460319</v>
       </c>
       <c r="AK253" t="n">
-        <v>-0.06788531746031801</v>
+        <v>-0.06788531746031889</v>
       </c>
       <c r="AL253" t="n">
-        <v>0.06788531746031801</v>
+        <v>0.06788531746031889</v>
       </c>
       <c r="AM253" t="n">
-        <v>2.082371701236749</v>
+        <v>2.082371701236776</v>
       </c>
     </row>
     <row r="254">
@@ -35841,13 +35840,13 @@
         <v>3.409065198412696</v>
       </c>
       <c r="AK255" t="n">
-        <v>0.6509348015873035</v>
+        <v>0.650934801587304</v>
       </c>
       <c r="AL255" t="n">
-        <v>0.6509348015873035</v>
+        <v>0.650934801587304</v>
       </c>
       <c r="AM255" t="n">
-        <v>16.03287688638679</v>
+        <v>16.0328768863868</v>
       </c>
     </row>
     <row r="256">
@@ -35975,16 +35974,16 @@
         <v>1</v>
       </c>
       <c r="AJ256" t="n">
-        <v>3.383508062770561</v>
+        <v>3.383508062770562</v>
       </c>
       <c r="AK256" t="n">
-        <v>0.7464919372294392</v>
+        <v>0.7464919372294379</v>
       </c>
       <c r="AL256" t="n">
-        <v>0.7464919372294392</v>
+        <v>0.7464919372294379</v>
       </c>
       <c r="AM256" t="n">
-        <v>18.07486530821887</v>
+        <v>18.07486530821884</v>
       </c>
     </row>
     <row r="257">
@@ -36252,13 +36251,13 @@
         <v>1.710446558441558</v>
       </c>
       <c r="AK258" t="n">
-        <v>-0.210446558441558</v>
+        <v>-0.2104465584415585</v>
       </c>
       <c r="AL258" t="n">
-        <v>0.210446558441558</v>
+        <v>0.2104465584415585</v>
       </c>
       <c r="AM258" t="n">
-        <v>14.02977056277054</v>
+        <v>14.02977056277056</v>
       </c>
     </row>
     <row r="259">
@@ -36389,13 +36388,13 @@
         <v>2.655179078884078</v>
       </c>
       <c r="AK259" t="n">
-        <v>0.2848209211159221</v>
+        <v>0.2848209211159216</v>
       </c>
       <c r="AL259" t="n">
-        <v>0.2848209211159221</v>
+        <v>0.2848209211159216</v>
       </c>
       <c r="AM259" t="n">
-        <v>9.687786432514356</v>
+        <v>9.68778643251434</v>
       </c>
     </row>
     <row r="260">
@@ -36957,13 +36956,13 @@
         <v>3.914962510822512</v>
       </c>
       <c r="AK263" t="n">
-        <v>-2.904962510822512</v>
+        <v>-2.904962510822513</v>
       </c>
       <c r="AL263" t="n">
-        <v>2.904962510822512</v>
+        <v>2.904962510822513</v>
       </c>
       <c r="AM263" t="n">
-        <v>287.6200505764863</v>
+        <v>287.6200505764864</v>
       </c>
     </row>
     <row r="264">
@@ -37243,13 +37242,13 @@
         <v>1.638850002405003</v>
       </c>
       <c r="AK265" t="n">
-        <v>-0.3788500024050028</v>
+        <v>-0.378850002405003</v>
       </c>
       <c r="AL265" t="n">
-        <v>0.3788500024050028</v>
+        <v>0.378850002405003</v>
       </c>
       <c r="AM265" t="n">
-        <v>30.06746050833355</v>
+        <v>30.06746050833357</v>
       </c>
     </row>
     <row r="266">
@@ -37514,16 +37513,16 @@
         <v>1</v>
       </c>
       <c r="AJ267" t="n">
-        <v>1.682450015667883</v>
+        <v>1.682450015667884</v>
       </c>
       <c r="AK267" t="n">
-        <v>-0.2824500156678835</v>
+        <v>-0.2824500156678837</v>
       </c>
       <c r="AL267" t="n">
-        <v>0.2824500156678835</v>
+        <v>0.2824500156678837</v>
       </c>
       <c r="AM267" t="n">
-        <v>20.17500111913454</v>
+        <v>20.17500111913456</v>
       </c>
     </row>
     <row r="268">
@@ -37651,16 +37650,16 @@
         <v>1</v>
       </c>
       <c r="AJ268" t="n">
-        <v>1.843607148869647</v>
+        <v>1.843607148869648</v>
       </c>
       <c r="AK268" t="n">
-        <v>0.1563928511303527</v>
+        <v>0.1563928511303523</v>
       </c>
       <c r="AL268" t="n">
-        <v>0.1563928511303527</v>
+        <v>0.1563928511303523</v>
       </c>
       <c r="AM268" t="n">
-        <v>7.819642556517636</v>
+        <v>7.819642556517614</v>
       </c>
     </row>
     <row r="269">
@@ -37943,16 +37942,16 @@
         <v>0</v>
       </c>
       <c r="AJ270" t="n">
-        <v>8.527872221019726</v>
+        <v>8.527872221019727</v>
       </c>
       <c r="AK270" t="n">
-        <v>-0.5878722210197251</v>
+        <v>-0.5878722210197269</v>
       </c>
       <c r="AL270" t="n">
-        <v>0.5878722210197251</v>
+        <v>0.5878722210197269</v>
       </c>
       <c r="AM270" t="n">
-        <v>7.403932254656488</v>
+        <v>7.40393225465651</v>
       </c>
     </row>
     <row r="271">
@@ -38234,13 +38233,13 @@
         <v>21.13365673585673</v>
       </c>
       <c r="AK272" t="n">
-        <v>0.06634326414326708</v>
+        <v>0.06634326414327063</v>
       </c>
       <c r="AL272" t="n">
-        <v>0.06634326414326708</v>
+        <v>0.06634326414327063</v>
       </c>
       <c r="AM272" t="n">
-        <v>0.31293992520409</v>
+        <v>0.3129399252041067</v>
       </c>
     </row>
     <row r="273">
@@ -38517,16 +38516,16 @@
         <v>0</v>
       </c>
       <c r="AJ274" t="n">
-        <v>1.460113564213564</v>
+        <v>1.460113564213565</v>
       </c>
       <c r="AK274" t="n">
-        <v>-0.8201135642135643</v>
+        <v>-0.8201135642135645</v>
       </c>
       <c r="AL274" t="n">
-        <v>0.8201135642135643</v>
+        <v>0.8201135642135645</v>
       </c>
       <c r="AM274" t="n">
-        <v>128.1427444083694</v>
+        <v>128.1427444083695</v>
       </c>
     </row>
     <row r="275">
@@ -38657,13 +38656,13 @@
         <v>1.878365063212931</v>
       </c>
       <c r="AK275" t="n">
-        <v>-0.4383650632129306</v>
+        <v>-0.4383650632129312</v>
       </c>
       <c r="AL275" t="n">
-        <v>0.4383650632129306</v>
+        <v>0.4383650632129312</v>
       </c>
       <c r="AM275" t="n">
-        <v>30.44201827867574</v>
+        <v>30.44201827867578</v>
       </c>
     </row>
     <row r="276">
@@ -38791,16 +38790,16 @@
         <v>1</v>
       </c>
       <c r="AJ276" t="n">
-        <v>2.021782837902837</v>
+        <v>2.021782837902836</v>
       </c>
       <c r="AK276" t="n">
-        <v>-0.4917828379028368</v>
+        <v>-0.4917828379028359</v>
       </c>
       <c r="AL276" t="n">
-        <v>0.4917828379028368</v>
+        <v>0.4917828379028359</v>
       </c>
       <c r="AM276" t="n">
-        <v>32.14266914397626</v>
+        <v>32.14266914397621</v>
       </c>
     </row>
     <row r="277">
@@ -38931,13 +38930,13 @@
         <v>2.281959298941797</v>
       </c>
       <c r="AK277" t="n">
-        <v>-0.8019592989417967</v>
+        <v>-0.8019592989417972</v>
       </c>
       <c r="AL277" t="n">
-        <v>0.8019592989417967</v>
+        <v>0.8019592989417972</v>
       </c>
       <c r="AM277" t="n">
-        <v>54.18643911768897</v>
+        <v>54.186439117689</v>
       </c>
     </row>
     <row r="278">
@@ -39068,13 +39067,13 @@
         <v>3.395822896825397</v>
       </c>
       <c r="AK278" t="n">
-        <v>-0.4058228968253972</v>
+        <v>-0.4058228968253967</v>
       </c>
       <c r="AL278" t="n">
-        <v>0.4058228968253972</v>
+        <v>0.4058228968253967</v>
       </c>
       <c r="AM278" t="n">
-        <v>13.57267213462867</v>
+        <v>13.57267213462865</v>
       </c>
     </row>
     <row r="279">
@@ -39211,13 +39210,13 @@
         <v>12.32520932659932</v>
       </c>
       <c r="AK279" t="n">
-        <v>0.5747906734006776</v>
+        <v>0.5747906734006758</v>
       </c>
       <c r="AL279" t="n">
-        <v>0.5747906734006776</v>
+        <v>0.5747906734006758</v>
       </c>
       <c r="AM279" t="n">
-        <v>4.455741654268818</v>
+        <v>4.455741654268804</v>
       </c>
     </row>
     <row r="280">
@@ -39795,13 +39794,13 @@
         <v>1.983785465367964</v>
       </c>
       <c r="AK283" t="n">
-        <v>-0.003785465367963869</v>
+        <v>-0.003785465367964314</v>
       </c>
       <c r="AL283" t="n">
-        <v>0.003785465367963869</v>
+        <v>0.003785465367964314</v>
       </c>
       <c r="AM283" t="n">
-        <v>0.1911851195941348</v>
+        <v>0.1911851195941572</v>
       </c>
     </row>
     <row r="284">
@@ -39932,13 +39931,13 @@
         <v>2.109296645021645</v>
       </c>
       <c r="AK284" t="n">
-        <v>-0.05929664502164478</v>
+        <v>-0.05929664502164522</v>
       </c>
       <c r="AL284" t="n">
-        <v>0.05929664502164478</v>
+        <v>0.05929664502164522</v>
       </c>
       <c r="AM284" t="n">
-        <v>2.892519269348526</v>
+        <v>2.892519269348548</v>
       </c>
     </row>
     <row r="285">
@@ -40340,16 +40339,16 @@
         <v>1</v>
       </c>
       <c r="AJ287" t="n">
-        <v>1.799720318292818</v>
+        <v>1.799720318292819</v>
       </c>
       <c r="AK287" t="n">
-        <v>0.4402796817071819</v>
+        <v>0.4402796817071815</v>
       </c>
       <c r="AL287" t="n">
-        <v>0.4402796817071819</v>
+        <v>0.4402796817071815</v>
       </c>
       <c r="AM287" t="n">
-        <v>19.65534293335633</v>
+        <v>19.65534293335631</v>
       </c>
     </row>
     <row r="288">
@@ -40477,16 +40476,16 @@
         <v>1</v>
       </c>
       <c r="AJ288" t="n">
-        <v>1.799720318292818</v>
+        <v>1.799720318292819</v>
       </c>
       <c r="AK288" t="n">
-        <v>-0.01972031829281828</v>
+        <v>-0.01972031829281873</v>
       </c>
       <c r="AL288" t="n">
-        <v>0.01972031829281828</v>
+        <v>0.01972031829281873</v>
       </c>
       <c r="AM288" t="n">
-        <v>1.107883050158331</v>
+        <v>1.107883050158356</v>
       </c>
     </row>
     <row r="289">
@@ -40888,16 +40887,16 @@
         <v>1</v>
       </c>
       <c r="AJ291" t="n">
-        <v>3.868108915343913</v>
+        <v>3.868108915343912</v>
       </c>
       <c r="AK291" t="n">
-        <v>1.421891084656087</v>
+        <v>1.421891084656088</v>
       </c>
       <c r="AL291" t="n">
-        <v>1.421891084656087</v>
+        <v>1.421891084656088</v>
       </c>
       <c r="AM291" t="n">
-        <v>26.87884848121148</v>
+        <v>26.87884848121149</v>
       </c>
     </row>
     <row r="292">
@@ -41025,16 +41024,16 @@
         <v>1</v>
       </c>
       <c r="AJ292" t="n">
-        <v>3.592270449735451</v>
+        <v>3.592270449735452</v>
       </c>
       <c r="AK292" t="n">
-        <v>5.55772955026455</v>
+        <v>5.557729550264549</v>
       </c>
       <c r="AL292" t="n">
-        <v>5.55772955026455</v>
+        <v>5.557729550264549</v>
       </c>
       <c r="AM292" t="n">
-        <v>60.74021366409343</v>
+        <v>60.74021366409342</v>
       </c>
     </row>
     <row r="293">
@@ -41451,13 +41450,13 @@
         <v>1.701051937229436</v>
       </c>
       <c r="AK295" t="n">
-        <v>0.09894806277056434</v>
+        <v>0.09894806277056389</v>
       </c>
       <c r="AL295" t="n">
-        <v>0.09894806277056434</v>
+        <v>0.09894806277056389</v>
       </c>
       <c r="AM295" t="n">
-        <v>5.497114598364685</v>
+        <v>5.497114598364661</v>
       </c>
     </row>
     <row r="296">
@@ -41588,13 +41587,13 @@
         <v>2.216885169552668</v>
       </c>
       <c r="AK296" t="n">
-        <v>-0.9768851695526679</v>
+        <v>-0.9768851695526684</v>
       </c>
       <c r="AL296" t="n">
-        <v>0.9768851695526679</v>
+        <v>0.9768851695526684</v>
       </c>
       <c r="AM296" t="n">
-        <v>78.78106206069903</v>
+        <v>78.78106206069906</v>
       </c>
     </row>
     <row r="297">
@@ -41722,16 +41721,16 @@
         <v>1</v>
       </c>
       <c r="AJ297" t="n">
-        <v>1.578882447089946</v>
+        <v>1.578882447089947</v>
       </c>
       <c r="AK297" t="n">
-        <v>-0.01888244708994602</v>
+        <v>-0.01888244708994646</v>
       </c>
       <c r="AL297" t="n">
-        <v>0.01888244708994602</v>
+        <v>0.01888244708994646</v>
       </c>
       <c r="AM297" t="n">
-        <v>1.21041327499654</v>
+        <v>1.210413274996568</v>
       </c>
     </row>
     <row r="298">
@@ -41862,13 +41861,13 @@
         <v>1.878365063212931</v>
       </c>
       <c r="AK298" t="n">
-        <v>-0.7283650632129306</v>
+        <v>-0.7283650632129313</v>
       </c>
       <c r="AL298" t="n">
-        <v>0.7283650632129306</v>
+        <v>0.7283650632129313</v>
       </c>
       <c r="AM298" t="n">
-        <v>63.33609245329832</v>
+        <v>63.33609245329838</v>
       </c>
     </row>
     <row r="299">
@@ -41999,13 +41998,13 @@
         <v>1.878365063212931</v>
       </c>
       <c r="AK299" t="n">
-        <v>-0.3283650632129305</v>
+        <v>-0.3283650632129311</v>
       </c>
       <c r="AL299" t="n">
-        <v>0.3283650632129305</v>
+        <v>0.3283650632129311</v>
       </c>
       <c r="AM299" t="n">
-        <v>21.184842787931</v>
+        <v>21.18484278793104</v>
       </c>
     </row>
     <row r="300">
@@ -42547,13 +42546,13 @@
         <v>1.808515538720537</v>
       </c>
       <c r="AK303" t="n">
-        <v>-0.9985155387205369</v>
+        <v>-0.9985155387205373</v>
       </c>
       <c r="AL303" t="n">
-        <v>0.9985155387205369</v>
+        <v>0.9985155387205373</v>
       </c>
       <c r="AM303" t="n">
-        <v>123.2735232988317</v>
+        <v>123.2735232988318</v>
       </c>
     </row>
     <row r="304">
@@ -42681,16 +42680,16 @@
         <v>1</v>
       </c>
       <c r="AJ304" t="n">
-        <v>1.803988981481481</v>
+        <v>1.803988981481482</v>
       </c>
       <c r="AK304" t="n">
-        <v>0.296011018518519</v>
+        <v>0.2960110185185185</v>
       </c>
       <c r="AL304" t="n">
-        <v>0.296011018518519</v>
+        <v>0.2960110185185185</v>
       </c>
       <c r="AM304" t="n">
-        <v>14.09576278659614</v>
+        <v>14.09576278659612</v>
       </c>
     </row>
     <row r="305">
@@ -42821,13 +42820,13 @@
         <v>1.878365063212931</v>
       </c>
       <c r="AK305" t="n">
-        <v>-0.4083650632129305</v>
+        <v>-0.4083650632129312</v>
       </c>
       <c r="AL305" t="n">
-        <v>0.4083650632129305</v>
+        <v>0.4083650632129312</v>
       </c>
       <c r="AM305" t="n">
-        <v>27.77993627298847</v>
+        <v>27.77993627298852</v>
       </c>
     </row>
     <row r="306">
@@ -42958,13 +42957,13 @@
         <v>1.878365063212931</v>
       </c>
       <c r="AK306" t="n">
-        <v>0.7616349367870696</v>
+        <v>0.761634936787069</v>
       </c>
       <c r="AL306" t="n">
-        <v>0.7616349367870696</v>
+        <v>0.761634936787069</v>
       </c>
       <c r="AM306" t="n">
-        <v>28.84980821163142</v>
+        <v>28.8498082116314</v>
       </c>
     </row>
     <row r="307">
@@ -43092,16 +43091,16 @@
         <v>1</v>
       </c>
       <c r="AJ307" t="n">
-        <v>4.717393465608462</v>
+        <v>4.717393465608463</v>
       </c>
       <c r="AK307" t="n">
-        <v>2.762606534391538</v>
+        <v>2.762606534391537</v>
       </c>
       <c r="AL307" t="n">
-        <v>2.762606534391538</v>
+        <v>2.762606534391537</v>
       </c>
       <c r="AM307" t="n">
-        <v>36.93324243838955</v>
+        <v>36.93324243838953</v>
       </c>
     </row>
     <row r="308">
@@ -43232,13 +43231,13 @@
         <v>1.878365063212931</v>
       </c>
       <c r="AK308" t="n">
-        <v>-0.3783650632129305</v>
+        <v>-0.3783650632129312</v>
       </c>
       <c r="AL308" t="n">
-        <v>0.3783650632129305</v>
+        <v>0.3783650632129312</v>
       </c>
       <c r="AM308" t="n">
-        <v>25.2243375475287</v>
+        <v>25.22433754752875</v>
       </c>
     </row>
     <row r="309">
@@ -43372,16 +43371,16 @@
         <v>0</v>
       </c>
       <c r="AJ309" t="n">
-        <v>22.55823345543346</v>
+        <v>22.55823345543345</v>
       </c>
       <c r="AK309" t="n">
-        <v>2.341766544566539</v>
+        <v>2.341766544566546</v>
       </c>
       <c r="AL309" t="n">
-        <v>2.341766544566539</v>
+        <v>2.341766544566546</v>
       </c>
       <c r="AM309" t="n">
-        <v>9.40468491793791</v>
+        <v>9.404684917937937</v>
       </c>
     </row>
     <row r="310">
@@ -43518,13 +43517,13 @@
         <v>25.88769765512267</v>
       </c>
       <c r="AK310" t="n">
-        <v>2.612302344877328</v>
+        <v>2.612302344877332</v>
       </c>
       <c r="AL310" t="n">
-        <v>2.612302344877328</v>
+        <v>2.612302344877332</v>
       </c>
       <c r="AM310" t="n">
-        <v>9.16597313992045</v>
+        <v>9.165973139920462</v>
       </c>
     </row>
     <row r="311">
@@ -43795,16 +43794,16 @@
         <v>1</v>
       </c>
       <c r="AJ312" t="n">
-        <v>2.821245079365078</v>
+        <v>2.821245079365079</v>
       </c>
       <c r="AK312" t="n">
-        <v>-1.671245079365078</v>
+        <v>-1.671245079365079</v>
       </c>
       <c r="AL312" t="n">
-        <v>1.671245079365078</v>
+        <v>1.671245079365079</v>
       </c>
       <c r="AM312" t="n">
-        <v>145.3256590752242</v>
+        <v>145.3256590752243</v>
       </c>
     </row>
     <row r="313">
@@ -44081,16 +44080,16 @@
         <v>0</v>
       </c>
       <c r="AJ314" t="n">
-        <v>9.520466381673881</v>
+        <v>9.520466381673879</v>
       </c>
       <c r="AK314" t="n">
-        <v>-0.1504663816738816</v>
+        <v>-0.1504663816738798</v>
       </c>
       <c r="AL314" t="n">
-        <v>0.1504663816738816</v>
+        <v>0.1504663816738798</v>
       </c>
       <c r="AM314" t="n">
-        <v>1.605831181151351</v>
+        <v>1.605831181151332</v>
       </c>
     </row>
     <row r="315">
@@ -44227,13 +44226,13 @@
         <v>10.17074230880231</v>
       </c>
       <c r="AK315" t="n">
-        <v>0.8292576911976877</v>
+        <v>0.8292576911976894</v>
       </c>
       <c r="AL315" t="n">
-        <v>0.8292576911976877</v>
+        <v>0.8292576911976894</v>
       </c>
       <c r="AM315" t="n">
-        <v>7.538706283615343</v>
+        <v>7.538706283615358</v>
       </c>
     </row>
     <row r="316">
@@ -44796,16 +44795,16 @@
         <v>0</v>
       </c>
       <c r="AJ319" t="n">
-        <v>24.74713760221262</v>
+        <v>24.74713760221261</v>
       </c>
       <c r="AK319" t="n">
-        <v>3.252862397787382</v>
+        <v>3.252862397787386</v>
       </c>
       <c r="AL319" t="n">
-        <v>3.252862397787382</v>
+        <v>3.252862397787386</v>
       </c>
       <c r="AM319" t="n">
-        <v>11.61736570638351</v>
+        <v>11.61736570638352</v>
       </c>
     </row>
     <row r="320">
@@ -44939,16 +44938,16 @@
         <v>0</v>
       </c>
       <c r="AJ320" t="n">
-        <v>24.73443045935548</v>
+        <v>24.73443045935547</v>
       </c>
       <c r="AK320" t="n">
-        <v>3.265569540644524</v>
+        <v>3.265569540644528</v>
       </c>
       <c r="AL320" t="n">
-        <v>3.265569540644524</v>
+        <v>3.265569540644528</v>
       </c>
       <c r="AM320" t="n">
-        <v>11.66274835944473</v>
+        <v>11.66274835944474</v>
       </c>
     </row>
     <row r="321">
@@ -45081,13 +45080,13 @@
         <v>11.34167798941799</v>
       </c>
       <c r="AK321" t="n">
-        <v>0.7583220105820132</v>
+        <v>0.7583220105820114</v>
       </c>
       <c r="AL321" t="n">
-        <v>0.7583220105820132</v>
+        <v>0.7583220105820114</v>
       </c>
       <c r="AM321" t="n">
-        <v>6.267124054396804</v>
+        <v>6.267124054396788</v>
       </c>
     </row>
     <row r="322">
@@ -45220,13 +45219,13 @@
         <v>11.34167798941799</v>
       </c>
       <c r="AK322" t="n">
-        <v>-1.241677989417987</v>
+        <v>-1.241677989417989</v>
       </c>
       <c r="AL322" t="n">
-        <v>1.241677989417987</v>
+        <v>1.241677989417989</v>
       </c>
       <c r="AM322" t="n">
-        <v>12.29384147938601</v>
+        <v>12.29384147938603</v>
       </c>
     </row>
     <row r="323">
@@ -45489,16 +45488,16 @@
         <v>0</v>
       </c>
       <c r="AJ324" t="n">
-        <v>12.12427630351129</v>
+        <v>12.12427630351128</v>
       </c>
       <c r="AK324" t="n">
-        <v>-0.02427630351128585</v>
+        <v>-0.02427630351128407</v>
       </c>
       <c r="AL324" t="n">
-        <v>0.02427630351128585</v>
+        <v>0.02427630351128407</v>
       </c>
       <c r="AM324" t="n">
-        <v>0.200630607531288</v>
+        <v>0.2006306075312733</v>
       </c>
     </row>
     <row r="325">
@@ -45629,13 +45628,13 @@
         <v>11.07501061568061</v>
       </c>
       <c r="AK325" t="n">
-        <v>1.024989384319394</v>
+        <v>1.024989384319392</v>
       </c>
       <c r="AL325" t="n">
-        <v>1.024989384319394</v>
+        <v>1.024989384319392</v>
       </c>
       <c r="AM325" t="n">
-        <v>8.470986647267717</v>
+        <v>8.470986647267702</v>
       </c>
     </row>
     <row r="326">
@@ -45907,13 +45906,13 @@
         <v>10.00478754689754</v>
       </c>
       <c r="AK327" t="n">
-        <v>0.09521245310245519</v>
+        <v>0.09521245310245696</v>
       </c>
       <c r="AL327" t="n">
-        <v>0.09521245310245519</v>
+        <v>0.09521245310245696</v>
       </c>
       <c r="AM327" t="n">
-        <v>0.9426975554698535</v>
+        <v>0.942697555469871</v>
       </c>
     </row>
     <row r="328">
@@ -46470,16 +46469,16 @@
         <v>1</v>
       </c>
       <c r="AJ331" t="n">
-        <v>3.762659856902356</v>
+        <v>3.762659856902358</v>
       </c>
       <c r="AK331" t="n">
-        <v>0.7573401430976436</v>
+        <v>0.7573401430976419</v>
       </c>
       <c r="AL331" t="n">
-        <v>0.7573401430976436</v>
+        <v>0.7573401430976419</v>
       </c>
       <c r="AM331" t="n">
-        <v>16.75531290039035</v>
+        <v>16.75531290039031</v>
       </c>
     </row>
     <row r="332">
@@ -46607,16 +46606,16 @@
         <v>1</v>
       </c>
       <c r="AJ332" t="n">
-        <v>3.560121695526695</v>
+        <v>3.560121695526696</v>
       </c>
       <c r="AK332" t="n">
-        <v>0.02987830447330531</v>
+        <v>0.02987830447330353</v>
       </c>
       <c r="AL332" t="n">
-        <v>0.02987830447330531</v>
+        <v>0.02987830447330353</v>
       </c>
       <c r="AM332" t="n">
-        <v>0.8322647485600364</v>
+        <v>0.832264748559987</v>
       </c>
     </row>
     <row r="333">
@@ -46893,16 +46892,16 @@
         <v>0</v>
       </c>
       <c r="AJ334" t="n">
-        <v>7.742596576479056</v>
+        <v>7.742596576479059</v>
       </c>
       <c r="AK334" t="n">
-        <v>1.357403423520943</v>
+        <v>1.357403423520941</v>
       </c>
       <c r="AL334" t="n">
-        <v>1.357403423520943</v>
+        <v>1.357403423520941</v>
       </c>
       <c r="AM334" t="n">
-        <v>14.91652113759278</v>
+        <v>14.91652113759276</v>
       </c>
     </row>
     <row r="335">
@@ -47178,13 +47177,13 @@
         <v>11.06648275132274</v>
       </c>
       <c r="AK336" t="n">
-        <v>-1.966482751322738</v>
+        <v>-1.96648275132274</v>
       </c>
       <c r="AL336" t="n">
-        <v>1.966482751322738</v>
+        <v>1.96648275132274</v>
       </c>
       <c r="AM336" t="n">
-        <v>21.60970056398614</v>
+        <v>21.60970056398616</v>
       </c>
     </row>
     <row r="337">
@@ -47600,16 +47599,16 @@
         <v>0</v>
       </c>
       <c r="AJ339" t="n">
-        <v>9.089237950937907</v>
+        <v>9.089237950937909</v>
       </c>
       <c r="AK339" t="n">
-        <v>0.01076204906209277</v>
+        <v>0.01076204906209099</v>
       </c>
       <c r="AL339" t="n">
-        <v>0.01076204906209277</v>
+        <v>0.01076204906209099</v>
       </c>
       <c r="AM339" t="n">
-        <v>0.1182642754076129</v>
+        <v>0.1182642754075933</v>
       </c>
     </row>
     <row r="340">
@@ -48166,16 +48165,16 @@
         <v>1</v>
       </c>
       <c r="AJ343" t="n">
-        <v>3.620766801346798</v>
+        <v>3.620766801346799</v>
       </c>
       <c r="AK343" t="n">
-        <v>-0.2107668013467983</v>
+        <v>-0.2107668013467991</v>
       </c>
       <c r="AL343" t="n">
-        <v>0.2107668013467983</v>
+        <v>0.2107668013467991</v>
       </c>
       <c r="AM343" t="n">
-        <v>6.180844614275609</v>
+        <v>6.180844614275634</v>
       </c>
     </row>
     <row r="344">
@@ -48309,16 +48308,16 @@
         <v>0</v>
       </c>
       <c r="AJ344" t="n">
-        <v>9.089237950937907</v>
+        <v>9.089237950937909</v>
       </c>
       <c r="AK344" t="n">
-        <v>0.01076204906209277</v>
+        <v>0.01076204906209099</v>
       </c>
       <c r="AL344" t="n">
-        <v>0.01076204906209277</v>
+        <v>0.01076204906209099</v>
       </c>
       <c r="AM344" t="n">
-        <v>0.1182642754076129</v>
+        <v>0.1182642754075933</v>
       </c>
     </row>
     <row r="345">
@@ -48732,13 +48731,13 @@
         <v>1</v>
       </c>
       <c r="AJ347" t="n">
-        <v>5.341694126984128</v>
+        <v>5.341694126984129</v>
       </c>
       <c r="AK347" t="n">
-        <v>-3.451694126984129</v>
+        <v>-3.45169412698413</v>
       </c>
       <c r="AL347" t="n">
-        <v>3.451694126984129</v>
+        <v>3.45169412698413</v>
       </c>
       <c r="AM347" t="n">
         <v>182.6293188880492</v>
@@ -49435,16 +49434,16 @@
         <v>1</v>
       </c>
       <c r="AJ352" t="n">
-        <v>5.234663359788362</v>
+        <v>5.234663359788363</v>
       </c>
       <c r="AK352" t="n">
-        <v>4.895336640211639</v>
+        <v>4.895336640211638</v>
       </c>
       <c r="AL352" t="n">
-        <v>4.895336640211639</v>
+        <v>4.895336640211638</v>
       </c>
       <c r="AM352" t="n">
-        <v>48.32513958747916</v>
+        <v>48.32513958747914</v>
       </c>
     </row>
     <row r="353">
@@ -49717,16 +49716,16 @@
         <v>1</v>
       </c>
       <c r="AJ354" t="n">
-        <v>3.961672806637804</v>
+        <v>3.961672806637805</v>
       </c>
       <c r="AK354" t="n">
-        <v>-1.931672806637804</v>
+        <v>-1.931672806637805</v>
       </c>
       <c r="AL354" t="n">
-        <v>1.931672806637804</v>
+        <v>1.931672806637805</v>
       </c>
       <c r="AM354" t="n">
-        <v>95.15629589348791</v>
+        <v>95.15629589348795</v>
       </c>
     </row>
     <row r="355">
@@ -49854,16 +49853,16 @@
         <v>1</v>
       </c>
       <c r="AJ355" t="n">
-        <v>3.464777423039922</v>
+        <v>3.464777423039923</v>
       </c>
       <c r="AK355" t="n">
-        <v>4.445222576960078</v>
+        <v>4.445222576960077</v>
       </c>
       <c r="AL355" t="n">
-        <v>4.445222576960078</v>
+        <v>4.445222576960077</v>
       </c>
       <c r="AM355" t="n">
-        <v>56.19750413350288</v>
+        <v>56.19750413350287</v>
       </c>
     </row>
     <row r="356">
@@ -50557,13 +50556,13 @@
         <v>0</v>
       </c>
       <c r="AJ360" t="n">
-        <v>8.334308612313588</v>
+        <v>8.33430861231359</v>
       </c>
       <c r="AK360" t="n">
-        <v>-5.234308612313589</v>
+        <v>-5.23430861231359</v>
       </c>
       <c r="AL360" t="n">
-        <v>5.234308612313589</v>
+        <v>5.23430861231359</v>
       </c>
       <c r="AM360" t="n">
         <v>168.8486649133416</v>
@@ -51121,16 +51120,16 @@
         <v>0</v>
       </c>
       <c r="AJ364" t="n">
-        <v>10.34722089947088</v>
+        <v>10.34722089947087</v>
       </c>
       <c r="AK364" t="n">
-        <v>-0.2472208994708769</v>
+        <v>-0.2472208994708751</v>
       </c>
       <c r="AL364" t="n">
-        <v>0.2472208994708769</v>
+        <v>0.2472208994708751</v>
       </c>
       <c r="AM364" t="n">
-        <v>2.447731677929474</v>
+        <v>2.447731677929457</v>
       </c>
     </row>
     <row r="365">
@@ -51399,16 +51398,16 @@
         <v>0</v>
       </c>
       <c r="AJ366" t="n">
-        <v>10.34722089947088</v>
+        <v>10.34722089947087</v>
       </c>
       <c r="AK366" t="n">
-        <v>-1.247220899470877</v>
+        <v>-1.247220899470875</v>
       </c>
       <c r="AL366" t="n">
-        <v>1.247220899470877</v>
+        <v>1.247220899470875</v>
       </c>
       <c r="AM366" t="n">
-        <v>13.70572417000964</v>
+        <v>13.70572417000962</v>
       </c>
     </row>
     <row r="367">
@@ -51536,16 +51535,16 @@
         <v>1</v>
       </c>
       <c r="AJ367" t="n">
-        <v>3.549325214045211</v>
+        <v>3.549325214045213</v>
       </c>
       <c r="AK367" t="n">
-        <v>-1.359325214045211</v>
+        <v>-1.359325214045213</v>
       </c>
       <c r="AL367" t="n">
-        <v>1.359325214045211</v>
+        <v>1.359325214045213</v>
       </c>
       <c r="AM367" t="n">
-        <v>62.06964447695029</v>
+        <v>62.06964447695036</v>
       </c>
     </row>
     <row r="368">
@@ -51675,16 +51674,16 @@
         <v>0</v>
       </c>
       <c r="AJ368" t="n">
-        <v>16.25151349668851</v>
+        <v>16.2515134966885</v>
       </c>
       <c r="AK368" t="n">
-        <v>-4.15151349668851</v>
+        <v>-4.151513496688503</v>
       </c>
       <c r="AL368" t="n">
-        <v>4.15151349668851</v>
+        <v>4.151513496688503</v>
       </c>
       <c r="AM368" t="n">
-        <v>34.31002889825216</v>
+        <v>34.31002889825209</v>
       </c>
     </row>
     <row r="369">
@@ -51817,13 +51816,13 @@
         <v>10.78000764050762</v>
       </c>
       <c r="AK369" t="n">
-        <v>1.319992359492378</v>
+        <v>1.31999235949238</v>
       </c>
       <c r="AL369" t="n">
-        <v>1.319992359492378</v>
+        <v>1.31999235949238</v>
       </c>
       <c r="AM369" t="n">
-        <v>10.90902776439982</v>
+        <v>10.90902776439983</v>
       </c>
     </row>
     <row r="370">
@@ -51951,16 +51950,16 @@
         <v>1</v>
       </c>
       <c r="AJ370" t="n">
-        <v>3.464777423039922</v>
+        <v>3.464777423039923</v>
       </c>
       <c r="AK370" t="n">
-        <v>-0.504777423039922</v>
+        <v>-0.5047774230399233</v>
       </c>
       <c r="AL370" t="n">
-        <v>0.504777423039922</v>
+        <v>0.5047774230399233</v>
       </c>
       <c r="AM370" t="n">
-        <v>17.05329131891628</v>
+        <v>17.05329131891633</v>
       </c>
     </row>
     <row r="371">
@@ -52094,16 +52093,16 @@
         <v>0</v>
       </c>
       <c r="AJ371" t="n">
-        <v>18.01475225237727</v>
+        <v>18.01475225237726</v>
       </c>
       <c r="AK371" t="n">
-        <v>-1.214752252377266</v>
+        <v>-1.214752252377263</v>
       </c>
       <c r="AL371" t="n">
-        <v>1.214752252377266</v>
+        <v>1.214752252377263</v>
       </c>
       <c r="AM371" t="n">
-        <v>7.230668168912301</v>
+        <v>7.230668168912278</v>
       </c>
     </row>
     <row r="372">
@@ -52231,16 +52230,16 @@
         <v>1</v>
       </c>
       <c r="AJ372" t="n">
-        <v>2.09260718253968</v>
+        <v>2.092607182539681</v>
       </c>
       <c r="AK372" t="n">
-        <v>-0.07260718253968035</v>
+        <v>-0.07260718253968079</v>
       </c>
       <c r="AL372" t="n">
-        <v>0.07260718253968035</v>
+        <v>0.07260718253968079</v>
       </c>
       <c r="AM372" t="n">
-        <v>3.594414977211898</v>
+        <v>3.59441497721192</v>
       </c>
     </row>
     <row r="373">
@@ -52505,16 +52504,16 @@
         <v>1</v>
       </c>
       <c r="AJ374" t="n">
-        <v>4.773025097402598</v>
+        <v>4.773025097402597</v>
       </c>
       <c r="AK374" t="n">
-        <v>0.4669749025974026</v>
+        <v>0.4669749025974035</v>
       </c>
       <c r="AL374" t="n">
-        <v>0.4669749025974026</v>
+        <v>0.4669749025974035</v>
       </c>
       <c r="AM374" t="n">
-        <v>8.911734782393179</v>
+        <v>8.911734782393196</v>
       </c>
     </row>
     <row r="375">
@@ -52642,16 +52641,16 @@
         <v>1</v>
       </c>
       <c r="AJ375" t="n">
-        <v>3.550627142857141</v>
+        <v>3.550627142857142</v>
       </c>
       <c r="AK375" t="n">
-        <v>-0.7006271428571411</v>
+        <v>-0.700627142857142</v>
       </c>
       <c r="AL375" t="n">
-        <v>0.7006271428571411</v>
+        <v>0.700627142857142</v>
       </c>
       <c r="AM375" t="n">
-        <v>24.58340852130319</v>
+        <v>24.58340852130323</v>
       </c>
     </row>
     <row r="376">
@@ -52919,13 +52918,13 @@
         <v>3.395822896825397</v>
       </c>
       <c r="AK377" t="n">
-        <v>0.1641771031746027</v>
+        <v>0.1641771031746031</v>
       </c>
       <c r="AL377" t="n">
-        <v>0.1641771031746027</v>
+        <v>0.1641771031746031</v>
       </c>
       <c r="AM377" t="n">
-        <v>4.611716381309063</v>
+        <v>4.611716381309075</v>
       </c>
     </row>
   </sheetData>
@@ -52998,10 +52997,10 @@
         <v>0.9156740904867036</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9503597492453506</v>
+        <v>0.9503597492453505</v>
       </c>
       <c r="D3" t="n">
-        <v>1.53425010525932</v>
+        <v>1.534250105259319</v>
       </c>
       <c r="E3" t="n">
         <v>76</v>
@@ -53126,7 +53125,7 @@
         <v>0.8970942214372927</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9840948935138931</v>
+        <v>0.9840948935138933</v>
       </c>
       <c r="F4" t="n">
         <v>1.448944801952477</v>
@@ -53169,7 +53168,7 @@
         <v>1.209512394810745</v>
       </c>
       <c r="F6" t="n">
-        <v>2.117122378580558</v>
+        <v>2.117122378580559</v>
       </c>
     </row>
     <row r="7">
@@ -53210,7 +53209,7 @@
         <v>0.02277936671062199</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1646728521891827</v>
+        <v>0.1646728521891825</v>
       </c>
       <c r="F8" t="n">
         <v>0.3630553964789631</v>
@@ -53227,294 +53226,99 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>machinery_type</t>
+          <t>feature</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>mean_actual</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>mean_pred</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>mean_residual</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>mae</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>rmse</t>
+          <t>importance</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>power_kw</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3.084814814814814</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2.731556544100619</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.353258270714196</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.071974481232074</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.699697425419207</v>
+        <v>0.7925956229910326</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Water Pump</t>
+          <t>year</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.831176470588235</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.63003504161704</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.2011414289711957</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.646282057342248</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.9857099516268644</v>
+        <v>0.1024851593091179</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Four-Wheel Tractor</t>
+          <t>machinery_type_code</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C4" t="n">
-        <v>16.3125</v>
-      </c>
-      <c r="D4" t="n">
-        <v>16.20494248750092</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.107557512499082</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.394763546950729</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.611853074138289</v>
+        <v>0.0452428241979799</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Thresher</t>
+          <t>abemis_total_count</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2.808333333333334</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3.021875515503016</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.2135421821696827</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.4954368858918856</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.7245451723665211</v>
+        <v>0.0199319937766228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Combine Harvester</t>
+          <t>machinery_family_code</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5.4975</v>
-      </c>
-      <c r="D6" t="n">
-        <v>8.650121040764787</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-3.152621040764786</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3.152621040764787</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.731294956979727</v>
+        <v>0.01424307331534578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hand Tractor</t>
+          <t>analysis_subset_code</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.5625</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.484282254689755</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.07821774531024533</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.1433781812169314</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.176568114213345</v>
+        <v>0.01411443635449676</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sheller</t>
+          <t>abemis_dominant_region_share</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2.3225</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.984019016608392</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.3384809833916078</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.4973769134337879</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.60899172633728</v>
+        <v>0.01098042326348976</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Walking-Type Agricultural Tractor</t>
+          <t>abemis_region_breadth</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>9.053262888407843</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.0467371115921568</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.04757405242906524</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.06208481294151112</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Seeder</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>10.55810120069744</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.4581012006974357</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.9178412932900377</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.025811556646132</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Mechanical Dryer</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.485404001924002</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1.014595998075998</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1.014595998075998</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.014595998075998</v>
+        <v>0.0004064667919143085</v>
       </c>
     </row>
   </sheetData>
@@ -53528,99 +53332,159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>feature</t>
+          <t>category</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>importance</t>
+          <t>code</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>power_kw</t>
+          <t>Combine Harvester</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7925956229910326</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>Four-Wheel Tractor</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1024851593091179</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>machinery_type_code</t>
+          <t>Hand Tractor</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0452428241979799</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>abemis_total_count</t>
+          <t>Mechanical Dryer</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0199319937766228</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>machinery_family_code</t>
+          <t>Rice Mill</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01424307331534578</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>analysis_subset_code</t>
+          <t>Rice Transplanter</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01411443635449676</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>abemis_dominant_region_share</t>
+          <t>Rotary Tiller</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01098042326348976</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>abemis_region_breadth</t>
+          <t>Seeder</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0004064667919143085</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sheller</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Small Engine</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sprayer</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Thresher</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Walking-Type Agricultural Tractor</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Water Pump</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -53634,7 +53498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53652,7 +53516,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Combine Harvester</t>
+          <t>Harvest Machinery</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -53662,7 +53526,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Four-Wheel Tractor</t>
+          <t>Mobile Field Machinery</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -53672,7 +53536,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hand Tractor</t>
+          <t>Postharvest / Processing</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -53682,111 +53546,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mechanical Dryer</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Rice Mill</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Rice Transplanter</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Rotary Tiller</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Seeder</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sheller</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Small Engine</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sprayer</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Thresher</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Walking-Type Agricultural Tractor</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Water Pump</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -53800,72 +53564,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Harvest Machinery</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Mobile Field Machinery</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Postharvest / Processing</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Stationary Engine / Irrigation</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
